--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09331504129077169</v>
+        <v>0.09375014458268499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>220066.27</v>
+        <v>221880.84</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04362624419284022</v>
+        <v>0.04288928232233253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>102884.43</v>
+        <v>101507.15</v>
       </c>
       <c r="I3" t="n">
-        <v>382.47</v>
+        <v>377.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04044258564278617</v>
+        <v>0.04051501861870061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>95376.36</v>
+        <v>95887.92</v>
       </c>
       <c r="I4" t="n">
-        <v>274.07</v>
+        <v>275.54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0387030725398106</v>
+        <v>0.03880118221239624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -613,16 +613,16 @@
         <v>429</v>
       </c>
       <c r="H5" t="n">
-        <v>91274.03999999999</v>
+        <v>91831.74000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>212.76</v>
+        <v>214.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03869383713267933</v>
+        <v>0.03861796703395206</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -648,16 +648,16 @@
         <v>561</v>
       </c>
       <c r="H6" t="n">
-        <v>91252.25999999999</v>
+        <v>91398.12</v>
       </c>
       <c r="I6" t="n">
-        <v>162.66</v>
+        <v>162.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03693164258216233</v>
+        <v>0.0366940175241545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -683,16 +683,16 @@
         <v>327</v>
       </c>
       <c r="H7" t="n">
-        <v>87096.45</v>
+        <v>86844.66</v>
       </c>
       <c r="I7" t="n">
-        <v>266.35</v>
+        <v>265.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03434513070091919</v>
+        <v>0.03444354089406344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         <v>48</v>
       </c>
       <c r="H8" t="n">
-        <v>80996.64</v>
+        <v>81518.39999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1687.43</v>
+        <v>1698.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03313967261261937</v>
+        <v>0.03317379911739736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -753,16 +753,16 @@
         <v>473</v>
       </c>
       <c r="H9" t="n">
-        <v>78153.78999999999</v>
+        <v>78513.27</v>
       </c>
       <c r="I9" t="n">
-        <v>165.23</v>
+        <v>165.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,33 +771,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03202820535741049</v>
+        <v>0.03179043621247283</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1045</v>
+        <v>671</v>
       </c>
       <c r="H10" t="n">
-        <v>75532.60000000001</v>
+        <v>75239.23</v>
       </c>
       <c r="I10" t="n">
-        <v>72.28</v>
+        <v>112.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,33 +806,33 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03056938417843054</v>
+        <v>0.03148168470805764</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>671</v>
+        <v>1045</v>
       </c>
       <c r="H11" t="n">
-        <v>72092.24000000001</v>
+        <v>74508.5</v>
       </c>
       <c r="I11" t="n">
-        <v>107.44</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02929156934665587</v>
+        <v>0.02932342832806397</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         <v>195</v>
       </c>
       <c r="H12" t="n">
-        <v>69078.75</v>
+        <v>69400.5</v>
       </c>
       <c r="I12" t="n">
-        <v>354.25</v>
+        <v>355.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02881579322803722</v>
+        <v>0.02889939939840335</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         <v>138</v>
       </c>
       <c r="H13" t="n">
-        <v>67956.72</v>
+        <v>68396.94</v>
       </c>
       <c r="I13" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02803515114683</v>
+        <v>0.02814648988563864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>187</v>
       </c>
       <c r="H14" t="n">
-        <v>66115.72</v>
+        <v>66615.00999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>353.56</v>
+        <v>356.23</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02759569757067534</v>
+        <v>0.02763876302991832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -963,16 +963,16 @@
         <v>263</v>
       </c>
       <c r="H15" t="n">
-        <v>65079.35</v>
+        <v>65413.36</v>
       </c>
       <c r="I15" t="n">
-        <v>247.45</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02649259645792284</v>
+        <v>0.02682313394451339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -998,16 +998,16 @@
         <v>437</v>
       </c>
       <c r="H16" t="n">
-        <v>62477.89</v>
+        <v>63482.99</v>
       </c>
       <c r="I16" t="n">
-        <v>142.97</v>
+        <v>145.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02581128376700502</v>
+        <v>0.02559536577567592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>213</v>
       </c>
       <c r="H17" t="n">
-        <v>60871.14</v>
+        <v>60577.2</v>
       </c>
       <c r="I17" t="n">
-        <v>285.78</v>
+        <v>284.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,33 +1051,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02481576793879566</v>
+        <v>0.02543125716604602</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1170</v>
+        <v>224</v>
       </c>
       <c r="H18" t="n">
-        <v>58523.4</v>
+        <v>60188.8</v>
       </c>
       <c r="I18" t="n">
-        <v>50.02</v>
+        <v>268.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,33 +1086,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02458351737892666</v>
+        <v>0.02483139879042405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>224</v>
+        <v>1170</v>
       </c>
       <c r="H19" t="n">
-        <v>57975.68</v>
+        <v>58769.1</v>
       </c>
       <c r="I19" t="n">
-        <v>258.82</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02416185192624112</v>
+        <v>0.02403124678630322</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1138,16 +1138,16 @@
         <v>353</v>
       </c>
       <c r="H20" t="n">
-        <v>56981.26</v>
+        <v>56875.36</v>
       </c>
       <c r="I20" t="n">
-        <v>161.42</v>
+        <v>161.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02346749178456895</v>
+        <v>0.0235320760565999</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         <v>898</v>
       </c>
       <c r="H21" t="n">
-        <v>55343.74</v>
+        <v>55693.96</v>
       </c>
       <c r="I21" t="n">
-        <v>61.63</v>
+        <v>62.02</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02182425928504744</v>
+        <v>0.02172115191517515</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1208,16 +1208,16 @@
         <v>864</v>
       </c>
       <c r="H22" t="n">
-        <v>51468.48</v>
+        <v>51408</v>
       </c>
       <c r="I22" t="n">
-        <v>59.57</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02156162262439664</v>
+        <v>0.02158714396813544</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Total SA</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H23" t="n">
-        <v>50849.1</v>
+        <v>51090.84</v>
       </c>
       <c r="I23" t="n">
-        <v>91.62</v>
+        <v>91.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,33 +1261,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02150852539386499</v>
+        <v>0.02137741536215709</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Total SA</t>
+          <t>Coca-Cola Femsa</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>556</v>
+        <v>457</v>
       </c>
       <c r="H24" t="n">
-        <v>50723.88</v>
+        <v>50594.47</v>
       </c>
       <c r="I24" t="n">
-        <v>91.23</v>
+        <v>110.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,33 +1296,33 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02143621105354501</v>
+        <v>0.02133023202426478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola Femsa</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>457</v>
+        <v>555</v>
       </c>
       <c r="H25" t="n">
-        <v>50553.34</v>
+        <v>50482.8</v>
       </c>
       <c r="I25" t="n">
-        <v>110.62</v>
+        <v>90.95999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02080582031131387</v>
+        <v>0.02084348352196394</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         <v>426</v>
       </c>
       <c r="H26" t="n">
-        <v>49066.68</v>
+        <v>49330.8</v>
       </c>
       <c r="I26" t="n">
-        <v>115.18</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02028519013547083</v>
+        <v>0.01978137885380538</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1383,16 +1383,16 @@
         <v>1087</v>
       </c>
       <c r="H27" t="n">
-        <v>47838.87</v>
+        <v>46817.09</v>
       </c>
       <c r="I27" t="n">
-        <v>44.01</v>
+        <v>43.07</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01949374797071752</v>
+        <v>0.01967325899768232</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1418,16 +1418,16 @@
         <v>920</v>
       </c>
       <c r="H28" t="n">
-        <v>45972.4</v>
+        <v>46561.2</v>
       </c>
       <c r="I28" t="n">
-        <v>49.97</v>
+        <v>50.61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01942755664596116</v>
+        <v>0.01913172593738814</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>426</v>
       </c>
       <c r="H29" t="n">
-        <v>45816.3</v>
+        <v>45279.54</v>
       </c>
       <c r="I29" t="n">
-        <v>107.55</v>
+        <v>106.29</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01931433174181996</v>
+        <v>0.01911887273474926</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1488,16 +1488,16 @@
         <v>938</v>
       </c>
       <c r="H30" t="n">
-        <v>45549.28</v>
+        <v>45249.12</v>
       </c>
       <c r="I30" t="n">
-        <v>48.56</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0191794345852233</v>
+        <v>0.01906512758762021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1523,16 +1523,16 @@
         <v>331</v>
       </c>
       <c r="H31" t="n">
-        <v>45231.15</v>
+        <v>45121.92</v>
       </c>
       <c r="I31" t="n">
-        <v>136.65</v>
+        <v>136.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01763360637275996</v>
+        <v>0.01761542829826753</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1558,16 +1558,16 @@
         <v>1504</v>
       </c>
       <c r="H32" t="n">
-        <v>41585.6</v>
+        <v>41690.88</v>
       </c>
       <c r="I32" t="n">
-        <v>27.65</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01721093172498845</v>
+        <v>0.01712847698409073</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>40588.8</v>
+        <v>40538.4</v>
       </c>
       <c r="I33" t="n">
-        <v>72.48</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01663298944501941</v>
+        <v>0.01651118101238373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>39225.83</v>
+        <v>39077.43</v>
       </c>
       <c r="I34" t="n">
-        <v>105.73</v>
+        <v>105.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01404019765653961</v>
+        <v>0.0138311277027751</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         <v>373</v>
       </c>
       <c r="H35" t="n">
-        <v>33111.21</v>
+        <v>32734.48</v>
       </c>
       <c r="I35" t="n">
-        <v>88.77</v>
+        <v>87.76000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0132635838750453</v>
+        <v>0.0132655318584479</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
         <v>121</v>
       </c>
       <c r="H36" t="n">
-        <v>31279.71</v>
+        <v>31395.87</v>
       </c>
       <c r="I36" t="n">
-        <v>258.51</v>
+        <v>259.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,33 +1716,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01131070233706557</v>
+        <v>0.01134917511825654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>522</v>
+        <v>87</v>
       </c>
       <c r="H37" t="n">
-        <v>26674.2</v>
+        <v>26860.38</v>
       </c>
       <c r="I37" t="n">
-        <v>51.1</v>
+        <v>308.74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,33 +1751,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01127713175935282</v>
+        <v>0.01131903220319218</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>87</v>
+        <v>522</v>
       </c>
       <c r="H38" t="n">
-        <v>26595.03</v>
+        <v>26789.04</v>
       </c>
       <c r="I38" t="n">
-        <v>305.69</v>
+        <v>51.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.00892862030577941</v>
+        <v>0.008940623531845356</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         <v>575</v>
       </c>
       <c r="H39" t="n">
-        <v>21056.5</v>
+        <v>21160</v>
       </c>
       <c r="I39" t="n">
-        <v>36.62</v>
+        <v>36.8</v>
       </c>
     </row>
   </sheetData>
@@ -1873,7 +1873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06088739438070104</v>
+        <v>0.06091261416153827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>157942.86</v>
+        <v>158195.32</v>
       </c>
       <c r="I2" t="n">
-        <v>162.66</v>
+        <v>162.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05792566217070964</v>
+        <v>0.05810007774211991</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>150260.08</v>
+        <v>150890.92</v>
       </c>
       <c r="I3" t="n">
-        <v>50.02</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1952,33 +1952,33 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04962602096768302</v>
+        <v>0.05031450686794062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1781</v>
+        <v>556</v>
       </c>
       <c r="H4" t="n">
-        <v>128730.68</v>
+        <v>130671.12</v>
       </c>
       <c r="I4" t="n">
-        <v>72.28</v>
+        <v>235.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1987,33 +1987,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04954242856852353</v>
+        <v>0.04919554523710353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>556</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>128513.84</v>
+        <v>127765.08</v>
       </c>
       <c r="I5" t="n">
-        <v>231.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2022,33 +2022,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04889971851558727</v>
+        <v>0.04889529338217581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1781</v>
       </c>
       <c r="H6" t="n">
-        <v>126846.64</v>
+        <v>126985.3</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04862040641040827</v>
+        <v>0.04882432924246566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2074,16 +2074,16 @@
         <v>1095</v>
       </c>
       <c r="H7" t="n">
-        <v>126122.1</v>
+        <v>126801</v>
       </c>
       <c r="I7" t="n">
-        <v>115.18</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04374617231988664</v>
+        <v>0.04361324340553217</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2109,16 +2109,16 @@
         <v>703</v>
       </c>
       <c r="H8" t="n">
-        <v>113478.26</v>
+        <v>113267.36</v>
       </c>
       <c r="I8" t="n">
-        <v>161.42</v>
+        <v>161.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04292668616217924</v>
+        <v>0.04309598683081148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>450</v>
       </c>
       <c r="H9" t="n">
-        <v>111352.5</v>
+        <v>111924</v>
       </c>
       <c r="I9" t="n">
-        <v>247.45</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.04022573879900305</v>
+        <v>0.04035115705451105</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>104346.2</v>
+        <v>104795.44</v>
       </c>
       <c r="I10" t="n">
-        <v>51.1</v>
+        <v>51.32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2197,33 +2197,33 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03702720000832686</v>
+        <v>0.03693599146646787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1082</v>
+        <v>796</v>
       </c>
       <c r="H11" t="n">
-        <v>96049.14</v>
+        <v>95925.96000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>88.77</v>
+        <v>120.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2232,33 +2232,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03672501988470964</v>
+        <v>0.03656263461118546</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>796</v>
+        <v>1082</v>
       </c>
       <c r="H12" t="n">
-        <v>95265.28</v>
+        <v>94956.32000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>119.68</v>
+        <v>87.76000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03649948925714888</v>
+        <v>0.03652675979351429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         <v>295</v>
       </c>
       <c r="H13" t="n">
-        <v>94680.25</v>
+        <v>94863.14999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>320.95</v>
+        <v>321.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03563117918617109</v>
+        <v>0.03596209239664216</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2319,16 +2319,16 @@
         <v>804</v>
       </c>
       <c r="H14" t="n">
-        <v>92427.84</v>
+        <v>93396.66</v>
       </c>
       <c r="I14" t="n">
-        <v>114.96</v>
+        <v>116.17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03490857755971605</v>
+        <v>0.03470327403859117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>710</v>
       </c>
       <c r="H15" t="n">
-        <v>90553.39999999999</v>
+        <v>90127.39999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>127.54</v>
+        <v>126.94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03365857743924647</v>
+        <v>0.03339724123229679</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         <v>1798</v>
       </c>
       <c r="H16" t="n">
-        <v>87310.88</v>
+        <v>86735.52</v>
       </c>
       <c r="I16" t="n">
-        <v>48.56</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03164846628244258</v>
+        <v>0.03186286792610597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
         <v>327</v>
       </c>
       <c r="H17" t="n">
-        <v>82096.62</v>
+        <v>82750.62</v>
       </c>
       <c r="I17" t="n">
-        <v>251.06</v>
+        <v>253.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2442,33 +2442,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03134437406557767</v>
+        <v>0.03126904092912397</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>756</v>
+        <v>910</v>
       </c>
       <c r="H18" t="n">
-        <v>81307.8</v>
+        <v>81208.39999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>107.55</v>
+        <v>89.23999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,33 +2477,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03130254702578425</v>
+        <v>0.03108083001490628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Snap-On</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>910</v>
+        <v>215</v>
       </c>
       <c r="H19" t="n">
-        <v>81199.3</v>
+        <v>80719.60000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>89.23</v>
+        <v>375.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2512,33 +2512,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03107923303858121</v>
+        <v>0.03094053433425089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Eastman Chemical</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1179</v>
+        <v>756</v>
       </c>
       <c r="H20" t="n">
-        <v>80620.02</v>
+        <v>80355.24000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>68.38</v>
+        <v>106.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2547,33 +2547,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03106706271926067</v>
+        <v>0.03091991507390646</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Snap-On</t>
+          <t>Eastman Chemical</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>215</v>
+        <v>1179</v>
       </c>
       <c r="H21" t="n">
-        <v>80588.45</v>
+        <v>80301.69</v>
       </c>
       <c r="I21" t="n">
-        <v>374.83</v>
+        <v>68.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02867161851272491</v>
+        <v>0.02891290057480838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2599,16 +2599,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>74374.63</v>
+        <v>75089.3</v>
       </c>
       <c r="I22" t="n">
-        <v>75.97</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0264364162014051</v>
+        <v>0.02610630157825672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>68576.48</v>
+        <v>67800.32000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>87.47</v>
+        <v>86.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02530670833436536</v>
+        <v>0.02494930501675999</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2669,16 +2669,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>65646</v>
+        <v>64795.5</v>
       </c>
       <c r="I24" t="n">
-        <v>20.84</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02474769862133644</v>
+        <v>0.02471211999006409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2704,16 +2704,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>64195.92</v>
+        <v>64179.51</v>
       </c>
       <c r="I25" t="n">
-        <v>39.12</v>
+        <v>39.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0228457286737754</v>
+        <v>0.02267430944162246</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2739,16 +2739,16 @@
         <v>586</v>
       </c>
       <c r="H26" t="n">
-        <v>59262.18</v>
+        <v>58887.14</v>
       </c>
       <c r="I26" t="n">
-        <v>101.13</v>
+        <v>100.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02213856257426347</v>
+        <v>0.02253804905225389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2774,16 +2774,16 @@
         <v>953</v>
       </c>
       <c r="H27" t="n">
-        <v>57427.78</v>
+        <v>58533.26</v>
       </c>
       <c r="I27" t="n">
-        <v>60.26</v>
+        <v>61.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02070796987258077</v>
+        <v>0.02091978943311</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>53716.8</v>
+        <v>54330.5</v>
       </c>
       <c r="I28" t="n">
-        <v>74.40000000000001</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01585334244790148</v>
+        <v>0.01572328917193462</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>41123.82</v>
+        <v>40834.74</v>
       </c>
       <c r="I29" t="n">
-        <v>281.67</v>
+        <v>279.69</v>
       </c>
     </row>
   </sheetData>
@@ -2914,7 +2914,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09203583649307145</v>
+        <v>0.09245410470585647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>274953.15</v>
+        <v>277338.73</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03770522927941235</v>
+        <v>0.03775219006872154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>411</v>
       </c>
       <c r="H3" t="n">
-        <v>112642.77</v>
+        <v>113246.94</v>
       </c>
       <c r="I3" t="n">
-        <v>274.07</v>
+        <v>275.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03546299487105675</v>
+        <v>0.03484494619910864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3010,16 +3010,16 @@
         <v>277</v>
       </c>
       <c r="H4" t="n">
-        <v>105944.19</v>
+        <v>104525.95</v>
       </c>
       <c r="I4" t="n">
-        <v>382.47</v>
+        <v>377.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03484648735588707</v>
+        <v>0.03475922224333402</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>104102.4</v>
+        <v>104268.8</v>
       </c>
       <c r="I5" t="n">
-        <v>162.66</v>
+        <v>162.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03368599553299084</v>
+        <v>0.0337529966839747</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>100635.48</v>
+        <v>101250.38</v>
       </c>
       <c r="I6" t="n">
-        <v>212.76</v>
+        <v>214.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3098,33 +3098,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03058526857704252</v>
+        <v>0.03132431017276065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>553</v>
+        <v>838</v>
       </c>
       <c r="H7" t="n">
-        <v>91372.19</v>
+        <v>93964.94</v>
       </c>
       <c r="I7" t="n">
-        <v>165.23</v>
+        <v>112.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3133,33 +3133,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0304022232952268</v>
+        <v>0.03060009192581645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>341</v>
+        <v>553</v>
       </c>
       <c r="H8" t="n">
-        <v>90825.35000000001</v>
+        <v>91792.47</v>
       </c>
       <c r="I8" t="n">
-        <v>266.35</v>
+        <v>165.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3168,33 +3168,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03013757350522978</v>
+        <v>0.03019016040267237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>838</v>
+        <v>341</v>
       </c>
       <c r="H9" t="n">
-        <v>90034.72</v>
+        <v>90562.78</v>
       </c>
       <c r="I9" t="n">
-        <v>107.44</v>
+        <v>265.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02789624287542166</v>
+        <v>0.02740529693906539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3220,16 +3220,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>83338.84</v>
+        <v>82208.89999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>72.28</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02512479257027088</v>
+        <v>0.02542441183773856</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>75059.25</v>
+        <v>76266.75</v>
       </c>
       <c r="I11" t="n">
-        <v>142.97</v>
+        <v>145.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02460040017305685</v>
+        <v>0.02462537389554234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>73492.64999999999</v>
+        <v>73869.84</v>
       </c>
       <c r="I12" t="n">
-        <v>247.45</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02414301793414635</v>
+        <v>0.02422569991126345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3325,16 +3325,16 @@
         <v>204</v>
       </c>
       <c r="H13" t="n">
-        <v>72126.24000000001</v>
+        <v>72670.92</v>
       </c>
       <c r="I13" t="n">
-        <v>353.56</v>
+        <v>356.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3343,33 +3343,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02324185030247292</v>
+        <v>0.02373718503951058</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>141</v>
+        <v>265</v>
       </c>
       <c r="H14" t="n">
-        <v>69434.03999999999</v>
+        <v>71205.5</v>
       </c>
       <c r="I14" t="n">
-        <v>492.44</v>
+        <v>268.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3378,33 +3378,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02301787389444034</v>
+        <v>0.023296590909125</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>426</v>
+        <v>141</v>
       </c>
       <c r="H15" t="n">
-        <v>68764.92</v>
+        <v>69883.83</v>
       </c>
       <c r="I15" t="n">
-        <v>161.42</v>
+        <v>495.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3413,33 +3413,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02295841865532815</v>
+        <v>0.02288098557020303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>265</v>
+        <v>426</v>
       </c>
       <c r="H16" t="n">
-        <v>68587.3</v>
+        <v>68637.12</v>
       </c>
       <c r="I16" t="n">
-        <v>258.82</v>
+        <v>161.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02242445290016678</v>
+        <v>0.0224287471163673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3465,16 +3465,16 @@
         <v>1311</v>
       </c>
       <c r="H17" t="n">
-        <v>66992.10000000001</v>
+        <v>67280.52</v>
       </c>
       <c r="I17" t="n">
-        <v>51.1</v>
+        <v>51.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0223844255524974</v>
+        <v>0.02218508639789641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3500,16 +3500,16 @@
         <v>234</v>
       </c>
       <c r="H18" t="n">
-        <v>66872.52</v>
+        <v>66549.60000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>285.78</v>
+        <v>284.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02169997397452516</v>
+        <v>0.02171174614977511</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3535,16 +3535,16 @@
         <v>183</v>
       </c>
       <c r="H19" t="n">
-        <v>64827.75</v>
+        <v>65129.7</v>
       </c>
       <c r="I19" t="n">
-        <v>354.25</v>
+        <v>355.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02112787880664411</v>
+        <v>0.02115459877553388</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3570,16 +3570,16 @@
         <v>548</v>
       </c>
       <c r="H20" t="n">
-        <v>63118.64</v>
+        <v>63458.4</v>
       </c>
       <c r="I20" t="n">
-        <v>115.18</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02073519706974911</v>
+        <v>0.02099690536686334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3605,16 +3605,16 @@
         <v>268</v>
       </c>
       <c r="H21" t="n">
-        <v>61945.52</v>
+        <v>62985.36</v>
       </c>
       <c r="I21" t="n">
-        <v>231.14</v>
+        <v>235.02</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3623,33 +3623,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02013943294590802</v>
+        <v>0.02011045332517957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1010</v>
+        <v>1201</v>
       </c>
       <c r="H22" t="n">
-        <v>60165.7</v>
+        <v>60326.23</v>
       </c>
       <c r="I22" t="n">
-        <v>59.57</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3658,33 +3658,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02011835147445612</v>
+        <v>0.02003337010412662</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>656</v>
+        <v>1010</v>
       </c>
       <c r="H23" t="n">
-        <v>60102.72</v>
+        <v>60095</v>
       </c>
       <c r="I23" t="n">
-        <v>91.62</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3693,33 +3693,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02010874464322923</v>
+        <v>0.01989161138371596</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1201</v>
+        <v>656</v>
       </c>
       <c r="H24" t="n">
-        <v>60074.02</v>
+        <v>59669.76</v>
       </c>
       <c r="I24" t="n">
-        <v>50.02</v>
+        <v>90.95999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01820501212151135</v>
+        <v>0.01808665790852196</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3745,16 +3745,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>54386.7</v>
+        <v>54255.36</v>
       </c>
       <c r="I25" t="n">
-        <v>136.65</v>
+        <v>136.32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01728024582776492</v>
+        <v>0.01700784617716044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3780,16 +3780,16 @@
         <v>480</v>
       </c>
       <c r="H26" t="n">
-        <v>51624</v>
+        <v>51019.2</v>
       </c>
       <c r="I26" t="n">
-        <v>107.55</v>
+        <v>106.29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01644925157931117</v>
+        <v>0.01636153122099972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3815,16 +3815,16 @@
         <v>678</v>
       </c>
       <c r="H27" t="n">
-        <v>49141.44</v>
+        <v>49080.42</v>
       </c>
       <c r="I27" t="n">
-        <v>72.48</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01610432951765841</v>
+        <v>0.01607896719458056</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3850,16 +3850,16 @@
         <v>1740</v>
       </c>
       <c r="H28" t="n">
-        <v>48111</v>
+        <v>48232.8</v>
       </c>
       <c r="I28" t="n">
-        <v>27.65</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3868,33 +3868,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01599455055009151</v>
+        <v>0.01602919296227758</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>984</v>
+        <v>399</v>
       </c>
       <c r="H29" t="n">
-        <v>47783.04</v>
+        <v>48083.49</v>
       </c>
       <c r="I29" t="n">
-        <v>48.56</v>
+        <v>120.51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3903,33 +3903,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01598426755861799</v>
+        <v>0.01582406552029119</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>399</v>
+        <v>984</v>
       </c>
       <c r="H30" t="n">
-        <v>47752.32</v>
+        <v>47468.16</v>
       </c>
       <c r="I30" t="n">
-        <v>119.68</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01535501676592889</v>
+        <v>0.01548797694267944</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,16 +3955,16 @@
         <v>918</v>
       </c>
       <c r="H31" t="n">
-        <v>45872.46</v>
+        <v>46459.98</v>
       </c>
       <c r="I31" t="n">
-        <v>49.97</v>
+        <v>50.61</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01461940128018558</v>
+        <v>0.01439386391024829</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,16 +3990,16 @@
         <v>492</v>
       </c>
       <c r="H32" t="n">
-        <v>43674.84</v>
+        <v>43177.92</v>
       </c>
       <c r="I32" t="n">
-        <v>88.77</v>
+        <v>87.76000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01331438522556388</v>
+        <v>0.01339883596968917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4025,16 +4025,16 @@
         <v>346</v>
       </c>
       <c r="H33" t="n">
-        <v>39776.16</v>
+        <v>40193.09</v>
       </c>
       <c r="I33" t="n">
-        <v>114.96</v>
+        <v>116.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01330712821856043</v>
+        <v>0.01320248260709608</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,16 +4060,16 @@
         <v>376</v>
       </c>
       <c r="H34" t="n">
-        <v>39754.48</v>
+        <v>39604.08</v>
       </c>
       <c r="I34" t="n">
-        <v>105.73</v>
+        <v>105.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01323446442334326</v>
+        <v>0.01311824877802693</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>310</v>
       </c>
       <c r="H35" t="n">
-        <v>39537.4</v>
+        <v>39351.4</v>
       </c>
       <c r="I35" t="n">
-        <v>127.54</v>
+        <v>126.94</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01299933137124126</v>
+        <v>0.01297109293203201</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4130,16 +4130,16 @@
         <v>121</v>
       </c>
       <c r="H36" t="n">
-        <v>38834.95</v>
+        <v>38909.97</v>
       </c>
       <c r="I36" t="n">
-        <v>320.95</v>
+        <v>321.57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0128578163873461</v>
+        <v>0.01290715749560185</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         <v>153</v>
       </c>
       <c r="H37" t="n">
-        <v>38412.18</v>
+        <v>38718.18</v>
       </c>
       <c r="I37" t="n">
-        <v>251.06</v>
+        <v>253.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01220098026499122</v>
+        <v>0.01219612703668193</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4200,16 +4200,16 @@
         <v>141</v>
       </c>
       <c r="H38" t="n">
-        <v>36449.91</v>
+        <v>36585.27</v>
       </c>
       <c r="I38" t="n">
-        <v>258.51</v>
+        <v>259.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01186963831284629</v>
+        <v>0.01193896183659163</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4235,16 +4235,16 @@
         <v>116</v>
       </c>
       <c r="H39" t="n">
-        <v>35460.04</v>
+        <v>35813.84</v>
       </c>
       <c r="I39" t="n">
-        <v>305.69</v>
+        <v>308.74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0117993578151321</v>
+        <v>0.01186394212433216</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4270,16 +4270,16 @@
         <v>464</v>
       </c>
       <c r="H40" t="n">
-        <v>35250.08</v>
+        <v>35588.8</v>
       </c>
       <c r="I40" t="n">
-        <v>75.97</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01168235196651333</v>
+        <v>0.01150281808462173</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4305,16 +4305,16 @@
         <v>399</v>
       </c>
       <c r="H41" t="n">
-        <v>34900.53</v>
+        <v>34505.52</v>
       </c>
       <c r="I41" t="n">
-        <v>87.47</v>
+        <v>86.48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01137978699278567</v>
+        <v>0.01133444376775357</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4340,16 +4340,16 @@
         <v>381</v>
       </c>
       <c r="H42" t="n">
-        <v>33996.63</v>
+        <v>34000.44</v>
       </c>
       <c r="I42" t="n">
-        <v>89.23</v>
+        <v>89.23999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01129211043169652</v>
+        <v>0.011264157791337</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4375,16 +4375,16 @@
         <v>90</v>
       </c>
       <c r="H43" t="n">
-        <v>33734.7</v>
+        <v>33789.6</v>
       </c>
       <c r="I43" t="n">
-        <v>374.83</v>
+        <v>375.44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.01128429107359686</v>
+        <v>0.01119369513323051</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4410,16 +4410,16 @@
         <v>493</v>
       </c>
       <c r="H44" t="n">
-        <v>33711.34</v>
+        <v>33578.23</v>
       </c>
       <c r="I44" t="n">
-        <v>68.38</v>
+        <v>68.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.009231796602964226</v>
+        <v>0.009191631564431924</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4445,16 +4445,16 @@
         <v>705</v>
       </c>
       <c r="H45" t="n">
-        <v>27579.6</v>
+        <v>27572.55</v>
       </c>
       <c r="I45" t="n">
-        <v>39.12</v>
+        <v>39.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.009047653397579715</v>
+        <v>0.008893852910979686</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4480,16 +4480,16 @@
         <v>1297</v>
       </c>
       <c r="H46" t="n">
-        <v>27029.48</v>
+        <v>26679.29</v>
       </c>
       <c r="I46" t="n">
-        <v>20.84</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,33 +4498,33 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.008716441991224979</v>
+        <v>0.008824757035757417</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HWC</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hancock Whitney Corp</t>
+          <t>Amdocs Ltd</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>350</v>
+        <v>431</v>
       </c>
       <c r="H47" t="n">
-        <v>26040</v>
+        <v>26472.02</v>
       </c>
       <c r="I47" t="n">
-        <v>74.40000000000001</v>
+        <v>61.42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4533,33 +4533,33 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008699842591902981</v>
+        <v>0.008779913222687992</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>HWC</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Hancock Whitney Corp</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>257</v>
+        <v>350</v>
       </c>
       <c r="H48" t="n">
-        <v>25990.41</v>
+        <v>26337.5</v>
       </c>
       <c r="I48" t="n">
-        <v>101.13</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4568,33 +4568,33 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.00869370024510809</v>
+        <v>0.008609375388522619</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Amdocs Ltd</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>431</v>
+        <v>257</v>
       </c>
       <c r="H49" t="n">
-        <v>25972.06</v>
+        <v>25825.93</v>
       </c>
       <c r="I49" t="n">
-        <v>60.26</v>
+        <v>100.49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.007685712683778765</v>
+        <v>0.00769185403834888</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4620,16 +4620,16 @@
         <v>627</v>
       </c>
       <c r="H50" t="n">
-        <v>22960.74</v>
+        <v>23073.6</v>
       </c>
       <c r="I50" t="n">
-        <v>36.62</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.00612847212052389</v>
+        <v>0.006060465321366275</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4655,10 +4655,10 @@
         <v>65</v>
       </c>
       <c r="H51" t="n">
-        <v>18308.55</v>
+        <v>18179.85</v>
       </c>
       <c r="I51" t="n">
-        <v>281.67</v>
+        <v>279.69</v>
       </c>
     </row>
   </sheetData>
@@ -4725,7 +4725,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07034693799556635</v>
+        <v>0.07024919274354881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>155540.14</v>
+        <v>155994.82</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -4760,7 +4760,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05292943354574435</v>
+        <v>0.05325424542690152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4786,16 +4786,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>117029.28</v>
+        <v>118255.97</v>
       </c>
       <c r="I3" t="n">
-        <v>114.96</v>
+        <v>116.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04142561645666401</v>
+        <v>0.04151467963041482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4821,16 +4821,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>91593.84</v>
+        <v>92187.17999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04020868427057179</v>
+        <v>0.04011312116787216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4856,16 +4856,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>88903.14999999999</v>
+        <v>89074.89</v>
       </c>
       <c r="I5" t="n">
-        <v>320.95</v>
+        <v>321.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0377563263680701</v>
+        <v>0.0392350311393264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4891,16 +4891,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>83480.88</v>
+        <v>87125.00999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>107.44</v>
+        <v>112.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03499013022584133</v>
+        <v>0.03492786958398735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4926,16 +4926,16 @@
         <v>2798</v>
       </c>
       <c r="H7" t="n">
-        <v>77364.7</v>
+        <v>77560.56</v>
       </c>
       <c r="I7" t="n">
-        <v>27.65</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03401097264707818</v>
+        <v>0.03420260364312252</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4961,16 +4961,16 @@
         <v>246</v>
       </c>
       <c r="H8" t="n">
-        <v>75199.74000000001</v>
+        <v>75950.03999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>305.69</v>
+        <v>308.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03391039117954939</v>
+        <v>0.03393786347142914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4996,16 +4996,16 @@
         <v>303</v>
       </c>
       <c r="H9" t="n">
-        <v>74977.35000000001</v>
+        <v>75362.16</v>
       </c>
       <c r="I9" t="n">
-        <v>247.45</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0338129575469682</v>
+        <v>0.0334250273356116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>816</v>
       </c>
       <c r="H10" t="n">
-        <v>74761.92</v>
+        <v>74223.36</v>
       </c>
       <c r="I10" t="n">
-        <v>91.62</v>
+        <v>90.95999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03317397418911026</v>
+        <v>0.03264434374909019</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5066,16 +5066,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>73349.10000000001</v>
+        <v>72489.78</v>
       </c>
       <c r="I11" t="n">
-        <v>107.55</v>
+        <v>106.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03150156023615094</v>
+        <v>0.03160296846019486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5101,16 +5101,16 @@
         <v>197</v>
       </c>
       <c r="H12" t="n">
-        <v>69651.32000000001</v>
+        <v>70177.31</v>
       </c>
       <c r="I12" t="n">
-        <v>353.56</v>
+        <v>356.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03074486775135813</v>
+        <v>0.03082496433890713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5136,16 +5136,16 @@
         <v>568</v>
       </c>
       <c r="H13" t="n">
-        <v>67978.24000000001</v>
+        <v>68449.67999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>119.68</v>
+        <v>120.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03063071350699342</v>
+        <v>0.03066316967182202</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5171,16 +5171,16 @@
         <v>588</v>
       </c>
       <c r="H14" t="n">
-        <v>67725.84</v>
+        <v>68090.39999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>115.18</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03036898640845374</v>
+        <v>0.03040058207892142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5206,16 +5206,16 @@
         <v>245</v>
       </c>
       <c r="H15" t="n">
-        <v>67147.14999999999</v>
+        <v>67507.3</v>
       </c>
       <c r="I15" t="n">
-        <v>274.07</v>
+        <v>275.54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02999211910575256</v>
+        <v>0.03005212550606148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5241,16 +5241,16 @@
         <v>1076</v>
       </c>
       <c r="H16" t="n">
-        <v>66313.88</v>
+        <v>66733.52</v>
       </c>
       <c r="I16" t="n">
-        <v>61.63</v>
+        <v>62.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02915127630912734</v>
+        <v>0.02899181382841385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5276,16 +5276,16 @@
         <v>1082</v>
       </c>
       <c r="H17" t="n">
-        <v>64454.74</v>
+        <v>64379</v>
       </c>
       <c r="I17" t="n">
-        <v>59.57</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5294,33 +5294,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02852333298734286</v>
+        <v>0.02783503239574792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1433</v>
+        <v>263</v>
       </c>
       <c r="H18" t="n">
-        <v>63066.33</v>
+        <v>61810.26</v>
       </c>
       <c r="I18" t="n">
-        <v>44.01</v>
+        <v>235.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5329,33 +5329,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02749372411714197</v>
+        <v>0.02779407485574738</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>263</v>
+        <v>1433</v>
       </c>
       <c r="H19" t="n">
-        <v>60789.82</v>
+        <v>61719.31</v>
       </c>
       <c r="I19" t="n">
-        <v>231.14</v>
+        <v>43.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02578752521151212</v>
+        <v>0.02580284490307282</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
         <v>1557</v>
       </c>
       <c r="H20" t="n">
-        <v>57017.34</v>
+        <v>57297.6</v>
       </c>
       <c r="I20" t="n">
-        <v>36.62</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02565872177548746</v>
+        <v>0.02547452710084316</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5416,16 +5416,16 @@
         <v>213</v>
       </c>
       <c r="H21" t="n">
-        <v>56732.55</v>
+        <v>56568.54</v>
       </c>
       <c r="I21" t="n">
-        <v>266.35</v>
+        <v>265.58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5434,33 +5434,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02283358061476402</v>
+        <v>0.02299071236555417</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="H22" t="n">
-        <v>50486.04</v>
+        <v>51053</v>
       </c>
       <c r="I22" t="n">
-        <v>382.47</v>
+        <v>268.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02280545362404674</v>
+        <v>0.02265255034315506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5486,16 +5486,16 @@
         <v>369</v>
       </c>
       <c r="H23" t="n">
-        <v>50423.85</v>
+        <v>50302.08</v>
       </c>
       <c r="I23" t="n">
-        <v>136.65</v>
+        <v>136.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5504,33 +5504,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02224099164037252</v>
+        <v>0.02243104187943365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="H24" t="n">
-        <v>49175.8</v>
+        <v>49810.2</v>
       </c>
       <c r="I24" t="n">
-        <v>258.82</v>
+        <v>377.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02216358927357151</v>
+        <v>0.02208623748523677</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5556,16 +5556,16 @@
         <v>443</v>
       </c>
       <c r="H25" t="n">
-        <v>49004.66</v>
+        <v>49044.53</v>
       </c>
       <c r="I25" t="n">
-        <v>110.62</v>
+        <v>110.71</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5574,33 +5574,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02175586323833068</v>
+        <v>0.02185677618856968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>298</v>
+        <v>959</v>
       </c>
       <c r="H26" t="n">
-        <v>48103.16</v>
+        <v>48534.99</v>
       </c>
       <c r="I26" t="n">
-        <v>161.42</v>
+        <v>50.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5609,33 +5609,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02167358082281059</v>
+        <v>0.02162205053079643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>959</v>
+        <v>298</v>
       </c>
       <c r="H27" t="n">
-        <v>47921.23</v>
+        <v>48013.76</v>
       </c>
       <c r="I27" t="n">
-        <v>49.97</v>
+        <v>161.12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02055093895710328</v>
+        <v>0.02036375564384881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5661,16 +5661,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>45439.02</v>
+        <v>45219.6</v>
       </c>
       <c r="I28" t="n">
-        <v>285.78</v>
+        <v>284.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01970132202283673</v>
+        <v>0.01959224528536271</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5696,16 +5696,16 @@
         <v>601</v>
       </c>
       <c r="H29" t="n">
-        <v>43560.48</v>
+        <v>43506.39</v>
       </c>
       <c r="I29" t="n">
-        <v>72.48</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0194318564967175</v>
+        <v>0.01912815740358648</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5731,16 +5731,16 @@
         <v>484</v>
       </c>
       <c r="H30" t="n">
-        <v>42964.68</v>
+        <v>42475.84</v>
       </c>
       <c r="I30" t="n">
-        <v>88.77</v>
+        <v>87.76000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01823462089280469</v>
+        <v>0.01844829376269805</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5766,16 +5766,16 @@
         <v>282</v>
       </c>
       <c r="H31" t="n">
-        <v>40317.54</v>
+        <v>40966.14</v>
       </c>
       <c r="I31" t="n">
-        <v>142.97</v>
+        <v>145.27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01809750011702619</v>
+        <v>0.01804848152340973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5801,16 +5801,16 @@
         <v>246</v>
       </c>
       <c r="H32" t="n">
-        <v>40014.36</v>
+        <v>40078.32</v>
       </c>
       <c r="I32" t="n">
-        <v>162.66</v>
+        <v>162.92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01726267710246316</v>
+        <v>0.01712341754217067</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5836,16 +5836,16 @@
         <v>361</v>
       </c>
       <c r="H33" t="n">
-        <v>38168.53</v>
+        <v>38024.13</v>
       </c>
       <c r="I33" t="n">
-        <v>105.73</v>
+        <v>105.33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5854,33 +5854,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01701475344107884</v>
+        <v>0.0170096596072665</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>372</v>
+        <v>736</v>
       </c>
       <c r="H34" t="n">
-        <v>37620.36</v>
+        <v>37771.52</v>
       </c>
       <c r="I34" t="n">
-        <v>101.13</v>
+        <v>51.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5889,33 +5889,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01700988696061384</v>
+        <v>0.01686616636322286</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>736</v>
+        <v>148</v>
       </c>
       <c r="H35" t="n">
-        <v>37609.6</v>
+        <v>37452.88</v>
       </c>
       <c r="I35" t="n">
-        <v>51.1</v>
+        <v>253.06</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5924,27 +5924,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01680513296097521</v>
+        <v>0.0168343730446518</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>148</v>
+        <v>372</v>
       </c>
       <c r="H36" t="n">
-        <v>37156.88</v>
+        <v>37382.28</v>
       </c>
       <c r="I36" t="n">
-        <v>251.06</v>
+        <v>100.49</v>
       </c>
     </row>
   </sheetData>
@@ -6011,7 +6011,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1055048698465055</v>
+        <v>0.1056919338973152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6037,16 +6037,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>223125.46</v>
+        <v>224632.19</v>
       </c>
       <c r="I2" t="n">
-        <v>53.25</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09878148214496005</v>
+        <v>0.09907674104849262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6072,16 +6072,16 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>208906.6</v>
+        <v>210572.6</v>
       </c>
       <c r="I3" t="n">
-        <v>213.17</v>
+        <v>214.87</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09426169830265532</v>
+        <v>0.09454402552631756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6107,16 +6107,16 @@
         <v>4300</v>
       </c>
       <c r="H4" t="n">
-        <v>199348</v>
+        <v>200939</v>
       </c>
       <c r="I4" t="n">
-        <v>46.36</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08632773899002505</v>
+        <v>0.08601059194777598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6142,16 +6142,16 @@
         <v>934</v>
       </c>
       <c r="H5" t="n">
-        <v>182568.98</v>
+        <v>182802.48</v>
       </c>
       <c r="I5" t="n">
-        <v>195.47</v>
+        <v>195.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05498725160983549</v>
+        <v>0.05527740587405885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1475</v>
       </c>
       <c r="H6" t="n">
-        <v>116289</v>
+        <v>117483.75</v>
       </c>
       <c r="I6" t="n">
-        <v>78.84</v>
+        <v>79.65000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03801489728055227</v>
+        <v>0.0380178409049317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6212,16 +6212,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>80395.25999999999</v>
+        <v>80801.16</v>
       </c>
       <c r="I7" t="n">
-        <v>29.71</v>
+        <v>29.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0265850871201268</v>
+        <v>0.02609946123329131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6247,16 +6247,16 @@
         <v>147</v>
       </c>
       <c r="H8" t="n">
-        <v>56223.09</v>
+        <v>55470.45</v>
       </c>
       <c r="I8" t="n">
-        <v>382.47</v>
+        <v>377.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02444927576287074</v>
+        <v>0.02448593759309503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6282,16 +6282,16 @@
         <v>105</v>
       </c>
       <c r="H9" t="n">
-        <v>51706.2</v>
+        <v>52041.15</v>
       </c>
       <c r="I9" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02345673055019665</v>
+        <v>0.02340222824730478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6317,16 +6317,16 @@
         <v>1860</v>
       </c>
       <c r="H10" t="n">
-        <v>49607.13</v>
+        <v>49737.89</v>
       </c>
       <c r="I10" t="n">
-        <v>26.67</v>
+        <v>26.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0211512889902343</v>
+        <v>0.02108030783300208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6352,16 +6352,16 @@
         <v>275</v>
       </c>
       <c r="H11" t="n">
-        <v>44731.5</v>
+        <v>44803</v>
       </c>
       <c r="I11" t="n">
-        <v>162.66</v>
+        <v>162.92</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02047585116129473</v>
+        <v>0.02048385034949116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6387,16 +6387,16 @@
         <v>158</v>
       </c>
       <c r="H12" t="n">
-        <v>43303.06</v>
+        <v>43535.32</v>
       </c>
       <c r="I12" t="n">
-        <v>274.07</v>
+        <v>275.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02032441622591334</v>
+        <v>0.02035760281701005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6422,16 +6422,16 @@
         <v>980</v>
       </c>
       <c r="H13" t="n">
-        <v>42982.8</v>
+        <v>43267</v>
       </c>
       <c r="I13" t="n">
-        <v>43.86</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02032191957800597</v>
+        <v>0.02034495547923019</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6457,16 +6457,16 @@
         <v>202</v>
       </c>
       <c r="H14" t="n">
-        <v>42977.52</v>
+        <v>43240.12</v>
       </c>
       <c r="I14" t="n">
-        <v>212.76</v>
+        <v>214.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0198990876666941</v>
+        <v>0.01974341647607556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6492,16 +6492,16 @@
         <v>158</v>
       </c>
       <c r="H15" t="n">
-        <v>42083.3</v>
+        <v>41961.64</v>
       </c>
       <c r="I15" t="n">
-        <v>266.35</v>
+        <v>265.58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01755382740970911</v>
+        <v>0.01757951720735941</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -6527,16 +6527,16 @@
         <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>37123.46</v>
+        <v>37362.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1687.43</v>
+        <v>1698.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6545,33 +6545,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01750089658267298</v>
+        <v>0.01750884173831503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>37011.52</v>
+        <v>37212.39</v>
       </c>
       <c r="I17" t="n">
-        <v>165.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6580,33 +6580,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0174207154111479</v>
+        <v>0.01749442998399222</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="H18" t="n">
-        <v>36841.95</v>
+        <v>37181.76</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>165.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6615,33 +6615,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01667866720517975</v>
+        <v>0.01659340597450356</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>488</v>
+        <v>99</v>
       </c>
       <c r="H19" t="n">
-        <v>35272.64</v>
+        <v>35266.77</v>
       </c>
       <c r="I19" t="n">
-        <v>72.28</v>
+        <v>356.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6650,33 +6650,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01655090313992012</v>
+        <v>0.0163711506565321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>99</v>
+        <v>488</v>
       </c>
       <c r="H20" t="n">
-        <v>35002.44</v>
+        <v>34794.4</v>
       </c>
       <c r="I20" t="n">
-        <v>353.56</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01554571864721497</v>
+        <v>0.01614407260000992</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>306</v>
       </c>
       <c r="H21" t="n">
-        <v>32876.64</v>
+        <v>34311.78</v>
       </c>
       <c r="I21" t="n">
-        <v>107.44</v>
+        <v>112.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01474284774800349</v>
+        <v>0.01474521493409502</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6737,16 +6737,16 @@
         <v>126</v>
       </c>
       <c r="H22" t="n">
-        <v>31178.7</v>
+        <v>31338.72</v>
       </c>
       <c r="I22" t="n">
-        <v>247.45</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01407059692794567</v>
+        <v>0.01406621098703875</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>84</v>
       </c>
       <c r="H23" t="n">
-        <v>29757</v>
+        <v>29895.6</v>
       </c>
       <c r="I23" t="n">
-        <v>354.25</v>
+        <v>355.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.013588275760341</v>
+        <v>0.01373858000801158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6807,16 +6807,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>28736.97</v>
+        <v>29199.27</v>
       </c>
       <c r="I24" t="n">
-        <v>142.97</v>
+        <v>145.27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01307666626482299</v>
+        <v>0.01302257036466119</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6842,16 +6842,16 @@
         <v>250</v>
       </c>
       <c r="H25" t="n">
-        <v>27655</v>
+        <v>27677.5</v>
       </c>
       <c r="I25" t="n">
-        <v>110.62</v>
+        <v>110.71</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0126054523433062</v>
+        <v>0.01302191164915182</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6877,16 +6877,16 @@
         <v>103</v>
       </c>
       <c r="H26" t="n">
-        <v>26658.46</v>
+        <v>27676.1</v>
       </c>
       <c r="I26" t="n">
-        <v>258.82</v>
+        <v>268.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01206468218937013</v>
+        <v>0.01208097418490625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>414</v>
       </c>
       <c r="H27" t="n">
-        <v>25514.82</v>
+        <v>25676.28</v>
       </c>
       <c r="I27" t="n">
-        <v>61.63</v>
+        <v>62.02</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01203187585758732</v>
+        <v>0.01189346611005394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6947,16 +6947,16 @@
         <v>524</v>
       </c>
       <c r="H28" t="n">
-        <v>25445.44</v>
+        <v>25277.76</v>
       </c>
       <c r="I28" t="n">
-        <v>48.56</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01117276890996234</v>
+        <v>0.01119793310882332</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6982,16 +6982,16 @@
         <v>259</v>
       </c>
       <c r="H29" t="n">
-        <v>23628.57</v>
+        <v>23799.51</v>
       </c>
       <c r="I29" t="n">
-        <v>91.23</v>
+        <v>91.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01089257219585834</v>
+        <v>0.01089703656925492</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>23036</v>
+        <v>23160</v>
       </c>
       <c r="I30" t="n">
-        <v>115.18</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01083062884815659</v>
+        <v>0.0106994219164446</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7052,16 +7052,16 @@
         <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>22905</v>
+        <v>22740</v>
       </c>
       <c r="I31" t="n">
-        <v>91.62</v>
+        <v>90.95999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.00988481067074881</v>
+        <v>0.009625833263944712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7087,16 +7087,16 @@
         <v>475</v>
       </c>
       <c r="H32" t="n">
-        <v>20904.75</v>
+        <v>20458.25</v>
       </c>
       <c r="I32" t="n">
-        <v>44.01</v>
+        <v>43.07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.008907874235995594</v>
+        <v>0.008977337255193733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7122,16 +7122,16 @@
         <v>377</v>
       </c>
       <c r="H33" t="n">
-        <v>18838.69</v>
+        <v>19079.97</v>
       </c>
       <c r="I33" t="n">
-        <v>49.97</v>
+        <v>50.61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7140,33 +7140,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.00889962773230156</v>
+        <v>0.008771930938929745</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H34" t="n">
-        <v>18821.25</v>
+        <v>18643.41</v>
       </c>
       <c r="I34" t="n">
-        <v>107.55</v>
+        <v>105.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7175,33 +7175,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.008849013870179461</v>
+        <v>0.008751858936337155</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H35" t="n">
-        <v>18714.21</v>
+        <v>18600.75</v>
       </c>
       <c r="I35" t="n">
-        <v>105.73</v>
+        <v>106.29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.008562008116328092</v>
+        <v>0.008555425266332913</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -7227,16 +7227,16 @@
         <v>362</v>
       </c>
       <c r="H36" t="n">
-        <v>18107.24</v>
+        <v>18183.26</v>
       </c>
       <c r="I36" t="n">
-        <v>50.02</v>
+        <v>50.23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7245,33 +7245,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.008529173413546342</v>
+        <v>0.008477668605562831</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>132</v>
+        <v>650</v>
       </c>
       <c r="H37" t="n">
-        <v>18037.8</v>
+        <v>18018</v>
       </c>
       <c r="I37" t="n">
-        <v>136.65</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7280,33 +7280,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.00849829630969196</v>
+        <v>0.008466489262346706</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>650</v>
+        <v>132</v>
       </c>
       <c r="H38" t="n">
-        <v>17972.5</v>
+        <v>17994.24</v>
       </c>
       <c r="I38" t="n">
-        <v>27.65</v>
+        <v>136.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008336108765709524</v>
+        <v>0.008330586842542578</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7332,16 +7332,16 @@
         <v>345</v>
       </c>
       <c r="H39" t="n">
-        <v>17629.5</v>
+        <v>17705.4</v>
       </c>
       <c r="I39" t="n">
-        <v>51.1</v>
+        <v>51.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.008053959181177978</v>
+        <v>0.008004169782096957</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7367,16 +7367,16 @@
         <v>235</v>
       </c>
       <c r="H40" t="n">
-        <v>17032.8</v>
+        <v>17011.65</v>
       </c>
       <c r="I40" t="n">
-        <v>72.48</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.007661607179735219</v>
+        <v>0.007614751288291091</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7402,16 +7402,16 @@
         <v>272</v>
       </c>
       <c r="H41" t="n">
-        <v>16203.04</v>
+        <v>16184</v>
       </c>
       <c r="I41" t="n">
-        <v>59.57</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7420,33 +7420,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.007303631372017016</v>
+        <v>0.007225920933332876</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="H42" t="n">
-        <v>15445.98</v>
+        <v>15357.6</v>
       </c>
       <c r="I42" t="n">
-        <v>88.77</v>
+        <v>284.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7455,33 +7455,33 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.007297077671260175</v>
+        <v>0.007184817085548328</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="H43" t="n">
-        <v>15432.12</v>
+        <v>15270.24</v>
       </c>
       <c r="I43" t="n">
-        <v>285.78</v>
+        <v>87.76000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.006723004693059717</v>
+        <v>0.006714593019186166</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7507,16 +7507,16 @@
         <v>55</v>
       </c>
       <c r="H44" t="n">
-        <v>14218.05</v>
+        <v>14270.85</v>
       </c>
       <c r="I44" t="n">
-        <v>258.51</v>
+        <v>259.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.004761835748323989</v>
+        <v>0.004761572110572531</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7542,16 +7542,16 @@
         <v>275</v>
       </c>
       <c r="H45" t="n">
-        <v>10070.5</v>
+        <v>10120</v>
       </c>
       <c r="I45" t="n">
-        <v>36.62</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.004191819822973004</v>
+        <v>0.004212702117502641</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7577,16 +7577,16 @@
         <v>29</v>
       </c>
       <c r="H46" t="n">
-        <v>8865.01</v>
+        <v>8953.459999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>305.69</v>
+        <v>308.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.002671460545882135</v>
+        <v>0.002653306071733262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7612,261 +7612,13 @@
         <v>35</v>
       </c>
       <c r="H47" t="n">
-        <v>5649.7</v>
+        <v>5639.2</v>
       </c>
       <c r="I47" t="n">
-        <v>161.42</v>
+        <v>161.12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66747FDD-EF11-48DE-8659-FB96CD58A8C7}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5DBEAED-2D17-4D75-906D-38A31D57452D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7106B705-CA5D-4C1B-B85C-274E088BEB5B}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -7621,4 +7621,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92702C67-0FD4-4B7D-AF21-EF95385FEFD8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CE20EE7-E3DA-405C-8133-B8A51713B4EF}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F42E151D-750B-459C-96D6-41FCA0CFF83E}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09375014458268499</v>
+        <v>0.09382997433615292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04288928232233253</v>
+        <v>0.04339789037794425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>101507.15</v>
+        <v>102623.5</v>
       </c>
       <c r="I3" t="n">
-        <v>377.35</v>
+        <v>381.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04051501861870061</v>
+        <v>0.04127356378138135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>95887.92</v>
+        <v>97600.08</v>
       </c>
       <c r="I4" t="n">
-        <v>275.54</v>
+        <v>280.46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,33 +596,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03880118221239624</v>
+        <v>0.03876235281652007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>429</v>
+        <v>561</v>
       </c>
       <c r="H5" t="n">
-        <v>91831.74000000001</v>
+        <v>91661.78999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>214.06</v>
+        <v>163.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,33 +631,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03861796703395206</v>
+        <v>0.03849134303778898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>561</v>
+        <v>429</v>
       </c>
       <c r="H6" t="n">
-        <v>91398.12</v>
+        <v>91020.92999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>162.92</v>
+        <v>212.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0366940175241545</v>
+        <v>0.03682759266740557</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -683,16 +683,16 @@
         <v>327</v>
       </c>
       <c r="H7" t="n">
-        <v>86844.66</v>
+        <v>87086.64</v>
       </c>
       <c r="I7" t="n">
-        <v>265.58</v>
+        <v>266.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,33 +701,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03444354089406344</v>
+        <v>0.03302002495255532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASML Holding</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>48</v>
+        <v>473</v>
       </c>
       <c r="H8" t="n">
-        <v>81518.39999999999</v>
+        <v>78082.84</v>
       </c>
       <c r="I8" t="n">
-        <v>1698.3</v>
+        <v>165.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,33 +736,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03317379911739736</v>
+        <v>0.03197311509920541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>ASML Holding</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>473</v>
+        <v>48</v>
       </c>
       <c r="H9" t="n">
-        <v>78513.27</v>
+        <v>75607.2</v>
       </c>
       <c r="I9" t="n">
-        <v>165.99</v>
+        <v>1575.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03179043621247283</v>
+        <v>0.03123013235626032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -788,16 +788,16 @@
         <v>671</v>
       </c>
       <c r="H10" t="n">
-        <v>75239.23</v>
+        <v>73850.25999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>112.13</v>
+        <v>110.06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03148168470805764</v>
+        <v>0.03120799012236468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         <v>1045</v>
       </c>
       <c r="H11" t="n">
-        <v>74508.5</v>
+        <v>73797.89999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>71.3</v>
+        <v>70.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,33 +841,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02932342832806397</v>
+        <v>0.02949474957564807</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="H12" t="n">
-        <v>69400.5</v>
+        <v>69746.58</v>
       </c>
       <c r="I12" t="n">
-        <v>355.9</v>
+        <v>505.41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,33 +876,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02889939939840335</v>
+        <v>0.02942343855766064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="H13" t="n">
-        <v>68396.94</v>
+        <v>69577.95</v>
       </c>
       <c r="I13" t="n">
-        <v>495.63</v>
+        <v>356.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,33 +911,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02814648988563864</v>
+        <v>0.02769900002863774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>187</v>
+        <v>263</v>
       </c>
       <c r="H14" t="n">
-        <v>66615.00999999999</v>
+        <v>65500.15</v>
       </c>
       <c r="I14" t="n">
-        <v>356.23</v>
+        <v>249.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02763876302991832</v>
+        <v>0.0276880726924295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>263</v>
+        <v>187</v>
       </c>
       <c r="H15" t="n">
-        <v>65413.36</v>
+        <v>65474.31</v>
       </c>
       <c r="I15" t="n">
-        <v>248.72</v>
+        <v>350.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02682313394451339</v>
+        <v>0.02700490273715056</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -998,16 +998,16 @@
         <v>437</v>
       </c>
       <c r="H16" t="n">
-        <v>63482.99</v>
+        <v>63858.81</v>
       </c>
       <c r="I16" t="n">
-        <v>145.27</v>
+        <v>146.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02559536577567592</v>
+        <v>0.02567841123568331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>213</v>
       </c>
       <c r="H17" t="n">
-        <v>60577.2</v>
+        <v>60722.04</v>
       </c>
       <c r="I17" t="n">
-        <v>284.4</v>
+        <v>285.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02543125716604602</v>
+        <v>0.02495275830070314</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1068,16 +1068,16 @@
         <v>224</v>
       </c>
       <c r="H18" t="n">
-        <v>60188.8</v>
+        <v>59006.08</v>
       </c>
       <c r="I18" t="n">
-        <v>268.7</v>
+        <v>263.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02483139879042405</v>
+        <v>0.02460515567622763</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         <v>1170</v>
       </c>
       <c r="H19" t="n">
-        <v>58769.1</v>
+        <v>58184.1</v>
       </c>
       <c r="I19" t="n">
-        <v>50.23</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02403124678630322</v>
+        <v>0.02456373413669215</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1138,16 +1138,16 @@
         <v>353</v>
       </c>
       <c r="H20" t="n">
-        <v>56875.36</v>
+        <v>58086.15</v>
       </c>
       <c r="I20" t="n">
-        <v>161.12</v>
+        <v>164.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0235320760565999</v>
+        <v>0.0241407269719964</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         <v>898</v>
       </c>
       <c r="H21" t="n">
-        <v>55693.96</v>
+        <v>57085.86</v>
       </c>
       <c r="I21" t="n">
-        <v>62.02</v>
+        <v>63.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,33 +1191,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02172115191517515</v>
+        <v>0.02201494565265655</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>864</v>
+        <v>555</v>
       </c>
       <c r="H22" t="n">
-        <v>51408</v>
+        <v>52059</v>
       </c>
       <c r="I22" t="n">
-        <v>59.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02158714396813544</v>
+        <v>0.02165561221136926</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Total SA</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>556</v>
+        <v>864</v>
       </c>
       <c r="H23" t="n">
-        <v>51090.84</v>
+        <v>51209.28</v>
       </c>
       <c r="I23" t="n">
-        <v>91.89</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02137741536215709</v>
+        <v>0.0216468542727906</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1278,16 +1278,16 @@
         <v>457</v>
       </c>
       <c r="H24" t="n">
-        <v>50594.47</v>
+        <v>51188.57</v>
       </c>
       <c r="I24" t="n">
-        <v>110.71</v>
+        <v>112.01</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,33 +1296,33 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02133023202426478</v>
+        <v>0.02142918291959918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Total SA</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H25" t="n">
-        <v>50482.8</v>
+        <v>50673.84</v>
       </c>
       <c r="I25" t="n">
-        <v>90.95999999999999</v>
+        <v>91.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02084348352196394</v>
+        <v>0.02134943535527451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         <v>426</v>
       </c>
       <c r="H26" t="n">
-        <v>49330.8</v>
+        <v>50485.26</v>
       </c>
       <c r="I26" t="n">
-        <v>115.8</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01978137885380538</v>
+        <v>0.01997289969874214</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1383,16 +1383,16 @@
         <v>1087</v>
       </c>
       <c r="H27" t="n">
-        <v>46817.09</v>
+        <v>47230.15</v>
       </c>
       <c r="I27" t="n">
-        <v>43.07</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01967325899768232</v>
+        <v>0.01995456765444542</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1418,16 +1418,16 @@
         <v>920</v>
       </c>
       <c r="H28" t="n">
-        <v>46561.2</v>
+        <v>47186.8</v>
       </c>
       <c r="I28" t="n">
-        <v>50.61</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,33 +1436,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01913172593738814</v>
+        <v>0.01908416134546836</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>426</v>
+        <v>331</v>
       </c>
       <c r="H29" t="n">
-        <v>45279.54</v>
+        <v>45128.54</v>
       </c>
       <c r="I29" t="n">
-        <v>106.29</v>
+        <v>136.34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01911887273474926</v>
+        <v>0.01907168625188698</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1488,16 +1488,16 @@
         <v>938</v>
       </c>
       <c r="H30" t="n">
-        <v>45249.12</v>
+        <v>45099.04</v>
       </c>
       <c r="I30" t="n">
-        <v>48.24</v>
+        <v>48.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,33 +1506,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01906512758762021</v>
+        <v>0.0190597439928111</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>331</v>
+        <v>426</v>
       </c>
       <c r="H31" t="n">
-        <v>45121.92</v>
+        <v>45070.8</v>
       </c>
       <c r="I31" t="n">
-        <v>136.32</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01761542829826753</v>
+        <v>0.01763042811831626</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01712847698409073</v>
+        <v>0.01679494361367651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>40538.4</v>
+        <v>39715.2</v>
       </c>
       <c r="I33" t="n">
-        <v>72.39</v>
+        <v>70.92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01651118101238373</v>
+        <v>0.01626009617781233</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>39077.43</v>
+        <v>38450.44</v>
       </c>
       <c r="I34" t="n">
-        <v>105.33</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0138311277027751</v>
+        <v>0.01408739582007062</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         <v>373</v>
       </c>
       <c r="H35" t="n">
-        <v>32734.48</v>
+        <v>33312.63</v>
       </c>
       <c r="I35" t="n">
-        <v>87.76000000000001</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0132655318584479</v>
+        <v>0.01315351031456807</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
         <v>121</v>
       </c>
       <c r="H36" t="n">
-        <v>31395.87</v>
+        <v>31104.26</v>
       </c>
       <c r="I36" t="n">
-        <v>259.47</v>
+        <v>257.06</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01134917511825654</v>
+        <v>0.01143720385502213</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         <v>87</v>
       </c>
       <c r="H37" t="n">
-        <v>26860.38</v>
+        <v>27045.69</v>
       </c>
       <c r="I37" t="n">
-        <v>308.74</v>
+        <v>310.87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01131903220319218</v>
+        <v>0.01112337701781256</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         <v>522</v>
       </c>
       <c r="H38" t="n">
-        <v>26789.04</v>
+        <v>26303.58</v>
       </c>
       <c r="I38" t="n">
-        <v>51.32</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008940623531845356</v>
+        <v>0.009009026267269484</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         <v>575</v>
       </c>
       <c r="H39" t="n">
-        <v>21160</v>
+        <v>21303.75</v>
       </c>
       <c r="I39" t="n">
-        <v>36.8</v>
+        <v>37.05</v>
       </c>
     </row>
   </sheetData>
@@ -1873,7 +1873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06091261416153827</v>
+        <v>0.06102736460189603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>158195.32</v>
+        <v>158651.69</v>
       </c>
       <c r="I2" t="n">
-        <v>162.92</v>
+        <v>163.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05810007774211991</v>
+        <v>0.05746432381730997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>150890.92</v>
+        <v>149388.92</v>
       </c>
       <c r="I3" t="n">
-        <v>50.23</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05031450686794062</v>
+        <v>0.05087810075909463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1969,16 +1969,16 @@
         <v>556</v>
       </c>
       <c r="H4" t="n">
-        <v>130671.12</v>
+        <v>132266.84</v>
       </c>
       <c r="I4" t="n">
-        <v>235.02</v>
+        <v>237.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1987,33 +1987,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04919554523710353</v>
+        <v>0.04991706367560859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1095</v>
       </c>
       <c r="H5" t="n">
-        <v>127765.08</v>
+        <v>129768.45</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2022,33 +2022,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04889529338217581</v>
+        <v>0.04914644225063354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1781</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>126985.3</v>
+        <v>127765.08</v>
       </c>
       <c r="I6" t="n">
-        <v>71.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2057,33 +2057,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04882432924246566</v>
+        <v>0.04838063295423506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1095</v>
+        <v>1781</v>
       </c>
       <c r="H7" t="n">
-        <v>126801</v>
+        <v>125774.22</v>
       </c>
       <c r="I7" t="n">
-        <v>115.8</v>
+        <v>70.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04361324340553217</v>
+        <v>0.04449724519294512</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2109,16 +2109,16 @@
         <v>703</v>
       </c>
       <c r="H8" t="n">
-        <v>113267.36</v>
+        <v>115678.65</v>
       </c>
       <c r="I8" t="n">
-        <v>161.12</v>
+        <v>164.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04309598683081148</v>
+        <v>0.04311009431633532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>450</v>
       </c>
       <c r="H9" t="n">
-        <v>111924</v>
+        <v>112072.5</v>
       </c>
       <c r="I9" t="n">
-        <v>248.72</v>
+        <v>249.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.04035115705451105</v>
+        <v>0.03958038454223364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>104795.44</v>
+        <v>102896.38</v>
       </c>
       <c r="I10" t="n">
-        <v>51.32</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2197,33 +2197,33 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03693599146646787</v>
+        <v>0.03717125834000352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>796</v>
+        <v>1082</v>
       </c>
       <c r="H11" t="n">
-        <v>95925.96000000001</v>
+        <v>96633.42</v>
       </c>
       <c r="I11" t="n">
-        <v>120.51</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2232,33 +2232,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03656263461118546</v>
+        <v>0.03701909737269474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1082</v>
+        <v>295</v>
       </c>
       <c r="H12" t="n">
-        <v>94956.32000000001</v>
+        <v>96237.85000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>87.76000000000001</v>
+        <v>326.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2267,33 +2267,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03652675979351429</v>
+        <v>0.03652250955267146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>295</v>
+        <v>796</v>
       </c>
       <c r="H13" t="n">
-        <v>94863.14999999999</v>
+        <v>94946.88</v>
       </c>
       <c r="I13" t="n">
-        <v>321.57</v>
+        <v>119.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03596209239664216</v>
+        <v>0.03615351045587453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2319,16 +2319,16 @@
         <v>804</v>
       </c>
       <c r="H14" t="n">
-        <v>93396.66</v>
+        <v>93987.60000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>116.17</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03470327403859117</v>
+        <v>0.03372640512577319</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>710</v>
       </c>
       <c r="H15" t="n">
-        <v>90127.39999999999</v>
+        <v>87677.89999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>126.94</v>
+        <v>123.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03339724123229679</v>
+        <v>0.03325324710204078</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         <v>1798</v>
       </c>
       <c r="H16" t="n">
-        <v>86735.52</v>
+        <v>86447.84</v>
       </c>
       <c r="I16" t="n">
-        <v>48.24</v>
+        <v>48.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03186286792610597</v>
+        <v>0.03160528347253169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
         <v>327</v>
       </c>
       <c r="H17" t="n">
-        <v>82750.62</v>
+        <v>82163.66</v>
       </c>
       <c r="I17" t="n">
-        <v>253.06</v>
+        <v>251.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2442,33 +2442,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03126904092912397</v>
+        <v>0.03124333139376215</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Snap-On</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>910</v>
+        <v>215</v>
       </c>
       <c r="H18" t="n">
-        <v>81208.39999999999</v>
+        <v>81222.7</v>
       </c>
       <c r="I18" t="n">
-        <v>89.23999999999999</v>
+        <v>377.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,33 +2477,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03108083001490628</v>
+        <v>0.03111531569509855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Snap-On</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>215</v>
+        <v>910</v>
       </c>
       <c r="H19" t="n">
-        <v>80719.60000000001</v>
+        <v>80889.89999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>375.44</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03094053433425089</v>
+        <v>0.03076715761559006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,16 +2529,16 @@
         <v>756</v>
       </c>
       <c r="H20" t="n">
-        <v>80355.24000000001</v>
+        <v>79984.8</v>
       </c>
       <c r="I20" t="n">
-        <v>106.29</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03091991507390646</v>
+        <v>0.03038564929246939</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2564,16 +2564,16 @@
         <v>1179</v>
       </c>
       <c r="H21" t="n">
-        <v>80301.69</v>
+        <v>78993</v>
       </c>
       <c r="I21" t="n">
-        <v>68.11</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02891290057480838</v>
+        <v>0.02882378852951337</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2599,16 +2599,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>75089.3</v>
+        <v>74932.66</v>
       </c>
       <c r="I22" t="n">
-        <v>76.7</v>
+        <v>76.54000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02610630157825672</v>
+        <v>0.02627325267841692</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>67800.32000000001</v>
+        <v>68302.08</v>
       </c>
       <c r="I23" t="n">
-        <v>86.48</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02494930501675999</v>
+        <v>0.02539696060266098</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2669,16 +2669,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>64795.5</v>
+        <v>66024</v>
       </c>
       <c r="I24" t="n">
-        <v>20.57</v>
+        <v>20.96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02471211999006409</v>
+        <v>0.02439708798751306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2704,16 +2704,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>64179.51</v>
+        <v>63424.65</v>
       </c>
       <c r="I25" t="n">
-        <v>39.11</v>
+        <v>38.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2722,33 +2722,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02267430944162246</v>
+        <v>0.02315707438522962</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Amdocs Ltd</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>586</v>
+        <v>953</v>
       </c>
       <c r="H26" t="n">
-        <v>58887.14</v>
+        <v>60201.01</v>
       </c>
       <c r="I26" t="n">
-        <v>100.49</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2757,33 +2757,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02253804905225389</v>
+        <v>0.02223241099304655</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Amdocs Ltd</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>953</v>
+        <v>586</v>
       </c>
       <c r="H27" t="n">
-        <v>58533.26</v>
+        <v>57797.18</v>
       </c>
       <c r="I27" t="n">
-        <v>61.42</v>
+        <v>98.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02091978943311</v>
+        <v>0.02102944039491366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>54330.5</v>
+        <v>54669.84</v>
       </c>
       <c r="I28" t="n">
-        <v>75.25</v>
+        <v>75.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01572328917193462</v>
+        <v>0.01572556689990399</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>40834.74</v>
+        <v>40881.46</v>
       </c>
       <c r="I29" t="n">
-        <v>279.69</v>
+        <v>280.01</v>
       </c>
     </row>
   </sheetData>
@@ -2914,7 +2914,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09245410470585647</v>
+        <v>0.09240120267509336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03775219006872154</v>
+        <v>0.03840429995200272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>411</v>
       </c>
       <c r="H3" t="n">
-        <v>113246.94</v>
+        <v>115269.06</v>
       </c>
       <c r="I3" t="n">
-        <v>275.54</v>
+        <v>280.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03484494619910864</v>
+        <v>0.03520800464216386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3010,16 +3010,16 @@
         <v>277</v>
       </c>
       <c r="H4" t="n">
-        <v>104525.95</v>
+        <v>105675.5</v>
       </c>
       <c r="I4" t="n">
-        <v>377.35</v>
+        <v>381.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03475922224333402</v>
+        <v>0.03483955091037391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>104268.8</v>
+        <v>104569.6</v>
       </c>
       <c r="I5" t="n">
-        <v>162.92</v>
+        <v>163.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0337529966839747</v>
+        <v>0.03343583847865304</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>101250.38</v>
+        <v>100356.41</v>
       </c>
       <c r="I6" t="n">
-        <v>214.06</v>
+        <v>212.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03132431017276065</v>
+        <v>0.03072844818702606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3115,16 +3115,16 @@
         <v>838</v>
       </c>
       <c r="H7" t="n">
-        <v>93964.94</v>
+        <v>92230.28</v>
       </c>
       <c r="I7" t="n">
-        <v>112.13</v>
+        <v>110.06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03060009192581645</v>
+        <v>0.03041492101480107</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3150,16 +3150,16 @@
         <v>553</v>
       </c>
       <c r="H8" t="n">
-        <v>91792.47</v>
+        <v>91289.24000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>165.99</v>
+        <v>165.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03019016040267237</v>
+        <v>0.03025695801333959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
         <v>341</v>
       </c>
       <c r="H9" t="n">
-        <v>90562.78</v>
+        <v>90815.12</v>
       </c>
       <c r="I9" t="n">
-        <v>265.58</v>
+        <v>266.32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02740529693906539</v>
+        <v>0.02712839635362541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3220,16 +3220,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>82208.89999999999</v>
+        <v>81424.86</v>
       </c>
       <c r="I10" t="n">
-        <v>71.3</v>
+        <v>70.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02542441183773856</v>
+        <v>0.02556029072148878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>76266.75</v>
+        <v>76718.25</v>
       </c>
       <c r="I11" t="n">
-        <v>145.27</v>
+        <v>146.13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02462537389554234</v>
+        <v>0.02464393739486333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>73869.84</v>
+        <v>73967.85000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>248.72</v>
+        <v>249.05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02422569991126345</v>
+        <v>0.02379724011463026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3325,16 +3325,16 @@
         <v>204</v>
       </c>
       <c r="H13" t="n">
-        <v>72670.92</v>
+        <v>71426.52</v>
       </c>
       <c r="I13" t="n">
-        <v>356.23</v>
+        <v>350.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3343,33 +3343,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02373718503951058</v>
+        <v>0.02374269670163511</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>265</v>
+        <v>141</v>
       </c>
       <c r="H14" t="n">
-        <v>71205.5</v>
+        <v>71262.81</v>
       </c>
       <c r="I14" t="n">
-        <v>268.7</v>
+        <v>505.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3378,33 +3378,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.023296590909125</v>
+        <v>0.0233547158216218</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>141</v>
+        <v>426</v>
       </c>
       <c r="H15" t="n">
-        <v>69883.83</v>
+        <v>70098.3</v>
       </c>
       <c r="I15" t="n">
-        <v>495.63</v>
+        <v>164.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3413,33 +3413,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02288098557020303</v>
+        <v>0.02325742990998181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>426</v>
+        <v>265</v>
       </c>
       <c r="H16" t="n">
-        <v>68637.12</v>
+        <v>69806.3</v>
       </c>
       <c r="I16" t="n">
-        <v>161.12</v>
+        <v>263.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3448,33 +3448,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0224287471163673</v>
+        <v>0.02222540629978386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1311</v>
+        <v>234</v>
       </c>
       <c r="H17" t="n">
-        <v>67280.52</v>
+        <v>66708.72</v>
       </c>
       <c r="I17" t="n">
-        <v>51.32</v>
+        <v>285.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3483,33 +3483,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02218508639789641</v>
+        <v>0.0220097014443966</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>234</v>
+        <v>1311</v>
       </c>
       <c r="H18" t="n">
-        <v>66549.60000000001</v>
+        <v>66061.28999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>284.4</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02171174614977511</v>
+        <v>0.02175480569248122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3535,16 +3535,16 @@
         <v>183</v>
       </c>
       <c r="H19" t="n">
-        <v>65129.7</v>
+        <v>65296.23</v>
       </c>
       <c r="I19" t="n">
-        <v>355.9</v>
+        <v>356.81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02115459877553388</v>
+        <v>0.02163727964682708</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3570,16 +3570,16 @@
         <v>548</v>
       </c>
       <c r="H20" t="n">
-        <v>63458.4</v>
+        <v>64943.48</v>
       </c>
       <c r="I20" t="n">
-        <v>115.8</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02099690536686334</v>
+        <v>0.02124115273756858</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3605,16 +3605,16 @@
         <v>268</v>
       </c>
       <c r="H21" t="n">
-        <v>62985.36</v>
+        <v>63754.52</v>
       </c>
       <c r="I21" t="n">
-        <v>235.02</v>
+        <v>237.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3623,33 +3623,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02011045332517957</v>
+        <v>0.02050094021836036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1201</v>
+        <v>656</v>
       </c>
       <c r="H22" t="n">
-        <v>60326.23</v>
+        <v>61532.8</v>
       </c>
       <c r="I22" t="n">
-        <v>50.23</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02003337010412662</v>
+        <v>0.01994451144770985</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3675,16 +3675,16 @@
         <v>1010</v>
       </c>
       <c r="H23" t="n">
-        <v>60095</v>
+        <v>59862.7</v>
       </c>
       <c r="I23" t="n">
-        <v>59.5</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3693,33 +3693,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01989161138371596</v>
+        <v>0.01989887702539023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>656</v>
+        <v>1201</v>
       </c>
       <c r="H24" t="n">
-        <v>59669.76</v>
+        <v>59725.73</v>
       </c>
       <c r="I24" t="n">
-        <v>90.95999999999999</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01808665790852196</v>
+        <v>0.01807896080415255</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3745,16 +3745,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>54255.36</v>
+        <v>54263.32</v>
       </c>
       <c r="I25" t="n">
-        <v>136.32</v>
+        <v>136.34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01700784617716044</v>
+        <v>0.01691975252303182</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3780,16 +3780,16 @@
         <v>480</v>
       </c>
       <c r="H26" t="n">
-        <v>51019.2</v>
+        <v>50784</v>
       </c>
       <c r="I26" t="n">
-        <v>106.29</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3798,33 +3798,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01636153122099972</v>
+        <v>0.01606976684571694</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>678</v>
+        <v>1740</v>
       </c>
       <c r="H27" t="n">
-        <v>49080.42</v>
+        <v>48232.8</v>
       </c>
       <c r="I27" t="n">
-        <v>72.39</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3833,33 +3833,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01607896719458056</v>
+        <v>0.01602011105026891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1740</v>
+        <v>678</v>
       </c>
       <c r="H28" t="n">
-        <v>48232.8</v>
+        <v>48083.76</v>
       </c>
       <c r="I28" t="n">
-        <v>27.72</v>
+        <v>70.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01602919296227758</v>
+        <v>0.0158565107966672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,16 +3885,16 @@
         <v>399</v>
       </c>
       <c r="H29" t="n">
-        <v>48083.49</v>
+        <v>47592.72</v>
       </c>
       <c r="I29" t="n">
-        <v>120.51</v>
+        <v>119.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01582406552029119</v>
+        <v>0.01576255659432995</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,16 +3920,16 @@
         <v>984</v>
       </c>
       <c r="H30" t="n">
-        <v>47468.16</v>
+        <v>47310.72</v>
       </c>
       <c r="I30" t="n">
-        <v>48.24</v>
+        <v>48.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01548797694267944</v>
+        <v>0.0156870933786229</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,16 +3955,16 @@
         <v>918</v>
       </c>
       <c r="H31" t="n">
-        <v>46459.98</v>
+        <v>47084.22</v>
       </c>
       <c r="I31" t="n">
-        <v>50.61</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01439386391024829</v>
+        <v>0.01463970392512071</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,16 +3990,16 @@
         <v>492</v>
       </c>
       <c r="H32" t="n">
-        <v>43177.92</v>
+        <v>43940.52</v>
       </c>
       <c r="I32" t="n">
-        <v>87.76000000000001</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01339883596968917</v>
+        <v>0.0134758978851622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4025,16 +4025,16 @@
         <v>346</v>
       </c>
       <c r="H33" t="n">
-        <v>40193.09</v>
+        <v>40447.4</v>
       </c>
       <c r="I33" t="n">
-        <v>116.17</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4043,33 +4043,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01320248260709608</v>
+        <v>0.0131515326625754</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>376</v>
+        <v>121</v>
       </c>
       <c r="H34" t="n">
-        <v>39604.08</v>
+        <v>39473.83</v>
       </c>
       <c r="I34" t="n">
-        <v>105.33</v>
+        <v>326.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4078,33 +4078,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01311824877802693</v>
+        <v>0.01298321804031031</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Allison Transmission</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>310</v>
+        <v>376</v>
       </c>
       <c r="H35" t="n">
-        <v>39351.4</v>
+        <v>38968.64</v>
       </c>
       <c r="I35" t="n">
-        <v>126.94</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4113,33 +4113,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01297109293203201</v>
+        <v>0.01280827331653277</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="H36" t="n">
-        <v>38909.97</v>
+        <v>38443.55</v>
       </c>
       <c r="I36" t="n">
-        <v>321.57</v>
+        <v>251.27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4148,33 +4148,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01290715749560185</v>
+        <v>0.01275441623565398</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Allison Transmission</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>153</v>
+        <v>310</v>
       </c>
       <c r="H37" t="n">
-        <v>38718.18</v>
+        <v>38281.9</v>
       </c>
       <c r="I37" t="n">
-        <v>253.06</v>
+        <v>123.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01219612703668193</v>
+        <v>0.01207593362640692</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4200,16 +4200,16 @@
         <v>141</v>
       </c>
       <c r="H38" t="n">
-        <v>36585.27</v>
+        <v>36245.46</v>
       </c>
       <c r="I38" t="n">
-        <v>259.47</v>
+        <v>257.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01193896183659163</v>
+        <v>0.01201445026293417</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4235,16 +4235,16 @@
         <v>116</v>
       </c>
       <c r="H39" t="n">
-        <v>35813.84</v>
+        <v>36060.92</v>
       </c>
       <c r="I39" t="n">
-        <v>308.74</v>
+        <v>310.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.01186394212433216</v>
+        <v>0.01183241899346969</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4270,16 +4270,16 @@
         <v>464</v>
       </c>
       <c r="H40" t="n">
-        <v>35588.8</v>
+        <v>35514.56</v>
       </c>
       <c r="I40" t="n">
-        <v>76.7</v>
+        <v>76.54000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01150281808462173</v>
+        <v>0.01158131472674083</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4305,16 +4305,16 @@
         <v>399</v>
       </c>
       <c r="H41" t="n">
-        <v>34505.52</v>
+        <v>34760.88</v>
       </c>
       <c r="I41" t="n">
-        <v>86.48</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4323,33 +4323,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01133444376775357</v>
+        <v>0.01132787826350005</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Snap-On</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>381</v>
+        <v>90</v>
       </c>
       <c r="H42" t="n">
-        <v>34000.44</v>
+        <v>34000.2</v>
       </c>
       <c r="I42" t="n">
-        <v>89.23999999999999</v>
+        <v>377.78</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4358,33 +4358,33 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.011264157791337</v>
+        <v>0.01128352988097128</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Snap-On</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>90</v>
+        <v>381</v>
       </c>
       <c r="H43" t="n">
-        <v>33789.6</v>
+        <v>33867.09</v>
       </c>
       <c r="I43" t="n">
-        <v>375.44</v>
+        <v>88.89</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.01119369513323051</v>
+        <v>0.01100496899787855</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4410,16 +4410,16 @@
         <v>493</v>
       </c>
       <c r="H44" t="n">
-        <v>33578.23</v>
+        <v>33031</v>
       </c>
       <c r="I44" t="n">
-        <v>68.11</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.009191631564431924</v>
+        <v>0.009078324800836915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4445,16 +4445,16 @@
         <v>705</v>
       </c>
       <c r="H45" t="n">
-        <v>27572.55</v>
+        <v>27248.25</v>
       </c>
       <c r="I45" t="n">
-        <v>39.11</v>
+        <v>38.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4463,33 +4463,33 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.008893852910979686</v>
+        <v>0.009071001703789492</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hormel Foods</t>
+          <t>Amdocs Ltd</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1297</v>
+        <v>431</v>
       </c>
       <c r="H46" t="n">
-        <v>26679.29</v>
+        <v>27226.27</v>
       </c>
       <c r="I46" t="n">
-        <v>20.57</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,33 +4498,33 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.008824757035757417</v>
+        <v>0.00905729172000872</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Amdocs Ltd</t>
+          <t>Hormel Foods</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>431</v>
+        <v>1297</v>
       </c>
       <c r="H47" t="n">
-        <v>26472.02</v>
+        <v>27185.12</v>
       </c>
       <c r="I47" t="n">
-        <v>61.42</v>
+        <v>20.96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008779913222687992</v>
+        <v>0.008829695994119985</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4550,16 +4550,16 @@
         <v>350</v>
       </c>
       <c r="H48" t="n">
-        <v>26337.5</v>
+        <v>26502</v>
       </c>
       <c r="I48" t="n">
-        <v>75.25</v>
+        <v>75.72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.008609375388522619</v>
+        <v>0.008445186755200132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4585,16 +4585,16 @@
         <v>257</v>
       </c>
       <c r="H49" t="n">
-        <v>25825.93</v>
+        <v>25347.91</v>
       </c>
       <c r="I49" t="n">
-        <v>100.49</v>
+        <v>98.63</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.00769185403834888</v>
+        <v>0.007739677320089245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4620,16 +4620,16 @@
         <v>627</v>
       </c>
       <c r="H50" t="n">
-        <v>23073.6</v>
+        <v>23230.35</v>
       </c>
       <c r="I50" t="n">
-        <v>36.8</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.006060465321366275</v>
+        <v>0.006063927492090405</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4655,10 +4655,10 @@
         <v>65</v>
       </c>
       <c r="H51" t="n">
-        <v>18179.85</v>
+        <v>18200.65</v>
       </c>
       <c r="I51" t="n">
-        <v>279.69</v>
+        <v>280.01</v>
       </c>
     </row>
   </sheetData>
@@ -4725,7 +4725,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07024919274354881</v>
+        <v>0.0699686476226017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05325424542690152</v>
+        <v>0.05337717582807953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4786,16 +4786,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>118255.97</v>
+        <v>119004.2</v>
       </c>
       <c r="I3" t="n">
-        <v>116.17</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04151467963041482</v>
+        <v>0.04216480316627614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4821,16 +4821,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>92187.17999999999</v>
+        <v>94006.25999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04011312116787216</v>
+        <v>0.04053190048333794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4856,16 +4856,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>89074.89</v>
+        <v>90365.71000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>321.57</v>
+        <v>326.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0392350311393264</v>
+        <v>0.03835692909967096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4891,16 +4891,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>87125.00999999999</v>
+        <v>85516.62</v>
       </c>
       <c r="I6" t="n">
-        <v>112.13</v>
+        <v>110.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03492786958398735</v>
+        <v>0.03478838266585811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4944,33 +4944,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03420260364312252</v>
+        <v>0.03433098781069802</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>246</v>
+        <v>816</v>
       </c>
       <c r="H8" t="n">
-        <v>75950.03999999999</v>
+        <v>76540.8</v>
       </c>
       <c r="I8" t="n">
-        <v>308.74</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4979,33 +4979,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03393786347142914</v>
+        <v>0.03430103485272008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>303</v>
+        <v>246</v>
       </c>
       <c r="H9" t="n">
-        <v>75362.16</v>
+        <v>76474.02</v>
       </c>
       <c r="I9" t="n">
-        <v>248.72</v>
+        <v>310.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5014,33 +5014,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0334250273356116</v>
+        <v>0.03384717891397876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>816</v>
+        <v>303</v>
       </c>
       <c r="H10" t="n">
-        <v>74223.36</v>
+        <v>75462.14999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>90.95999999999999</v>
+        <v>249.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03264434374909019</v>
+        <v>0.03236408587411684</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5066,16 +5066,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>72489.78</v>
+        <v>72155.60000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>106.29</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5084,33 +5084,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03160296846019486</v>
+        <v>0.03125544069152849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>197</v>
+        <v>588</v>
       </c>
       <c r="H12" t="n">
-        <v>70177.31</v>
+        <v>69683.88</v>
       </c>
       <c r="I12" t="n">
-        <v>356.23</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5119,33 +5119,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03082496433890713</v>
+        <v>0.03093775902715232</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>568</v>
+        <v>197</v>
       </c>
       <c r="H13" t="n">
-        <v>68449.67999999999</v>
+        <v>68975.61</v>
       </c>
       <c r="I13" t="n">
-        <v>120.51</v>
+        <v>350.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5154,33 +5154,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03066316967182202</v>
+        <v>0.03081983551439428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>588</v>
+        <v>245</v>
       </c>
       <c r="H14" t="n">
-        <v>68090.39999999999</v>
+        <v>68712.7</v>
       </c>
       <c r="I14" t="n">
-        <v>115.8</v>
+        <v>280.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5189,33 +5189,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03040058207892142</v>
+        <v>0.03068017166211557</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>245</v>
+        <v>1076</v>
       </c>
       <c r="H15" t="n">
-        <v>67507.3</v>
+        <v>68401.32000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>275.54</v>
+        <v>63.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5224,33 +5224,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03005212550606148</v>
+        <v>0.03038850036061962</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1076</v>
+        <v>568</v>
       </c>
       <c r="H16" t="n">
-        <v>66733.52</v>
+        <v>67751.03999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>62.02</v>
+        <v>119.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02899181382841385</v>
+        <v>0.02876441132883845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5276,16 +5276,16 @@
         <v>1082</v>
       </c>
       <c r="H17" t="n">
-        <v>64379</v>
+        <v>64130.14</v>
       </c>
       <c r="I17" t="n">
-        <v>59.5</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02783503239574792</v>
+        <v>0.02806242756210372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5311,16 +5311,16 @@
         <v>263</v>
       </c>
       <c r="H18" t="n">
-        <v>61810.26</v>
+        <v>62565.07</v>
       </c>
       <c r="I18" t="n">
-        <v>235.02</v>
+        <v>237.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02779407485574738</v>
+        <v>0.02792732079357846</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5346,16 +5346,16 @@
         <v>1433</v>
       </c>
       <c r="H19" t="n">
-        <v>61719.31</v>
+        <v>62263.85</v>
       </c>
       <c r="I19" t="n">
-        <v>43.07</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02580284490307282</v>
+        <v>0.02587439044519479</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
         <v>1557</v>
       </c>
       <c r="H20" t="n">
-        <v>57297.6</v>
+        <v>57686.85</v>
       </c>
       <c r="I20" t="n">
-        <v>36.8</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02547452710084316</v>
+        <v>0.02544349036732966</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5416,16 +5416,16 @@
         <v>213</v>
       </c>
       <c r="H21" t="n">
-        <v>56568.54</v>
+        <v>56726.16</v>
       </c>
       <c r="I21" t="n">
-        <v>265.58</v>
+        <v>266.32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5434,33 +5434,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02299071236555417</v>
+        <v>0.02258716768274085</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>51053</v>
+        <v>50358</v>
       </c>
       <c r="I22" t="n">
-        <v>268.7</v>
+        <v>381.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02265255034315506</v>
+        <v>0.02256539594598959</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5486,16 +5486,16 @@
         <v>369</v>
       </c>
       <c r="H23" t="n">
-        <v>50302.08</v>
+        <v>50309.46</v>
       </c>
       <c r="I23" t="n">
-        <v>136.32</v>
+        <v>136.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5504,33 +5504,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02243104187943365</v>
+        <v>0.02244893016179442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="H24" t="n">
-        <v>49810.2</v>
+        <v>50049.8</v>
       </c>
       <c r="I24" t="n">
-        <v>377.35</v>
+        <v>263.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02208623748523677</v>
+        <v>0.0222563440347056</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5556,16 +5556,16 @@
         <v>443</v>
       </c>
       <c r="H25" t="n">
-        <v>49044.53</v>
+        <v>49620.43</v>
       </c>
       <c r="I25" t="n">
-        <v>110.71</v>
+        <v>112.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02185677618856968</v>
+        <v>0.02206198620674807</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5591,16 +5591,16 @@
         <v>959</v>
       </c>
       <c r="H26" t="n">
-        <v>48534.99</v>
+        <v>49187.11</v>
       </c>
       <c r="I26" t="n">
-        <v>50.61</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02162205053079643</v>
+        <v>0.02199416370336614</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5626,16 +5626,16 @@
         <v>298</v>
       </c>
       <c r="H27" t="n">
-        <v>48013.76</v>
+        <v>49035.9</v>
       </c>
       <c r="I27" t="n">
-        <v>161.12</v>
+        <v>164.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02036375564384881</v>
+        <v>0.02033092681036432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5661,16 +5661,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>45219.6</v>
+        <v>45327.72</v>
       </c>
       <c r="I28" t="n">
-        <v>284.4</v>
+        <v>285.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5679,33 +5679,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01959224528536271</v>
+        <v>0.01938825635928479</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>601</v>
+        <v>484</v>
       </c>
       <c r="H29" t="n">
-        <v>43506.39</v>
+        <v>43226.04</v>
       </c>
       <c r="I29" t="n">
-        <v>72.39</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5714,33 +5714,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01912815740358648</v>
+        <v>0.01911773782056572</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>484</v>
+        <v>601</v>
       </c>
       <c r="H30" t="n">
-        <v>42475.84</v>
+        <v>42622.92</v>
       </c>
       <c r="I30" t="n">
-        <v>87.76000000000001</v>
+        <v>70.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01844829376269805</v>
+        <v>0.01848339714446673</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5766,16 +5766,16 @@
         <v>282</v>
       </c>
       <c r="H31" t="n">
-        <v>40966.14</v>
+        <v>41208.66</v>
       </c>
       <c r="I31" t="n">
-        <v>145.27</v>
+        <v>146.13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01804848152340973</v>
+        <v>0.01802826288990875</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5801,16 +5801,16 @@
         <v>246</v>
       </c>
       <c r="H32" t="n">
-        <v>40078.32</v>
+        <v>40193.94</v>
       </c>
       <c r="I32" t="n">
-        <v>162.92</v>
+        <v>163.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01712341754217067</v>
+        <v>0.01678138915701127</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5836,16 +5836,16 @@
         <v>361</v>
       </c>
       <c r="H33" t="n">
-        <v>38024.13</v>
+        <v>37414.04</v>
       </c>
       <c r="I33" t="n">
-        <v>105.33</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5854,33 +5854,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0170096596072665</v>
+        <v>0.01667965315927905</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>736</v>
+        <v>148</v>
       </c>
       <c r="H34" t="n">
-        <v>37771.52</v>
+        <v>37187.22</v>
       </c>
       <c r="I34" t="n">
-        <v>51.32</v>
+        <v>251.27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5889,33 +5889,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01686616636322286</v>
+        <v>0.01663471923699347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>148</v>
+        <v>736</v>
       </c>
       <c r="H35" t="n">
-        <v>37452.88</v>
+        <v>37087.04</v>
       </c>
       <c r="I35" t="n">
-        <v>253.06</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0168343730446518</v>
+        <v>0.01645679561658778</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>372</v>
       </c>
       <c r="H36" t="n">
-        <v>37382.28</v>
+        <v>36690.36</v>
       </c>
       <c r="I36" t="n">
-        <v>100.49</v>
+        <v>98.63</v>
       </c>
     </row>
   </sheetData>
@@ -6011,7 +6011,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1056919338973152</v>
+        <v>0.1057738677172289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6037,16 +6037,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>224632.19</v>
+        <v>224013.74</v>
       </c>
       <c r="I2" t="n">
-        <v>53.61</v>
+        <v>53.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09907674104849262</v>
+        <v>0.09949206915577477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6072,16 +6072,16 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>210572.6</v>
+        <v>210709.8</v>
       </c>
       <c r="I3" t="n">
-        <v>214.87</v>
+        <v>215.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09454402552631756</v>
+        <v>0.09449276618169615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6107,16 +6107,16 @@
         <v>4300</v>
       </c>
       <c r="H4" t="n">
-        <v>200939</v>
+        <v>200122</v>
       </c>
       <c r="I4" t="n">
-        <v>46.73</v>
+        <v>46.54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08601059194777598</v>
+        <v>0.08532263045513913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6142,16 +6142,16 @@
         <v>934</v>
       </c>
       <c r="H5" t="n">
-        <v>182802.48</v>
+        <v>180700.98</v>
       </c>
       <c r="I5" t="n">
-        <v>195.72</v>
+        <v>193.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05527740587405885</v>
+        <v>0.05495063959140097</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1475</v>
       </c>
       <c r="H6" t="n">
-        <v>117483.75</v>
+        <v>116377.5</v>
       </c>
       <c r="I6" t="n">
-        <v>79.65000000000001</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0380178409049317</v>
+        <v>0.03785847988363926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6212,16 +6212,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>80801.16</v>
+        <v>80178.78</v>
       </c>
       <c r="I7" t="n">
-        <v>29.86</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02609946123329131</v>
+        <v>0.02647985515761691</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6247,16 +6247,16 @@
         <v>147</v>
       </c>
       <c r="H8" t="n">
-        <v>55470.45</v>
+        <v>56080.5</v>
       </c>
       <c r="I8" t="n">
-        <v>377.35</v>
+        <v>381.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02448593759309503</v>
+        <v>0.02505744915785651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6282,16 +6282,16 @@
         <v>105</v>
       </c>
       <c r="H9" t="n">
-        <v>52041.15</v>
+        <v>53068.05</v>
       </c>
       <c r="I9" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02340222824730478</v>
+        <v>0.02321338544366233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6317,16 +6317,16 @@
         <v>1860</v>
       </c>
       <c r="H10" t="n">
-        <v>49737.89</v>
+        <v>49162.59</v>
       </c>
       <c r="I10" t="n">
-        <v>26.74</v>
+        <v>26.43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02108030783300208</v>
+        <v>0.02121592125437242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6352,16 +6352,16 @@
         <v>275</v>
       </c>
       <c r="H11" t="n">
-        <v>44803</v>
+        <v>44932.25</v>
       </c>
       <c r="I11" t="n">
-        <v>162.92</v>
+        <v>163.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02048385034949116</v>
+        <v>0.02092337529169368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6387,16 +6387,16 @@
         <v>158</v>
       </c>
       <c r="H12" t="n">
-        <v>43535.32</v>
+        <v>44312.68</v>
       </c>
       <c r="I12" t="n">
-        <v>275.54</v>
+        <v>280.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6405,33 +6405,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02035760281701005</v>
+        <v>0.02023667113338681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprott Physical Gold and Silver Trust</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>980</v>
+        <v>202</v>
       </c>
       <c r="H13" t="n">
-        <v>43267</v>
+        <v>42858.34</v>
       </c>
       <c r="I13" t="n">
-        <v>44.15</v>
+        <v>212.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6440,33 +6440,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02034495547923019</v>
+        <v>0.02003168072998228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CEF</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Sprott Physical Gold and Silver Trust</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>202</v>
+        <v>980</v>
       </c>
       <c r="H14" t="n">
-        <v>43240.12</v>
+        <v>42424.2</v>
       </c>
       <c r="I14" t="n">
-        <v>214.06</v>
+        <v>43.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01974341647607556</v>
+        <v>0.01986847788520239</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6492,16 +6492,16 @@
         <v>158</v>
       </c>
       <c r="H15" t="n">
-        <v>41961.64</v>
+        <v>42078.56</v>
       </c>
       <c r="I15" t="n">
-        <v>265.58</v>
+        <v>266.32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6510,33 +6510,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01757951720735941</v>
+        <v>0.01757079015466609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ASML Holding</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>37362.6</v>
+        <v>37212.39</v>
       </c>
       <c r="I16" t="n">
-        <v>1698.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6545,33 +6545,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01750884173831503</v>
+        <v>0.01746007909398</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="H17" t="n">
-        <v>37212.39</v>
+        <v>36977.92</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>165.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6580,33 +6580,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01749442998399222</v>
+        <v>0.01636696849969783</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>224</v>
+        <v>99</v>
       </c>
       <c r="H18" t="n">
-        <v>37181.76</v>
+        <v>34662.87</v>
       </c>
       <c r="I18" t="n">
-        <v>165.99</v>
+        <v>350.13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6615,33 +6615,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01659340597450356</v>
+        <v>0.01636244977725673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>ASML Holding</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="H19" t="n">
-        <v>35266.77</v>
+        <v>34653.3</v>
       </c>
       <c r="I19" t="n">
-        <v>356.23</v>
+        <v>1575.15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0163711506565321</v>
+        <v>0.01627238696446505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6667,16 +6667,16 @@
         <v>488</v>
       </c>
       <c r="H20" t="n">
-        <v>34794.4</v>
+        <v>34462.56</v>
       </c>
       <c r="I20" t="n">
-        <v>71.3</v>
+        <v>70.62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01614407260000992</v>
+        <v>0.01590210669922841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>306</v>
       </c>
       <c r="H21" t="n">
-        <v>34311.78</v>
+        <v>33678.36</v>
       </c>
       <c r="I21" t="n">
-        <v>112.13</v>
+        <v>110.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01474521493409502</v>
+        <v>0.01481701837185057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6737,16 +6737,16 @@
         <v>126</v>
       </c>
       <c r="H22" t="n">
-        <v>31338.72</v>
+        <v>31380.3</v>
       </c>
       <c r="I22" t="n">
-        <v>248.72</v>
+        <v>249.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01406621098703875</v>
+        <v>0.01415207207457673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>84</v>
       </c>
       <c r="H23" t="n">
-        <v>29895.6</v>
+        <v>29972.04</v>
       </c>
       <c r="I23" t="n">
-        <v>355.9</v>
+        <v>356.81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01373858000801158</v>
+        <v>0.01386880908819811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6807,16 +6807,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>29199.27</v>
+        <v>29372.13</v>
       </c>
       <c r="I24" t="n">
-        <v>145.27</v>
+        <v>146.13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01302257036466119</v>
+        <v>0.01322210294221998</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6842,16 +6842,16 @@
         <v>250</v>
       </c>
       <c r="H25" t="n">
-        <v>27677.5</v>
+        <v>28002.5</v>
       </c>
       <c r="I25" t="n">
-        <v>110.71</v>
+        <v>112.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01302191164915182</v>
+        <v>0.01281119667083573</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6877,16 +6877,16 @@
         <v>103</v>
       </c>
       <c r="H26" t="n">
-        <v>27676.1</v>
+        <v>27132.26</v>
       </c>
       <c r="I26" t="n">
-        <v>268.7</v>
+        <v>263.42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01208097418490625</v>
+        <v>0.01242671335742475</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>414</v>
       </c>
       <c r="H27" t="n">
-        <v>25676.28</v>
+        <v>26317.98</v>
       </c>
       <c r="I27" t="n">
-        <v>62.02</v>
+        <v>63.57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01189346611005394</v>
+        <v>0.01189595942355342</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6947,16 +6947,16 @@
         <v>524</v>
       </c>
       <c r="H28" t="n">
-        <v>25277.76</v>
+        <v>25193.92</v>
       </c>
       <c r="I28" t="n">
-        <v>48.24</v>
+        <v>48.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6965,33 +6965,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01119793310882332</v>
+        <v>0.0111915108985447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Total SA</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>259</v>
+        <v>200</v>
       </c>
       <c r="H29" t="n">
-        <v>23799.51</v>
+        <v>23702</v>
       </c>
       <c r="I29" t="n">
-        <v>91.89</v>
+        <v>118.51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7000,33 +7000,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01089703656925492</v>
+        <v>0.01114583261129783</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Total SA</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="H30" t="n">
-        <v>23160</v>
+        <v>23605.26</v>
       </c>
       <c r="I30" t="n">
-        <v>115.8</v>
+        <v>91.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0106994219164446</v>
+        <v>0.0110725225960203</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7052,16 +7052,16 @@
         <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>22740</v>
+        <v>23450</v>
       </c>
       <c r="I31" t="n">
-        <v>90.95999999999999</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.009625833263944712</v>
+        <v>0.009745118367957953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7087,16 +7087,16 @@
         <v>475</v>
       </c>
       <c r="H32" t="n">
-        <v>20458.25</v>
+        <v>20638.75</v>
       </c>
       <c r="I32" t="n">
-        <v>43.07</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.008977337255193733</v>
+        <v>0.009130147157744361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7122,16 +7122,16 @@
         <v>377</v>
       </c>
       <c r="H33" t="n">
-        <v>19079.97</v>
+        <v>19336.33</v>
       </c>
       <c r="I33" t="n">
-        <v>50.61</v>
+        <v>51.29</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7140,33 +7140,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.008771930938929745</v>
+        <v>0.008742335004917522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H34" t="n">
-        <v>18643.41</v>
+        <v>18515</v>
       </c>
       <c r="I34" t="n">
-        <v>105.33</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7175,33 +7175,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.008751858936337155</v>
+        <v>0.008661725151715278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H35" t="n">
-        <v>18600.75</v>
+        <v>18344.28</v>
       </c>
       <c r="I35" t="n">
-        <v>106.29</v>
+        <v>103.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7210,33 +7210,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.008555425266332913</v>
+        <v>0.008507663630494404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>362</v>
+        <v>650</v>
       </c>
       <c r="H36" t="n">
-        <v>18183.26</v>
+        <v>18018</v>
       </c>
       <c r="I36" t="n">
-        <v>50.23</v>
+        <v>27.72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7245,33 +7245,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.008477668605562831</v>
+        <v>0.008500231583344665</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>650</v>
+        <v>362</v>
       </c>
       <c r="H37" t="n">
-        <v>18018</v>
+        <v>18002.26</v>
       </c>
       <c r="I37" t="n">
-        <v>27.72</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008466489262346706</v>
+        <v>0.008497691277520932</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -7297,16 +7297,16 @@
         <v>132</v>
       </c>
       <c r="H38" t="n">
-        <v>17994.24</v>
+        <v>17996.88</v>
       </c>
       <c r="I38" t="n">
-        <v>136.32</v>
+        <v>136.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008330586842542578</v>
+        <v>0.008208563867660756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7332,16 +7332,16 @@
         <v>345</v>
       </c>
       <c r="H39" t="n">
-        <v>17705.4</v>
+        <v>17384.55</v>
       </c>
       <c r="I39" t="n">
-        <v>51.32</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.008004169782096957</v>
+        <v>0.007869376379095674</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7367,16 +7367,16 @@
         <v>235</v>
       </c>
       <c r="H40" t="n">
-        <v>17011.65</v>
+        <v>16666.2</v>
       </c>
       <c r="I40" t="n">
-        <v>72.39</v>
+        <v>70.92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.007614751288291091</v>
+        <v>0.007612153888289361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7402,16 +7402,16 @@
         <v>272</v>
       </c>
       <c r="H41" t="n">
-        <v>16184</v>
+        <v>16121.44</v>
       </c>
       <c r="I41" t="n">
-        <v>59.5</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7420,33 +7420,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.007225920933332876</v>
+        <v>0.007337583658456278</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="H42" t="n">
-        <v>15357.6</v>
+        <v>15539.94</v>
       </c>
       <c r="I42" t="n">
-        <v>284.4</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7455,33 +7455,33 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.007184817085548328</v>
+        <v>0.007268825417926108</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="H43" t="n">
-        <v>15270.24</v>
+        <v>15394.32</v>
       </c>
       <c r="I43" t="n">
-        <v>87.76000000000001</v>
+        <v>285.08</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.006714593019186166</v>
+        <v>0.006675763165002721</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7507,16 +7507,16 @@
         <v>55</v>
       </c>
       <c r="H44" t="n">
-        <v>14270.85</v>
+        <v>14138.3</v>
       </c>
       <c r="I44" t="n">
-        <v>259.47</v>
+        <v>257.06</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.004761572110572531</v>
+        <v>0.004810881219624812</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7542,16 +7542,16 @@
         <v>275</v>
       </c>
       <c r="H45" t="n">
-        <v>10120</v>
+        <v>10188.75</v>
       </c>
       <c r="I45" t="n">
-        <v>36.8</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.004212702117502641</v>
+        <v>0.004256773470504055</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7577,16 +7577,16 @@
         <v>29</v>
       </c>
       <c r="H46" t="n">
-        <v>8953.459999999999</v>
+        <v>9015.23</v>
       </c>
       <c r="I46" t="n">
-        <v>308.74</v>
+        <v>310.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/11/2026</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.002653306071733262</v>
+        <v>0.002719378497276329</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7612,261 +7612,13 @@
         <v>35</v>
       </c>
       <c r="H47" t="n">
-        <v>5639.2</v>
+        <v>5759.25</v>
       </c>
       <c r="I47" t="n">
-        <v>161.12</v>
+        <v>164.55</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92702C67-0FD4-4B7D-AF21-EF95385FEFD8}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CE20EE7-E3DA-405C-8133-B8A51713B4EF}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F42E151D-750B-459C-96D6-41FCA0CFF83E}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -7621,4 +7621,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C4DFC9E-8176-4CDF-A91E-D36E49066EE1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76271C3B-6B9A-49C2-A08A-E77642183CB6}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B79042-351A-452C-824E-FBDF010A0D0B}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09382997433615292</v>
+        <v>0.09409683445333643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04339789037794425</v>
+        <v>0.04285395263054025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>102623.5</v>
+        <v>101049.85</v>
       </c>
       <c r="I3" t="n">
-        <v>381.5</v>
+        <v>375.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04127356378138135</v>
+        <v>0.0405984318882125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>97600.08</v>
+        <v>95731.32000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>280.46</v>
+        <v>275.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,33 +596,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03876235281652007</v>
+        <v>0.03961964276451008</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>561</v>
+        <v>429</v>
       </c>
       <c r="H5" t="n">
-        <v>91661.78999999999</v>
+        <v>93423.33</v>
       </c>
       <c r="I5" t="n">
-        <v>163.39</v>
+        <v>217.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,33 +631,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03849134303778898</v>
+        <v>0.03857996319397679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>429</v>
+        <v>561</v>
       </c>
       <c r="H6" t="n">
-        <v>91020.92999999999</v>
+        <v>90971.75999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>212.17</v>
+        <v>162.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03682759266740557</v>
+        <v>0.03705436869744858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -683,16 +683,16 @@
         <v>327</v>
       </c>
       <c r="H7" t="n">
-        <v>87086.64</v>
+        <v>87374.39999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>266.32</v>
+        <v>267.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03302002495255532</v>
+        <v>0.03396445205705554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         <v>473</v>
       </c>
       <c r="H8" t="n">
-        <v>78082.84</v>
+        <v>80088.36</v>
       </c>
       <c r="I8" t="n">
-        <v>165.08</v>
+        <v>169.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03197311509920541</v>
+        <v>0.03239646579938223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -753,16 +753,16 @@
         <v>48</v>
       </c>
       <c r="H9" t="n">
-        <v>75607.2</v>
+        <v>76391.03999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>1575.15</v>
+        <v>1591.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03123013235626032</v>
+        <v>0.0313217990310251</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -788,16 +788,16 @@
         <v>671</v>
       </c>
       <c r="H10" t="n">
-        <v>73850.25999999999</v>
+        <v>73856.97</v>
       </c>
       <c r="I10" t="n">
-        <v>110.06</v>
+        <v>110.07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03120799012236468</v>
+        <v>0.03100425522357591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         <v>1045</v>
       </c>
       <c r="H11" t="n">
-        <v>73797.89999999999</v>
+        <v>73108.2</v>
       </c>
       <c r="I11" t="n">
-        <v>70.62</v>
+        <v>69.95999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,33 +841,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02949474957564807</v>
+        <v>0.02965514887548856</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="H12" t="n">
-        <v>69746.58</v>
+        <v>69927</v>
       </c>
       <c r="I12" t="n">
-        <v>505.41</v>
+        <v>358.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,33 +876,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02942343855766064</v>
+        <v>0.02909347076293329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="H13" t="n">
-        <v>69577.95</v>
+        <v>68602.56</v>
       </c>
       <c r="I13" t="n">
-        <v>356.81</v>
+        <v>497.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,33 +911,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02769900002863774</v>
+        <v>0.02795397801809916</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>263</v>
+        <v>187</v>
       </c>
       <c r="H14" t="n">
-        <v>65500.15</v>
+        <v>65915.63</v>
       </c>
       <c r="I14" t="n">
-        <v>249.05</v>
+        <v>352.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0276880726924295</v>
+        <v>0.02770081913639076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>187</v>
+        <v>263</v>
       </c>
       <c r="H15" t="n">
-        <v>65474.31</v>
+        <v>65318.68</v>
       </c>
       <c r="I15" t="n">
-        <v>350.13</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02700490273715056</v>
+        <v>0.02718178299645595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -998,16 +998,16 @@
         <v>437</v>
       </c>
       <c r="H16" t="n">
-        <v>63858.81</v>
+        <v>64094.79</v>
       </c>
       <c r="I16" t="n">
-        <v>146.13</v>
+        <v>146.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02567841123568331</v>
+        <v>0.02565298240034535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>213</v>
       </c>
       <c r="H17" t="n">
-        <v>60722.04</v>
+        <v>60489.87</v>
       </c>
       <c r="I17" t="n">
-        <v>285.08</v>
+        <v>283.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,33 +1051,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02495275830070314</v>
+        <v>0.02546902607549628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>224</v>
+        <v>1170</v>
       </c>
       <c r="H18" t="n">
-        <v>59006.08</v>
+        <v>60056.1</v>
       </c>
       <c r="I18" t="n">
-        <v>263.42</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,33 +1086,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02460515567622763</v>
+        <v>0.0250246759405161</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1170</v>
+        <v>224</v>
       </c>
       <c r="H19" t="n">
-        <v>58184.1</v>
+        <v>59008.32</v>
       </c>
       <c r="I19" t="n">
-        <v>49.73</v>
+        <v>263.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,33 +1121,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02456373413669215</v>
+        <v>0.02377904688053805</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>353</v>
+        <v>898</v>
       </c>
       <c r="H20" t="n">
-        <v>58086.15</v>
+        <v>56071.12</v>
       </c>
       <c r="I20" t="n">
-        <v>164.55</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,33 +1156,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0241407269719964</v>
+        <v>0.02306471008191431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>898</v>
+        <v>353</v>
       </c>
       <c r="H21" t="n">
-        <v>57085.86</v>
+        <v>54386.71</v>
       </c>
       <c r="I21" t="n">
-        <v>63.57</v>
+        <v>154.07</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02201494565265655</v>
+        <v>0.02206578953662768</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1208,16 +1208,16 @@
         <v>555</v>
       </c>
       <c r="H22" t="n">
-        <v>52059</v>
+        <v>52031.25</v>
       </c>
       <c r="I22" t="n">
-        <v>93.8</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02165561221136926</v>
+        <v>0.02195699843532162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Total SA</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>864</v>
+        <v>556</v>
       </c>
       <c r="H23" t="n">
-        <v>51209.28</v>
+        <v>51774.72</v>
       </c>
       <c r="I23" t="n">
-        <v>59.27</v>
+        <v>93.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0216468542727906</v>
+        <v>0.0216095776813671</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1278,16 +1278,16 @@
         <v>457</v>
       </c>
       <c r="H24" t="n">
-        <v>51188.57</v>
+        <v>50955.5</v>
       </c>
       <c r="I24" t="n">
-        <v>112.01</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,33 +1296,33 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02142918291959918</v>
+        <v>0.02151201216947191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Total SA</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>556</v>
+        <v>864</v>
       </c>
       <c r="H25" t="n">
-        <v>50673.84</v>
+        <v>50725.44</v>
       </c>
       <c r="I25" t="n">
-        <v>91.14</v>
+        <v>58.71</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02134943535527451</v>
+        <v>0.02137221604958523</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         <v>426</v>
       </c>
       <c r="H26" t="n">
-        <v>50485.26</v>
+        <v>50395.8</v>
       </c>
       <c r="I26" t="n">
-        <v>118.51</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,33 +1366,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01997289969874214</v>
+        <v>0.02007374571871202</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1087</v>
+        <v>920</v>
       </c>
       <c r="H27" t="n">
-        <v>47230.15</v>
+        <v>47334</v>
       </c>
       <c r="I27" t="n">
-        <v>43.45</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,33 +1401,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01995456765444542</v>
+        <v>0.01960560004833916</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>920</v>
+        <v>1087</v>
       </c>
       <c r="H28" t="n">
-        <v>47186.8</v>
+        <v>46230.11</v>
       </c>
       <c r="I28" t="n">
-        <v>51.29</v>
+        <v>42.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01908416134546836</v>
+        <v>0.01902052504240279</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>331</v>
       </c>
       <c r="H29" t="n">
-        <v>45128.54</v>
+        <v>44850.5</v>
       </c>
       <c r="I29" t="n">
-        <v>136.34</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01907168625188698</v>
+        <v>0.01887531756925268</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1488,16 +1488,16 @@
         <v>938</v>
       </c>
       <c r="H30" t="n">
-        <v>45099.04</v>
+        <v>44508.1</v>
       </c>
       <c r="I30" t="n">
-        <v>48.08</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0190597439928111</v>
+        <v>0.01883031343067006</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1523,16 +1523,16 @@
         <v>426</v>
       </c>
       <c r="H31" t="n">
-        <v>45070.8</v>
+        <v>44401.98</v>
       </c>
       <c r="I31" t="n">
-        <v>105.8</v>
+        <v>104.23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01763042811831626</v>
+        <v>0.01757213986994499</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1558,16 +1558,16 @@
         <v>1504</v>
       </c>
       <c r="H32" t="n">
-        <v>41690.88</v>
+        <v>41435.2</v>
       </c>
       <c r="I32" t="n">
-        <v>27.72</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01679494361367651</v>
+        <v>0.01672396537724579</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>39715.2</v>
+        <v>39435.2</v>
       </c>
       <c r="I33" t="n">
-        <v>70.92</v>
+        <v>70.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01626009617781233</v>
+        <v>0.01619305903528565</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>38450.44</v>
+        <v>38183.32</v>
       </c>
       <c r="I34" t="n">
-        <v>103.64</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01408739582007062</v>
+        <v>0.01378736475815305</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         <v>373</v>
       </c>
       <c r="H35" t="n">
-        <v>33312.63</v>
+        <v>32510.68</v>
       </c>
       <c r="I35" t="n">
-        <v>89.31</v>
+        <v>87.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01315351031456807</v>
+        <v>0.01359476553522338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
         <v>121</v>
       </c>
       <c r="H36" t="n">
-        <v>31104.26</v>
+        <v>32056.53</v>
       </c>
       <c r="I36" t="n">
-        <v>257.06</v>
+        <v>264.93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01143720385502213</v>
+        <v>0.01127086496529422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         <v>87</v>
       </c>
       <c r="H37" t="n">
-        <v>27045.69</v>
+        <v>26576.76</v>
       </c>
       <c r="I37" t="n">
-        <v>310.87</v>
+        <v>305.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01112337701781256</v>
+        <v>0.01103768483376136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         <v>522</v>
       </c>
       <c r="H38" t="n">
-        <v>26303.58</v>
+        <v>26026.92</v>
       </c>
       <c r="I38" t="n">
-        <v>50.39</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.009009026267269484</v>
+        <v>0.008832253036099967</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         <v>575</v>
       </c>
       <c r="H39" t="n">
-        <v>21303.75</v>
+        <v>20826.5</v>
       </c>
       <c r="I39" t="n">
-        <v>37.05</v>
+        <v>36.22</v>
       </c>
     </row>
   </sheetData>
@@ -1873,7 +1873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06102736460189603</v>
+        <v>0.06079918795079362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>158651.69</v>
+        <v>157457.36</v>
       </c>
       <c r="I2" t="n">
-        <v>163.39</v>
+        <v>162.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05746432381730997</v>
+        <v>0.05953961276762654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>149388.92</v>
+        <v>154195.32</v>
       </c>
       <c r="I3" t="n">
-        <v>49.73</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05087810075909463</v>
+        <v>0.05304533511509683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1969,16 +1969,16 @@
         <v>556</v>
       </c>
       <c r="H4" t="n">
-        <v>132266.84</v>
+        <v>137376.48</v>
       </c>
       <c r="I4" t="n">
-        <v>237.89</v>
+        <v>247.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04991706367560859</v>
+        <v>0.05001884706033354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2004,16 +2004,16 @@
         <v>1095</v>
       </c>
       <c r="H5" t="n">
-        <v>129768.45</v>
+        <v>129538.5</v>
       </c>
       <c r="I5" t="n">
-        <v>118.51</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04914644225063354</v>
+        <v>0.04933407439619326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04838063295423506</v>
+        <v>0.04811145968455096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2074,16 +2074,16 @@
         <v>1781</v>
       </c>
       <c r="H7" t="n">
-        <v>125774.22</v>
+        <v>124598.76</v>
       </c>
       <c r="I7" t="n">
-        <v>70.62</v>
+        <v>69.95999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2092,33 +2092,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04449724519294512</v>
+        <v>0.04315478707223719</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>703</v>
+        <v>450</v>
       </c>
       <c r="H8" t="n">
-        <v>115678.65</v>
+        <v>111762</v>
       </c>
       <c r="I8" t="n">
-        <v>164.55</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2127,33 +2127,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04311009431633532</v>
+        <v>0.04182232963875349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>450</v>
+        <v>703</v>
       </c>
       <c r="H9" t="n">
-        <v>112072.5</v>
+        <v>108311.21</v>
       </c>
       <c r="I9" t="n">
-        <v>249.05</v>
+        <v>154.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03958038454223364</v>
+        <v>0.03931360095155067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>102896.38</v>
+        <v>101814.12</v>
       </c>
       <c r="I10" t="n">
-        <v>50.39</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2197,33 +2197,33 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03717125834000352</v>
+        <v>0.03684636205399829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1082</v>
+        <v>796</v>
       </c>
       <c r="H11" t="n">
-        <v>96633.42</v>
+        <v>95424.48</v>
       </c>
       <c r="I11" t="n">
-        <v>89.31</v>
+        <v>119.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03701909737269474</v>
+        <v>0.03682553800229193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2249,16 +2249,16 @@
         <v>295</v>
       </c>
       <c r="H12" t="n">
-        <v>96237.85000000001</v>
+        <v>95370.55</v>
       </c>
       <c r="I12" t="n">
-        <v>326.23</v>
+        <v>323.29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2267,33 +2267,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03652250955267146</v>
+        <v>0.03674789861648445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Principal Financial</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="H13" t="n">
-        <v>94946.88</v>
+        <v>95169.48</v>
       </c>
       <c r="I13" t="n">
-        <v>119.28</v>
+        <v>118.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,33 +2302,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03615351045587453</v>
+        <v>0.03641491457736906</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Principal Financial</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>804</v>
+        <v>1082</v>
       </c>
       <c r="H14" t="n">
-        <v>93987.60000000001</v>
+        <v>94307.12</v>
       </c>
       <c r="I14" t="n">
-        <v>116.9</v>
+        <v>87.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03372640512577319</v>
+        <v>0.0335563395047127</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>710</v>
       </c>
       <c r="H15" t="n">
-        <v>87677.89999999999</v>
+        <v>86904</v>
       </c>
       <c r="I15" t="n">
-        <v>123.49</v>
+        <v>122.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03325324710204078</v>
+        <v>0.03294281575621968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         <v>1798</v>
       </c>
       <c r="H16" t="n">
-        <v>86447.84</v>
+        <v>85315.10000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>48.08</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03160528347253169</v>
+        <v>0.03203087442714552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
         <v>327</v>
       </c>
       <c r="H17" t="n">
-        <v>82163.66</v>
+        <v>82953.36</v>
       </c>
       <c r="I17" t="n">
-        <v>251.27</v>
+        <v>253.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2442,33 +2442,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03124333139376215</v>
+        <v>0.0311251806997144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Snap-On</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>215</v>
+        <v>910</v>
       </c>
       <c r="H18" t="n">
-        <v>81222.7</v>
+        <v>80607.8</v>
       </c>
       <c r="I18" t="n">
-        <v>377.78</v>
+        <v>88.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,33 +2477,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03111531569509855</v>
+        <v>0.03111687888047304</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Snap-On</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>910</v>
+        <v>215</v>
       </c>
       <c r="H19" t="n">
-        <v>80889.89999999999</v>
+        <v>80586.3</v>
       </c>
       <c r="I19" t="n">
-        <v>88.89</v>
+        <v>374.82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03076715761559006</v>
+        <v>0.03042631424942017</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,16 +2529,16 @@
         <v>756</v>
       </c>
       <c r="H20" t="n">
-        <v>79984.8</v>
+        <v>78797.88</v>
       </c>
       <c r="I20" t="n">
-        <v>105.8</v>
+        <v>104.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03038564929246939</v>
+        <v>0.02999177772377091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2564,16 +2564,16 @@
         <v>1179</v>
       </c>
       <c r="H21" t="n">
-        <v>78993</v>
+        <v>77672.52</v>
       </c>
       <c r="I21" t="n">
-        <v>67</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02882378852951337</v>
+        <v>0.02904723920491277</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2599,16 +2599,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>74932.66</v>
+        <v>75226.36</v>
       </c>
       <c r="I22" t="n">
-        <v>76.54000000000001</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02627325267841692</v>
+        <v>0.02617073220269506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>68302.08</v>
+        <v>67776.8</v>
       </c>
       <c r="I23" t="n">
-        <v>87.12</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02539696060266098</v>
+        <v>0.02528714834362489</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2669,16 +2669,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>66024</v>
+        <v>65488.5</v>
       </c>
       <c r="I24" t="n">
-        <v>20.96</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02439708798751306</v>
+        <v>0.02406569202536512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2704,16 +2704,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>63424.65</v>
+        <v>62325.18</v>
       </c>
       <c r="I25" t="n">
-        <v>38.65</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02315707438522962</v>
+        <v>0.02292533868912653</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2739,16 +2739,16 @@
         <v>953</v>
       </c>
       <c r="H26" t="n">
-        <v>60201.01</v>
+        <v>59371.9</v>
       </c>
       <c r="I26" t="n">
-        <v>63.17</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02223241099304655</v>
+        <v>0.02241685032993747</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2774,16 +2774,16 @@
         <v>586</v>
       </c>
       <c r="H27" t="n">
-        <v>57797.18</v>
+        <v>58055.02</v>
       </c>
       <c r="I27" t="n">
-        <v>98.63</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02102944039491366</v>
+        <v>0.02116827216128173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>54669.84</v>
+        <v>54821.46</v>
       </c>
       <c r="I28" t="n">
-        <v>75.72</v>
+        <v>75.93000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01572556689990399</v>
+        <v>0.01575459791432044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>40881.46</v>
+        <v>40801.16</v>
       </c>
       <c r="I29" t="n">
-        <v>280.01</v>
+        <v>279.46</v>
       </c>
     </row>
   </sheetData>
@@ -2914,7 +2914,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09240120267509336</v>
+        <v>0.09262381986830845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03840429995200272</v>
+        <v>0.03775972218417706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>411</v>
       </c>
       <c r="H3" t="n">
-        <v>115269.06</v>
+        <v>113061.99</v>
       </c>
       <c r="I3" t="n">
-        <v>280.46</v>
+        <v>275.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03520800464216386</v>
+        <v>0.03475164181932985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3010,16 +3010,16 @@
         <v>277</v>
       </c>
       <c r="H4" t="n">
-        <v>105675.5</v>
+        <v>104055.05</v>
       </c>
       <c r="I4" t="n">
-        <v>381.5</v>
+        <v>375.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03483955091037391</v>
+        <v>0.03466058391159697</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>104569.6</v>
+        <v>103782.4</v>
       </c>
       <c r="I5" t="n">
-        <v>163.39</v>
+        <v>162.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03343583847865304</v>
+        <v>0.03440102295318539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>100356.41</v>
+        <v>103005.21</v>
       </c>
       <c r="I6" t="n">
-        <v>212.17</v>
+        <v>217.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3098,33 +3098,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03072844818702606</v>
+        <v>0.03127127265851545</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>838</v>
+        <v>553</v>
       </c>
       <c r="H7" t="n">
-        <v>92230.28</v>
+        <v>93633.96000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>110.06</v>
+        <v>169.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3133,33 +3133,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03041492101480107</v>
+        <v>0.03080527926530185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>553</v>
+        <v>838</v>
       </c>
       <c r="H8" t="n">
-        <v>91289.24000000001</v>
+        <v>92238.66</v>
       </c>
       <c r="I8" t="n">
-        <v>165.08</v>
+        <v>110.07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03025695801333959</v>
+        <v>0.03043007326118822</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
         <v>341</v>
       </c>
       <c r="H9" t="n">
-        <v>90815.12</v>
+        <v>91115.2</v>
       </c>
       <c r="I9" t="n">
-        <v>266.32</v>
+        <v>267.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02712839635362541</v>
+        <v>0.02693960807781463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3220,16 +3220,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>81424.86</v>
+        <v>80663.88</v>
       </c>
       <c r="I10" t="n">
-        <v>70.62</v>
+        <v>69.95999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02556029072148878</v>
+        <v>0.02571655326158204</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>76718.25</v>
+        <v>77001.75</v>
       </c>
       <c r="I11" t="n">
-        <v>146.13</v>
+        <v>146.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02464393739486333</v>
+        <v>0.02463486947906788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>73967.85000000001</v>
+        <v>73762.92</v>
       </c>
       <c r="I12" t="n">
-        <v>249.05</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02379724011463026</v>
+        <v>0.02401536177128067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3325,16 +3325,16 @@
         <v>204</v>
       </c>
       <c r="H13" t="n">
-        <v>71426.52</v>
+        <v>71907.96000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>350.13</v>
+        <v>352.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02374269670163511</v>
+        <v>0.02340952026405985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
         <v>141</v>
       </c>
       <c r="H14" t="n">
-        <v>71262.81</v>
+        <v>70093.92</v>
       </c>
       <c r="I14" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3378,33 +3378,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0233547158216218</v>
+        <v>0.02331434780131773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>426</v>
+        <v>265</v>
       </c>
       <c r="H15" t="n">
-        <v>70098.3</v>
+        <v>69808.95</v>
       </c>
       <c r="I15" t="n">
-        <v>164.55</v>
+        <v>263.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3413,33 +3413,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02325742990998181</v>
+        <v>0.02219376945091591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="H16" t="n">
-        <v>69806.3</v>
+        <v>66453.66</v>
       </c>
       <c r="I16" t="n">
-        <v>263.42</v>
+        <v>283.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3448,33 +3448,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02222540629978386</v>
+        <v>0.02211487820219168</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="H17" t="n">
-        <v>66708.72</v>
+        <v>66217.44</v>
       </c>
       <c r="I17" t="n">
-        <v>285.08</v>
+        <v>247.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3483,33 +3483,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0220097014443966</v>
+        <v>0.0219199645175738</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1311</v>
+        <v>426</v>
       </c>
       <c r="H18" t="n">
-        <v>66061.28999999999</v>
+        <v>65633.82000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>50.39</v>
+        <v>154.07</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02175480569248122</v>
+        <v>0.02191661810189259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3535,16 +3535,16 @@
         <v>183</v>
       </c>
       <c r="H19" t="n">
-        <v>65296.23</v>
+        <v>65623.8</v>
       </c>
       <c r="I19" t="n">
-        <v>356.81</v>
+        <v>358.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3553,33 +3553,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02163727964682708</v>
+        <v>0.02183067333029538</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>548</v>
+        <v>1311</v>
       </c>
       <c r="H20" t="n">
-        <v>64943.48</v>
+        <v>65366.46</v>
       </c>
       <c r="I20" t="n">
-        <v>118.51</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3588,33 +3588,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02124115273756858</v>
+        <v>0.02165097548384479</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>268</v>
+        <v>548</v>
       </c>
       <c r="H21" t="n">
-        <v>63754.52</v>
+        <v>64828.4</v>
       </c>
       <c r="I21" t="n">
-        <v>237.89</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3623,33 +3623,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02050094021836036</v>
+        <v>0.02058858201767264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>656</v>
+        <v>1201</v>
       </c>
       <c r="H22" t="n">
-        <v>61532.8</v>
+        <v>61647.33</v>
       </c>
       <c r="I22" t="n">
-        <v>93.8</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3658,33 +3658,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01994451144770985</v>
+        <v>0.02053937768410842</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1010</v>
+        <v>656</v>
       </c>
       <c r="H23" t="n">
-        <v>59862.7</v>
+        <v>61500</v>
       </c>
       <c r="I23" t="n">
-        <v>59.27</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3693,33 +3693,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01989887702539023</v>
+        <v>0.01980366719467228</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1201</v>
+        <v>1010</v>
       </c>
       <c r="H24" t="n">
-        <v>59725.73</v>
+        <v>59297.1</v>
       </c>
       <c r="I24" t="n">
-        <v>49.73</v>
+        <v>58.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01807896080415255</v>
+        <v>0.01801086340042736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3745,16 +3745,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>54263.32</v>
+        <v>53929</v>
       </c>
       <c r="I25" t="n">
-        <v>136.34</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01691975252303182</v>
+        <v>0.01670883384206533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3780,16 +3780,16 @@
         <v>480</v>
       </c>
       <c r="H26" t="n">
-        <v>50784</v>
+        <v>50030.4</v>
       </c>
       <c r="I26" t="n">
-        <v>105.8</v>
+        <v>104.23</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01606976684571694</v>
+        <v>0.01600969346411553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3815,16 +3815,16 @@
         <v>1740</v>
       </c>
       <c r="H27" t="n">
-        <v>48232.8</v>
+        <v>47937</v>
       </c>
       <c r="I27" t="n">
-        <v>27.72</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3833,33 +3833,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01602011105026891</v>
+        <v>0.01597466631075766</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>678</v>
+        <v>399</v>
       </c>
       <c r="H28" t="n">
-        <v>48083.76</v>
+        <v>47832.12</v>
       </c>
       <c r="I28" t="n">
-        <v>70.92</v>
+        <v>119.88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3868,33 +3868,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0158565107966672</v>
+        <v>0.0159454903752376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>399</v>
+        <v>678</v>
       </c>
       <c r="H29" t="n">
-        <v>47592.72</v>
+        <v>47744.76</v>
       </c>
       <c r="I29" t="n">
-        <v>119.28</v>
+        <v>70.42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3903,33 +3903,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01576255659432995</v>
+        <v>0.01577394148513647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>984</v>
+        <v>918</v>
       </c>
       <c r="H30" t="n">
-        <v>47310.72</v>
+        <v>47231.1</v>
       </c>
       <c r="I30" t="n">
-        <v>48.08</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3938,33 +3938,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0156870933786229</v>
+        <v>0.01559349553777511</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>918</v>
+        <v>984</v>
       </c>
       <c r="H31" t="n">
-        <v>47084.22</v>
+        <v>46690.8</v>
       </c>
       <c r="I31" t="n">
-        <v>51.29</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01463970392512071</v>
+        <v>0.01432169727157512</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,16 +3990,16 @@
         <v>492</v>
       </c>
       <c r="H32" t="n">
-        <v>43940.52</v>
+        <v>42882.72</v>
       </c>
       <c r="I32" t="n">
-        <v>89.31</v>
+        <v>87.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0134758978851622</v>
+        <v>0.01367823029622598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4025,16 +4025,16 @@
         <v>346</v>
       </c>
       <c r="H33" t="n">
-        <v>40447.4</v>
+        <v>40956.02</v>
       </c>
       <c r="I33" t="n">
-        <v>116.9</v>
+        <v>118.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0131515326625754</v>
+        <v>0.01306441015920235</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,16 +4060,16 @@
         <v>121</v>
       </c>
       <c r="H34" t="n">
-        <v>39473.83</v>
+        <v>39118.09</v>
       </c>
       <c r="I34" t="n">
-        <v>326.23</v>
+        <v>323.29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4078,33 +4078,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01298321804031031</v>
+        <v>0.01296253150615297</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>376</v>
+        <v>153</v>
       </c>
       <c r="H35" t="n">
-        <v>38968.64</v>
+        <v>38813.04</v>
       </c>
       <c r="I35" t="n">
-        <v>103.64</v>
+        <v>253.68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4113,33 +4113,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01280827331653277</v>
+        <v>0.01292408446291728</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>153</v>
+        <v>376</v>
       </c>
       <c r="H36" t="n">
-        <v>38443.55</v>
+        <v>38697.92</v>
       </c>
       <c r="I36" t="n">
-        <v>251.27</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01275441623565398</v>
+        <v>0.01267229507066358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         <v>310</v>
       </c>
       <c r="H37" t="n">
-        <v>38281.9</v>
+        <v>37944</v>
       </c>
       <c r="I37" t="n">
-        <v>123.49</v>
+        <v>122.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01207593362640692</v>
+        <v>0.01247562802453608</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4200,16 +4200,16 @@
         <v>141</v>
       </c>
       <c r="H38" t="n">
-        <v>36245.46</v>
+        <v>37355.13</v>
       </c>
       <c r="I38" t="n">
-        <v>257.06</v>
+        <v>264.93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4218,33 +4218,33 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01201445026293417</v>
+        <v>0.0119074153251798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GGG</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Graco Inc.</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>116</v>
+        <v>464</v>
       </c>
       <c r="H39" t="n">
-        <v>36060.92</v>
+        <v>35653.76</v>
       </c>
       <c r="I39" t="n">
-        <v>310.87</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4253,33 +4253,33 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.01183241899346969</v>
+        <v>0.01183458235793833</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GGG</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Graco Inc.</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>464</v>
+        <v>116</v>
       </c>
       <c r="H40" t="n">
-        <v>35514.56</v>
+        <v>35435.68</v>
       </c>
       <c r="I40" t="n">
-        <v>76.54000000000001</v>
+        <v>305.48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01158131472674083</v>
+        <v>0.01151993579049883</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4305,16 +4305,16 @@
         <v>399</v>
       </c>
       <c r="H41" t="n">
-        <v>34760.88</v>
+        <v>34493.55</v>
       </c>
       <c r="I41" t="n">
-        <v>87.12</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4323,33 +4323,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01132787826350005</v>
+        <v>0.01127126905160035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Snap-On</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>90</v>
+        <v>381</v>
       </c>
       <c r="H42" t="n">
-        <v>34000.2</v>
+        <v>33748.98</v>
       </c>
       <c r="I42" t="n">
-        <v>377.78</v>
+        <v>88.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4358,33 +4358,33 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01128352988097128</v>
+        <v>0.01126619933203539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Snap-On</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>381</v>
+        <v>90</v>
       </c>
       <c r="H43" t="n">
-        <v>33867.09</v>
+        <v>33733.8</v>
       </c>
       <c r="I43" t="n">
-        <v>88.89</v>
+        <v>374.82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.01100496899787855</v>
+        <v>0.01084707579677606</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4410,16 +4410,16 @@
         <v>493</v>
       </c>
       <c r="H44" t="n">
-        <v>33031</v>
+        <v>32478.84</v>
       </c>
       <c r="I44" t="n">
-        <v>67</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4428,33 +4428,33 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.009078324800836915</v>
+        <v>0.009005475116784397</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Hormel Foods</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>705</v>
+        <v>1297</v>
       </c>
       <c r="H45" t="n">
-        <v>27248.25</v>
+        <v>26964.63</v>
       </c>
       <c r="I45" t="n">
-        <v>38.65</v>
+        <v>20.79</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.009071001703789492</v>
+        <v>0.008967625886330087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4480,16 +4480,16 @@
         <v>431</v>
       </c>
       <c r="H46" t="n">
-        <v>27226.27</v>
+        <v>26851.3</v>
       </c>
       <c r="I46" t="n">
-        <v>63.17</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,33 +4498,33 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.00905729172000872</v>
+        <v>0.00894244427531575</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hormel Foods</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1297</v>
+        <v>705</v>
       </c>
       <c r="H47" t="n">
-        <v>27185.12</v>
+        <v>26775.9</v>
       </c>
       <c r="I47" t="n">
-        <v>20.96</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008829695994119985</v>
+        <v>0.008875515961691435</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4550,16 +4550,16 @@
         <v>350</v>
       </c>
       <c r="H48" t="n">
-        <v>26502</v>
+        <v>26575.5</v>
       </c>
       <c r="I48" t="n">
-        <v>75.72</v>
+        <v>75.93000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.008445186755200132</v>
+        <v>0.008503299021484678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4585,16 +4585,16 @@
         <v>257</v>
       </c>
       <c r="H49" t="n">
-        <v>25347.91</v>
+        <v>25460.99</v>
       </c>
       <c r="I49" t="n">
-        <v>98.63</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.007739677320089245</v>
+        <v>0.00758452089176327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4620,16 +4620,16 @@
         <v>627</v>
       </c>
       <c r="H50" t="n">
-        <v>23230.35</v>
+        <v>22709.94</v>
       </c>
       <c r="I50" t="n">
-        <v>37.05</v>
+        <v>36.22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.006063927492090405</v>
+        <v>0.006066597425919692</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4655,10 +4655,10 @@
         <v>65</v>
       </c>
       <c r="H51" t="n">
-        <v>18200.65</v>
+        <v>18164.9</v>
       </c>
       <c r="I51" t="n">
-        <v>280.01</v>
+        <v>279.46</v>
       </c>
     </row>
   </sheetData>
@@ -4725,7 +4725,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0699686476226017</v>
+        <v>0.07036331314009088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05337717582807953</v>
+        <v>0.05435325142955147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4786,16 +4786,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>119004.2</v>
+        <v>120500.66</v>
       </c>
       <c r="I3" t="n">
-        <v>116.9</v>
+        <v>118.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04216480316627614</v>
+        <v>0.04170712785492216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4821,16 +4821,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>94006.25999999999</v>
+        <v>92464.32000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04053190048333794</v>
+        <v>0.04039318917706123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4856,16 +4856,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>90365.71000000001</v>
+        <v>89551.33</v>
       </c>
       <c r="I5" t="n">
-        <v>326.23</v>
+        <v>323.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03835692909967096</v>
+        <v>0.03857679014396284</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4891,16 +4891,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>85516.62</v>
+        <v>85524.39</v>
       </c>
       <c r="I6" t="n">
-        <v>110.06</v>
+        <v>110.07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03478838266585811</v>
+        <v>0.03477005811521557</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4926,16 +4926,16 @@
         <v>2798</v>
       </c>
       <c r="H7" t="n">
-        <v>77560.56</v>
+        <v>77084.89999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>27.72</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03433098781069802</v>
+        <v>0.03450623203524933</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4961,16 +4961,16 @@
         <v>816</v>
       </c>
       <c r="H8" t="n">
-        <v>76540.8</v>
+        <v>76500</v>
       </c>
       <c r="I8" t="n">
-        <v>93.8</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4979,33 +4979,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03430103485272008</v>
+        <v>0.03394379398493046</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>246</v>
+        <v>303</v>
       </c>
       <c r="H9" t="n">
-        <v>76474.02</v>
+        <v>75253.08</v>
       </c>
       <c r="I9" t="n">
-        <v>310.87</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5014,33 +5014,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03384717891397876</v>
+        <v>0.03389643248998012</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>303</v>
+        <v>246</v>
       </c>
       <c r="H10" t="n">
-        <v>75462.14999999999</v>
+        <v>75148.08</v>
       </c>
       <c r="I10" t="n">
-        <v>249.05</v>
+        <v>305.48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03236408587411684</v>
+        <v>0.03206366893272174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5066,16 +5066,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>72155.60000000001</v>
+        <v>71084.86</v>
       </c>
       <c r="I11" t="n">
-        <v>105.8</v>
+        <v>104.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03125544069152849</v>
+        <v>0.03137604317470271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5101,16 +5101,16 @@
         <v>588</v>
       </c>
       <c r="H12" t="n">
-        <v>69683.88</v>
+        <v>69560.39999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>118.51</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03093775902715232</v>
+        <v>0.03132197438994368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5136,16 +5136,16 @@
         <v>197</v>
       </c>
       <c r="H13" t="n">
-        <v>68975.61</v>
+        <v>69440.53</v>
       </c>
       <c r="I13" t="n">
-        <v>350.13</v>
+        <v>352.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5154,33 +5154,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03081983551439428</v>
+        <v>0.03071363177447152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>245</v>
+        <v>568</v>
       </c>
       <c r="H14" t="n">
-        <v>68712.7</v>
+        <v>68091.84</v>
       </c>
       <c r="I14" t="n">
-        <v>280.46</v>
+        <v>119.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5189,33 +5189,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03068017166211557</v>
+        <v>0.03040023850707583</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1076</v>
+        <v>245</v>
       </c>
       <c r="H15" t="n">
-        <v>68401.32000000001</v>
+        <v>67397.05</v>
       </c>
       <c r="I15" t="n">
-        <v>63.57</v>
+        <v>275.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5224,33 +5224,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03038850036061962</v>
+        <v>0.0303047893075859</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>568</v>
+        <v>1076</v>
       </c>
       <c r="H16" t="n">
-        <v>67751.03999999999</v>
+        <v>67185.44</v>
       </c>
       <c r="I16" t="n">
-        <v>119.28</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5259,33 +5259,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02876441132883845</v>
+        <v>0.02931091961259939</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1082</v>
+        <v>263</v>
       </c>
       <c r="H17" t="n">
-        <v>64130.14</v>
+        <v>64982.04</v>
       </c>
       <c r="I17" t="n">
-        <v>59.27</v>
+        <v>247.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5294,33 +5294,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02806242756210372</v>
+        <v>0.02865335261670884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>263</v>
+        <v>1082</v>
       </c>
       <c r="H18" t="n">
-        <v>62565.07</v>
+        <v>63524.22</v>
       </c>
       <c r="I18" t="n">
-        <v>237.89</v>
+        <v>58.71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02792732079357846</v>
+        <v>0.0274901858750584</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5346,16 +5346,16 @@
         <v>1433</v>
       </c>
       <c r="H19" t="n">
-        <v>62263.85</v>
+        <v>60945.49</v>
       </c>
       <c r="I19" t="n">
-        <v>43.45</v>
+        <v>42.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5364,33 +5364,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02587439044519479</v>
+        <v>0.02567155408576949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1557</v>
+        <v>213</v>
       </c>
       <c r="H20" t="n">
-        <v>57686.85</v>
+        <v>56913.6</v>
       </c>
       <c r="I20" t="n">
-        <v>37.05</v>
+        <v>267.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5399,33 +5399,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02544349036732966</v>
+        <v>0.0254374259184464</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>213</v>
+        <v>1557</v>
       </c>
       <c r="H21" t="n">
-        <v>56726.16</v>
+        <v>56394.54</v>
       </c>
       <c r="I21" t="n">
-        <v>266.32</v>
+        <v>36.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5434,33 +5434,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02258716768274085</v>
+        <v>0.02257641273148613</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="H22" t="n">
-        <v>50358</v>
+        <v>50051.7</v>
       </c>
       <c r="I22" t="n">
-        <v>381.5</v>
+        <v>263.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02256539594598959</v>
+        <v>0.02255286730256796</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5486,16 +5486,16 @@
         <v>369</v>
       </c>
       <c r="H23" t="n">
-        <v>50309.46</v>
+        <v>49999.5</v>
       </c>
       <c r="I23" t="n">
-        <v>136.34</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5504,33 +5504,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02244893016179442</v>
+        <v>0.02236626301246361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="H24" t="n">
-        <v>50049.8</v>
+        <v>49585.8</v>
       </c>
       <c r="I24" t="n">
-        <v>263.42</v>
+        <v>375.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0222563440347056</v>
+        <v>0.02227997487928265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5556,16 +5556,16 @@
         <v>443</v>
       </c>
       <c r="H25" t="n">
-        <v>49620.43</v>
+        <v>49394.5</v>
       </c>
       <c r="I25" t="n">
-        <v>112.01</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02206198620674807</v>
+        <v>0.02225564009211531</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5591,16 +5591,16 @@
         <v>959</v>
       </c>
       <c r="H26" t="n">
-        <v>49187.11</v>
+        <v>49340.55</v>
       </c>
       <c r="I26" t="n">
-        <v>51.29</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02199416370336614</v>
+        <v>0.02070953987662637</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5626,16 +5626,16 @@
         <v>298</v>
       </c>
       <c r="H27" t="n">
-        <v>49035.9</v>
+        <v>45912.86</v>
       </c>
       <c r="I27" t="n">
-        <v>164.55</v>
+        <v>154.07</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02033092681036432</v>
+        <v>0.02036743201143507</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5661,16 +5661,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>45327.72</v>
+        <v>45154.41</v>
       </c>
       <c r="I28" t="n">
-        <v>285.08</v>
+        <v>283.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5679,33 +5679,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01938825635928479</v>
+        <v>0.0190900293439644</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>484</v>
+        <v>601</v>
       </c>
       <c r="H29" t="n">
-        <v>43226.04</v>
+        <v>42322.42</v>
       </c>
       <c r="I29" t="n">
-        <v>89.31</v>
+        <v>70.42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5714,33 +5714,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01911773782056572</v>
+        <v>0.01902824289083776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>601</v>
+        <v>484</v>
       </c>
       <c r="H30" t="n">
-        <v>42622.92</v>
+        <v>42185.44</v>
       </c>
       <c r="I30" t="n">
-        <v>70.92</v>
+        <v>87.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01848339714446673</v>
+        <v>0.0186563423900134</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5766,16 +5766,16 @@
         <v>282</v>
       </c>
       <c r="H31" t="n">
-        <v>41208.66</v>
+        <v>41360.94</v>
       </c>
       <c r="I31" t="n">
-        <v>146.13</v>
+        <v>146.67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01802826288990875</v>
+        <v>0.01799347090668841</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5801,16 +5801,16 @@
         <v>246</v>
       </c>
       <c r="H32" t="n">
-        <v>40193.94</v>
+        <v>39891.36</v>
       </c>
       <c r="I32" t="n">
-        <v>163.39</v>
+        <v>162.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5819,33 +5819,33 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01678138915701127</v>
+        <v>0.01693495502640396</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>361</v>
+        <v>148</v>
       </c>
       <c r="H33" t="n">
-        <v>37414.04</v>
+        <v>37544.64</v>
       </c>
       <c r="I33" t="n">
-        <v>103.64</v>
+        <v>253.68</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5854,33 +5854,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01667965315927905</v>
+        <v>0.01675880635013723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>148</v>
+        <v>361</v>
       </c>
       <c r="H34" t="n">
-        <v>37187.22</v>
+        <v>37154.12</v>
       </c>
       <c r="I34" t="n">
-        <v>251.27</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5889,33 +5889,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01663471923699347</v>
+        <v>0.01662345170818771</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>736</v>
+        <v>372</v>
       </c>
       <c r="H35" t="n">
-        <v>37087.04</v>
+        <v>36854.04</v>
       </c>
       <c r="I35" t="n">
-        <v>50.39</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5924,27 +5924,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01645679561658778</v>
+        <v>0.016552598911742</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>372</v>
+        <v>736</v>
       </c>
       <c r="H36" t="n">
-        <v>36690.36</v>
+        <v>36696.96</v>
       </c>
       <c r="I36" t="n">
-        <v>98.63</v>
+        <v>49.86</v>
       </c>
     </row>
   </sheetData>
@@ -6011,7 +6011,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1057738677172289</v>
+        <v>0.1052041493891977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6037,16 +6037,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>224013.74</v>
+        <v>222698.5</v>
       </c>
       <c r="I2" t="n">
-        <v>53.46</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09949206915577477</v>
+        <v>0.0990545073597105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6072,16 +6072,16 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>210709.8</v>
+        <v>209680.8</v>
       </c>
       <c r="I3" t="n">
-        <v>215.01</v>
+        <v>213.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09449276618169615</v>
+        <v>0.09368570551785546</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6107,16 +6107,16 @@
         <v>4300</v>
       </c>
       <c r="H4" t="n">
-        <v>200122</v>
+        <v>198316</v>
       </c>
       <c r="I4" t="n">
-        <v>46.54</v>
+        <v>46.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08532263045513913</v>
+        <v>0.08811310764663112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6142,16 +6142,16 @@
         <v>934</v>
       </c>
       <c r="H5" t="n">
-        <v>180700.98</v>
+        <v>186519.8</v>
       </c>
       <c r="I5" t="n">
-        <v>193.47</v>
+        <v>199.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05495063959140097</v>
+        <v>0.05488686722135973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1475</v>
       </c>
       <c r="H6" t="n">
-        <v>116377.5</v>
+        <v>116185.75</v>
       </c>
       <c r="I6" t="n">
-        <v>78.90000000000001</v>
+        <v>78.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03785847988363926</v>
+        <v>0.03760850225318856</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6212,16 +6212,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>80178.78</v>
+        <v>79610.52</v>
       </c>
       <c r="I7" t="n">
-        <v>29.63</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02647985515761691</v>
+        <v>0.02608652950762427</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6247,16 +6247,16 @@
         <v>147</v>
       </c>
       <c r="H8" t="n">
-        <v>56080.5</v>
+        <v>55220.55</v>
       </c>
       <c r="I8" t="n">
-        <v>381.5</v>
+        <v>375.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02505744915785651</v>
+        <v>0.02465846922254792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6282,16 +6282,16 @@
         <v>105</v>
       </c>
       <c r="H9" t="n">
-        <v>53068.05</v>
+        <v>52197.6</v>
       </c>
       <c r="I9" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02321338544366233</v>
+        <v>0.02320854597910529</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6317,16 +6317,16 @@
         <v>1860</v>
       </c>
       <c r="H10" t="n">
-        <v>49162.59</v>
+        <v>49128.37</v>
       </c>
       <c r="I10" t="n">
-        <v>26.43</v>
+        <v>26.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02121592125437242</v>
+        <v>0.02106648153383109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6352,16 +6352,16 @@
         <v>275</v>
       </c>
       <c r="H11" t="n">
-        <v>44932.25</v>
+        <v>44594</v>
       </c>
       <c r="I11" t="n">
-        <v>163.39</v>
+        <v>162.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6370,33 +6370,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02092337529169368</v>
+        <v>0.02078093088962022</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="H12" t="n">
-        <v>44312.68</v>
+        <v>43989.54</v>
       </c>
       <c r="I12" t="n">
-        <v>280.46</v>
+        <v>217.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6405,33 +6405,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02023667113338681</v>
+        <v>0.02053276647110311</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="H13" t="n">
-        <v>42858.34</v>
+        <v>43464.22</v>
       </c>
       <c r="I13" t="n">
-        <v>212.17</v>
+        <v>275.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02003168072998228</v>
+        <v>0.02007849123289701</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6457,16 +6457,16 @@
         <v>980</v>
       </c>
       <c r="H14" t="n">
-        <v>42424.2</v>
+        <v>42502.6</v>
       </c>
       <c r="I14" t="n">
-        <v>43.29</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01986847788520239</v>
+        <v>0.01994385546940547</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6492,16 +6492,16 @@
         <v>158</v>
       </c>
       <c r="H15" t="n">
-        <v>42078.56</v>
+        <v>42217.6</v>
       </c>
       <c r="I15" t="n">
-        <v>266.32</v>
+        <v>267.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6510,33 +6510,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01757079015466609</v>
+        <v>0.017917270716712</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="H16" t="n">
-        <v>37212.39</v>
+        <v>37927.68</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>169.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6545,33 +6545,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01746007909398</v>
+        <v>0.01774799340747717</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>36977.92</v>
+        <v>37569.35</v>
       </c>
       <c r="I17" t="n">
-        <v>165.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6580,33 +6580,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01636696849969783</v>
+        <v>0.01654014999085422</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>ASML Holding</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>34662.87</v>
+        <v>35012.56</v>
       </c>
       <c r="I18" t="n">
-        <v>350.13</v>
+        <v>1591.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6615,33 +6615,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01636244977725673</v>
+        <v>0.01648532725277284</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ASML Holding</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="H19" t="n">
-        <v>34653.3</v>
+        <v>34896.51</v>
       </c>
       <c r="I19" t="n">
-        <v>1575.15</v>
+        <v>352.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01627238696446505</v>
+        <v>0.01612817400269385</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6667,16 +6667,16 @@
         <v>488</v>
       </c>
       <c r="H20" t="n">
-        <v>34462.56</v>
+        <v>34140.48</v>
       </c>
       <c r="I20" t="n">
-        <v>70.62</v>
+        <v>69.95999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01590210669922841</v>
+        <v>0.01591131121817305</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>306</v>
       </c>
       <c r="H21" t="n">
-        <v>33678.36</v>
+        <v>33681.42</v>
       </c>
       <c r="I21" t="n">
-        <v>110.06</v>
+        <v>110.07</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01481701837185057</v>
+        <v>0.01478317689759897</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6737,16 +6737,16 @@
         <v>126</v>
       </c>
       <c r="H22" t="n">
-        <v>31380.3</v>
+        <v>31293.36</v>
       </c>
       <c r="I22" t="n">
-        <v>249.05</v>
+        <v>248.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01415207207457673</v>
+        <v>0.01423000814806193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>84</v>
       </c>
       <c r="H23" t="n">
-        <v>29972.04</v>
+        <v>30122.4</v>
       </c>
       <c r="I23" t="n">
-        <v>356.81</v>
+        <v>358.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01386880908819811</v>
+        <v>0.01392685092523587</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6807,16 +6807,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>29372.13</v>
+        <v>29480.67</v>
       </c>
       <c r="I24" t="n">
-        <v>146.13</v>
+        <v>146.67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01322210294221998</v>
+        <v>0.01316832248184827</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6842,16 +6842,16 @@
         <v>250</v>
       </c>
       <c r="H25" t="n">
-        <v>28002.5</v>
+        <v>27875</v>
       </c>
       <c r="I25" t="n">
-        <v>112.01</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01281119667083573</v>
+        <v>0.012817934088377</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6877,16 +6877,16 @@
         <v>103</v>
       </c>
       <c r="H26" t="n">
-        <v>27132.26</v>
+        <v>27133.29</v>
       </c>
       <c r="I26" t="n">
-        <v>263.42</v>
+        <v>263.43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01242671335742475</v>
+        <v>0.01221177553676681</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>414</v>
       </c>
       <c r="H27" t="n">
-        <v>26317.98</v>
+        <v>25850.16</v>
       </c>
       <c r="I27" t="n">
-        <v>63.57</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01189595942355342</v>
+        <v>0.01174581296947727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6947,16 +6947,16 @@
         <v>524</v>
       </c>
       <c r="H28" t="n">
-        <v>25193.92</v>
+        <v>24863.8</v>
       </c>
       <c r="I28" t="n">
-        <v>48.08</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6965,33 +6965,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0111915108985447</v>
+        <v>0.01139353022719337</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Total SA</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="H29" t="n">
-        <v>23702</v>
+        <v>24118.08</v>
       </c>
       <c r="I29" t="n">
-        <v>118.51</v>
+        <v>93.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7000,33 +7000,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01114583261129783</v>
+        <v>0.0111771304007365</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Total SA</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>259</v>
+        <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>23605.26</v>
+        <v>23660</v>
       </c>
       <c r="I30" t="n">
-        <v>91.14</v>
+        <v>118.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0110725225960203</v>
+        <v>0.01107202002397556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7052,16 +7052,16 @@
         <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>23450</v>
+        <v>23437.5</v>
       </c>
       <c r="I31" t="n">
-        <v>93.8</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.009745118367957953</v>
+        <v>0.00954343170215886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7087,16 +7087,16 @@
         <v>475</v>
       </c>
       <c r="H32" t="n">
-        <v>20638.75</v>
+        <v>20201.75</v>
       </c>
       <c r="I32" t="n">
-        <v>43.45</v>
+        <v>42.53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.009130147157744361</v>
+        <v>0.009163097480449946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7122,16 +7122,16 @@
         <v>377</v>
       </c>
       <c r="H33" t="n">
-        <v>19336.33</v>
+        <v>19396.65</v>
       </c>
       <c r="I33" t="n">
-        <v>51.29</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7140,33 +7140,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.008742335004917522</v>
+        <v>0.008777996680307239</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>175</v>
+        <v>362</v>
       </c>
       <c r="H34" t="n">
-        <v>18515</v>
+        <v>18581.46</v>
       </c>
       <c r="I34" t="n">
-        <v>105.8</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7175,33 +7175,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.008661725151715278</v>
+        <v>0.008616806965005663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H35" t="n">
-        <v>18344.28</v>
+        <v>18240.25</v>
       </c>
       <c r="I35" t="n">
-        <v>103.64</v>
+        <v>104.23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7210,33 +7210,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.008507663630494404</v>
+        <v>0.008605747936151849</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>650</v>
+        <v>177</v>
       </c>
       <c r="H36" t="n">
-        <v>18018</v>
+        <v>18216.84</v>
       </c>
       <c r="I36" t="n">
-        <v>27.72</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7245,33 +7245,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.008500231583344665</v>
+        <v>0.008459613806051942</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>362</v>
+        <v>650</v>
       </c>
       <c r="H37" t="n">
-        <v>18002.26</v>
+        <v>17907.5</v>
       </c>
       <c r="I37" t="n">
-        <v>49.73</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008497691277520932</v>
+        <v>0.008449457073016614</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -7297,16 +7297,16 @@
         <v>132</v>
       </c>
       <c r="H38" t="n">
-        <v>17996.88</v>
+        <v>17886</v>
       </c>
       <c r="I38" t="n">
-        <v>136.34</v>
+        <v>135.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008208563867660756</v>
+        <v>0.008126189518780604</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7332,16 +7332,16 @@
         <v>345</v>
       </c>
       <c r="H39" t="n">
-        <v>17384.55</v>
+        <v>17201.7</v>
       </c>
       <c r="I39" t="n">
-        <v>50.39</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.007869376379095674</v>
+        <v>0.007817708278219281</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7367,16 +7367,16 @@
         <v>235</v>
       </c>
       <c r="H40" t="n">
-        <v>16666.2</v>
+        <v>16548.7</v>
       </c>
       <c r="I40" t="n">
-        <v>70.92</v>
+        <v>70.42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.007612153888289361</v>
+        <v>0.007543911099958128</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7402,16 +7402,16 @@
         <v>272</v>
       </c>
       <c r="H41" t="n">
-        <v>16121.44</v>
+        <v>15969.12</v>
       </c>
       <c r="I41" t="n">
-        <v>59.27</v>
+        <v>58.71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7420,33 +7420,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.007337583658456278</v>
+        <v>0.007244566195066721</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="H42" t="n">
-        <v>15539.94</v>
+        <v>15335.46</v>
       </c>
       <c r="I42" t="n">
-        <v>89.31</v>
+        <v>283.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7455,33 +7455,33 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.007268825417926108</v>
+        <v>0.007164436657510807</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="H43" t="n">
-        <v>15394.32</v>
+        <v>15165.84</v>
       </c>
       <c r="I43" t="n">
-        <v>285.08</v>
+        <v>87.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.006675763165002721</v>
+        <v>0.006883501421753664</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7507,16 +7507,16 @@
         <v>55</v>
       </c>
       <c r="H44" t="n">
-        <v>14138.3</v>
+        <v>14571.15</v>
       </c>
       <c r="I44" t="n">
-        <v>257.06</v>
+        <v>264.93</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.004810881219624812</v>
+        <v>0.004705401832482499</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7542,16 +7542,16 @@
         <v>275</v>
       </c>
       <c r="H45" t="n">
-        <v>10188.75</v>
+        <v>9960.5</v>
       </c>
       <c r="I45" t="n">
-        <v>37.05</v>
+        <v>36.22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.004256773470504055</v>
+        <v>0.004185008624247363</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7577,16 +7577,16 @@
         <v>29</v>
       </c>
       <c r="H46" t="n">
-        <v>9015.23</v>
+        <v>8858.92</v>
       </c>
       <c r="I46" t="n">
-        <v>310.87</v>
+        <v>305.48</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/14/2026</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.002719378497276329</v>
+        <v>0.002547426746806913</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7612,261 +7612,13 @@
         <v>35</v>
       </c>
       <c r="H47" t="n">
-        <v>5759.25</v>
+        <v>5392.45</v>
       </c>
       <c r="I47" t="n">
-        <v>164.55</v>
+        <v>154.07</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C4DFC9E-8176-4CDF-A91E-D36E49066EE1}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76271C3B-6B9A-49C2-A08A-E77642183CB6}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B79042-351A-452C-824E-FBDF010A0D0B}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -7621,4 +7621,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28791961-BD52-4D6A-AF4C-2E59F69032A8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{749F9DBE-E4D1-46EA-BE8E-176D775640B4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4ED2200-AA92-43C6-BA0C-A03D2E4E84D8}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09409683445333643</v>
+        <v>0.09493425818951846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04285395263054025</v>
+        <v>0.04331590177290296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>101049.85</v>
+        <v>101238.15</v>
       </c>
       <c r="I3" t="n">
-        <v>375.65</v>
+        <v>376.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0405984318882125</v>
+        <v>0.04056814558317896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>95731.32000000001</v>
+        <v>94816.08</v>
       </c>
       <c r="I4" t="n">
-        <v>275.09</v>
+        <v>272.46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03961964276451008</v>
+        <v>0.03882870908235793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -613,16 +613,16 @@
         <v>429</v>
       </c>
       <c r="H5" t="n">
-        <v>93423.33</v>
+        <v>90750.66</v>
       </c>
       <c r="I5" t="n">
-        <v>217.77</v>
+        <v>211.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03857996319397679</v>
+        <v>0.03827042690364052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -648,16 +648,16 @@
         <v>561</v>
       </c>
       <c r="H6" t="n">
-        <v>90971.75999999999</v>
+        <v>89445.84</v>
       </c>
       <c r="I6" t="n">
-        <v>162.16</v>
+        <v>159.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03705436869744858</v>
+        <v>0.03739533043478878</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -683,16 +683,16 @@
         <v>327</v>
       </c>
       <c r="H7" t="n">
-        <v>87374.39999999999</v>
+        <v>87400.56</v>
       </c>
       <c r="I7" t="n">
-        <v>267.2</v>
+        <v>267.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03396445205705554</v>
+        <v>0.03305245113310933</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         <v>473</v>
       </c>
       <c r="H8" t="n">
-        <v>80088.36</v>
+        <v>77250.36</v>
       </c>
       <c r="I8" t="n">
-        <v>169.32</v>
+        <v>163.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03239646579938223</v>
+        <v>0.03290535236619662</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -753,16 +753,16 @@
         <v>48</v>
       </c>
       <c r="H9" t="n">
-        <v>76391.03999999999</v>
+        <v>76906.56</v>
       </c>
       <c r="I9" t="n">
-        <v>1591.48</v>
+        <v>1602.22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,33 +771,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0313217990310251</v>
+        <v>0.0315216227614214</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>671</v>
+        <v>1045</v>
       </c>
       <c r="H10" t="n">
-        <v>73856.97</v>
+        <v>73672.5</v>
       </c>
       <c r="I10" t="n">
-        <v>110.07</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,33 +806,33 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03100425522357591</v>
+        <v>0.03093161893471415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1045</v>
+        <v>671</v>
       </c>
       <c r="H11" t="n">
-        <v>73108.2</v>
+        <v>72293.53999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>69.95999999999999</v>
+        <v>107.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02965514887548856</v>
+        <v>0.03003587387222888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         <v>195</v>
       </c>
       <c r="H12" t="n">
-        <v>69927</v>
+        <v>70200</v>
       </c>
       <c r="I12" t="n">
-        <v>358.6</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02909347076293329</v>
+        <v>0.02894970479228528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         <v>138</v>
       </c>
       <c r="H13" t="n">
-        <v>68602.56</v>
+        <v>67661.39999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02795397801809916</v>
+        <v>0.02791712108048639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>187</v>
       </c>
       <c r="H14" t="n">
-        <v>65915.63</v>
+        <v>65248.04</v>
       </c>
       <c r="I14" t="n">
-        <v>352.49</v>
+        <v>348.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02770081913639076</v>
+        <v>0.02791696277174946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -963,16 +963,16 @@
         <v>263</v>
       </c>
       <c r="H15" t="n">
-        <v>65318.68</v>
+        <v>65247.67</v>
       </c>
       <c r="I15" t="n">
-        <v>248.36</v>
+        <v>248.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02718178299645595</v>
+        <v>0.02748913127087969</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -998,16 +998,16 @@
         <v>437</v>
       </c>
       <c r="H16" t="n">
-        <v>64094.79</v>
+        <v>64247.74</v>
       </c>
       <c r="I16" t="n">
-        <v>146.67</v>
+        <v>147.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02565298240034535</v>
+        <v>0.02560150067783094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>213</v>
       </c>
       <c r="H17" t="n">
-        <v>60489.87</v>
+        <v>59835.96</v>
       </c>
       <c r="I17" t="n">
-        <v>283.99</v>
+        <v>280.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,33 +1051,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02546902607549628</v>
+        <v>0.02498286436281131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1170</v>
+        <v>224</v>
       </c>
       <c r="H18" t="n">
-        <v>60056.1</v>
+        <v>58390.08</v>
       </c>
       <c r="I18" t="n">
-        <v>51.33</v>
+        <v>260.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,33 +1086,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0250246759405161</v>
+        <v>0.02424896217284611</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>224</v>
+        <v>1170</v>
       </c>
       <c r="H19" t="n">
-        <v>59008.32</v>
+        <v>56674.8</v>
       </c>
       <c r="I19" t="n">
-        <v>263.43</v>
+        <v>48.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,33 +1121,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02377904688053805</v>
+        <v>0.02401155896804918</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>898</v>
+        <v>353</v>
       </c>
       <c r="H20" t="n">
-        <v>56071.12</v>
+        <v>56119.94</v>
       </c>
       <c r="I20" t="n">
-        <v>62.44</v>
+        <v>158.98</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,33 +1156,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02306471008191431</v>
+        <v>0.02399067077200299</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>353</v>
+        <v>898</v>
       </c>
       <c r="H21" t="n">
-        <v>54386.71</v>
+        <v>56071.12</v>
       </c>
       <c r="I21" t="n">
-        <v>154.07</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02206578953662768</v>
+        <v>0.02198908356004927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1208,16 +1208,16 @@
         <v>555</v>
       </c>
       <c r="H22" t="n">
-        <v>52031.25</v>
+        <v>51393</v>
       </c>
       <c r="I22" t="n">
-        <v>93.75</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02195699843532162</v>
+        <v>0.02196418630220561</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Total SA</t>
+          <t>Coca-Cola Femsa</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>556</v>
+        <v>457</v>
       </c>
       <c r="H23" t="n">
-        <v>51774.72</v>
+        <v>51334.81</v>
       </c>
       <c r="I23" t="n">
-        <v>93.12</v>
+        <v>112.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,33 +1261,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0216095776813671</v>
+        <v>0.0216100154287695</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coca-Cola Femsa</t>
+          <t>Total SA</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="H24" t="n">
-        <v>50955.5</v>
+        <v>50507.04</v>
       </c>
       <c r="I24" t="n">
-        <v>111.5</v>
+        <v>90.84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,33 +1296,33 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02151201216947191</v>
+        <v>0.02127443513538679</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>864</v>
+        <v>426</v>
       </c>
       <c r="H25" t="n">
-        <v>50725.44</v>
+        <v>49722.72</v>
       </c>
       <c r="I25" t="n">
-        <v>58.71</v>
+        <v>116.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,33 +1331,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02137221604958523</v>
+        <v>0.02112677159135853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>426</v>
+        <v>864</v>
       </c>
       <c r="H26" t="n">
-        <v>50395.8</v>
+        <v>49377.6</v>
       </c>
       <c r="I26" t="n">
-        <v>118.3</v>
+        <v>57.15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02007374571871202</v>
+        <v>0.01958715494546354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1383,16 +1383,16 @@
         <v>920</v>
       </c>
       <c r="H27" t="n">
-        <v>47334</v>
+        <v>45779.2</v>
       </c>
       <c r="I27" t="n">
-        <v>51.45</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01960560004833916</v>
+        <v>0.01939871192652414</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1418,16 +1418,16 @@
         <v>1087</v>
       </c>
       <c r="H28" t="n">
-        <v>46230.11</v>
+        <v>45338.77</v>
       </c>
       <c r="I28" t="n">
-        <v>42.53</v>
+        <v>41.71</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,33 +1436,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01902052504240279</v>
+        <v>0.01922791391383105</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>331</v>
+        <v>938</v>
       </c>
       <c r="H29" t="n">
-        <v>44850.5</v>
+        <v>44939.58</v>
       </c>
       <c r="I29" t="n">
-        <v>135.5</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,33 +1471,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01887531756925268</v>
+        <v>0.01902551833296895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>938</v>
+        <v>331</v>
       </c>
       <c r="H30" t="n">
-        <v>44508.1</v>
+        <v>44466.54</v>
       </c>
       <c r="I30" t="n">
-        <v>47.45</v>
+        <v>134.34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01883031343067006</v>
+        <v>0.01866434336757717</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1523,16 +1523,16 @@
         <v>426</v>
       </c>
       <c r="H31" t="n">
-        <v>44401.98</v>
+        <v>43622.4</v>
       </c>
       <c r="I31" t="n">
-        <v>104.23</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01757213986994499</v>
+        <v>0.01767060947554463</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1558,16 +1558,16 @@
         <v>1504</v>
       </c>
       <c r="H32" t="n">
-        <v>41435.2</v>
+        <v>41299.84</v>
       </c>
       <c r="I32" t="n">
-        <v>27.55</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01672396537724579</v>
+        <v>0.01686561382685281</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>39435.2</v>
+        <v>39418.4</v>
       </c>
       <c r="I33" t="n">
-        <v>70.42</v>
+        <v>70.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01619305903528565</v>
+        <v>0.01624192874670935</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>38183.32</v>
+        <v>37960.72</v>
       </c>
       <c r="I34" t="n">
-        <v>102.92</v>
+        <v>102.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,33 +1646,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01378736475815305</v>
+        <v>0.01370022207464045</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>373</v>
+        <v>121</v>
       </c>
       <c r="H35" t="n">
-        <v>32510.68</v>
+        <v>32020.23</v>
       </c>
       <c r="I35" t="n">
-        <v>87.16</v>
+        <v>264.63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,33 +1681,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01359476553522338</v>
+        <v>0.01354300438440753</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>121</v>
+        <v>373</v>
       </c>
       <c r="H36" t="n">
-        <v>32056.53</v>
+        <v>31652.78</v>
       </c>
       <c r="I36" t="n">
-        <v>264.93</v>
+        <v>84.86</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01127086496529422</v>
+        <v>0.01125912702281449</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         <v>87</v>
       </c>
       <c r="H37" t="n">
-        <v>26576.76</v>
+        <v>26314.89</v>
       </c>
       <c r="I37" t="n">
-        <v>305.48</v>
+        <v>302.47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01103768483376136</v>
+        <v>0.01118058449622296</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         <v>522</v>
       </c>
       <c r="H38" t="n">
-        <v>26026.92</v>
+        <v>26131.32</v>
       </c>
       <c r="I38" t="n">
-        <v>49.86</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008832253036099967</v>
+        <v>0.008802607565673802</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         <v>575</v>
       </c>
       <c r="H39" t="n">
-        <v>20826.5</v>
+        <v>20573.5</v>
       </c>
       <c r="I39" t="n">
-        <v>36.22</v>
+        <v>35.78</v>
       </c>
     </row>
   </sheetData>
@@ -1873,7 +1873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06079918795079362</v>
+        <v>0.06021245127124281</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>157457.36</v>
+        <v>154816.24</v>
       </c>
       <c r="I2" t="n">
-        <v>162.16</v>
+        <v>159.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05953961276762654</v>
+        <v>0.05659445148193318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>154195.32</v>
+        <v>145513.76</v>
       </c>
       <c r="I3" t="n">
-        <v>51.33</v>
+        <v>48.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05304533511509683</v>
+        <v>0.05342963120545276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05001884706033354</v>
+        <v>0.04970833200092904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2004,16 +2004,16 @@
         <v>1095</v>
       </c>
       <c r="H5" t="n">
-        <v>129538.5</v>
+        <v>127808.4</v>
       </c>
       <c r="I5" t="n">
-        <v>118.3</v>
+        <v>116.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04933407439619326</v>
+        <v>0.04969148361739337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04811145968455096</v>
+        <v>0.04883405957826442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2074,16 +2074,16 @@
         <v>1781</v>
       </c>
       <c r="H7" t="n">
-        <v>124598.76</v>
+        <v>125560.5</v>
       </c>
       <c r="I7" t="n">
-        <v>69.95999999999999</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2092,33 +2092,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04315478707223719</v>
+        <v>0.04346779497216077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>450</v>
+        <v>703</v>
       </c>
       <c r="H8" t="n">
-        <v>111762</v>
+        <v>111762.94</v>
       </c>
       <c r="I8" t="n">
-        <v>248.36</v>
+        <v>158.98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2127,33 +2127,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04182232963875349</v>
+        <v>0.04342017456403272</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>703</v>
+        <v>450</v>
       </c>
       <c r="H9" t="n">
-        <v>108311.21</v>
+        <v>111640.5</v>
       </c>
       <c r="I9" t="n">
-        <v>154.07</v>
+        <v>248.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03931360095155067</v>
+        <v>0.03975725353053171</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>101814.12</v>
+        <v>102222.52</v>
       </c>
       <c r="I10" t="n">
-        <v>49.86</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03684636205399829</v>
+        <v>0.03729905414839445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2214,16 +2214,16 @@
         <v>796</v>
       </c>
       <c r="H11" t="n">
-        <v>95424.48</v>
+        <v>95902.08</v>
       </c>
       <c r="I11" t="n">
-        <v>119.88</v>
+        <v>120.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03682553800229193</v>
+        <v>0.03654275152476121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2249,16 +2249,16 @@
         <v>295</v>
       </c>
       <c r="H12" t="n">
-        <v>95370.55</v>
+        <v>93957.5</v>
       </c>
       <c r="I12" t="n">
-        <v>323.29</v>
+        <v>318.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03674789861648445</v>
+        <v>0.03647315665518889</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         <v>804</v>
       </c>
       <c r="H13" t="n">
-        <v>95169.48</v>
+        <v>93778.56</v>
       </c>
       <c r="I13" t="n">
-        <v>118.37</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03641491457736906</v>
+        <v>0.03571084119661887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2319,16 +2319,16 @@
         <v>1082</v>
       </c>
       <c r="H14" t="n">
-        <v>94307.12</v>
+        <v>91818.52</v>
       </c>
       <c r="I14" t="n">
-        <v>87.16</v>
+        <v>84.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2337,33 +2337,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0335563395047127</v>
+        <v>0.03350315067494616</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Allison Transmission</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>710</v>
+        <v>1798</v>
       </c>
       <c r="H15" t="n">
-        <v>86904</v>
+        <v>86142.17999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>122.4</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,33 +2372,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03294281575621968</v>
+        <v>0.03276116062089078</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Allison Transmission</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1798</v>
+        <v>710</v>
       </c>
       <c r="H16" t="n">
-        <v>85315.10000000001</v>
+        <v>84234.39999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>47.45</v>
+        <v>118.64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03203087442714552</v>
+        <v>0.0324689586229603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
         <v>327</v>
       </c>
       <c r="H17" t="n">
-        <v>82953.36</v>
+        <v>83483.10000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>253.68</v>
+        <v>255.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0311251806997144</v>
+        <v>0.03151701717462456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
         <v>910</v>
       </c>
       <c r="H18" t="n">
-        <v>80607.8</v>
+        <v>81035.5</v>
       </c>
       <c r="I18" t="n">
-        <v>88.58</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03111687888047304</v>
+        <v>0.03118845035996774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,16 +2494,16 @@
         <v>215</v>
       </c>
       <c r="H19" t="n">
-        <v>80586.3</v>
+        <v>80190.7</v>
       </c>
       <c r="I19" t="n">
-        <v>374.82</v>
+        <v>372.98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03042631424942017</v>
+        <v>0.03010866810673415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,16 +2529,16 @@
         <v>756</v>
       </c>
       <c r="H20" t="n">
-        <v>78797.88</v>
+        <v>77414.39999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>104.23</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02999177772377091</v>
+        <v>0.02983763548820918</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2564,16 +2564,16 @@
         <v>1179</v>
       </c>
       <c r="H21" t="n">
-        <v>77672.52</v>
+        <v>76717.53</v>
       </c>
       <c r="I21" t="n">
-        <v>65.88</v>
+        <v>65.06999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02904723920491277</v>
+        <v>0.02904445077291648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2599,16 +2599,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>75226.36</v>
+        <v>74678.12</v>
       </c>
       <c r="I22" t="n">
-        <v>76.84</v>
+        <v>76.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02617073220269506</v>
+        <v>0.02657987296303257</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>67776.8</v>
+        <v>68341.28</v>
       </c>
       <c r="I23" t="n">
-        <v>86.45</v>
+        <v>87.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02528714834362489</v>
+        <v>0.02545809420808658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2669,16 +2669,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>65488.5</v>
+        <v>65457</v>
       </c>
       <c r="I24" t="n">
-        <v>20.79</v>
+        <v>20.78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02406569202536512</v>
+        <v>0.02446342118313347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2704,16 +2704,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>62325.18</v>
+        <v>62899.53</v>
       </c>
       <c r="I25" t="n">
-        <v>37.98</v>
+        <v>38.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02292533868912653</v>
+        <v>0.02275784127153428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2739,16 +2739,16 @@
         <v>953</v>
       </c>
       <c r="H26" t="n">
-        <v>59371.9</v>
+        <v>58514.2</v>
       </c>
       <c r="I26" t="n">
-        <v>62.3</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02241685032993747</v>
+        <v>0.02244478492630042</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2774,16 +2774,16 @@
         <v>586</v>
       </c>
       <c r="H27" t="n">
-        <v>58055.02</v>
+        <v>57709.28</v>
       </c>
       <c r="I27" t="n">
-        <v>99.06999999999999</v>
+        <v>98.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02116827216128173</v>
+        <v>0.0209341165430692</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>54821.46</v>
+        <v>53825.1</v>
       </c>
       <c r="I28" t="n">
-        <v>75.93000000000001</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01575459791432044</v>
+        <v>0.01579094133668992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>40801.16</v>
+        <v>40601.14</v>
       </c>
       <c r="I29" t="n">
-        <v>279.46</v>
+        <v>278.09</v>
       </c>
     </row>
   </sheetData>
@@ -2914,7 +2914,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09262381986830845</v>
+        <v>0.09340434336698515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03775972218417706</v>
+        <v>0.03771387205400041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>411</v>
       </c>
       <c r="H3" t="n">
-        <v>113061.99</v>
+        <v>111981.06</v>
       </c>
       <c r="I3" t="n">
-        <v>275.09</v>
+        <v>272.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03475164181932985</v>
+        <v>0.03510979054907934</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3010,16 +3010,16 @@
         <v>277</v>
       </c>
       <c r="H4" t="n">
-        <v>104055.05</v>
+        <v>104248.95</v>
       </c>
       <c r="I4" t="n">
-        <v>375.65</v>
+        <v>376.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03466058391159697</v>
+        <v>0.03436638165941177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>103782.4</v>
+        <v>102041.6</v>
       </c>
       <c r="I5" t="n">
-        <v>162.16</v>
+        <v>159.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03440102295318539</v>
+        <v>0.03369847052533202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>103005.21</v>
+        <v>100058.42</v>
       </c>
       <c r="I6" t="n">
-        <v>217.77</v>
+        <v>211.54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3098,33 +3098,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03127127265851545</v>
+        <v>0.03069568933714587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>553</v>
+        <v>341</v>
       </c>
       <c r="H7" t="n">
-        <v>93633.96000000001</v>
+        <v>91142.48</v>
       </c>
       <c r="I7" t="n">
-        <v>169.32</v>
+        <v>267.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3133,33 +3133,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03080527926530185</v>
+        <v>0.03041732735762833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>838</v>
+        <v>553</v>
       </c>
       <c r="H8" t="n">
-        <v>92238.66</v>
+        <v>90315.96000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>110.07</v>
+        <v>163.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3168,33 +3168,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03043007326118822</v>
+        <v>0.030407277605089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>341</v>
+        <v>838</v>
       </c>
       <c r="H9" t="n">
-        <v>91115.2</v>
+        <v>90286.12</v>
       </c>
       <c r="I9" t="n">
-        <v>267.2</v>
+        <v>107.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02693960807781463</v>
+        <v>0.02737631400093466</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3220,16 +3220,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>80663.88</v>
+        <v>81286.5</v>
       </c>
       <c r="I10" t="n">
-        <v>69.95999999999999</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02571655326158204</v>
+        <v>0.02599514660268486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>77001.75</v>
+        <v>77185.5</v>
       </c>
       <c r="I11" t="n">
-        <v>146.67</v>
+        <v>147.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02463486947906788</v>
+        <v>0.02481545586199539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>73762.92</v>
+        <v>73682.73</v>
       </c>
       <c r="I12" t="n">
-        <v>248.36</v>
+        <v>248.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02401536177128067</v>
+        <v>0.02397245877440964</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3325,16 +3325,16 @@
         <v>204</v>
       </c>
       <c r="H13" t="n">
-        <v>71907.96000000001</v>
+        <v>71179.67999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>352.49</v>
+        <v>348.92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02340952026405985</v>
+        <v>0.02328292585370038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
         <v>141</v>
       </c>
       <c r="H14" t="n">
-        <v>70093.92</v>
+        <v>69132.3</v>
       </c>
       <c r="I14" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02331434780131773</v>
+        <v>0.02326448671323362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3395,16 +3395,16 @@
         <v>265</v>
       </c>
       <c r="H15" t="n">
-        <v>69808.95</v>
+        <v>69077.55</v>
       </c>
       <c r="I15" t="n">
-        <v>263.43</v>
+        <v>260.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3413,33 +3413,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02219376945091591</v>
+        <v>0.02280912582463288</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>234</v>
+        <v>426</v>
       </c>
       <c r="H16" t="n">
-        <v>66453.66</v>
+        <v>67725.48</v>
       </c>
       <c r="I16" t="n">
-        <v>283.99</v>
+        <v>158.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02211487820219168</v>
+        <v>0.02230123611888876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3483,33 +3483,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0219199645175738</v>
+        <v>0.02218759039178185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>426</v>
+        <v>183</v>
       </c>
       <c r="H18" t="n">
-        <v>65633.82000000001</v>
+        <v>65880</v>
       </c>
       <c r="I18" t="n">
-        <v>154.07</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3518,33 +3518,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02191661810189259</v>
+        <v>0.02213885043911794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="H19" t="n">
-        <v>65623.8</v>
+        <v>65735.28</v>
       </c>
       <c r="I19" t="n">
-        <v>358.6</v>
+        <v>280.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02183067333029538</v>
+        <v>0.02210294210749117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3570,16 +3570,16 @@
         <v>1311</v>
       </c>
       <c r="H20" t="n">
-        <v>65366.46</v>
+        <v>65628.66</v>
       </c>
       <c r="I20" t="n">
-        <v>49.86</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02165097548384479</v>
+        <v>0.02154181969778036</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3605,16 +3605,16 @@
         <v>548</v>
       </c>
       <c r="H21" t="n">
-        <v>64828.4</v>
+        <v>63962.56</v>
       </c>
       <c r="I21" t="n">
-        <v>118.3</v>
+        <v>116.72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3623,33 +3623,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02058858201767264</v>
+        <v>0.02045838632214669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1201</v>
+        <v>656</v>
       </c>
       <c r="H22" t="n">
-        <v>61647.33</v>
+        <v>60745.6</v>
       </c>
       <c r="I22" t="n">
-        <v>51.33</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3658,33 +3658,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02053937768410842</v>
+        <v>0.01959312418293979</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>656</v>
+        <v>1201</v>
       </c>
       <c r="H23" t="n">
-        <v>61500</v>
+        <v>58176.44</v>
       </c>
       <c r="I23" t="n">
-        <v>93.75</v>
+        <v>48.44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01980366719467228</v>
+        <v>0.01943990587126953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         <v>1010</v>
       </c>
       <c r="H24" t="n">
-        <v>59297.1</v>
+        <v>57721.5</v>
       </c>
       <c r="I24" t="n">
-        <v>58.71</v>
+        <v>57.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01801086340042736</v>
+        <v>0.01800714929426724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3745,16 +3745,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>53929</v>
+        <v>53467.32</v>
       </c>
       <c r="I25" t="n">
-        <v>135.5</v>
+        <v>134.34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01670883384206533</v>
+        <v>0.01655380150177386</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3780,16 +3780,16 @@
         <v>480</v>
       </c>
       <c r="H26" t="n">
-        <v>50030.4</v>
+        <v>49152</v>
       </c>
       <c r="I26" t="n">
-        <v>104.23</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3798,33 +3798,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01600969346411553</v>
+        <v>0.01618990885352685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1740</v>
+        <v>399</v>
       </c>
       <c r="H27" t="n">
-        <v>47937</v>
+        <v>48071.52</v>
       </c>
       <c r="I27" t="n">
-        <v>27.55</v>
+        <v>120.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3833,33 +3833,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01597466631075766</v>
+        <v>0.01609186314443676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>399</v>
+        <v>1740</v>
       </c>
       <c r="H28" t="n">
-        <v>47832.12</v>
+        <v>47780.4</v>
       </c>
       <c r="I28" t="n">
-        <v>119.88</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0159454903752376</v>
+        <v>0.01607300975478691</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,16 +3885,16 @@
         <v>678</v>
       </c>
       <c r="H29" t="n">
-        <v>47744.76</v>
+        <v>47724.42</v>
       </c>
       <c r="I29" t="n">
-        <v>70.42</v>
+        <v>70.39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3903,33 +3903,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01577394148513647</v>
+        <v>0.01587734268942842</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>918</v>
+        <v>984</v>
       </c>
       <c r="H30" t="n">
-        <v>47231.1</v>
+        <v>47143.44</v>
       </c>
       <c r="I30" t="n">
-        <v>51.45</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3938,33 +3938,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01559349553777511</v>
+        <v>0.0153843659542755</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>984</v>
+        <v>918</v>
       </c>
       <c r="H31" t="n">
-        <v>46690.8</v>
+        <v>45679.68</v>
       </c>
       <c r="I31" t="n">
-        <v>47.45</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01432169727157512</v>
+        <v>0.01406127427076702</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,16 +3990,16 @@
         <v>492</v>
       </c>
       <c r="H32" t="n">
-        <v>42882.72</v>
+        <v>41751.12</v>
       </c>
       <c r="I32" t="n">
-        <v>87.16</v>
+        <v>84.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01367823029622598</v>
+        <v>0.01359189963541155</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4025,16 +4025,16 @@
         <v>346</v>
       </c>
       <c r="H33" t="n">
-        <v>40956.02</v>
+        <v>40357.44</v>
       </c>
       <c r="I33" t="n">
-        <v>118.37</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4043,33 +4043,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01306441015920235</v>
+        <v>0.01315524058188148</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="H34" t="n">
-        <v>39118.09</v>
+        <v>39060.9</v>
       </c>
       <c r="I34" t="n">
-        <v>323.29</v>
+        <v>255.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4078,33 +4078,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01296253150615297</v>
+        <v>0.01297930255485254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="H35" t="n">
-        <v>38813.04</v>
+        <v>38538.5</v>
       </c>
       <c r="I35" t="n">
-        <v>253.68</v>
+        <v>318.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01292408446291728</v>
+        <v>0.01295701392807463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4130,16 +4130,16 @@
         <v>376</v>
       </c>
       <c r="H36" t="n">
-        <v>38697.92</v>
+        <v>38472.32</v>
       </c>
       <c r="I36" t="n">
-        <v>102.92</v>
+        <v>102.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4148,33 +4148,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01267229507066358</v>
+        <v>0.01256651166360337</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Allison Transmission</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>310</v>
+        <v>141</v>
       </c>
       <c r="H37" t="n">
-        <v>37944</v>
+        <v>37312.83</v>
       </c>
       <c r="I37" t="n">
-        <v>122.4</v>
+        <v>264.63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4183,33 +4183,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01247562802453608</v>
+        <v>0.01238652207749104</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Allison Transmission</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>141</v>
+        <v>310</v>
       </c>
       <c r="H38" t="n">
-        <v>37355.13</v>
+        <v>36778.4</v>
       </c>
       <c r="I38" t="n">
-        <v>264.93</v>
+        <v>118.64</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0119074153251798</v>
+        <v>0.01192024589130989</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4235,16 +4235,16 @@
         <v>464</v>
       </c>
       <c r="H39" t="n">
-        <v>35653.76</v>
+        <v>35393.92</v>
       </c>
       <c r="I39" t="n">
-        <v>76.84</v>
+        <v>76.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.01183458235793833</v>
+        <v>0.01181671727433306</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4270,16 +4270,16 @@
         <v>116</v>
       </c>
       <c r="H40" t="n">
-        <v>35435.68</v>
+        <v>35086.52</v>
       </c>
       <c r="I40" t="n">
-        <v>305.48</v>
+        <v>302.47</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01151993579049883</v>
+        <v>0.01171376456475711</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4305,16 +4305,16 @@
         <v>399</v>
       </c>
       <c r="H41" t="n">
-        <v>34493.55</v>
+        <v>34780.83</v>
       </c>
       <c r="I41" t="n">
-        <v>86.45</v>
+        <v>87.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01127126905160035</v>
+        <v>0.0114265585335746</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4340,16 +4340,16 @@
         <v>381</v>
       </c>
       <c r="H42" t="n">
-        <v>33748.98</v>
+        <v>33928.05</v>
       </c>
       <c r="I42" t="n">
-        <v>88.58</v>
+        <v>89.05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01126619933203539</v>
+        <v>0.01130536538842458</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4375,16 +4375,16 @@
         <v>90</v>
       </c>
       <c r="H43" t="n">
-        <v>33733.8</v>
+        <v>33568.2</v>
       </c>
       <c r="I43" t="n">
-        <v>374.82</v>
+        <v>372.98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.01084707579677606</v>
+        <v>0.01080399252958515</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4410,16 +4410,16 @@
         <v>493</v>
       </c>
       <c r="H44" t="n">
-        <v>32478.84</v>
+        <v>32079.51</v>
       </c>
       <c r="I44" t="n">
-        <v>65.88</v>
+        <v>65.06999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4428,33 +4428,33 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.009005475116784397</v>
+        <v>0.009100902997882271</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hormel Foods</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1297</v>
+        <v>705</v>
       </c>
       <c r="H45" t="n">
-        <v>26964.63</v>
+        <v>27022.65</v>
       </c>
       <c r="I45" t="n">
-        <v>20.79</v>
+        <v>38.33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4463,33 +4463,33 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.008967625886330087</v>
+        <v>0.009076994421046924</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Amdocs Ltd</t>
+          <t>Hormel Foods</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>431</v>
+        <v>1297</v>
       </c>
       <c r="H46" t="n">
-        <v>26851.3</v>
+        <v>26951.66</v>
       </c>
       <c r="I46" t="n">
-        <v>62.3</v>
+        <v>20.78</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,33 +4498,33 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.00894244427531575</v>
+        <v>0.008912554334758347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Amdocs Ltd</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>705</v>
+        <v>431</v>
       </c>
       <c r="H47" t="n">
-        <v>26775.9</v>
+        <v>26463.4</v>
       </c>
       <c r="I47" t="n">
-        <v>37.98</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008875515961691435</v>
+        <v>0.008787639682719612</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4550,16 +4550,16 @@
         <v>350</v>
       </c>
       <c r="H48" t="n">
-        <v>26575.5</v>
+        <v>26092.5</v>
       </c>
       <c r="I48" t="n">
-        <v>75.93000000000001</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.008503299021484678</v>
+        <v>0.008523887564634913</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4585,16 +4585,16 @@
         <v>257</v>
       </c>
       <c r="H49" t="n">
-        <v>25460.99</v>
+        <v>25309.36</v>
       </c>
       <c r="I49" t="n">
-        <v>99.06999999999999</v>
+        <v>98.48</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.00758452089176327</v>
+        <v>0.007555521161272885</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4620,16 +4620,16 @@
         <v>627</v>
       </c>
       <c r="H50" t="n">
-        <v>22709.94</v>
+        <v>22434.06</v>
       </c>
       <c r="I50" t="n">
-        <v>36.22</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.006066597425919692</v>
+        <v>0.006087728533443989</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4655,10 +4655,10 @@
         <v>65</v>
       </c>
       <c r="H51" t="n">
-        <v>18164.9</v>
+        <v>18075.85</v>
       </c>
       <c r="I51" t="n">
-        <v>279.46</v>
+        <v>278.09</v>
       </c>
     </row>
   </sheetData>
@@ -4725,7 +4725,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07036331314009088</v>
+        <v>0.07093228165761697</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05435325142955147</v>
+        <v>0.05399195355672864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4786,16 +4786,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>120500.66</v>
+        <v>118739.52</v>
       </c>
       <c r="I3" t="n">
-        <v>118.37</v>
+        <v>116.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04170712785492216</v>
+        <v>0.04146757034362876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4821,16 +4821,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>92464.32000000001</v>
+        <v>91195.8</v>
       </c>
       <c r="I4" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04039318917706123</v>
+        <v>0.04011649286240677</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4856,16 +4856,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>89551.33</v>
+        <v>88224.5</v>
       </c>
       <c r="I5" t="n">
-        <v>323.29</v>
+        <v>318.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03857679014396284</v>
+        <v>0.03806551786809404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4891,16 +4891,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>85524.39</v>
+        <v>83713.98</v>
       </c>
       <c r="I6" t="n">
-        <v>110.07</v>
+        <v>107.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03477005811521557</v>
+        <v>0.03493670925215477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4926,16 +4926,16 @@
         <v>2798</v>
       </c>
       <c r="H7" t="n">
-        <v>77084.89999999999</v>
+        <v>76833.08</v>
       </c>
       <c r="I7" t="n">
-        <v>27.55</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03450623203524933</v>
+        <v>0.03435855558344945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4961,16 +4961,16 @@
         <v>816</v>
       </c>
       <c r="H8" t="n">
-        <v>76500</v>
+        <v>75561.60000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>93.75</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03394379398493046</v>
+        <v>0.0341810689367812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4996,16 +4996,16 @@
         <v>303</v>
       </c>
       <c r="H9" t="n">
-        <v>75253.08</v>
+        <v>75171.27</v>
       </c>
       <c r="I9" t="n">
-        <v>248.36</v>
+        <v>248.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03389643248998012</v>
+        <v>0.03383383024713855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>246</v>
       </c>
       <c r="H10" t="n">
-        <v>75148.08</v>
+        <v>74407.62</v>
       </c>
       <c r="I10" t="n">
-        <v>305.48</v>
+        <v>302.47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03206366893272174</v>
+        <v>0.03175543628735022</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5066,16 +5066,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>71084.86</v>
+        <v>69836.8</v>
       </c>
       <c r="I11" t="n">
-        <v>104.23</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5084,33 +5084,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03137604317470271</v>
+        <v>0.03125545622634916</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>588</v>
+        <v>197</v>
       </c>
       <c r="H12" t="n">
-        <v>69560.39999999999</v>
+        <v>68737.24000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>118.3</v>
+        <v>348.92</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5119,33 +5119,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03132197438994368</v>
+        <v>0.03120731161499662</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>197</v>
+        <v>588</v>
       </c>
       <c r="H13" t="n">
-        <v>69440.53</v>
+        <v>68631.36</v>
       </c>
       <c r="I13" t="n">
-        <v>352.49</v>
+        <v>116.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03071363177447152</v>
+        <v>0.03111695180041431</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5171,16 +5171,16 @@
         <v>568</v>
       </c>
       <c r="H14" t="n">
-        <v>68091.84</v>
+        <v>68432.64</v>
       </c>
       <c r="I14" t="n">
-        <v>119.88</v>
+        <v>120.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5189,33 +5189,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03040023850707583</v>
+        <v>0.03054983847137313</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>245</v>
+        <v>1076</v>
       </c>
       <c r="H15" t="n">
-        <v>67397.05</v>
+        <v>67185.44</v>
       </c>
       <c r="I15" t="n">
-        <v>275.09</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5224,33 +5224,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0303047893075859</v>
+        <v>0.03035306760702957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1076</v>
+        <v>245</v>
       </c>
       <c r="H16" t="n">
-        <v>67185.44</v>
+        <v>66752.7</v>
       </c>
       <c r="I16" t="n">
-        <v>62.44</v>
+        <v>272.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02931091961259939</v>
+        <v>0.02954793219394421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02865335261670884</v>
+        <v>0.02811753523780406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5311,16 +5311,16 @@
         <v>1082</v>
       </c>
       <c r="H18" t="n">
-        <v>63524.22</v>
+        <v>61836.3</v>
       </c>
       <c r="I18" t="n">
-        <v>58.71</v>
+        <v>57.15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0274901858750584</v>
+        <v>0.02717816511828328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5346,16 +5346,16 @@
         <v>1433</v>
       </c>
       <c r="H19" t="n">
-        <v>60945.49</v>
+        <v>59770.43</v>
       </c>
       <c r="I19" t="n">
-        <v>42.53</v>
+        <v>41.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02567155408576949</v>
+        <v>0.025886886445514</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
         <v>213</v>
       </c>
       <c r="H20" t="n">
-        <v>56913.6</v>
+        <v>56930.64</v>
       </c>
       <c r="I20" t="n">
-        <v>267.2</v>
+        <v>267.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0254374259184464</v>
+        <v>0.02533160465016561</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5416,16 +5416,16 @@
         <v>1557</v>
       </c>
       <c r="H21" t="n">
-        <v>56394.54</v>
+        <v>55709.46</v>
       </c>
       <c r="I21" t="n">
-        <v>36.22</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5434,33 +5434,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02257641273148613</v>
+        <v>0.02262732619570221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Coca-Cola Femsa</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>190</v>
+        <v>443</v>
       </c>
       <c r="H22" t="n">
-        <v>50051.7</v>
+        <v>49762.19</v>
       </c>
       <c r="I22" t="n">
-        <v>263.43</v>
+        <v>112.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5469,33 +5469,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02255286730256796</v>
+        <v>0.02258913516899745</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>369</v>
+        <v>132</v>
       </c>
       <c r="H23" t="n">
-        <v>49999.5</v>
+        <v>49678.2</v>
       </c>
       <c r="I23" t="n">
-        <v>135.5</v>
+        <v>376.35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5504,33 +5504,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02236626301246361</v>
+        <v>0.02254059950772272</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>132</v>
+        <v>369</v>
       </c>
       <c r="H24" t="n">
-        <v>49585.8</v>
+        <v>49571.46</v>
       </c>
       <c r="I24" t="n">
-        <v>375.65</v>
+        <v>134.34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5539,33 +5539,33 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02227997487928265</v>
+        <v>0.02252051954892665</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola Femsa</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>443</v>
+        <v>190</v>
       </c>
       <c r="H25" t="n">
-        <v>49394.5</v>
+        <v>49527.3</v>
       </c>
       <c r="I25" t="n">
-        <v>111.5</v>
+        <v>260.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02225564009211531</v>
+        <v>0.02169865083684456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5591,16 +5591,16 @@
         <v>959</v>
       </c>
       <c r="H26" t="n">
-        <v>49340.55</v>
+        <v>47719.84</v>
       </c>
       <c r="I26" t="n">
-        <v>51.45</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02070953987662637</v>
+        <v>0.02154232180980451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5626,16 +5626,16 @@
         <v>298</v>
       </c>
       <c r="H27" t="n">
-        <v>45912.86</v>
+        <v>47376.04</v>
       </c>
       <c r="I27" t="n">
-        <v>154.07</v>
+        <v>158.98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02036743201143507</v>
+        <v>0.02031016897585435</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5661,16 +5661,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>45154.41</v>
+        <v>44666.28</v>
       </c>
       <c r="I28" t="n">
-        <v>283.99</v>
+        <v>280.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0190900293439644</v>
+        <v>0.01923619583543655</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5696,16 +5696,16 @@
         <v>601</v>
       </c>
       <c r="H29" t="n">
-        <v>42322.42</v>
+        <v>42304.39</v>
       </c>
       <c r="I29" t="n">
-        <v>70.42</v>
+        <v>70.39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5714,33 +5714,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01902824289083776</v>
+        <v>0.01885208022871146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>484</v>
+        <v>282</v>
       </c>
       <c r="H30" t="n">
-        <v>42185.44</v>
+        <v>41459.64</v>
       </c>
       <c r="I30" t="n">
-        <v>87.16</v>
+        <v>147.02</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5749,33 +5749,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0186563423900134</v>
+        <v>0.01867592588003398</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>282</v>
+        <v>484</v>
       </c>
       <c r="H31" t="n">
-        <v>41360.94</v>
+        <v>41072.24</v>
       </c>
       <c r="I31" t="n">
-        <v>146.67</v>
+        <v>84.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01799347090668841</v>
+        <v>0.01783471383807905</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5801,16 +5801,16 @@
         <v>246</v>
       </c>
       <c r="H32" t="n">
-        <v>39891.36</v>
+        <v>39222.24</v>
       </c>
       <c r="I32" t="n">
-        <v>162.16</v>
+        <v>159.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01693495502640396</v>
+        <v>0.01718091474488745</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5836,16 +5836,16 @@
         <v>148</v>
       </c>
       <c r="H33" t="n">
-        <v>37544.64</v>
+        <v>37784.4</v>
       </c>
       <c r="I33" t="n">
-        <v>253.68</v>
+        <v>255.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01675880635013723</v>
+        <v>0.01679583060754107</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5871,16 +5871,16 @@
         <v>361</v>
       </c>
       <c r="H34" t="n">
-        <v>37154.12</v>
+        <v>36937.52</v>
       </c>
       <c r="I34" t="n">
-        <v>102.92</v>
+        <v>102.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5889,33 +5889,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01662345170818771</v>
+        <v>0.01675337895552112</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>372</v>
+        <v>736</v>
       </c>
       <c r="H35" t="n">
-        <v>36854.04</v>
+        <v>36844.16</v>
       </c>
       <c r="I35" t="n">
-        <v>99.06999999999999</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5924,27 +5924,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.016552598911742</v>
+        <v>0.01665807190471369</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>736</v>
+        <v>372</v>
       </c>
       <c r="H36" t="n">
-        <v>36696.96</v>
+        <v>36634.56</v>
       </c>
       <c r="I36" t="n">
-        <v>49.86</v>
+        <v>98.48</v>
       </c>
     </row>
   </sheetData>
@@ -6011,7 +6011,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1052041493891977</v>
+        <v>0.1058138565722073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6037,16 +6037,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>222698.5</v>
+        <v>221776.7</v>
       </c>
       <c r="I2" t="n">
-        <v>53.15</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0990545073597105</v>
+        <v>0.09925714542458786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6072,16 +6072,16 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>209680.8</v>
+        <v>208034.4</v>
       </c>
       <c r="I3" t="n">
-        <v>213.96</v>
+        <v>212.28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09368570551785546</v>
+        <v>0.09445618414068302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6107,16 +6107,16 @@
         <v>4300</v>
       </c>
       <c r="H4" t="n">
-        <v>198316</v>
+        <v>197972</v>
       </c>
       <c r="I4" t="n">
-        <v>46.12</v>
+        <v>46.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08811310764663112</v>
+        <v>0.08547165343777366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6142,16 +6142,16 @@
         <v>934</v>
       </c>
       <c r="H5" t="n">
-        <v>186519.8</v>
+        <v>179141.2</v>
       </c>
       <c r="I5" t="n">
-        <v>199.7</v>
+        <v>191.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05488686722135973</v>
+        <v>0.05514588032228943</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1475</v>
       </c>
       <c r="H6" t="n">
-        <v>116185.75</v>
+        <v>115581</v>
       </c>
       <c r="I6" t="n">
-        <v>78.77</v>
+        <v>78.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03760850225318856</v>
+        <v>0.03779002167737269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6212,16 +6212,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>79610.52</v>
+        <v>79204.62</v>
       </c>
       <c r="I7" t="n">
-        <v>29.42</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02608652950762427</v>
+        <v>0.02639586396307493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6247,16 +6247,16 @@
         <v>147</v>
       </c>
       <c r="H8" t="n">
-        <v>55220.55</v>
+        <v>55323.45</v>
       </c>
       <c r="I8" t="n">
-        <v>375.65</v>
+        <v>376.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02465846922254792</v>
+        <v>0.0245627969805759</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6282,16 +6282,16 @@
         <v>105</v>
       </c>
       <c r="H9" t="n">
-        <v>52197.6</v>
+        <v>51481.5</v>
       </c>
       <c r="I9" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02320854597910529</v>
+        <v>0.02351550666742898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6317,16 +6317,16 @@
         <v>1860</v>
       </c>
       <c r="H10" t="n">
-        <v>49128.37</v>
+        <v>49286.47</v>
       </c>
       <c r="I10" t="n">
-        <v>26.41</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02106648153383109</v>
+        <v>0.02091975557064831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6352,16 +6352,16 @@
         <v>275</v>
       </c>
       <c r="H11" t="n">
-        <v>44594</v>
+        <v>43846</v>
       </c>
       <c r="I11" t="n">
-        <v>162.16</v>
+        <v>159.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6370,33 +6370,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02078093088962022</v>
+        <v>0.02053933912418594</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="H12" t="n">
-        <v>43989.54</v>
+        <v>43048.68</v>
       </c>
       <c r="I12" t="n">
-        <v>217.77</v>
+        <v>272.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6405,33 +6405,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02053276647110311</v>
+        <v>0.02038780615950871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="H13" t="n">
-        <v>43464.22</v>
+        <v>42731.08</v>
       </c>
       <c r="I13" t="n">
-        <v>275.09</v>
+        <v>211.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02007849123289701</v>
+        <v>0.02015254836913387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6457,16 +6457,16 @@
         <v>980</v>
       </c>
       <c r="H14" t="n">
-        <v>42502.6</v>
+        <v>42238</v>
       </c>
       <c r="I14" t="n">
-        <v>43.37</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.01994385546940547</v>
+        <v>0.02014884592642009</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6492,16 +6492,16 @@
         <v>158</v>
       </c>
       <c r="H15" t="n">
-        <v>42217.6</v>
+        <v>42230.24</v>
       </c>
       <c r="I15" t="n">
-        <v>267.2</v>
+        <v>267.28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6510,33 +6510,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.017917270716712</v>
+        <v>0.017925195093563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>37927.68</v>
+        <v>37569.66</v>
       </c>
       <c r="I16" t="n">
-        <v>169.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6545,33 +6545,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01774799340747717</v>
+        <v>0.01745476539421647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="H17" t="n">
-        <v>37569.35</v>
+        <v>36583.68</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>163.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01654014999085422</v>
+        <v>0.01681788799317819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6597,16 +6597,16 @@
         <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>35012.56</v>
+        <v>35248.84</v>
       </c>
       <c r="I18" t="n">
-        <v>1591.48</v>
+        <v>1602.22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01648532725277284</v>
+        <v>0.01648115655378713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6632,16 +6632,16 @@
         <v>99</v>
       </c>
       <c r="H19" t="n">
-        <v>34896.51</v>
+        <v>34543.08</v>
       </c>
       <c r="I19" t="n">
-        <v>352.49</v>
+        <v>348.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01612817400269385</v>
+        <v>0.016414798856283</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6667,16 +6667,16 @@
         <v>488</v>
       </c>
       <c r="H20" t="n">
-        <v>34140.48</v>
+        <v>34404</v>
       </c>
       <c r="I20" t="n">
-        <v>69.95999999999999</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01591131121817305</v>
+        <v>0.01572986603899066</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>306</v>
       </c>
       <c r="H21" t="n">
-        <v>33681.42</v>
+        <v>32968.44</v>
       </c>
       <c r="I21" t="n">
-        <v>110.07</v>
+        <v>107.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01478317689759897</v>
+        <v>0.01491442211603771</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6737,16 +6737,16 @@
         <v>126</v>
       </c>
       <c r="H22" t="n">
-        <v>31293.36</v>
+        <v>31259.34</v>
       </c>
       <c r="I22" t="n">
-        <v>248.36</v>
+        <v>248.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01423000814806193</v>
+        <v>0.0144280757299732</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>84</v>
       </c>
       <c r="H23" t="n">
-        <v>30122.4</v>
+        <v>30240</v>
       </c>
       <c r="I23" t="n">
-        <v>358.6</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01392685092523587</v>
+        <v>0.01409935034583177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6807,16 +6807,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>29480.67</v>
+        <v>29551.02</v>
       </c>
       <c r="I24" t="n">
-        <v>146.67</v>
+        <v>147.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01316832248184827</v>
+        <v>0.01339869168938401</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6842,16 +6842,16 @@
         <v>250</v>
       </c>
       <c r="H25" t="n">
-        <v>27875</v>
+        <v>28082.5</v>
       </c>
       <c r="I25" t="n">
-        <v>111.5</v>
+        <v>112.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.012817934088377</v>
+        <v>0.01281017028951084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6877,16 +6877,16 @@
         <v>103</v>
       </c>
       <c r="H26" t="n">
-        <v>27133.29</v>
+        <v>26849.01</v>
       </c>
       <c r="I26" t="n">
-        <v>263.43</v>
+        <v>260.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01221177553676681</v>
+        <v>0.01233360006983876</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01174581296947727</v>
+        <v>0.01197799380650993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6947,16 +6947,16 @@
         <v>524</v>
       </c>
       <c r="H28" t="n">
-        <v>24863.8</v>
+        <v>25104.84</v>
       </c>
       <c r="I28" t="n">
-        <v>47.45</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01139353022719337</v>
+        <v>0.01122544369780054</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6982,16 +6982,16 @@
         <v>259</v>
       </c>
       <c r="H29" t="n">
-        <v>24118.08</v>
+        <v>23527.56</v>
       </c>
       <c r="I29" t="n">
-        <v>93.12</v>
+        <v>90.84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0111771304007365</v>
+        <v>0.0111378637513391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>23660</v>
+        <v>23344</v>
       </c>
       <c r="I30" t="n">
-        <v>118.3</v>
+        <v>116.72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01107202002397556</v>
+        <v>0.0110453026834947</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7052,16 +7052,16 @@
         <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>23437.5</v>
+        <v>23150</v>
       </c>
       <c r="I31" t="n">
-        <v>93.75</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.00954343170215886</v>
+        <v>0.00945279905360984</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7087,16 +7087,16 @@
         <v>475</v>
       </c>
       <c r="H32" t="n">
-        <v>20201.75</v>
+        <v>19812.25</v>
       </c>
       <c r="I32" t="n">
-        <v>42.53</v>
+        <v>41.71</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.009163097480449946</v>
+        <v>0.008950521667260148</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7122,16 +7122,16 @@
         <v>377</v>
       </c>
       <c r="H33" t="n">
-        <v>19396.65</v>
+        <v>18759.52</v>
       </c>
       <c r="I33" t="n">
-        <v>51.45</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7140,33 +7140,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.008777996680307239</v>
+        <v>0.008640928751265934</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>362</v>
+        <v>177</v>
       </c>
       <c r="H34" t="n">
-        <v>18581.46</v>
+        <v>18110.64</v>
       </c>
       <c r="I34" t="n">
-        <v>51.33</v>
+        <v>102.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.008616806965005663</v>
+        <v>0.008549970802947083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -7192,16 +7192,16 @@
         <v>175</v>
       </c>
       <c r="H35" t="n">
-        <v>18240.25</v>
+        <v>17920</v>
       </c>
       <c r="I35" t="n">
-        <v>104.23</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7210,33 +7210,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.008605747936151849</v>
+        <v>0.008516095360591655</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>177</v>
+        <v>650</v>
       </c>
       <c r="H36" t="n">
-        <v>18216.84</v>
+        <v>17849</v>
       </c>
       <c r="I36" t="n">
-        <v>102.92</v>
+        <v>27.46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7245,33 +7245,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.008459613806051942</v>
+        <v>0.00846069231317881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>650</v>
+        <v>132</v>
       </c>
       <c r="H37" t="n">
-        <v>17907.5</v>
+        <v>17732.88</v>
       </c>
       <c r="I37" t="n">
-        <v>27.55</v>
+        <v>134.34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7280,33 +7280,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008449457073016614</v>
+        <v>0.008366413617271312</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>132</v>
+        <v>362</v>
       </c>
       <c r="H38" t="n">
-        <v>17886</v>
+        <v>17535.28</v>
       </c>
       <c r="I38" t="n">
-        <v>135.5</v>
+        <v>48.44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008126189518780604</v>
+        <v>0.008240177497012176</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7332,16 +7332,16 @@
         <v>345</v>
       </c>
       <c r="H39" t="n">
-        <v>17201.7</v>
+        <v>17270.7</v>
       </c>
       <c r="I39" t="n">
-        <v>49.86</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.007817708278219281</v>
+        <v>0.007892333958290716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7367,16 +7367,16 @@
         <v>235</v>
       </c>
       <c r="H40" t="n">
-        <v>16548.7</v>
+        <v>16541.65</v>
       </c>
       <c r="I40" t="n">
-        <v>70.42</v>
+        <v>70.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.007543911099958128</v>
+        <v>0.007416717976431461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7402,16 +7402,16 @@
         <v>272</v>
       </c>
       <c r="H41" t="n">
-        <v>15969.12</v>
+        <v>15544.8</v>
       </c>
       <c r="I41" t="n">
-        <v>58.71</v>
+        <v>57.15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.007244566195066721</v>
+        <v>0.007237741132257271</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7437,16 +7437,16 @@
         <v>54</v>
       </c>
       <c r="H42" t="n">
-        <v>15335.46</v>
+        <v>15169.68</v>
       </c>
       <c r="I42" t="n">
-        <v>283.99</v>
+        <v>280.92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.007164436657510807</v>
+        <v>0.007044966009309573</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7472,16 +7472,16 @@
         <v>174</v>
       </c>
       <c r="H43" t="n">
-        <v>15165.84</v>
+        <v>14765.64</v>
       </c>
       <c r="I43" t="n">
-        <v>87.16</v>
+        <v>84.86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.006883501421753664</v>
+        <v>0.006944298691245187</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7507,16 +7507,16 @@
         <v>55</v>
       </c>
       <c r="H44" t="n">
-        <v>14571.15</v>
+        <v>14554.65</v>
       </c>
       <c r="I44" t="n">
-        <v>264.93</v>
+        <v>264.63</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.004705401832482499</v>
+        <v>0.004694611479665056</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7542,16 +7542,16 @@
         <v>275</v>
       </c>
       <c r="H45" t="n">
-        <v>9960.5</v>
+        <v>9839.5</v>
       </c>
       <c r="I45" t="n">
-        <v>36.22</v>
+        <v>35.78</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.004185008624247363</v>
+        <v>0.004185110513072249</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7577,16 +7577,16 @@
         <v>29</v>
       </c>
       <c r="H46" t="n">
-        <v>8858.92</v>
+        <v>8771.629999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>305.48</v>
+        <v>302.47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/15/2026</t>
+          <t>09/16/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.002547426746806913</v>
+        <v>0.002654832730961967</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7612,261 +7612,13 @@
         <v>35</v>
       </c>
       <c r="H47" t="n">
-        <v>5392.45</v>
+        <v>5564.3</v>
       </c>
       <c r="I47" t="n">
-        <v>154.07</v>
+        <v>158.98</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28791961-BD52-4D6A-AF4C-2E59F69032A8}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{749F9DBE-E4D1-46EA-BE8E-176D775640B4}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4ED2200-AA92-43C6-BA0C-A03D2E4E84D8}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -7621,4 +7621,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3302FE35-A9BD-4035-A1D5-6E5367E072A9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2CE8377-8E11-461B-9547-CF094DA14367}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0136688B-4610-45AF-859A-5B802095DE51}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09493425818951846</v>
+        <v>0.094626224438046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04331590177290296</v>
+        <v>0.04356884840572453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>101238.15</v>
+        <v>102160.82</v>
       </c>
       <c r="I3" t="n">
-        <v>376.35</v>
+        <v>379.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04056814558317896</v>
+        <v>0.04024209329304373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>94816.08</v>
+        <v>94360.2</v>
       </c>
       <c r="I4" t="n">
-        <v>272.46</v>
+        <v>271.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03882870908235793</v>
+        <v>0.03870821004900343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -613,16 +613,16 @@
         <v>429</v>
       </c>
       <c r="H5" t="n">
-        <v>90750.66</v>
+        <v>90763.53</v>
       </c>
       <c r="I5" t="n">
-        <v>211.54</v>
+        <v>211.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03827042690364052</v>
+        <v>0.0381941009114239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -648,16 +648,16 @@
         <v>561</v>
       </c>
       <c r="H6" t="n">
-        <v>89445.84</v>
+        <v>89558.03999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>159.44</v>
+        <v>159.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03739533043478878</v>
+        <v>0.03768399635687856</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -683,16 +683,16 @@
         <v>327</v>
       </c>
       <c r="H7" t="n">
-        <v>87400.56</v>
+        <v>88361.94</v>
       </c>
       <c r="I7" t="n">
-        <v>267.28</v>
+        <v>270.22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,33 +701,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03305245113310933</v>
+        <v>0.03336050521819559</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>ASML Holding</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>473</v>
+        <v>48</v>
       </c>
       <c r="H8" t="n">
-        <v>77250.36</v>
+        <v>78224.16</v>
       </c>
       <c r="I8" t="n">
-        <v>163.32</v>
+        <v>1629.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,33 +736,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03290535236619662</v>
+        <v>0.0329351195581912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASML Holding</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>48</v>
+        <v>473</v>
       </c>
       <c r="H9" t="n">
-        <v>76906.56</v>
+        <v>77226.71000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>1602.22</v>
+        <v>163.27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0315216227614214</v>
+        <v>0.03178478922124554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -788,16 +788,16 @@
         <v>1045</v>
       </c>
       <c r="H10" t="n">
-        <v>73672.5</v>
+        <v>74529.39999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>70.5</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03093161893471415</v>
+        <v>0.03154666366395439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         <v>671</v>
       </c>
       <c r="H11" t="n">
-        <v>72293.53999999999</v>
+        <v>73971.03999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>107.74</v>
+        <v>110.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03003587387222888</v>
+        <v>0.02960160911055178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         <v>195</v>
       </c>
       <c r="H12" t="n">
-        <v>70200</v>
+        <v>69410.25</v>
       </c>
       <c r="I12" t="n">
-        <v>360</v>
+        <v>355.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02894970479228528</v>
+        <v>0.02929422857573985</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         <v>138</v>
       </c>
       <c r="H13" t="n">
-        <v>67661.39999999999</v>
+        <v>68689.5</v>
       </c>
       <c r="I13" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02791712108048639</v>
+        <v>0.02785764091992292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>187</v>
       </c>
       <c r="H14" t="n">
-        <v>65248.04</v>
+        <v>65320.97</v>
       </c>
       <c r="I14" t="n">
-        <v>348.92</v>
+        <v>349.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02791696277174946</v>
+        <v>0.02756616356949272</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -963,16 +963,16 @@
         <v>263</v>
       </c>
       <c r="H15" t="n">
-        <v>65247.67</v>
+        <v>64637.51</v>
       </c>
       <c r="I15" t="n">
-        <v>248.09</v>
+        <v>245.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02748913127087969</v>
+        <v>0.02749871257346656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -998,16 +998,16 @@
         <v>437</v>
       </c>
       <c r="H16" t="n">
-        <v>64247.74</v>
+        <v>64479.35</v>
       </c>
       <c r="I16" t="n">
-        <v>147.02</v>
+        <v>147.55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02560150067783094</v>
+        <v>0.02566013984029544</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>213</v>
       </c>
       <c r="H17" t="n">
-        <v>59835.96</v>
+        <v>60168.24</v>
       </c>
       <c r="I17" t="n">
-        <v>280.92</v>
+        <v>282.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02498286436281131</v>
+        <v>0.02466011144144727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1068,16 +1068,16 @@
         <v>224</v>
       </c>
       <c r="H18" t="n">
-        <v>58390.08</v>
+        <v>57823.36</v>
       </c>
       <c r="I18" t="n">
-        <v>260.67</v>
+        <v>258.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02424896217284611</v>
+        <v>0.02430999403061244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         <v>1170</v>
       </c>
       <c r="H19" t="n">
-        <v>56674.8</v>
+        <v>57002.4</v>
       </c>
       <c r="I19" t="n">
-        <v>48.44</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,33 +1121,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02401155896804918</v>
+        <v>0.02382857406125121</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>353</v>
+        <v>898</v>
       </c>
       <c r="H20" t="n">
-        <v>56119.94</v>
+        <v>55873.56</v>
       </c>
       <c r="I20" t="n">
-        <v>158.98</v>
+        <v>62.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,33 +1156,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02399067077200299</v>
+        <v>0.0235166387930202</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>898</v>
+        <v>353</v>
       </c>
       <c r="H21" t="n">
-        <v>56071.12</v>
+        <v>55142.13</v>
       </c>
       <c r="I21" t="n">
-        <v>62.44</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02198908356004927</v>
+        <v>0.02195797319326999</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1208,16 +1208,16 @@
         <v>555</v>
       </c>
       <c r="H22" t="n">
-        <v>51393</v>
+        <v>51487.35</v>
       </c>
       <c r="I22" t="n">
-        <v>92.59999999999999</v>
+        <v>92.77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02196418630220561</v>
+        <v>0.02192800065912281</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
         <v>457</v>
       </c>
       <c r="H23" t="n">
-        <v>51334.81</v>
+        <v>51417.07</v>
       </c>
       <c r="I23" t="n">
-        <v>112.33</v>
+        <v>112.51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0216100154287695</v>
+        <v>0.02171773659380428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1278,16 +1278,16 @@
         <v>556</v>
       </c>
       <c r="H24" t="n">
-        <v>50507.04</v>
+        <v>50924.04</v>
       </c>
       <c r="I24" t="n">
-        <v>90.84</v>
+        <v>91.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02127443513538679</v>
+        <v>0.02116725355984722</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         <v>426</v>
       </c>
       <c r="H25" t="n">
-        <v>49722.72</v>
+        <v>49633.26</v>
       </c>
       <c r="I25" t="n">
-        <v>116.72</v>
+        <v>116.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02112677159135853</v>
+        <v>0.02112086180878674</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         <v>864</v>
       </c>
       <c r="H26" t="n">
-        <v>49377.6</v>
+        <v>49524.48</v>
       </c>
       <c r="I26" t="n">
-        <v>57.15</v>
+        <v>57.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,33 +1366,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01958715494546354</v>
+        <v>0.02002186178217055</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>920</v>
+        <v>1087</v>
       </c>
       <c r="H27" t="n">
-        <v>45779.2</v>
+        <v>46947.53</v>
       </c>
       <c r="I27" t="n">
-        <v>49.76</v>
+        <v>43.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,33 +1401,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01939871192652414</v>
+        <v>0.01922552976187559</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1087</v>
+        <v>938</v>
       </c>
       <c r="H28" t="n">
-        <v>45338.77</v>
+        <v>45080.28</v>
       </c>
       <c r="I28" t="n">
-        <v>41.71</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,33 +1436,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01922791391383105</v>
+        <v>0.01896253228950955</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>938</v>
+        <v>920</v>
       </c>
       <c r="H29" t="n">
-        <v>44939.58</v>
+        <v>44463.6</v>
       </c>
       <c r="I29" t="n">
-        <v>47.91</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01902551833296895</v>
+        <v>0.01886779554028565</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1488,16 +1488,16 @@
         <v>331</v>
       </c>
       <c r="H30" t="n">
-        <v>44466.54</v>
+        <v>44241.46</v>
       </c>
       <c r="I30" t="n">
-        <v>134.34</v>
+        <v>133.66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01866434336757717</v>
+        <v>0.01868372119212675</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1523,16 +1523,16 @@
         <v>426</v>
       </c>
       <c r="H31" t="n">
-        <v>43622.4</v>
+        <v>43809.84</v>
       </c>
       <c r="I31" t="n">
-        <v>102.4</v>
+        <v>102.84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01767060947554463</v>
+        <v>0.01772872835966935</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1558,16 +1558,16 @@
         <v>1504</v>
       </c>
       <c r="H32" t="n">
-        <v>41299.84</v>
+        <v>41570.56</v>
       </c>
       <c r="I32" t="n">
-        <v>27.46</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01686561382685281</v>
+        <v>0.01695179660372208</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>39418.4</v>
+        <v>39748.8</v>
       </c>
       <c r="I33" t="n">
-        <v>70.39</v>
+        <v>70.98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01624192874670935</v>
+        <v>0.01634586779337807</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>37960.72</v>
+        <v>38328.01</v>
       </c>
       <c r="I34" t="n">
-        <v>102.32</v>
+        <v>103.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01370022207464045</v>
+        <v>0.01415012804792856</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         <v>121</v>
       </c>
       <c r="H35" t="n">
-        <v>32020.23</v>
+        <v>33179.41</v>
       </c>
       <c r="I35" t="n">
-        <v>264.63</v>
+        <v>274.21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01354300438440753</v>
+        <v>0.01352133174639256</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
         <v>373</v>
       </c>
       <c r="H36" t="n">
-        <v>31652.78</v>
+        <v>31705</v>
       </c>
       <c r="I36" t="n">
-        <v>84.86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01125912702281449</v>
+        <v>0.01122407859310221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         <v>87</v>
       </c>
       <c r="H37" t="n">
-        <v>26314.89</v>
+        <v>26318.37</v>
       </c>
       <c r="I37" t="n">
-        <v>302.47</v>
+        <v>302.51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01118058449622296</v>
+        <v>0.01106416394983002</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         <v>522</v>
       </c>
       <c r="H38" t="n">
-        <v>26131.32</v>
+        <v>25943.4</v>
       </c>
       <c r="I38" t="n">
-        <v>50.06</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008802607565673802</v>
+        <v>0.008916274493670691</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         <v>575</v>
       </c>
       <c r="H39" t="n">
-        <v>20573.5</v>
+        <v>20907</v>
       </c>
       <c r="I39" t="n">
-        <v>35.78</v>
+        <v>36.36</v>
       </c>
     </row>
   </sheetData>
@@ -1873,7 +1873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06021245127124281</v>
+        <v>0.06029961936503339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>154816.24</v>
+        <v>155010.44</v>
       </c>
       <c r="I2" t="n">
-        <v>159.44</v>
+        <v>159.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05659445148193318</v>
+        <v>0.05693257535566726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>145513.76</v>
+        <v>146354.88</v>
       </c>
       <c r="I3" t="n">
-        <v>48.44</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05342963120545276</v>
+        <v>0.05351997124454261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1969,16 +1969,16 @@
         <v>556</v>
       </c>
       <c r="H4" t="n">
-        <v>137376.48</v>
+        <v>137582.2</v>
       </c>
       <c r="I4" t="n">
-        <v>247.08</v>
+        <v>247.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1987,33 +1987,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04970833200092904</v>
+        <v>0.0497010762123057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1095</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>127808.4</v>
+        <v>127765.08</v>
       </c>
       <c r="I5" t="n">
-        <v>116.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2022,33 +2022,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04969148361739337</v>
+        <v>0.04962847647023609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1095</v>
       </c>
       <c r="H6" t="n">
-        <v>127765.08</v>
+        <v>127578.45</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>116.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04883405957826442</v>
+        <v>0.04941159529252583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2074,16 +2074,16 @@
         <v>1781</v>
       </c>
       <c r="H7" t="n">
-        <v>125560.5</v>
+        <v>127020.92</v>
       </c>
       <c r="I7" t="n">
-        <v>70.5</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2092,33 +2092,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04346779497216077</v>
+        <v>0.04302243676687141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>703</v>
+        <v>450</v>
       </c>
       <c r="H8" t="n">
-        <v>111762.94</v>
+        <v>110596.5</v>
       </c>
       <c r="I8" t="n">
-        <v>158.98</v>
+        <v>245.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2127,33 +2127,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04342017456403272</v>
+        <v>0.04271867552489588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>450</v>
+        <v>703</v>
       </c>
       <c r="H9" t="n">
-        <v>111640.5</v>
+        <v>109815.63</v>
       </c>
       <c r="I9" t="n">
-        <v>248.09</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03975725353053171</v>
+        <v>0.03947896406427134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>102222.52</v>
+        <v>101487.4</v>
       </c>
       <c r="I10" t="n">
-        <v>50.06</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03729905414839445</v>
+        <v>0.03770260246015447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2214,16 +2214,16 @@
         <v>796</v>
       </c>
       <c r="H11" t="n">
-        <v>95902.08</v>
+        <v>96920.96000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>120.48</v>
+        <v>121.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2232,33 +2232,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03654275152476121</v>
+        <v>0.03626126631743194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Principal Financial</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>295</v>
+        <v>804</v>
       </c>
       <c r="H12" t="n">
-        <v>93957.5</v>
+        <v>93215.75999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>318.5</v>
+        <v>115.94</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2267,33 +2267,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03647315665518889</v>
+        <v>0.03577666119135021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Principal Financial</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>804</v>
+        <v>1082</v>
       </c>
       <c r="H13" t="n">
-        <v>93778.56</v>
+        <v>91970</v>
       </c>
       <c r="I13" t="n">
-        <v>116.64</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,33 +2302,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03571084119661887</v>
+        <v>0.03550667324202047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1082</v>
+        <v>295</v>
       </c>
       <c r="H14" t="n">
-        <v>91818.52</v>
+        <v>91275.95</v>
       </c>
       <c r="I14" t="n">
-        <v>84.86</v>
+        <v>309.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03350315067494616</v>
+        <v>0.03361453249611408</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>1798</v>
       </c>
       <c r="H15" t="n">
-        <v>86142.17999999999</v>
+        <v>86411.88</v>
       </c>
       <c r="I15" t="n">
-        <v>47.91</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03276116062089078</v>
+        <v>0.03307682059841287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         <v>710</v>
       </c>
       <c r="H16" t="n">
-        <v>84234.39999999999</v>
+        <v>85029.60000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>118.64</v>
+        <v>119.76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0324689586229603</v>
+        <v>0.03269147363118279</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
         <v>327</v>
       </c>
       <c r="H17" t="n">
-        <v>83483.10000000001</v>
+        <v>84039</v>
       </c>
       <c r="I17" t="n">
-        <v>255.3</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03151701717462456</v>
+        <v>0.03154788084472707</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
         <v>910</v>
       </c>
       <c r="H18" t="n">
-        <v>81035.5</v>
+        <v>81099.2</v>
       </c>
       <c r="I18" t="n">
-        <v>89.05</v>
+        <v>89.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03118845035996774</v>
+        <v>0.03108072642018981</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,16 +2494,16 @@
         <v>215</v>
       </c>
       <c r="H19" t="n">
-        <v>80190.7</v>
+        <v>79898.3</v>
       </c>
       <c r="I19" t="n">
-        <v>372.98</v>
+        <v>371.62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2512,33 +2512,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03010866810673415</v>
+        <v>0.03037999867341992</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Eastman Chemical</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>756</v>
+        <v>1179</v>
       </c>
       <c r="H20" t="n">
-        <v>77414.39999999999</v>
+        <v>78096.96000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>102.4</v>
+        <v>66.23999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2547,33 +2547,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02983763548820918</v>
+        <v>0.03024387853332992</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eastman Chemical</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1179</v>
+        <v>756</v>
       </c>
       <c r="H21" t="n">
-        <v>76717.53</v>
+        <v>77747.03999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>65.06999999999999</v>
+        <v>102.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02904445077291648</v>
+        <v>0.02916811630479458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2599,16 +2599,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>74678.12</v>
+        <v>74981.61</v>
       </c>
       <c r="I22" t="n">
-        <v>76.28</v>
+        <v>76.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02657987296303257</v>
+        <v>0.02645996270490215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>68341.28</v>
+        <v>68019.84</v>
       </c>
       <c r="I23" t="n">
-        <v>87.17</v>
+        <v>86.76000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02545809420808658</v>
+        <v>0.0254385014890416</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2669,16 +2669,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>65457</v>
+        <v>65394</v>
       </c>
       <c r="I24" t="n">
-        <v>20.78</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02446342118313347</v>
+        <v>0.02461496530541067</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2704,16 +2704,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>62899.53</v>
+        <v>63276.96</v>
       </c>
       <c r="I25" t="n">
-        <v>38.33</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2722,33 +2722,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02275784127153428</v>
+        <v>0.02256993447417172</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Amdocs Ltd</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>953</v>
+        <v>586</v>
       </c>
       <c r="H26" t="n">
-        <v>58514.2</v>
+        <v>58019.86</v>
       </c>
       <c r="I26" t="n">
-        <v>61.4</v>
+        <v>99.01000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2757,33 +2757,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02244478492630042</v>
+        <v>0.02243229333000149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Amdocs Ltd</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>586</v>
+        <v>953</v>
       </c>
       <c r="H27" t="n">
-        <v>57709.28</v>
+        <v>57666.03</v>
       </c>
       <c r="I27" t="n">
-        <v>98.48</v>
+        <v>60.51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0209341165430692</v>
+        <v>0.02098028681850133</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>53825.1</v>
+        <v>53933.4</v>
       </c>
       <c r="I28" t="n">
-        <v>74.55</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01579094133668992</v>
+        <v>0.01574003486849338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>40601.14</v>
+        <v>40462.44</v>
       </c>
       <c r="I29" t="n">
-        <v>278.09</v>
+        <v>277.14</v>
       </c>
     </row>
   </sheetData>
@@ -2914,7 +2914,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09340434336698515</v>
+        <v>0.09324860029289622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03771387205400041</v>
+        <v>0.0374699600212027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>411</v>
       </c>
       <c r="H3" t="n">
-        <v>111981.06</v>
+        <v>111442.65</v>
       </c>
       <c r="I3" t="n">
-        <v>272.46</v>
+        <v>271.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03510979054907934</v>
+        <v>0.03537070028815812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3010,16 +3010,16 @@
         <v>277</v>
       </c>
       <c r="H4" t="n">
-        <v>104248.95</v>
+        <v>105199.06</v>
       </c>
       <c r="I4" t="n">
-        <v>376.35</v>
+        <v>379.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03436638165941177</v>
+        <v>0.03435211588545563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>102041.6</v>
+        <v>102169.6</v>
       </c>
       <c r="I5" t="n">
-        <v>159.44</v>
+        <v>159.64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03369847052533202</v>
+        <v>0.03364705250563774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>100058.42</v>
+        <v>100072.61</v>
       </c>
       <c r="I6" t="n">
-        <v>211.54</v>
+        <v>211.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3098,33 +3098,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03069568933714587</v>
+        <v>0.03106097058095738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>341</v>
+        <v>838</v>
       </c>
       <c r="H7" t="n">
-        <v>91142.48</v>
+        <v>92381.12</v>
       </c>
       <c r="I7" t="n">
-        <v>267.28</v>
+        <v>110.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3133,33 +3133,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03041732735762833</v>
+        <v>0.03098158753002485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>553</v>
+        <v>341</v>
       </c>
       <c r="H8" t="n">
-        <v>90315.96000000001</v>
+        <v>92145.02</v>
       </c>
       <c r="I8" t="n">
-        <v>163.32</v>
+        <v>270.22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3168,33 +3168,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.030407277605089</v>
+        <v>0.03035731262745418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>838</v>
+        <v>553</v>
       </c>
       <c r="H9" t="n">
-        <v>90286.12</v>
+        <v>90288.31</v>
       </c>
       <c r="I9" t="n">
-        <v>107.74</v>
+        <v>163.27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02737631400093466</v>
+        <v>0.02764855514172662</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3220,16 +3220,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>81286.5</v>
+        <v>82231.96000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>70.5</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02599514660268486</v>
+        <v>0.02604535710154452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>77185.5</v>
+        <v>77463.75</v>
       </c>
       <c r="I11" t="n">
-        <v>147.02</v>
+        <v>147.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02481545586199539</v>
+        <v>0.02454240495986109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>73682.73</v>
+        <v>72993.69</v>
       </c>
       <c r="I12" t="n">
-        <v>248.09</v>
+        <v>245.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02397245877440964</v>
+        <v>0.02395923709586311</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3325,16 +3325,16 @@
         <v>204</v>
       </c>
       <c r="H13" t="n">
-        <v>71179.67999999999</v>
+        <v>71259.24000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>348.92</v>
+        <v>349.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02328292585370038</v>
+        <v>0.02359729274813605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
         <v>141</v>
       </c>
       <c r="H14" t="n">
-        <v>69132.3</v>
+        <v>70182.75</v>
       </c>
       <c r="I14" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02326448671323362</v>
+        <v>0.02300027235682583</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3395,16 +3395,16 @@
         <v>265</v>
       </c>
       <c r="H15" t="n">
-        <v>69077.55</v>
+        <v>68407.10000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>260.67</v>
+        <v>258.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02280912582463288</v>
+        <v>0.02237433985814716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3430,16 +3430,16 @@
         <v>426</v>
       </c>
       <c r="H16" t="n">
-        <v>67725.48</v>
+        <v>66545.46000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>158.98</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02230123611888876</v>
+        <v>0.02229739108628601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3465,16 +3465,16 @@
         <v>268</v>
       </c>
       <c r="H17" t="n">
-        <v>66217.44</v>
+        <v>66316.60000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>247.08</v>
+        <v>247.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3483,33 +3483,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02218759039178185</v>
+        <v>0.02222467204242456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="H18" t="n">
-        <v>65880</v>
+        <v>66100.32000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>360</v>
+        <v>282.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3518,33 +3518,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02213885043911794</v>
+        <v>0.02190740209527949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>234</v>
+        <v>1311</v>
       </c>
       <c r="H19" t="n">
-        <v>65735.28</v>
+        <v>65156.7</v>
       </c>
       <c r="I19" t="n">
-        <v>280.92</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3553,33 +3553,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02210294210749117</v>
+        <v>0.02190140045419882</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1311</v>
+        <v>183</v>
       </c>
       <c r="H20" t="n">
-        <v>65628.66</v>
+        <v>65138.85</v>
       </c>
       <c r="I20" t="n">
-        <v>50.06</v>
+        <v>355.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02154181969778036</v>
+        <v>0.02146720777955782</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3605,16 +3605,16 @@
         <v>548</v>
       </c>
       <c r="H21" t="n">
-        <v>63962.56</v>
+        <v>63847.48</v>
       </c>
       <c r="I21" t="n">
-        <v>116.72</v>
+        <v>116.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02045838632214669</v>
+        <v>0.02046176982874632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3640,16 +3640,16 @@
         <v>656</v>
       </c>
       <c r="H22" t="n">
-        <v>60745.6</v>
+        <v>60857.12</v>
       </c>
       <c r="I22" t="n">
-        <v>92.59999999999999</v>
+        <v>92.77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01959312418293979</v>
+        <v>0.01967352067751285</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3675,16 +3675,16 @@
         <v>1201</v>
       </c>
       <c r="H23" t="n">
-        <v>58176.44</v>
+        <v>58512.72</v>
       </c>
       <c r="I23" t="n">
-        <v>48.44</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01943990587126953</v>
+        <v>0.0194652217037148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         <v>1010</v>
       </c>
       <c r="H24" t="n">
-        <v>57721.5</v>
+        <v>57893.2</v>
       </c>
       <c r="I24" t="n">
-        <v>57.15</v>
+        <v>57.32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01800714929426724</v>
+        <v>0.01788612773350879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3745,16 +3745,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>53467.32</v>
+        <v>53196.68</v>
       </c>
       <c r="I25" t="n">
-        <v>134.34</v>
+        <v>133.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01655380150177386</v>
+        <v>0.01659721058785513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3780,16 +3780,16 @@
         <v>480</v>
       </c>
       <c r="H26" t="n">
-        <v>49152</v>
+        <v>49363.2</v>
       </c>
       <c r="I26" t="n">
-        <v>102.4</v>
+        <v>102.84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01618990885352685</v>
+        <v>0.01633463122548212</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3815,16 +3815,16 @@
         <v>399</v>
       </c>
       <c r="H27" t="n">
-        <v>48071.52</v>
+        <v>48582.24</v>
       </c>
       <c r="I27" t="n">
-        <v>120.48</v>
+        <v>121.76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3833,33 +3833,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01609186314443676</v>
+        <v>0.01618070678364853</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1740</v>
+        <v>678</v>
       </c>
       <c r="H28" t="n">
-        <v>47780.4</v>
+        <v>48124.44</v>
       </c>
       <c r="I28" t="n">
-        <v>27.46</v>
+        <v>70.98</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3868,33 +3868,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01607300975478691</v>
+        <v>0.01617033756174781</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>678</v>
+        <v>1740</v>
       </c>
       <c r="H29" t="n">
-        <v>47724.42</v>
+        <v>48093.6</v>
       </c>
       <c r="I29" t="n">
-        <v>70.39</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01587734268942842</v>
+        <v>0.0159004957093276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,16 +3920,16 @@
         <v>984</v>
       </c>
       <c r="H30" t="n">
-        <v>47143.44</v>
+        <v>47291.04</v>
       </c>
       <c r="I30" t="n">
-        <v>47.91</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0153843659542755</v>
+        <v>0.01491733611918865</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,16 +3955,16 @@
         <v>918</v>
       </c>
       <c r="H31" t="n">
-        <v>45679.68</v>
+        <v>44366.94</v>
       </c>
       <c r="I31" t="n">
-        <v>49.76</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01406127427076702</v>
+        <v>0.0140609876747071</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,16 +3990,16 @@
         <v>492</v>
       </c>
       <c r="H32" t="n">
-        <v>41751.12</v>
+        <v>41820</v>
       </c>
       <c r="I32" t="n">
-        <v>84.86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01359189963541155</v>
+        <v>0.0134878023722601</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4025,16 +4025,16 @@
         <v>346</v>
       </c>
       <c r="H33" t="n">
-        <v>40357.44</v>
+        <v>40115.24</v>
       </c>
       <c r="I33" t="n">
-        <v>116.64</v>
+        <v>115.94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01315524058188148</v>
+        <v>0.01322075792341363</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,16 +4060,16 @@
         <v>153</v>
       </c>
       <c r="H34" t="n">
-        <v>39060.9</v>
+        <v>39321</v>
       </c>
       <c r="I34" t="n">
-        <v>255.3</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4078,33 +4078,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01297930255485254</v>
+        <v>0.01306056622165042</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>121</v>
+        <v>376</v>
       </c>
       <c r="H35" t="n">
-        <v>38538.5</v>
+        <v>38844.56</v>
       </c>
       <c r="I35" t="n">
-        <v>318.5</v>
+        <v>103.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4113,33 +4113,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01295701392807463</v>
+        <v>0.01299972605618561</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>376</v>
+        <v>141</v>
       </c>
       <c r="H36" t="n">
-        <v>38472.32</v>
+        <v>38663.61</v>
       </c>
       <c r="I36" t="n">
-        <v>102.32</v>
+        <v>274.21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4148,33 +4148,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01256651166360337</v>
+        <v>0.01258784872712018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="H37" t="n">
-        <v>37312.83</v>
+        <v>37438.61</v>
       </c>
       <c r="I37" t="n">
-        <v>264.63</v>
+        <v>309.41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01238652207749104</v>
+        <v>0.01248260650445016</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4200,16 +4200,16 @@
         <v>310</v>
       </c>
       <c r="H38" t="n">
-        <v>36778.4</v>
+        <v>37125.6</v>
       </c>
       <c r="I38" t="n">
-        <v>118.64</v>
+        <v>119.76</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01192024589130989</v>
+        <v>0.01194873279164751</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4235,16 +4235,16 @@
         <v>464</v>
       </c>
       <c r="H39" t="n">
-        <v>35393.92</v>
+        <v>35537.76</v>
       </c>
       <c r="I39" t="n">
-        <v>76.28</v>
+        <v>76.59</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.01181671727433306</v>
+        <v>0.01179857408539395</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4270,16 +4270,16 @@
         <v>116</v>
       </c>
       <c r="H40" t="n">
-        <v>35086.52</v>
+        <v>35091.16</v>
       </c>
       <c r="I40" t="n">
-        <v>302.47</v>
+        <v>302.51</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01171376456475711</v>
+        <v>0.01163922967413624</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4305,16 +4305,16 @@
         <v>399</v>
       </c>
       <c r="H41" t="n">
-        <v>34780.83</v>
+        <v>34617.24</v>
       </c>
       <c r="I41" t="n">
-        <v>87.17</v>
+        <v>86.76000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0114265585335746</v>
+        <v>0.01141647296552202</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4340,16 +4340,16 @@
         <v>381</v>
       </c>
       <c r="H42" t="n">
-        <v>33928.05</v>
+        <v>33954.72</v>
       </c>
       <c r="I42" t="n">
-        <v>89.05</v>
+        <v>89.12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01130536538842458</v>
+        <v>0.01124536063057673</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4375,16 +4375,16 @@
         <v>90</v>
       </c>
       <c r="H43" t="n">
-        <v>33568.2</v>
+        <v>33445.8</v>
       </c>
       <c r="I43" t="n">
-        <v>372.98</v>
+        <v>371.62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.01080399252958515</v>
+        <v>0.01097991661935177</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4410,16 +4410,16 @@
         <v>493</v>
       </c>
       <c r="H44" t="n">
-        <v>32079.51</v>
+        <v>32656.32</v>
       </c>
       <c r="I44" t="n">
-        <v>65.06999999999999</v>
+        <v>66.23999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.009100902997882271</v>
+        <v>0.009140247196063548</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4445,16 +4445,16 @@
         <v>705</v>
       </c>
       <c r="H45" t="n">
-        <v>27022.65</v>
+        <v>27184.8</v>
       </c>
       <c r="I45" t="n">
-        <v>38.33</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.009076994421046924</v>
+        <v>0.009053137662664143</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4480,16 +4480,16 @@
         <v>1297</v>
       </c>
       <c r="H46" t="n">
-        <v>26951.66</v>
+        <v>26925.72</v>
       </c>
       <c r="I46" t="n">
-        <v>20.78</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,33 +4498,33 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.008912554334758347</v>
+        <v>0.00879063899462499</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>HWC</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Amdocs Ltd</t>
+          <t>Hancock Whitney Corp</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>431</v>
+        <v>350</v>
       </c>
       <c r="H47" t="n">
-        <v>26463.4</v>
+        <v>26145</v>
       </c>
       <c r="I47" t="n">
-        <v>61.4</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4533,33 +4533,33 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008787639682719612</v>
+        <v>0.008768720396190888</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>HWC</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hancock Whitney Corp</t>
+          <t>Amdocs Ltd</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>350</v>
+        <v>431</v>
       </c>
       <c r="H48" t="n">
-        <v>26092.5</v>
+        <v>26079.81</v>
       </c>
       <c r="I48" t="n">
-        <v>74.55</v>
+        <v>60.51</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.008523887564634913</v>
+        <v>0.00855547216991623</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4585,16 +4585,16 @@
         <v>257</v>
       </c>
       <c r="H49" t="n">
-        <v>25309.36</v>
+        <v>25445.57</v>
       </c>
       <c r="I49" t="n">
-        <v>98.48</v>
+        <v>99.01000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.007555521161272885</v>
+        <v>0.007665195120311419</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4620,16 +4620,16 @@
         <v>627</v>
       </c>
       <c r="H50" t="n">
-        <v>22434.06</v>
+        <v>22797.72</v>
       </c>
       <c r="I50" t="n">
-        <v>35.78</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.006087728533443989</v>
+        <v>0.006056815831442877</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4655,10 +4655,10 @@
         <v>65</v>
       </c>
       <c r="H51" t="n">
-        <v>18075.85</v>
+        <v>18014.1</v>
       </c>
       <c r="I51" t="n">
-        <v>278.09</v>
+        <v>277.14</v>
       </c>
     </row>
   </sheetData>
@@ -4725,7 +4725,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07093228165761697</v>
+        <v>0.0708222946198416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05399195355672864</v>
+        <v>0.05358471070585853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4786,16 +4786,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>118739.52</v>
+        <v>118026.92</v>
       </c>
       <c r="I3" t="n">
-        <v>116.64</v>
+        <v>115.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04146757034362876</v>
+        <v>0.04203238459678895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4821,16 +4821,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>91195.8</v>
+        <v>92581.5</v>
       </c>
       <c r="I4" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04011649286240677</v>
+        <v>0.03891113789160484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4856,16 +4856,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>88224.5</v>
+        <v>85706.57000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>318.5</v>
+        <v>309.41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03806551786809404</v>
+        <v>0.03888839682406486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4891,16 +4891,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>83713.98</v>
+        <v>85656.48</v>
       </c>
       <c r="I6" t="n">
-        <v>107.74</v>
+        <v>110.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03493670925215477</v>
+        <v>0.03511119131245637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4926,16 +4926,16 @@
         <v>2798</v>
       </c>
       <c r="H7" t="n">
-        <v>76833.08</v>
+        <v>77336.72</v>
       </c>
       <c r="I7" t="n">
-        <v>27.46</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03435855558344945</v>
+        <v>0.03436825893229203</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4961,16 +4961,16 @@
         <v>816</v>
       </c>
       <c r="H8" t="n">
-        <v>75561.60000000001</v>
+        <v>75700.32000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>92.59999999999999</v>
+        <v>92.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0341810689367812</v>
+        <v>0.03380892128765363</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4996,16 +4996,16 @@
         <v>303</v>
       </c>
       <c r="H9" t="n">
-        <v>75171.27</v>
+        <v>74468.31</v>
       </c>
       <c r="I9" t="n">
-        <v>248.09</v>
+        <v>245.77</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03383383024713855</v>
+        <v>0.03378583517696471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>246</v>
       </c>
       <c r="H10" t="n">
-        <v>74407.62</v>
+        <v>74417.46000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>302.47</v>
+        <v>302.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03175543628735022</v>
+        <v>0.03184243412105912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5066,16 +5066,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>69836.8</v>
+        <v>70136.88</v>
       </c>
       <c r="I11" t="n">
-        <v>102.4</v>
+        <v>102.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5084,33 +5084,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03125545622634916</v>
+        <v>0.03139878127218561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>197</v>
+        <v>568</v>
       </c>
       <c r="H12" t="n">
-        <v>68737.24000000001</v>
+        <v>69159.67999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>348.92</v>
+        <v>121.76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5119,33 +5119,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03120731161499662</v>
+        <v>0.0312418729002053</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>588</v>
+        <v>197</v>
       </c>
       <c r="H13" t="n">
-        <v>68631.36</v>
+        <v>68814.07000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>116.72</v>
+        <v>349.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5154,33 +5154,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03111695180041431</v>
+        <v>0.0311028613715555</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="H14" t="n">
-        <v>68432.64</v>
+        <v>68507.88</v>
       </c>
       <c r="I14" t="n">
-        <v>120.48</v>
+        <v>116.51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03054983847137313</v>
+        <v>0.03039499627142287</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5206,16 +5206,16 @@
         <v>1076</v>
       </c>
       <c r="H15" t="n">
-        <v>67185.44</v>
+        <v>66948.72</v>
       </c>
       <c r="I15" t="n">
-        <v>62.44</v>
+        <v>62.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03035306760702957</v>
+        <v>0.03016028974943951</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5241,16 +5241,16 @@
         <v>245</v>
       </c>
       <c r="H16" t="n">
-        <v>66752.7</v>
+        <v>66431.75</v>
       </c>
       <c r="I16" t="n">
-        <v>272.46</v>
+        <v>271.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02954793219394421</v>
+        <v>0.02954629454598421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5276,16 +5276,16 @@
         <v>263</v>
       </c>
       <c r="H17" t="n">
-        <v>64982.04</v>
+        <v>65079.35</v>
       </c>
       <c r="I17" t="n">
-        <v>247.08</v>
+        <v>247.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02811753523780406</v>
+        <v>0.0281574459310462</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5311,16 +5311,16 @@
         <v>1082</v>
       </c>
       <c r="H18" t="n">
-        <v>61836.3</v>
+        <v>62020.24</v>
       </c>
       <c r="I18" t="n">
-        <v>57.15</v>
+        <v>57.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02717816511828328</v>
+        <v>0.02809889301667942</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5346,16 +5346,16 @@
         <v>1433</v>
       </c>
       <c r="H19" t="n">
-        <v>59770.43</v>
+        <v>61891.27</v>
       </c>
       <c r="I19" t="n">
-        <v>41.71</v>
+        <v>43.19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.025886886445514</v>
+        <v>0.02613105291773776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
         <v>213</v>
       </c>
       <c r="H20" t="n">
-        <v>56930.64</v>
+        <v>57556.86</v>
       </c>
       <c r="I20" t="n">
-        <v>267.28</v>
+        <v>270.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02533160465016561</v>
+        <v>0.02570231864501446</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5416,16 +5416,16 @@
         <v>1557</v>
       </c>
       <c r="H21" t="n">
-        <v>55709.46</v>
+        <v>56612.52</v>
       </c>
       <c r="I21" t="n">
-        <v>35.78</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5434,33 +5434,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02262732619570221</v>
+        <v>0.02275966354969668</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Coca-Cola Femsa</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>443</v>
+        <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>49762.19</v>
+        <v>50130.96</v>
       </c>
       <c r="I22" t="n">
-        <v>112.33</v>
+        <v>379.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5469,33 +5469,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02258913516899745</v>
+        <v>0.02262844273214663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Coca-Cola Femsa</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>132</v>
+        <v>443</v>
       </c>
       <c r="H23" t="n">
-        <v>49678.2</v>
+        <v>49841.93</v>
       </c>
       <c r="I23" t="n">
-        <v>376.35</v>
+        <v>112.51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02254059950772272</v>
+        <v>0.0223917295118497</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5521,16 +5521,16 @@
         <v>369</v>
       </c>
       <c r="H24" t="n">
-        <v>49571.46</v>
+        <v>49320.54</v>
       </c>
       <c r="I24" t="n">
-        <v>134.34</v>
+        <v>133.66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02252051954892665</v>
+        <v>0.02226735961682268</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5556,16 +5556,16 @@
         <v>190</v>
       </c>
       <c r="H25" t="n">
-        <v>49527.3</v>
+        <v>49046.6</v>
       </c>
       <c r="I25" t="n">
-        <v>260.67</v>
+        <v>258.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5574,33 +5574,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02169865083684456</v>
+        <v>0.02113415619495895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>959</v>
+        <v>298</v>
       </c>
       <c r="H26" t="n">
-        <v>47719.84</v>
+        <v>46550.58</v>
       </c>
       <c r="I26" t="n">
-        <v>49.76</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5609,33 +5609,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02154232180980451</v>
+        <v>0.02104239741754816</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>298</v>
+        <v>959</v>
       </c>
       <c r="H27" t="n">
-        <v>47376.04</v>
+        <v>46348.47</v>
       </c>
       <c r="I27" t="n">
-        <v>158.98</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02031016897585435</v>
+        <v>0.02039128737537467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5661,16 +5661,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>44666.28</v>
+        <v>44914.32</v>
       </c>
       <c r="I28" t="n">
-        <v>280.92</v>
+        <v>282.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01923619583543655</v>
+        <v>0.01936735367073042</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5696,16 +5696,16 @@
         <v>601</v>
       </c>
       <c r="H29" t="n">
-        <v>42304.39</v>
+        <v>42658.98</v>
       </c>
       <c r="I29" t="n">
-        <v>70.39</v>
+        <v>70.98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01885208022871146</v>
+        <v>0.01889070380071884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5731,16 +5731,16 @@
         <v>282</v>
       </c>
       <c r="H30" t="n">
-        <v>41459.64</v>
+        <v>41609.1</v>
       </c>
       <c r="I30" t="n">
-        <v>147.02</v>
+        <v>147.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01867592588003398</v>
+        <v>0.01867773045707725</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5766,16 +5766,16 @@
         <v>484</v>
       </c>
       <c r="H31" t="n">
-        <v>41072.24</v>
+        <v>41140</v>
       </c>
       <c r="I31" t="n">
-        <v>84.86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01783471383807905</v>
+        <v>0.0178293964749947</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5801,16 +5801,16 @@
         <v>246</v>
       </c>
       <c r="H32" t="n">
-        <v>39222.24</v>
+        <v>39271.44</v>
       </c>
       <c r="I32" t="n">
-        <v>159.44</v>
+        <v>159.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01718091474488745</v>
+        <v>0.01726850159614464</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5836,16 +5836,16 @@
         <v>148</v>
       </c>
       <c r="H33" t="n">
-        <v>37784.4</v>
+        <v>38036</v>
       </c>
       <c r="I33" t="n">
-        <v>255.3</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01679583060754107</v>
+        <v>0.01693204366555554</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5871,16 +5871,16 @@
         <v>361</v>
       </c>
       <c r="H34" t="n">
-        <v>36937.52</v>
+        <v>37294.91</v>
       </c>
       <c r="I34" t="n">
-        <v>102.32</v>
+        <v>103.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5889,33 +5889,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01675337895552112</v>
+        <v>0.0167217534864011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>736</v>
+        <v>372</v>
       </c>
       <c r="H35" t="n">
-        <v>36844.16</v>
+        <v>36831.72</v>
       </c>
       <c r="I35" t="n">
-        <v>50.06</v>
+        <v>99.01000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5924,27 +5924,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01665807190471369</v>
+        <v>0.01660710836012445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>372</v>
+        <v>736</v>
       </c>
       <c r="H36" t="n">
-        <v>36634.56</v>
+        <v>36579.2</v>
       </c>
       <c r="I36" t="n">
-        <v>98.48</v>
+        <v>49.7</v>
       </c>
     </row>
   </sheetData>
@@ -6011,7 +6011,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1058138565722073</v>
+        <v>0.1057701143366562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6037,16 +6037,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>221776.7</v>
+        <v>223174.9</v>
       </c>
       <c r="I2" t="n">
-        <v>52.93</v>
+        <v>53.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09925714542458786</v>
+        <v>0.09907290930731499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6072,16 +6072,16 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>208034.4</v>
+        <v>209043.8</v>
       </c>
       <c r="I3" t="n">
-        <v>212.28</v>
+        <v>213.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09445618414068302</v>
+        <v>0.09521139200589711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6107,16 +6107,16 @@
         <v>4300</v>
       </c>
       <c r="H4" t="n">
-        <v>197972</v>
+        <v>200896</v>
       </c>
       <c r="I4" t="n">
-        <v>46.04</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08547165343777366</v>
+        <v>0.08525075509374147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6142,16 +6142,16 @@
         <v>934</v>
       </c>
       <c r="H5" t="n">
-        <v>179141.2</v>
+        <v>179879.06</v>
       </c>
       <c r="I5" t="n">
-        <v>191.8</v>
+        <v>192.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05514588032228943</v>
+        <v>0.05535095809804439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1475</v>
       </c>
       <c r="H6" t="n">
-        <v>115581</v>
+        <v>116790.5</v>
       </c>
       <c r="I6" t="n">
-        <v>78.36</v>
+        <v>79.18000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03779002167737269</v>
+        <v>0.03807637670606015</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6212,16 +6212,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>79204.62</v>
+        <v>80341.14</v>
       </c>
       <c r="I7" t="n">
-        <v>29.27</v>
+        <v>29.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02639586396307493</v>
+        <v>0.02645861152552536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6247,16 +6247,16 @@
         <v>147</v>
       </c>
       <c r="H8" t="n">
-        <v>55323.45</v>
+        <v>55827.66</v>
       </c>
       <c r="I8" t="n">
-        <v>376.35</v>
+        <v>379.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0245627969805759</v>
+        <v>0.02476955434129204</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6282,16 +6282,16 @@
         <v>105</v>
       </c>
       <c r="H9" t="n">
-        <v>51481.5</v>
+        <v>52263.75</v>
       </c>
       <c r="I9" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02351550666742898</v>
+        <v>0.023537729469059</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6317,16 +6317,16 @@
         <v>1860</v>
       </c>
       <c r="H10" t="n">
-        <v>49286.47</v>
+        <v>49664.6</v>
       </c>
       <c r="I10" t="n">
-        <v>26.5</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02091975557064831</v>
+        <v>0.02080616498313002</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6352,16 +6352,16 @@
         <v>275</v>
       </c>
       <c r="H11" t="n">
-        <v>43846</v>
+        <v>43901</v>
       </c>
       <c r="I11" t="n">
-        <v>159.44</v>
+        <v>159.64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6370,33 +6370,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02053933912418594</v>
+        <v>0.02052891374705041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CEF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Sprott Physical Gold and Silver Trust</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>158</v>
+        <v>980</v>
       </c>
       <c r="H12" t="n">
-        <v>43048.68</v>
+        <v>43316</v>
       </c>
       <c r="I12" t="n">
-        <v>272.46</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6405,33 +6405,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02038780615950871</v>
+        <v>0.02030412697564432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="H13" t="n">
-        <v>42731.08</v>
+        <v>42841.7</v>
       </c>
       <c r="I13" t="n">
-        <v>211.54</v>
+        <v>271.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6440,33 +6440,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02015254836913387</v>
+        <v>0.02025457246411529</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sprott Physical Gold and Silver Trust</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>980</v>
+        <v>202</v>
       </c>
       <c r="H14" t="n">
-        <v>42238</v>
+        <v>42737.14</v>
       </c>
       <c r="I14" t="n">
-        <v>43.1</v>
+        <v>211.57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02014884592642009</v>
+        <v>0.02023448715234597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6492,16 +6492,16 @@
         <v>158</v>
       </c>
       <c r="H15" t="n">
-        <v>42230.24</v>
+        <v>42694.76</v>
       </c>
       <c r="I15" t="n">
-        <v>267.28</v>
+        <v>270.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.017925195093563</v>
+        <v>0.01783755306002166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>37569.66</v>
+        <v>37637.23</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01745476539421647</v>
+        <v>0.01733293211366992</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6562,16 +6562,16 @@
         <v>224</v>
       </c>
       <c r="H17" t="n">
-        <v>36583.68</v>
+        <v>36572.48</v>
       </c>
       <c r="I17" t="n">
-        <v>163.32</v>
+        <v>163.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01681788799317819</v>
+        <v>0.01699182304588199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6597,16 +6597,16 @@
         <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>35248.84</v>
+        <v>35852.74</v>
       </c>
       <c r="I18" t="n">
-        <v>1602.22</v>
+        <v>1629.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6615,33 +6615,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01648115655378713</v>
+        <v>0.01649486560805573</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>99</v>
+        <v>488</v>
       </c>
       <c r="H19" t="n">
-        <v>34543.08</v>
+        <v>34804.16</v>
       </c>
       <c r="I19" t="n">
-        <v>348.92</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6650,33 +6650,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.016414798856283</v>
+        <v>0.01638942956961021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>488</v>
+        <v>99</v>
       </c>
       <c r="H20" t="n">
-        <v>34404</v>
+        <v>34581.69</v>
       </c>
       <c r="I20" t="n">
-        <v>70.5</v>
+        <v>349.31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01572986603899066</v>
+        <v>0.01598741527729477</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>306</v>
       </c>
       <c r="H21" t="n">
-        <v>32968.44</v>
+        <v>33733.44</v>
       </c>
       <c r="I21" t="n">
-        <v>107.74</v>
+        <v>110.24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01491442211603771</v>
+        <v>0.01467631550889244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6737,16 +6737,16 @@
         <v>126</v>
       </c>
       <c r="H22" t="n">
-        <v>31259.34</v>
+        <v>30967.02</v>
       </c>
       <c r="I22" t="n">
-        <v>248.09</v>
+        <v>245.77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0144280757299732</v>
+        <v>0.01417052394621059</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>84</v>
       </c>
       <c r="H23" t="n">
-        <v>30240</v>
+        <v>29899.8</v>
       </c>
       <c r="I23" t="n">
-        <v>360</v>
+        <v>355.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01409935034583177</v>
+        <v>0.01405571349844941</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6807,16 +6807,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>29551.02</v>
+        <v>29657.55</v>
       </c>
       <c r="I24" t="n">
-        <v>147.02</v>
+        <v>147.55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01339869168938401</v>
+        <v>0.01333057118432359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6842,16 +6842,16 @@
         <v>250</v>
       </c>
       <c r="H25" t="n">
-        <v>28082.5</v>
+        <v>28127.5</v>
       </c>
       <c r="I25" t="n">
-        <v>112.33</v>
+        <v>112.51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01281017028951084</v>
+        <v>0.01260114924855365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6877,16 +6877,16 @@
         <v>103</v>
       </c>
       <c r="H26" t="n">
-        <v>26849.01</v>
+        <v>26588.42</v>
       </c>
       <c r="I26" t="n">
-        <v>260.67</v>
+        <v>258.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01233360006983876</v>
+        <v>0.01220809704320277</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>414</v>
       </c>
       <c r="H27" t="n">
-        <v>25850.16</v>
+        <v>25759.08</v>
       </c>
       <c r="I27" t="n">
-        <v>62.44</v>
+        <v>62.22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01197799380650993</v>
+        <v>0.01193528182690043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6947,16 +6947,16 @@
         <v>524</v>
       </c>
       <c r="H28" t="n">
-        <v>25104.84</v>
+        <v>25183.44</v>
       </c>
       <c r="I28" t="n">
-        <v>47.91</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01122544369780054</v>
+        <v>0.0112425660590525</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6982,16 +6982,16 @@
         <v>259</v>
       </c>
       <c r="H29" t="n">
-        <v>23527.56</v>
+        <v>23721.81</v>
       </c>
       <c r="I29" t="n">
-        <v>90.84</v>
+        <v>91.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0111378637513391</v>
+        <v>0.01104360393696945</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>23344</v>
+        <v>23302</v>
       </c>
       <c r="I30" t="n">
-        <v>116.72</v>
+        <v>116.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0110453026834947</v>
+        <v>0.01099170819278019</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7052,16 +7052,16 @@
         <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>23150</v>
+        <v>23192.5</v>
       </c>
       <c r="I31" t="n">
-        <v>92.59999999999999</v>
+        <v>92.77</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.00945279905360984</v>
+        <v>0.009722869095696184</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7087,16 +7087,16 @@
         <v>475</v>
       </c>
       <c r="H32" t="n">
-        <v>19812.25</v>
+        <v>20515.25</v>
       </c>
       <c r="I32" t="n">
-        <v>41.71</v>
+        <v>43.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7105,33 +7105,33 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.008950521667260148</v>
+        <v>0.00866629070135231</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>377</v>
+        <v>177</v>
       </c>
       <c r="H33" t="n">
-        <v>18759.52</v>
+        <v>18285.87</v>
       </c>
       <c r="I33" t="n">
-        <v>49.76</v>
+        <v>103.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7140,33 +7140,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.008640928751265934</v>
+        <v>0.008635266998935607</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>177</v>
+        <v>377</v>
       </c>
       <c r="H34" t="n">
-        <v>18110.64</v>
+        <v>18220.41</v>
       </c>
       <c r="I34" t="n">
-        <v>102.32</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.008549970802947083</v>
+        <v>0.008529385462777409</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -7192,16 +7192,16 @@
         <v>175</v>
       </c>
       <c r="H35" t="n">
-        <v>17920</v>
+        <v>17997</v>
       </c>
       <c r="I35" t="n">
-        <v>102.4</v>
+        <v>102.84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.008516095360591655</v>
+        <v>0.008514693516933873</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -7227,16 +7227,16 @@
         <v>650</v>
       </c>
       <c r="H36" t="n">
-        <v>17849</v>
+        <v>17966</v>
       </c>
       <c r="I36" t="n">
-        <v>27.46</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.00846069231317881</v>
+        <v>0.008361669791967402</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -7262,16 +7262,16 @@
         <v>132</v>
       </c>
       <c r="H37" t="n">
-        <v>17732.88</v>
+        <v>17643.12</v>
       </c>
       <c r="I37" t="n">
-        <v>134.34</v>
+        <v>133.66</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008366413617271312</v>
+        <v>0.008358598701352367</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -7297,16 +7297,16 @@
         <v>362</v>
       </c>
       <c r="H38" t="n">
-        <v>17535.28</v>
+        <v>17636.64</v>
       </c>
       <c r="I38" t="n">
-        <v>48.44</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008240177497012176</v>
+        <v>0.008126304819553972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7332,16 +7332,16 @@
         <v>345</v>
       </c>
       <c r="H39" t="n">
-        <v>17270.7</v>
+        <v>17146.5</v>
       </c>
       <c r="I39" t="n">
-        <v>50.06</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.007892333958290716</v>
+        <v>0.007905356911416681</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7367,16 +7367,16 @@
         <v>235</v>
       </c>
       <c r="H40" t="n">
-        <v>16541.65</v>
+        <v>16680.3</v>
       </c>
       <c r="I40" t="n">
-        <v>70.39</v>
+        <v>70.98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.007416717976431461</v>
+        <v>0.007389119849173812</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7402,16 +7402,16 @@
         <v>272</v>
       </c>
       <c r="H41" t="n">
-        <v>15544.8</v>
+        <v>15591.04</v>
       </c>
       <c r="I41" t="n">
-        <v>57.15</v>
+        <v>57.32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.007237741132257271</v>
+        <v>0.007229347307794053</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7437,16 +7437,16 @@
         <v>54</v>
       </c>
       <c r="H42" t="n">
-        <v>15169.68</v>
+        <v>15253.92</v>
       </c>
       <c r="I42" t="n">
-        <v>280.92</v>
+        <v>282.48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7455,33 +7455,33 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.007044966009309573</v>
+        <v>0.007147655349566628</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>174</v>
+        <v>55</v>
       </c>
       <c r="H43" t="n">
-        <v>14765.64</v>
+        <v>15081.55</v>
       </c>
       <c r="I43" t="n">
-        <v>84.86</v>
+        <v>274.21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7490,33 +7490,33 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.006944298691245187</v>
+        <v>0.007009479968576867</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>55</v>
+        <v>174</v>
       </c>
       <c r="H44" t="n">
-        <v>14554.65</v>
+        <v>14790</v>
       </c>
       <c r="I44" t="n">
-        <v>264.63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.004694611479665056</v>
+        <v>0.004738863435145375</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7542,16 +7542,16 @@
         <v>275</v>
       </c>
       <c r="H45" t="n">
-        <v>9839.5</v>
+        <v>9999</v>
       </c>
       <c r="I45" t="n">
-        <v>35.78</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.004185110513072249</v>
+        <v>0.004157721147635663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7577,16 +7577,16 @@
         <v>29</v>
       </c>
       <c r="H46" t="n">
-        <v>8771.629999999999</v>
+        <v>8772.790000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>302.47</v>
+        <v>302.51</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/16/2026</t>
+          <t>09/17/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.002654832730961967</v>
+        <v>0.002591161616375844</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7612,261 +7612,13 @@
         <v>35</v>
       </c>
       <c r="H47" t="n">
-        <v>5564.3</v>
+        <v>5467.35</v>
       </c>
       <c r="I47" t="n">
-        <v>158.98</v>
+        <v>156.21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3302FE35-A9BD-4035-A1D5-6E5367E072A9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2CE8377-8E11-461B-9547-CF094DA14367}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0136688B-4610-45AF-859A-5B802095DE51}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -7621,4 +7621,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D26BF95A-43CA-4568-9DA7-5A6DF5446B79}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0021218C-751D-4994-9592-9E5B6BE2FE5B}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EA72EE7-E3C4-45CE-90A5-84E674A89DD2}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.094626224438046</v>
+        <v>0.09549178750515419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>221880.84</v>
+        <v>223573.42</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04356884840572453</v>
+        <v>0.04430895100149459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>102160.82</v>
+        <v>103739.85</v>
       </c>
       <c r="I3" t="n">
-        <v>379.78</v>
+        <v>385.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04024209329304373</v>
+        <v>0.04102512506949872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>94360.2</v>
+        <v>96051.48</v>
       </c>
       <c r="I4" t="n">
-        <v>271.15</v>
+        <v>276.01</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03870821004900343</v>
+        <v>0.03838909745034934</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -613,16 +613,16 @@
         <v>429</v>
       </c>
       <c r="H5" t="n">
-        <v>90763.53</v>
+        <v>89879.78999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>211.57</v>
+        <v>209.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0381941009114239</v>
+        <v>0.03829001080676121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -648,16 +648,16 @@
         <v>561</v>
       </c>
       <c r="H6" t="n">
-        <v>89558.03999999999</v>
+        <v>89647.8</v>
       </c>
       <c r="I6" t="n">
-        <v>159.64</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03768399635687856</v>
+        <v>0.03770867601651807</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -683,16 +683,16 @@
         <v>327</v>
       </c>
       <c r="H7" t="n">
-        <v>88361.94</v>
+        <v>88286.73</v>
       </c>
       <c r="I7" t="n">
-        <v>270.22</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03336050521819559</v>
+        <v>0.03444099506976998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         <v>48</v>
       </c>
       <c r="H8" t="n">
-        <v>78224.16</v>
+        <v>80636.16</v>
       </c>
       <c r="I8" t="n">
-        <v>1629.67</v>
+        <v>1679.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0329351195581912</v>
+        <v>0.03303931136905473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -753,16 +753,16 @@
         <v>473</v>
       </c>
       <c r="H9" t="n">
-        <v>77226.71000000001</v>
+        <v>77354.42</v>
       </c>
       <c r="I9" t="n">
-        <v>163.27</v>
+        <v>163.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03178478922124554</v>
+        <v>0.03144438757110003</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -788,16 +788,16 @@
         <v>1045</v>
       </c>
       <c r="H10" t="n">
-        <v>74529.39999999999</v>
+        <v>73620.25</v>
       </c>
       <c r="I10" t="n">
-        <v>71.31999999999999</v>
+        <v>70.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03154666366395439</v>
+        <v>0.03138500136081298</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         <v>671</v>
       </c>
       <c r="H11" t="n">
-        <v>73971.03999999999</v>
+        <v>73481.21000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>110.24</v>
+        <v>109.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02960160911055178</v>
+        <v>0.02940469505652981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         <v>195</v>
       </c>
       <c r="H12" t="n">
-        <v>69410.25</v>
+        <v>68844.75</v>
       </c>
       <c r="I12" t="n">
-        <v>355.95</v>
+        <v>353.05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02929422857573985</v>
+        <v>0.02910438551744082</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         <v>138</v>
       </c>
       <c r="H13" t="n">
-        <v>68689.5</v>
+        <v>68141.64</v>
       </c>
       <c r="I13" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02785764091992292</v>
+        <v>0.02792838564622484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>187</v>
       </c>
       <c r="H14" t="n">
-        <v>65320.97</v>
+        <v>65388.29</v>
       </c>
       <c r="I14" t="n">
-        <v>349.31</v>
+        <v>349.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02756616356949272</v>
+        <v>0.02759760565085077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -963,16 +963,16 @@
         <v>263</v>
       </c>
       <c r="H15" t="n">
-        <v>64637.51</v>
+        <v>64613.84</v>
       </c>
       <c r="I15" t="n">
-        <v>245.77</v>
+        <v>245.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02749871257346656</v>
+        <v>0.02732364916969267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -998,16 +998,16 @@
         <v>437</v>
       </c>
       <c r="H16" t="n">
-        <v>64479.35</v>
+        <v>63972.43</v>
       </c>
       <c r="I16" t="n">
-        <v>147.55</v>
+        <v>146.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,33 +1016,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02566013984029544</v>
+        <v>0.02551051180128589</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="H17" t="n">
-        <v>60168.24</v>
+        <v>59727.36</v>
       </c>
       <c r="I17" t="n">
-        <v>282.48</v>
+        <v>266.64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,33 +1051,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02466011144144727</v>
+        <v>0.02541588424886142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="H18" t="n">
-        <v>57823.36</v>
+        <v>59505.81</v>
       </c>
       <c r="I18" t="n">
-        <v>258.14</v>
+        <v>279.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02430999403061244</v>
+        <v>0.02429166792292164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         <v>1170</v>
       </c>
       <c r="H19" t="n">
-        <v>57002.4</v>
+        <v>56873.7</v>
       </c>
       <c r="I19" t="n">
-        <v>48.72</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02382857406125121</v>
+        <v>0.023711072043379</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1138,16 +1138,16 @@
         <v>898</v>
       </c>
       <c r="H20" t="n">
-        <v>55873.56</v>
+        <v>55514.36</v>
       </c>
       <c r="I20" t="n">
-        <v>62.22</v>
+        <v>61.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0235166387930202</v>
+        <v>0.0233470367953226</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         <v>353</v>
       </c>
       <c r="H21" t="n">
-        <v>55142.13</v>
+        <v>54662.05</v>
       </c>
       <c r="I21" t="n">
-        <v>156.21</v>
+        <v>154.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02195797319326999</v>
+        <v>0.02183935998510766</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1208,16 +1208,16 @@
         <v>555</v>
       </c>
       <c r="H22" t="n">
-        <v>51487.35</v>
+        <v>51132.15</v>
       </c>
       <c r="I22" t="n">
-        <v>92.77</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02192800065912281</v>
+        <v>0.02156761596489093</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Coca-Cola Femsa</t>
+          <t>Total SA</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="H23" t="n">
-        <v>51417.07</v>
+        <v>50495.92</v>
       </c>
       <c r="I23" t="n">
-        <v>112.51</v>
+        <v>90.81999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,33 +1261,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02171773659380428</v>
+        <v>0.02149454495758433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Total SA</t>
+          <t>Coca-Cola Femsa</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>556</v>
+        <v>457</v>
       </c>
       <c r="H24" t="n">
-        <v>50924.04</v>
+        <v>50324.84</v>
       </c>
       <c r="I24" t="n">
-        <v>91.59</v>
+        <v>110.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02116725355984722</v>
+        <v>0.02113183804032477</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         <v>426</v>
       </c>
       <c r="H25" t="n">
-        <v>49633.26</v>
+        <v>49475.64</v>
       </c>
       <c r="I25" t="n">
-        <v>116.51</v>
+        <v>116.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02112086180878674</v>
+        <v>0.0209091397517483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         <v>864</v>
       </c>
       <c r="H26" t="n">
-        <v>49524.48</v>
+        <v>48954.24</v>
       </c>
       <c r="I26" t="n">
-        <v>57.32</v>
+        <v>56.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02002186178217055</v>
+        <v>0.02007525553486079</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1383,16 +1383,16 @@
         <v>1087</v>
       </c>
       <c r="H27" t="n">
-        <v>46947.53</v>
+        <v>47001.88</v>
       </c>
       <c r="I27" t="n">
-        <v>43.19</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,33 +1401,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01922552976187559</v>
+        <v>0.01895206001618932</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>938</v>
+        <v>426</v>
       </c>
       <c r="H28" t="n">
-        <v>45080.28</v>
+        <v>44372.16</v>
       </c>
       <c r="I28" t="n">
-        <v>48.06</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,33 +1436,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01896253228950955</v>
+        <v>0.01892598885482625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>920</v>
+        <v>938</v>
       </c>
       <c r="H29" t="n">
-        <v>44463.6</v>
+        <v>44311.12</v>
       </c>
       <c r="I29" t="n">
-        <v>48.33</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,33 +1471,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01886779554028565</v>
+        <v>0.01889680828889694</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>331</v>
+        <v>920</v>
       </c>
       <c r="H30" t="n">
-        <v>44241.46</v>
+        <v>44242.8</v>
       </c>
       <c r="I30" t="n">
-        <v>133.66</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,33 +1506,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01868372119212675</v>
+        <v>0.01834345813974994</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>426</v>
+        <v>331</v>
       </c>
       <c r="H31" t="n">
-        <v>43809.84</v>
+        <v>42947.25</v>
       </c>
       <c r="I31" t="n">
-        <v>102.84</v>
+        <v>129.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01772872835966935</v>
+        <v>0.0177682994470381</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1558,16 +1558,16 @@
         <v>1504</v>
       </c>
       <c r="H32" t="n">
-        <v>41570.56</v>
+        <v>41600.64</v>
       </c>
       <c r="I32" t="n">
-        <v>27.64</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01695179660372208</v>
+        <v>0.01668793512203454</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>39748.8</v>
+        <v>39071.2</v>
       </c>
       <c r="I33" t="n">
-        <v>70.98</v>
+        <v>69.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01634586779337807</v>
+        <v>0.01616450872067748</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>38328.01</v>
+        <v>37845.71</v>
       </c>
       <c r="I34" t="n">
-        <v>103.31</v>
+        <v>102.01</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01415012804792856</v>
+        <v>0.01411564175417281</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         <v>121</v>
       </c>
       <c r="H35" t="n">
-        <v>33179.41</v>
+        <v>33048.73</v>
       </c>
       <c r="I35" t="n">
-        <v>274.21</v>
+        <v>273.13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01352133174639256</v>
+        <v>0.01323901603797988</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
         <v>373</v>
       </c>
       <c r="H36" t="n">
-        <v>31705</v>
+        <v>30996.3</v>
       </c>
       <c r="I36" t="n">
-        <v>85</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01122407859310221</v>
+        <v>0.01114698472731806</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         <v>87</v>
       </c>
       <c r="H37" t="n">
-        <v>26318.37</v>
+        <v>26098.26</v>
       </c>
       <c r="I37" t="n">
-        <v>302.51</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01106416394983002</v>
+        <v>0.01086234607470369</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         <v>522</v>
       </c>
       <c r="H38" t="n">
-        <v>25943.4</v>
+        <v>25431.84</v>
       </c>
       <c r="I38" t="n">
-        <v>49.7</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008916274493670691</v>
+        <v>0.008720961508873078</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1803,10 +1803,10 @@
         <v>575</v>
       </c>
       <c r="H39" t="n">
-        <v>20907</v>
+        <v>20418.25</v>
       </c>
       <c r="I39" t="n">
-        <v>36.36</v>
+        <v>35.51</v>
       </c>
     </row>
   </sheetData>
@@ -1873,7 +1873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06029961936503339</v>
+        <v>0.06062428813029756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>155010.44</v>
+        <v>155165.8</v>
       </c>
       <c r="I2" t="n">
-        <v>159.64</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05693257535566726</v>
+        <v>0.05705269927152342</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>146354.88</v>
+        <v>146024.44</v>
       </c>
       <c r="I3" t="n">
-        <v>48.72</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05351997124454261</v>
+        <v>0.053537028328406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1969,16 +1969,16 @@
         <v>556</v>
       </c>
       <c r="H4" t="n">
-        <v>137582.2</v>
+        <v>137026.2</v>
       </c>
       <c r="I4" t="n">
-        <v>247.45</v>
+        <v>246.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0497010762123057</v>
+        <v>0.05052917035703617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>127765.08</v>
+        <v>129327.69</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04962847647023609</v>
+        <v>0.04968743615977729</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2039,16 +2039,16 @@
         <v>1095</v>
       </c>
       <c r="H6" t="n">
-        <v>127578.45</v>
+        <v>127173.3</v>
       </c>
       <c r="I6" t="n">
-        <v>116.51</v>
+        <v>116.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04941159529252583</v>
+        <v>0.04902251228638156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2074,16 +2074,16 @@
         <v>1781</v>
       </c>
       <c r="H7" t="n">
-        <v>127020.92</v>
+        <v>125471.45</v>
       </c>
       <c r="I7" t="n">
-        <v>71.31999999999999</v>
+        <v>70.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04302243676687141</v>
+        <v>0.0431949488774793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2109,16 +2109,16 @@
         <v>450</v>
       </c>
       <c r="H8" t="n">
-        <v>110596.5</v>
+        <v>110556</v>
       </c>
       <c r="I8" t="n">
-        <v>245.77</v>
+        <v>245.68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04271867552489588</v>
+        <v>0.04253213481923552</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>703</v>
       </c>
       <c r="H9" t="n">
-        <v>109815.63</v>
+        <v>108859.55</v>
       </c>
       <c r="I9" t="n">
-        <v>156.21</v>
+        <v>154.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03947896406427134</v>
+        <v>0.03886992158555516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>101487.4</v>
+        <v>99486.24000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>49.7</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03770260246015447</v>
+        <v>0.03800760106230443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2214,16 +2214,16 @@
         <v>796</v>
       </c>
       <c r="H11" t="n">
-        <v>96920.96000000001</v>
+        <v>97279.16</v>
       </c>
       <c r="I11" t="n">
-        <v>121.76</v>
+        <v>122.21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03626126631743194</v>
+        <v>0.03696344572947685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2249,16 +2249,16 @@
         <v>804</v>
       </c>
       <c r="H12" t="n">
-        <v>93215.75999999999</v>
+        <v>94606.67999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>115.94</v>
+        <v>117.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2267,33 +2267,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03577666119135021</v>
+        <v>0.03558949503187957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1082</v>
+        <v>295</v>
       </c>
       <c r="H13" t="n">
-        <v>91970</v>
+        <v>91090.10000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>85</v>
+        <v>308.78</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,33 +2302,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03550667324202047</v>
+        <v>0.03513006324721814</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>295</v>
+        <v>1082</v>
       </c>
       <c r="H14" t="n">
-        <v>91275.95</v>
+        <v>89914.2</v>
       </c>
       <c r="I14" t="n">
-        <v>309.41</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03361453249611408</v>
+        <v>0.03318564197492561</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>1798</v>
       </c>
       <c r="H15" t="n">
-        <v>86411.88</v>
+        <v>84937.52</v>
       </c>
       <c r="I15" t="n">
-        <v>48.06</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,33 +2372,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03307682059841287</v>
+        <v>0.03286013656763152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Allison Transmission</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>710</v>
+        <v>327</v>
       </c>
       <c r="H16" t="n">
-        <v>85029.60000000001</v>
+        <v>84104.39999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>119.76</v>
+        <v>257.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2407,33 +2407,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03269147363118279</v>
+        <v>0.03248372991626421</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Allison Transmission</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>327</v>
+        <v>710</v>
       </c>
       <c r="H17" t="n">
-        <v>84039</v>
+        <v>83141</v>
       </c>
       <c r="I17" t="n">
-        <v>257</v>
+        <v>117.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03154788084472707</v>
+        <v>0.03184953510985005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
         <v>910</v>
       </c>
       <c r="H18" t="n">
-        <v>81099.2</v>
+        <v>81517.8</v>
       </c>
       <c r="I18" t="n">
-        <v>89.12</v>
+        <v>89.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03108072642018981</v>
+        <v>0.0312613069242926</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,16 +2494,16 @@
         <v>215</v>
       </c>
       <c r="H19" t="n">
-        <v>79898.3</v>
+        <v>80012.25</v>
       </c>
       <c r="I19" t="n">
-        <v>371.62</v>
+        <v>372.15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2512,33 +2512,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03037999867341992</v>
+        <v>0.03076616847171707</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Eastman Chemical</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1179</v>
+        <v>756</v>
       </c>
       <c r="H20" t="n">
-        <v>78096.96000000001</v>
+        <v>78744.96000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>66.23999999999999</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2547,33 +2547,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03024387853332992</v>
+        <v>0.03025963701732103</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Eastman Chemical</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>756</v>
+        <v>1179</v>
       </c>
       <c r="H21" t="n">
-        <v>77747.03999999999</v>
+        <v>77448.50999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>102.84</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02916811630479458</v>
+        <v>0.02916957757667827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2599,16 +2599,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>74981.61</v>
+        <v>74658.53999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>76.59</v>
+        <v>76.26000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02645996270490215</v>
+        <v>0.02621128072605366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>68019.84</v>
+        <v>67086.88</v>
       </c>
       <c r="I23" t="n">
-        <v>86.76000000000001</v>
+        <v>85.56999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0254385014890416</v>
+        <v>0.02563601227542029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2669,16 +2669,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>65394</v>
+        <v>65614.5</v>
       </c>
       <c r="I24" t="n">
-        <v>20.76</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02461496530541067</v>
+        <v>0.02450472939094759</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2704,16 +2704,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>63276.96</v>
+        <v>62719.02</v>
       </c>
       <c r="I25" t="n">
-        <v>38.56</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02256993447417172</v>
+        <v>0.02228409424461454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2739,16 +2739,16 @@
         <v>586</v>
       </c>
       <c r="H26" t="n">
-        <v>58019.86</v>
+        <v>57035.38</v>
       </c>
       <c r="I26" t="n">
-        <v>99.01000000000001</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02243229333000149</v>
+        <v>0.02207995790746861</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2774,16 +2774,16 @@
         <v>953</v>
       </c>
       <c r="H27" t="n">
-        <v>57666.03</v>
+        <v>56512.9</v>
       </c>
       <c r="I27" t="n">
-        <v>60.51</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02098028681850133</v>
+        <v>0.02114265299089174</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>53933.4</v>
+        <v>54113.9</v>
       </c>
       <c r="I28" t="n">
-        <v>74.7</v>
+        <v>74.95</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01574003486849338</v>
+        <v>0.01556479401935231</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>40462.44</v>
+        <v>39837.56</v>
       </c>
       <c r="I29" t="n">
-        <v>277.14</v>
+        <v>272.86</v>
       </c>
     </row>
   </sheetData>
@@ -2914,7 +2914,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09324860029289622</v>
+        <v>0.09421464517698616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>277338.73</v>
+        <v>279504.68</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0374699600212027</v>
+        <v>0.03823807069165453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>411</v>
       </c>
       <c r="H3" t="n">
-        <v>111442.65</v>
+        <v>113440.11</v>
       </c>
       <c r="I3" t="n">
-        <v>271.15</v>
+        <v>276.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03537070028815812</v>
+        <v>0.03600828501964191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3010,16 +3010,16 @@
         <v>277</v>
       </c>
       <c r="H4" t="n">
-        <v>105199.06</v>
+        <v>106825.05</v>
       </c>
       <c r="I4" t="n">
-        <v>379.78</v>
+        <v>385.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03435211588545563</v>
+        <v>0.03447355583291388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>102169.6</v>
+        <v>102272</v>
       </c>
       <c r="I5" t="n">
-        <v>159.64</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03364705250563774</v>
+        <v>0.03340375043851632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>100072.61</v>
+        <v>99098.23</v>
       </c>
       <c r="I6" t="n">
-        <v>211.57</v>
+        <v>209.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3098,33 +3098,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03106097058095738</v>
+        <v>0.03103354516105084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>838</v>
+        <v>341</v>
       </c>
       <c r="H7" t="n">
-        <v>92381.12</v>
+        <v>92066.59</v>
       </c>
       <c r="I7" t="n">
-        <v>110.24</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3133,33 +3133,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03098158753002485</v>
+        <v>0.0309333624568004</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>341</v>
+        <v>838</v>
       </c>
       <c r="H8" t="n">
-        <v>92145.02</v>
+        <v>91769.38</v>
       </c>
       <c r="I8" t="n">
-        <v>270.22</v>
+        <v>109.51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03035731262745418</v>
+        <v>0.03048445657135725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
         <v>553</v>
       </c>
       <c r="H9" t="n">
-        <v>90288.31</v>
+        <v>90437.62</v>
       </c>
       <c r="I9" t="n">
-        <v>163.27</v>
+        <v>163.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02764855514172662</v>
+        <v>0.02738039048535657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3220,16 +3220,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>82231.96000000001</v>
+        <v>81228.85000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>71.31999999999999</v>
+        <v>70.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02604535710154452</v>
+        <v>0.02590598125732985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>77463.75</v>
+        <v>76854.75</v>
       </c>
       <c r="I11" t="n">
-        <v>147.55</v>
+        <v>146.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02454240495986109</v>
+        <v>0.02459549602548101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>72993.69</v>
+        <v>72966.96000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>245.77</v>
+        <v>245.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02395923709586311</v>
+        <v>0.02404461755604055</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3325,16 +3325,16 @@
         <v>204</v>
       </c>
       <c r="H13" t="n">
-        <v>71259.24000000001</v>
+        <v>71332.67999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>349.31</v>
+        <v>349.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3343,33 +3343,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02359729274813605</v>
+        <v>0.02381773765772999</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>141</v>
+        <v>265</v>
       </c>
       <c r="H14" t="n">
-        <v>70182.75</v>
+        <v>70659.60000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>497.75</v>
+        <v>266.64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3378,33 +3378,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02300027235682583</v>
+        <v>0.02346831672680545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>265</v>
+        <v>141</v>
       </c>
       <c r="H15" t="n">
-        <v>68407.10000000001</v>
+        <v>69622.98</v>
       </c>
       <c r="I15" t="n">
-        <v>258.14</v>
+        <v>493.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3413,33 +3413,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02237433985814716</v>
+        <v>0.02226347484928227</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>426</v>
+        <v>268</v>
       </c>
       <c r="H16" t="n">
-        <v>66545.46000000001</v>
+        <v>66048.60000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>156.21</v>
+        <v>246.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3448,33 +3448,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02229739108628601</v>
+        <v>0.02223566598315845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>268</v>
+        <v>426</v>
       </c>
       <c r="H17" t="n">
-        <v>66316.60000000001</v>
+        <v>65966.10000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>247.45</v>
+        <v>154.85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02222467204242456</v>
+        <v>0.0220356039441062</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3500,16 +3500,16 @@
         <v>234</v>
       </c>
       <c r="H18" t="n">
-        <v>66100.32000000001</v>
+        <v>65372.58</v>
       </c>
       <c r="I18" t="n">
-        <v>282.48</v>
+        <v>279.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3518,33 +3518,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02190740209527949</v>
+        <v>0.02177793204676036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1311</v>
+        <v>183</v>
       </c>
       <c r="H19" t="n">
-        <v>65156.7</v>
+        <v>64608.15</v>
       </c>
       <c r="I19" t="n">
-        <v>49.7</v>
+        <v>353.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3553,33 +3553,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02190140045419882</v>
+        <v>0.02152976572547138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>183</v>
+        <v>1311</v>
       </c>
       <c r="H20" t="n">
-        <v>65138.85</v>
+        <v>63871.92</v>
       </c>
       <c r="I20" t="n">
-        <v>355.95</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02146720777955782</v>
+        <v>0.0214531817935522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3605,16 +3605,16 @@
         <v>548</v>
       </c>
       <c r="H21" t="n">
-        <v>63847.48</v>
+        <v>63644.72</v>
       </c>
       <c r="I21" t="n">
-        <v>116.51</v>
+        <v>116.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02046176982874632</v>
+        <v>0.02037202701100447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3640,16 +3640,16 @@
         <v>656</v>
       </c>
       <c r="H22" t="n">
-        <v>60857.12</v>
+        <v>60437.28</v>
       </c>
       <c r="I22" t="n">
-        <v>92.77</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01967352067751285</v>
+        <v>0.0196787705177817</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3675,16 +3675,16 @@
         <v>1201</v>
       </c>
       <c r="H23" t="n">
-        <v>58512.72</v>
+        <v>58380.61</v>
       </c>
       <c r="I23" t="n">
-        <v>48.72</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0194652217037148</v>
+        <v>0.0192897800984417</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         <v>1010</v>
       </c>
       <c r="H24" t="n">
-        <v>57893.2</v>
+        <v>57226.6</v>
       </c>
       <c r="I24" t="n">
-        <v>57.32</v>
+        <v>56.66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01788612773350879</v>
+        <v>0.01740683334626867</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3745,16 +3745,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>53196.68</v>
+        <v>51640.5</v>
       </c>
       <c r="I25" t="n">
-        <v>133.66</v>
+        <v>129.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01659721058785513</v>
+        <v>0.01685277960993262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3780,16 +3780,16 @@
         <v>480</v>
       </c>
       <c r="H26" t="n">
-        <v>49363.2</v>
+        <v>49996.8</v>
       </c>
       <c r="I26" t="n">
-        <v>102.84</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01633463122548212</v>
+        <v>0.0164364859402165</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3815,16 +3815,16 @@
         <v>399</v>
       </c>
       <c r="H27" t="n">
-        <v>48582.24</v>
+        <v>48761.79</v>
       </c>
       <c r="I27" t="n">
-        <v>121.76</v>
+        <v>122.21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3833,33 +3833,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01618070678364853</v>
+        <v>0.01622298463459024</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>678</v>
+        <v>1740</v>
       </c>
       <c r="H28" t="n">
-        <v>48124.44</v>
+        <v>48128.4</v>
       </c>
       <c r="I28" t="n">
-        <v>70.98</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3868,33 +3868,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01617033756174781</v>
+        <v>0.01594511844428102</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1740</v>
+        <v>678</v>
       </c>
       <c r="H29" t="n">
-        <v>48093.6</v>
+        <v>47304.06</v>
       </c>
       <c r="I29" t="n">
-        <v>27.64</v>
+        <v>69.77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0159004957093276</v>
+        <v>0.01566874887658501</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,16 +3920,16 @@
         <v>984</v>
       </c>
       <c r="H30" t="n">
-        <v>47291.04</v>
+        <v>46484.16</v>
       </c>
       <c r="I30" t="n">
-        <v>48.06</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01491733611918865</v>
+        <v>0.01488081751999015</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,16 +3955,16 @@
         <v>918</v>
       </c>
       <c r="H31" t="n">
-        <v>44366.94</v>
+        <v>44146.62</v>
       </c>
       <c r="I31" t="n">
-        <v>48.33</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0140609876747071</v>
+        <v>0.01378146731206831</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,16 +3990,16 @@
         <v>492</v>
       </c>
       <c r="H32" t="n">
-        <v>41820</v>
+        <v>40885.2</v>
       </c>
       <c r="I32" t="n">
-        <v>85</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0134878023722601</v>
+        <v>0.0137236990275071</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4025,16 +4025,16 @@
         <v>346</v>
       </c>
       <c r="H33" t="n">
-        <v>40115.24</v>
+        <v>40713.82</v>
       </c>
       <c r="I33" t="n">
-        <v>115.94</v>
+        <v>117.67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01322075792341363</v>
+        <v>0.01326452577161387</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,16 +4060,16 @@
         <v>153</v>
       </c>
       <c r="H34" t="n">
-        <v>39321</v>
+        <v>39351.6</v>
       </c>
       <c r="I34" t="n">
-        <v>257</v>
+        <v>257.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4078,33 +4078,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01306056622165042</v>
+        <v>0.01298128994206402</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>376</v>
+        <v>141</v>
       </c>
       <c r="H35" t="n">
-        <v>38844.56</v>
+        <v>38511.33</v>
       </c>
       <c r="I35" t="n">
-        <v>103.31</v>
+        <v>273.13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4113,33 +4113,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01299972605618561</v>
+        <v>0.01292885084748362</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>141</v>
+        <v>376</v>
       </c>
       <c r="H36" t="n">
-        <v>38663.61</v>
+        <v>38355.76</v>
       </c>
       <c r="I36" t="n">
-        <v>274.21</v>
+        <v>102.01</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01258784872712018</v>
+        <v>0.01259400513317961</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         <v>121</v>
       </c>
       <c r="H37" t="n">
-        <v>37438.61</v>
+        <v>37362.38</v>
       </c>
       <c r="I37" t="n">
-        <v>309.41</v>
+        <v>308.78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01248260650445016</v>
+        <v>0.01223623817164626</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4200,16 +4200,16 @@
         <v>310</v>
       </c>
       <c r="H38" t="n">
-        <v>37125.6</v>
+        <v>36301</v>
       </c>
       <c r="I38" t="n">
-        <v>119.76</v>
+        <v>117.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01194873279164751</v>
+        <v>0.01192735414060112</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4235,16 +4235,16 @@
         <v>464</v>
       </c>
       <c r="H39" t="n">
-        <v>35537.76</v>
+        <v>35384.64</v>
       </c>
       <c r="I39" t="n">
-        <v>76.59</v>
+        <v>76.26000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.01179857408539395</v>
+        <v>0.01172950332775218</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4270,16 +4270,16 @@
         <v>116</v>
       </c>
       <c r="H40" t="n">
-        <v>35091.16</v>
+        <v>34797.68</v>
       </c>
       <c r="I40" t="n">
-        <v>302.51</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01163922967413624</v>
+        <v>0.01150863351529601</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4305,16 +4305,16 @@
         <v>399</v>
       </c>
       <c r="H41" t="n">
-        <v>34617.24</v>
+        <v>34142.43</v>
       </c>
       <c r="I41" t="n">
-        <v>86.76000000000001</v>
+        <v>85.56999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01141647296552202</v>
+        <v>0.01150443690459006</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4340,16 +4340,16 @@
         <v>381</v>
       </c>
       <c r="H42" t="n">
-        <v>33954.72</v>
+        <v>34129.98</v>
       </c>
       <c r="I42" t="n">
-        <v>89.12</v>
+        <v>89.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01124536063057673</v>
+        <v>0.01128989403052352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4375,16 +4375,16 @@
         <v>90</v>
       </c>
       <c r="H43" t="n">
-        <v>33445.8</v>
+        <v>33493.5</v>
       </c>
       <c r="I43" t="n">
-        <v>371.62</v>
+        <v>372.15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.01097991661935177</v>
+        <v>0.01091630129608698</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4410,16 +4410,16 @@
         <v>493</v>
       </c>
       <c r="H44" t="n">
-        <v>32656.32</v>
+        <v>32385.17</v>
       </c>
       <c r="I44" t="n">
-        <v>66.23999999999999</v>
+        <v>65.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4428,33 +4428,33 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.009140247196063548</v>
+        <v>0.009106648602701387</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Hormel Foods</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>705</v>
+        <v>1297</v>
       </c>
       <c r="H45" t="n">
-        <v>27184.8</v>
+        <v>27016.51</v>
       </c>
       <c r="I45" t="n">
-        <v>38.56</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4463,33 +4463,33 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.009053137662664143</v>
+        <v>0.009082577922338938</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hormel Foods</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1297</v>
+        <v>705</v>
       </c>
       <c r="H46" t="n">
-        <v>26925.72</v>
+        <v>26945.1</v>
       </c>
       <c r="I46" t="n">
-        <v>20.76</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.00879063899462499</v>
+        <v>0.008842376734462155</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4515,16 +4515,16 @@
         <v>350</v>
       </c>
       <c r="H47" t="n">
-        <v>26145</v>
+        <v>26232.5</v>
       </c>
       <c r="I47" t="n">
-        <v>74.7</v>
+        <v>74.95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008768720396190888</v>
+        <v>0.008615119309726639</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4550,16 +4550,16 @@
         <v>431</v>
       </c>
       <c r="H48" t="n">
-        <v>26079.81</v>
+        <v>25558.3</v>
       </c>
       <c r="I48" t="n">
-        <v>60.51</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.00855547216991623</v>
+        <v>0.008431584164081074</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4585,16 +4585,16 @@
         <v>257</v>
       </c>
       <c r="H49" t="n">
-        <v>25445.57</v>
+        <v>25013.81</v>
       </c>
       <c r="I49" t="n">
-        <v>99.01000000000001</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.007665195120311419</v>
+        <v>0.007504945554032248</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4620,16 +4620,16 @@
         <v>627</v>
       </c>
       <c r="H50" t="n">
-        <v>22797.72</v>
+        <v>22264.77</v>
       </c>
       <c r="I50" t="n">
-        <v>36.36</v>
+        <v>35.51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.006056815831442877</v>
+        <v>0.005978366893157241</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4655,10 +4655,10 @@
         <v>65</v>
       </c>
       <c r="H51" t="n">
-        <v>18014.1</v>
+        <v>17735.9</v>
       </c>
       <c r="I51" t="n">
-        <v>277.14</v>
+        <v>272.86</v>
       </c>
     </row>
   </sheetData>
@@ -4725,7 +4725,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0708222946198416</v>
+        <v>0.0716395398211782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>155994.82</v>
+        <v>157447.23</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -4760,7 +4760,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05358471070585853</v>
+        <v>0.05450436628495581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4786,16 +4786,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>118026.92</v>
+        <v>119788.06</v>
       </c>
       <c r="I3" t="n">
-        <v>115.94</v>
+        <v>117.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04203238459678895</v>
+        <v>0.04178921399226684</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4821,16 +4821,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>92581.5</v>
+        <v>91843.08</v>
       </c>
       <c r="I4" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03891113789160484</v>
+        <v>0.03891765779783742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4856,16 +4856,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>85706.57000000001</v>
+        <v>85532.06</v>
       </c>
       <c r="I5" t="n">
-        <v>309.41</v>
+        <v>308.78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03888839682406486</v>
+        <v>0.03871618539443332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4891,16 +4891,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>85656.48</v>
+        <v>85089.27</v>
       </c>
       <c r="I6" t="n">
-        <v>110.24</v>
+        <v>109.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03511119131245637</v>
+        <v>0.03521418560826825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4926,16 +4926,16 @@
         <v>2798</v>
       </c>
       <c r="H7" t="n">
-        <v>77336.72</v>
+        <v>77392.67999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>27.64</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03436825893229203</v>
+        <v>0.03420652783691221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4961,16 +4961,16 @@
         <v>816</v>
       </c>
       <c r="H8" t="n">
-        <v>75700.32000000001</v>
+        <v>75178.08</v>
       </c>
       <c r="I8" t="n">
-        <v>92.77</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03380892128765363</v>
+        <v>0.03387116972086406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4996,16 +4996,16 @@
         <v>303</v>
       </c>
       <c r="H9" t="n">
-        <v>74468.31</v>
+        <v>74441.03999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>245.77</v>
+        <v>245.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03378583517696471</v>
+        <v>0.03357725361231843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>246</v>
       </c>
       <c r="H10" t="n">
-        <v>74417.46000000001</v>
+        <v>73795.08</v>
       </c>
       <c r="I10" t="n">
-        <v>302.51</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03184243412105912</v>
+        <v>0.03232236341675756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5066,16 +5066,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>70136.88</v>
+        <v>71037.12</v>
       </c>
       <c r="I11" t="n">
-        <v>102.84</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03139878127218561</v>
+        <v>0.03158441539910378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5101,16 +5101,16 @@
         <v>568</v>
       </c>
       <c r="H12" t="n">
-        <v>69159.67999999999</v>
+        <v>69415.28</v>
       </c>
       <c r="I12" t="n">
-        <v>121.76</v>
+        <v>122.21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0312418729002053</v>
+        <v>0.0313431299120757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5136,16 +5136,16 @@
         <v>197</v>
       </c>
       <c r="H13" t="n">
-        <v>68814.07000000001</v>
+        <v>68884.99000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>349.31</v>
+        <v>349.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0311028613715555</v>
+        <v>0.03107255109563377</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5171,16 +5171,16 @@
         <v>588</v>
       </c>
       <c r="H14" t="n">
-        <v>68507.88</v>
+        <v>68290.32000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>116.51</v>
+        <v>116.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5189,33 +5189,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03039499627142287</v>
+        <v>0.0307686657909487</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1076</v>
+        <v>245</v>
       </c>
       <c r="H15" t="n">
-        <v>66948.72</v>
+        <v>67622.45</v>
       </c>
       <c r="I15" t="n">
-        <v>62.22</v>
+        <v>276.01</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5224,33 +5224,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03016028974943951</v>
+        <v>0.03026627927641454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>245</v>
+        <v>1076</v>
       </c>
       <c r="H16" t="n">
-        <v>66431.75</v>
+        <v>66518.32000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>271.15</v>
+        <v>61.82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02954629454598421</v>
+        <v>0.02949187157429459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5276,16 +5276,16 @@
         <v>263</v>
       </c>
       <c r="H17" t="n">
-        <v>65079.35</v>
+        <v>64816.35</v>
       </c>
       <c r="I17" t="n">
-        <v>247.45</v>
+        <v>246.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5294,33 +5294,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0281574459310462</v>
+        <v>0.02819354189194995</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1082</v>
+        <v>1433</v>
       </c>
       <c r="H18" t="n">
-        <v>62020.24</v>
+        <v>61962.92</v>
       </c>
       <c r="I18" t="n">
-        <v>57.32</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5329,33 +5329,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02809889301667942</v>
+        <v>0.02789469351110165</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1433</v>
+        <v>1082</v>
       </c>
       <c r="H19" t="n">
-        <v>61891.27</v>
+        <v>61306.12</v>
       </c>
       <c r="I19" t="n">
-        <v>43.19</v>
+        <v>56.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02613105291773776</v>
+        <v>0.02616646442681868</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
         <v>213</v>
       </c>
       <c r="H20" t="n">
-        <v>57556.86</v>
+        <v>57507.87</v>
       </c>
       <c r="I20" t="n">
-        <v>270.22</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02570231864501446</v>
+        <v>0.02515689562744869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5416,16 +5416,16 @@
         <v>1557</v>
       </c>
       <c r="H21" t="n">
-        <v>56612.52</v>
+        <v>55289.07</v>
       </c>
       <c r="I21" t="n">
-        <v>36.36</v>
+        <v>35.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02275966354969668</v>
+        <v>0.02316247854108918</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5451,16 +5451,16 @@
         <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>50130.96</v>
+        <v>50905.8</v>
       </c>
       <c r="I22" t="n">
-        <v>379.78</v>
+        <v>385.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5469,33 +5469,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02262844273214663</v>
+        <v>0.02305136591227805</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Coca-Cola Femsa</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>443</v>
+        <v>190</v>
       </c>
       <c r="H23" t="n">
-        <v>49841.93</v>
+        <v>50661.6</v>
       </c>
       <c r="I23" t="n">
-        <v>112.51</v>
+        <v>266.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5504,33 +5504,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0223917295118497</v>
+        <v>0.02219666318310527</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Coca-Cola Femsa</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>369</v>
+        <v>443</v>
       </c>
       <c r="H24" t="n">
-        <v>49320.54</v>
+        <v>48783.16</v>
       </c>
       <c r="I24" t="n">
-        <v>133.66</v>
+        <v>110.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5539,33 +5539,33 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02226735961682268</v>
+        <v>0.02178469559403118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>190</v>
+        <v>369</v>
       </c>
       <c r="H25" t="n">
-        <v>49046.6</v>
+        <v>47877.75</v>
       </c>
       <c r="I25" t="n">
-        <v>258.14</v>
+        <v>129.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02113415619495895</v>
+        <v>0.02099641928861</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5591,16 +5591,16 @@
         <v>298</v>
       </c>
       <c r="H26" t="n">
-        <v>46550.58</v>
+        <v>46145.3</v>
       </c>
       <c r="I26" t="n">
-        <v>156.21</v>
+        <v>154.85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02104239741754816</v>
+        <v>0.02098413865858701</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5626,16 +5626,16 @@
         <v>959</v>
       </c>
       <c r="H27" t="n">
-        <v>46348.47</v>
+        <v>46118.31</v>
       </c>
       <c r="I27" t="n">
-        <v>48.33</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02039128737537467</v>
+        <v>0.02021131892974532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5661,16 +5661,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>44914.32</v>
+        <v>44419.83</v>
       </c>
       <c r="I28" t="n">
-        <v>282.48</v>
+        <v>279.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01936735367073042</v>
+        <v>0.01907923503441429</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5696,16 +5696,16 @@
         <v>601</v>
       </c>
       <c r="H29" t="n">
-        <v>42658.98</v>
+        <v>41931.77</v>
       </c>
       <c r="I29" t="n">
-        <v>70.98</v>
+        <v>69.77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01889070380071884</v>
+        <v>0.01878357625032261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5731,16 +5731,16 @@
         <v>282</v>
       </c>
       <c r="H30" t="n">
-        <v>41609.1</v>
+        <v>41281.98</v>
       </c>
       <c r="I30" t="n">
-        <v>147.55</v>
+        <v>146.39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01867773045707725</v>
+        <v>0.01830055026959646</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5766,16 +5766,16 @@
         <v>484</v>
       </c>
       <c r="H31" t="n">
-        <v>41140</v>
+        <v>40220.4</v>
       </c>
       <c r="I31" t="n">
-        <v>85</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0178293964749947</v>
+        <v>0.01788667620257512</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5801,16 +5801,16 @@
         <v>246</v>
       </c>
       <c r="H32" t="n">
-        <v>39271.44</v>
+        <v>39310.8</v>
       </c>
       <c r="I32" t="n">
-        <v>159.64</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01726850159614464</v>
+        <v>0.01732010189710572</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5836,16 +5836,16 @@
         <v>148</v>
       </c>
       <c r="H33" t="n">
-        <v>38036</v>
+        <v>38065.6</v>
       </c>
       <c r="I33" t="n">
-        <v>257</v>
+        <v>257.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01693204366555554</v>
+        <v>0.01675589817638696</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5871,16 +5871,16 @@
         <v>361</v>
       </c>
       <c r="H34" t="n">
-        <v>37294.91</v>
+        <v>36825.61</v>
       </c>
       <c r="I34" t="n">
-        <v>103.31</v>
+        <v>102.01</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0167217534864011</v>
+        <v>0.01647431729866471</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5906,16 +5906,16 @@
         <v>372</v>
       </c>
       <c r="H35" t="n">
-        <v>36831.72</v>
+        <v>36206.76</v>
       </c>
       <c r="I35" t="n">
-        <v>99.01000000000001</v>
+        <v>97.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01660710836012445</v>
+        <v>0.016315592771906</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>736</v>
       </c>
       <c r="H36" t="n">
-        <v>36579.2</v>
+        <v>35857.92</v>
       </c>
       <c r="I36" t="n">
-        <v>49.7</v>
+        <v>48.72</v>
       </c>
     </row>
   </sheetData>
@@ -6011,7 +6011,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1057701143366562</v>
+        <v>0.1056255747317636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6037,16 +6037,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>223174.9</v>
+        <v>222070</v>
       </c>
       <c r="I2" t="n">
-        <v>53.26</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09907290930731499</v>
+        <v>0.09895433059220057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6072,16 +6072,16 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>209043.8</v>
+        <v>208044.2</v>
       </c>
       <c r="I3" t="n">
-        <v>213.31</v>
+        <v>212.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09521139200589711</v>
+        <v>0.09565661710217371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6107,16 +6107,16 @@
         <v>4300</v>
       </c>
       <c r="H4" t="n">
-        <v>200896</v>
+        <v>201111</v>
       </c>
       <c r="I4" t="n">
-        <v>46.72</v>
+        <v>46.77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08525075509374147</v>
+        <v>0.08467822581549263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6142,16 +6142,16 @@
         <v>934</v>
       </c>
       <c r="H5" t="n">
-        <v>179879.06</v>
+        <v>178029.74</v>
       </c>
       <c r="I5" t="n">
-        <v>192.59</v>
+        <v>190.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05535095809804439</v>
+        <v>0.05481368972325943</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1475</v>
       </c>
       <c r="H6" t="n">
-        <v>116790.5</v>
+        <v>115241.75</v>
       </c>
       <c r="I6" t="n">
-        <v>79.18000000000001</v>
+        <v>78.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03807637670606015</v>
+        <v>0.03823927384702826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6212,16 +6212,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>80341.14</v>
+        <v>80395.25999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>29.69</v>
+        <v>29.71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02645861152552536</v>
+        <v>0.02696434424104914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6247,16 +6247,16 @@
         <v>147</v>
       </c>
       <c r="H8" t="n">
-        <v>55827.66</v>
+        <v>56690.55</v>
       </c>
       <c r="I8" t="n">
-        <v>379.78</v>
+        <v>385.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02476955434129204</v>
+        <v>0.02466050619426432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6282,16 +6282,16 @@
         <v>105</v>
       </c>
       <c r="H9" t="n">
-        <v>52263.75</v>
+        <v>51846.9</v>
       </c>
       <c r="I9" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.023537729469059</v>
+        <v>0.0232535984624204</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6317,16 +6317,16 @@
         <v>1860</v>
       </c>
       <c r="H10" t="n">
-        <v>49664.6</v>
+        <v>48888.98</v>
       </c>
       <c r="I10" t="n">
-        <v>26.7</v>
+        <v>26.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02080616498313002</v>
+        <v>0.0209020393641075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6352,16 +6352,16 @@
         <v>275</v>
       </c>
       <c r="H11" t="n">
-        <v>43901</v>
+        <v>43945</v>
       </c>
       <c r="I11" t="n">
-        <v>159.64</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02052891374705041</v>
+        <v>0.02080329631320322</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6387,16 +6387,16 @@
         <v>980</v>
       </c>
       <c r="H12" t="n">
-        <v>43316</v>
+        <v>43737.4</v>
       </c>
       <c r="I12" t="n">
-        <v>44.2</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02030412697564432</v>
+        <v>0.02074249989332564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6422,16 +6422,16 @@
         <v>158</v>
       </c>
       <c r="H13" t="n">
-        <v>42841.7</v>
+        <v>43609.58</v>
       </c>
       <c r="I13" t="n">
-        <v>271.15</v>
+        <v>276.01</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6440,33 +6440,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02025457246411529</v>
+        <v>0.02029008929458711</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="H14" t="n">
-        <v>42737.14</v>
+        <v>42658.42</v>
       </c>
       <c r="I14" t="n">
-        <v>211.57</v>
+        <v>269.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6475,33 +6475,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02023448715234597</v>
+        <v>0.02012960805482264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="H15" t="n">
-        <v>42694.76</v>
+        <v>42321.02</v>
       </c>
       <c r="I15" t="n">
-        <v>270.22</v>
+        <v>209.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01783755306002166</v>
+        <v>0.01800528639663268</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>37637.23</v>
+        <v>37854.79</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6545,33 +6545,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01733293211366992</v>
+        <v>0.01757885054746006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>ASML Holding</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>224</v>
+        <v>22</v>
       </c>
       <c r="H17" t="n">
-        <v>36572.48</v>
+        <v>36958.24</v>
       </c>
       <c r="I17" t="n">
-        <v>163.27</v>
+        <v>1679.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6580,33 +6580,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01699182304588199</v>
+        <v>0.01742413407540734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ASML Holding</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>22</v>
+        <v>224</v>
       </c>
       <c r="H18" t="n">
-        <v>35852.74</v>
+        <v>36632.96</v>
       </c>
       <c r="I18" t="n">
-        <v>1629.67</v>
+        <v>163.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6615,33 +6615,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01649486560805573</v>
+        <v>0.01646541800751621</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>488</v>
+        <v>99</v>
       </c>
       <c r="H19" t="n">
-        <v>34804.16</v>
+        <v>34617.33</v>
       </c>
       <c r="I19" t="n">
-        <v>71.31999999999999</v>
+        <v>349.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6650,33 +6650,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01638942956961021</v>
+        <v>0.01635234389628559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>99</v>
+        <v>488</v>
       </c>
       <c r="H20" t="n">
-        <v>34581.69</v>
+        <v>34379.6</v>
       </c>
       <c r="I20" t="n">
-        <v>349.31</v>
+        <v>70.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01598741527729477</v>
+        <v>0.01593875510783034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>306</v>
       </c>
       <c r="H21" t="n">
-        <v>33733.44</v>
+        <v>33510.06</v>
       </c>
       <c r="I21" t="n">
-        <v>110.24</v>
+        <v>109.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01467631550889244</v>
+        <v>0.01472378750489738</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6737,16 +6737,16 @@
         <v>126</v>
       </c>
       <c r="H22" t="n">
-        <v>30967.02</v>
+        <v>30955.68</v>
       </c>
       <c r="I22" t="n">
-        <v>245.77</v>
+        <v>245.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01417052394621059</v>
+        <v>0.014105701667763</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>84</v>
       </c>
       <c r="H23" t="n">
-        <v>29899.8</v>
+        <v>29656.2</v>
       </c>
       <c r="I23" t="n">
-        <v>355.95</v>
+        <v>353.05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01405571349844941</v>
+        <v>0.01399544335066222</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6807,16 +6807,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>29657.55</v>
+        <v>29424.39</v>
       </c>
       <c r="I24" t="n">
-        <v>147.55</v>
+        <v>146.39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01333057118432359</v>
+        <v>0.01309439398552462</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6842,16 +6842,16 @@
         <v>250</v>
       </c>
       <c r="H25" t="n">
-        <v>28127.5</v>
+        <v>27530</v>
       </c>
       <c r="I25" t="n">
-        <v>112.51</v>
+        <v>110.12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01260114924855365</v>
+        <v>0.01306296363483216</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6877,16 +6877,16 @@
         <v>103</v>
       </c>
       <c r="H26" t="n">
-        <v>26588.42</v>
+        <v>27463.92</v>
       </c>
       <c r="I26" t="n">
-        <v>258.14</v>
+        <v>266.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01220809704320277</v>
+        <v>0.01217330586925698</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>414</v>
       </c>
       <c r="H27" t="n">
-        <v>25759.08</v>
+        <v>25593.48</v>
       </c>
       <c r="I27" t="n">
-        <v>62.22</v>
+        <v>61.82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01193528182690043</v>
+        <v>0.01177390069244896</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6947,16 +6947,16 @@
         <v>524</v>
       </c>
       <c r="H28" t="n">
-        <v>25183.44</v>
+        <v>24753.76</v>
       </c>
       <c r="I28" t="n">
-        <v>48.06</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0112425660590525</v>
+        <v>0.01118820600062567</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6982,16 +6982,16 @@
         <v>259</v>
       </c>
       <c r="H29" t="n">
-        <v>23721.81</v>
+        <v>23522.38</v>
       </c>
       <c r="I29" t="n">
-        <v>91.59</v>
+        <v>90.81999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01104360393696945</v>
+        <v>0.01104818683239251</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>23302</v>
+        <v>23228</v>
       </c>
       <c r="I30" t="n">
-        <v>116.51</v>
+        <v>116.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01099170819278019</v>
+        <v>0.01095519903638198</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7052,16 +7052,16 @@
         <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>23192.5</v>
+        <v>23032.5</v>
       </c>
       <c r="I31" t="n">
-        <v>92.77</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.009722869095696184</v>
+        <v>0.009769188451459869</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7087,16 +7087,16 @@
         <v>475</v>
       </c>
       <c r="H32" t="n">
-        <v>20515.25</v>
+        <v>20539</v>
       </c>
       <c r="I32" t="n">
-        <v>43.19</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7105,33 +7105,33 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.00866629070135231</v>
+        <v>0.008669982330844272</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H33" t="n">
-        <v>18285.87</v>
+        <v>18228</v>
       </c>
       <c r="I33" t="n">
-        <v>103.31</v>
+        <v>104.16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.008635266998935607</v>
+        <v>0.008623336227750905</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -7157,16 +7157,16 @@
         <v>377</v>
       </c>
       <c r="H34" t="n">
-        <v>18220.41</v>
+        <v>18129.93</v>
       </c>
       <c r="I34" t="n">
-        <v>48.33</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7175,33 +7175,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.008529385462777409</v>
+        <v>0.008588062698583941</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H35" t="n">
-        <v>17997</v>
+        <v>18055.77</v>
       </c>
       <c r="I35" t="n">
-        <v>102.84</v>
+        <v>102.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.008514693516933873</v>
+        <v>0.00855154774666717</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -7227,16 +7227,16 @@
         <v>650</v>
       </c>
       <c r="H36" t="n">
-        <v>17966</v>
+        <v>17979</v>
       </c>
       <c r="I36" t="n">
-        <v>27.64</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7245,33 +7245,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.008361669791967402</v>
+        <v>0.008369767307386828</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>132</v>
+        <v>362</v>
       </c>
       <c r="H37" t="n">
-        <v>17643.12</v>
+        <v>17596.82</v>
       </c>
       <c r="I37" t="n">
-        <v>133.66</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7280,33 +7280,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008358598701352367</v>
+        <v>0.008146301699603349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>362</v>
+        <v>132</v>
       </c>
       <c r="H38" t="n">
-        <v>17636.64</v>
+        <v>17127</v>
       </c>
       <c r="I38" t="n">
-        <v>48.72</v>
+        <v>129.75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008126304819553972</v>
+        <v>0.007994762508764696</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7332,16 +7332,16 @@
         <v>345</v>
       </c>
       <c r="H39" t="n">
-        <v>17146.5</v>
+        <v>16808.4</v>
       </c>
       <c r="I39" t="n">
-        <v>49.7</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.007905356911416681</v>
+        <v>0.007798584419431981</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7367,16 +7367,16 @@
         <v>235</v>
       </c>
       <c r="H40" t="n">
-        <v>16680.3</v>
+        <v>16395.95</v>
       </c>
       <c r="I40" t="n">
-        <v>70.98</v>
+        <v>69.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.007389119849173812</v>
+        <v>0.007330349247940154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7402,16 +7402,16 @@
         <v>272</v>
       </c>
       <c r="H41" t="n">
-        <v>15591.04</v>
+        <v>15411.52</v>
       </c>
       <c r="I41" t="n">
-        <v>57.32</v>
+        <v>56.66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.007229347307794053</v>
+        <v>0.00717550910925335</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7437,16 +7437,16 @@
         <v>54</v>
       </c>
       <c r="H42" t="n">
-        <v>15253.92</v>
+        <v>15085.98</v>
       </c>
       <c r="I42" t="n">
-        <v>282.48</v>
+        <v>279.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.007147655349566628</v>
+        <v>0.007145148950586586</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7472,16 +7472,16 @@
         <v>55</v>
       </c>
       <c r="H43" t="n">
-        <v>15081.55</v>
+        <v>15022.15</v>
       </c>
       <c r="I43" t="n">
-        <v>274.21</v>
+        <v>273.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.007009479968576867</v>
+        <v>0.006877482033937331</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7507,16 +7507,16 @@
         <v>174</v>
       </c>
       <c r="H44" t="n">
-        <v>14790</v>
+        <v>14459.4</v>
       </c>
       <c r="I44" t="n">
-        <v>85</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.004738863435145375</v>
+        <v>0.004644752301748795</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7542,16 +7542,16 @@
         <v>275</v>
       </c>
       <c r="H45" t="n">
-        <v>9999</v>
+        <v>9765.25</v>
       </c>
       <c r="I45" t="n">
-        <v>36.36</v>
+        <v>35.51</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.004157721147635663</v>
+        <v>0.004137799960971762</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7577,16 +7577,16 @@
         <v>29</v>
       </c>
       <c r="H46" t="n">
-        <v>8772.790000000001</v>
+        <v>8699.42</v>
       </c>
       <c r="I46" t="n">
-        <v>302.51</v>
+        <v>299.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/17/2026</t>
+          <t>09/18/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.002591161616375844</v>
+        <v>0.002577854769453217</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7612,261 +7612,13 @@
         <v>35</v>
       </c>
       <c r="H47" t="n">
-        <v>5467.35</v>
+        <v>5419.75</v>
       </c>
       <c r="I47" t="n">
-        <v>156.21</v>
+        <v>154.85</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D26BF95A-43CA-4568-9DA7-5A6DF5446B79}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0021218C-751D-4994-9592-9E5B6BE2FE5B}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EA72EE7-E3C4-45CE-90A5-84E674A89DD2}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -7621,4 +7621,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98134DFC-9C7F-4F91-8C9A-03146AE1A1B7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D03BA1F6-C27A-46A3-B460-6DC7BFC36AB6}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EF6E36F-DFA6-4C75-8C30-E4069DA2BD16}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09549178750515419</v>
+        <v>0.1095689346521751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>223573.42</v>
+        <v>255846.16</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04430895100149459</v>
+        <v>0.04529290145129176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>103739.85</v>
+        <v>105760.04</v>
       </c>
       <c r="I3" t="n">
-        <v>385.65</v>
+        <v>393.16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04102512506949872</v>
+        <v>0.0410635670299699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>96051.48</v>
+        <v>95884.44</v>
       </c>
       <c r="I4" t="n">
-        <v>276.01</v>
+        <v>275.53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,33 +596,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03838909745034934</v>
+        <v>0.03813798759860614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>429</v>
+        <v>561</v>
       </c>
       <c r="H5" t="n">
-        <v>89879.78999999999</v>
+        <v>89053.14</v>
       </c>
       <c r="I5" t="n">
-        <v>209.51</v>
+        <v>158.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,33 +631,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03829001080676121</v>
+        <v>0.03773694257664829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>561</v>
+        <v>327</v>
       </c>
       <c r="H6" t="n">
-        <v>89647.8</v>
+        <v>88116.69</v>
       </c>
       <c r="I6" t="n">
-        <v>159.8</v>
+        <v>269.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,33 +666,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03770867601651807</v>
+        <v>0.0374190615600447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>327</v>
+        <v>429</v>
       </c>
       <c r="H7" t="n">
-        <v>88286.73</v>
+        <v>87374.42999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>269.99</v>
+        <v>203.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03444099506976998</v>
+        <v>0.03517879824324936</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         <v>48</v>
       </c>
       <c r="H8" t="n">
-        <v>80636.16</v>
+        <v>82143.36</v>
       </c>
       <c r="I8" t="n">
-        <v>1679.92</v>
+        <v>1711.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,33 +736,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03303931136905473</v>
+        <v>0.03220445701339115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>473</v>
+        <v>1045</v>
       </c>
       <c r="H9" t="n">
-        <v>77354.42</v>
+        <v>75198.2</v>
       </c>
       <c r="I9" t="n">
-        <v>163.54</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,33 +771,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03144438757110003</v>
+        <v>0.03206642849016298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1045</v>
+        <v>473</v>
       </c>
       <c r="H10" t="n">
-        <v>73620.25</v>
+        <v>74875.89999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>70.45</v>
+        <v>158.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03138500136081298</v>
+        <v>0.03202949526073948</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         <v>671</v>
       </c>
       <c r="H11" t="n">
-        <v>73481.21000000001</v>
+        <v>74789.66</v>
       </c>
       <c r="I11" t="n">
-        <v>109.51</v>
+        <v>111.46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,33 +841,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02940469505652981</v>
+        <v>0.02964516065787777</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="H12" t="n">
-        <v>68844.75</v>
+        <v>69222.17999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>353.05</v>
+        <v>501.61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,33 +876,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02910438551744082</v>
+        <v>0.02955450636747462</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="H13" t="n">
-        <v>68141.64</v>
+        <v>69010.5</v>
       </c>
       <c r="I13" t="n">
-        <v>493.78</v>
+        <v>353.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02792838564622484</v>
+        <v>0.02819305605437256</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>187</v>
       </c>
       <c r="H14" t="n">
-        <v>65388.29</v>
+        <v>65831.48</v>
       </c>
       <c r="I14" t="n">
-        <v>349.67</v>
+        <v>352.04</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02759760565085077</v>
+        <v>0.02760964036430588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -963,16 +963,16 @@
         <v>263</v>
       </c>
       <c r="H15" t="n">
-        <v>64613.84</v>
+        <v>64469.19</v>
       </c>
       <c r="I15" t="n">
-        <v>245.68</v>
+        <v>245.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02732364916969267</v>
+        <v>0.02733888090653194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -998,16 +998,16 @@
         <v>437</v>
       </c>
       <c r="H16" t="n">
-        <v>63972.43</v>
+        <v>63836.96</v>
       </c>
       <c r="I16" t="n">
-        <v>146.39</v>
+        <v>146.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02551051180128589</v>
+        <v>0.02598468533492379</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>224</v>
       </c>
       <c r="H17" t="n">
-        <v>59727.36</v>
+        <v>60674.88</v>
       </c>
       <c r="I17" t="n">
-        <v>266.64</v>
+        <v>270.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02541588424886142</v>
+        <v>0.0245955393823642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1068,16 +1068,16 @@
         <v>213</v>
       </c>
       <c r="H18" t="n">
-        <v>59505.81</v>
+        <v>57431.19</v>
       </c>
       <c r="I18" t="n">
-        <v>279.37</v>
+        <v>269.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,33 +1086,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02429166792292164</v>
+        <v>0.02390923826747489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1170</v>
+        <v>898</v>
       </c>
       <c r="H19" t="n">
-        <v>56873.7</v>
+        <v>55828.66</v>
       </c>
       <c r="I19" t="n">
-        <v>48.61</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,33 +1121,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.023711072043379</v>
+        <v>0.023845701464167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>898</v>
+        <v>1170</v>
       </c>
       <c r="H20" t="n">
-        <v>55514.36</v>
+        <v>55680.3</v>
       </c>
       <c r="I20" t="n">
-        <v>61.82</v>
+        <v>47.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0233470367953226</v>
+        <v>0.0229122552035447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         <v>353</v>
       </c>
       <c r="H21" t="n">
-        <v>54662.05</v>
+        <v>53500.68</v>
       </c>
       <c r="I21" t="n">
-        <v>154.85</v>
+        <v>151.56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02183935998510766</v>
+        <v>0.02180758590888005</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1208,16 +1208,16 @@
         <v>555</v>
       </c>
       <c r="H22" t="n">
-        <v>51132.15</v>
+        <v>50921.25</v>
       </c>
       <c r="I22" t="n">
-        <v>92.13</v>
+        <v>91.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02156761596489093</v>
+        <v>0.02175571065284956</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Total SA</t>
+          <t>Coca-Cola Femsa</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>556</v>
+        <v>457</v>
       </c>
       <c r="H23" t="n">
-        <v>50495.92</v>
+        <v>50800.12</v>
       </c>
       <c r="I23" t="n">
-        <v>90.81999999999999</v>
+        <v>111.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,33 +1261,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02149454495758433</v>
+        <v>0.0214444676818868</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Coca-Cola Femsa</t>
+          <t>Total SA</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="H24" t="n">
-        <v>50324.84</v>
+        <v>50073.36</v>
       </c>
       <c r="I24" t="n">
-        <v>110.12</v>
+        <v>90.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02113183804032477</v>
+        <v>0.02098233122698295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         <v>426</v>
       </c>
       <c r="H25" t="n">
-        <v>49475.64</v>
+        <v>48994.26</v>
       </c>
       <c r="I25" t="n">
-        <v>116.14</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0209091397517483</v>
+        <v>0.02096149204628086</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         <v>864</v>
       </c>
       <c r="H26" t="n">
-        <v>48954.24</v>
+        <v>48945.6</v>
       </c>
       <c r="I26" t="n">
-        <v>56.66</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,33 +1366,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02007525553486079</v>
+        <v>0.01908861243612926</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1087</v>
+        <v>426</v>
       </c>
       <c r="H27" t="n">
-        <v>47001.88</v>
+        <v>44572.38</v>
       </c>
       <c r="I27" t="n">
-        <v>43.24</v>
+        <v>104.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,33 +1401,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01895206001618932</v>
+        <v>0.01890843446438693</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>426</v>
+        <v>938</v>
       </c>
       <c r="H28" t="n">
-        <v>44372.16</v>
+        <v>44151.66</v>
       </c>
       <c r="I28" t="n">
-        <v>104.16</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,33 +1436,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01892598885482625</v>
+        <v>0.01878592612012802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>938</v>
+        <v>920</v>
       </c>
       <c r="H29" t="n">
-        <v>44311.12</v>
+        <v>43865.6</v>
       </c>
       <c r="I29" t="n">
-        <v>47.24</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,33 +1471,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01889680828889694</v>
+        <v>0.01852768473164964</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>920</v>
+        <v>1087</v>
       </c>
       <c r="H30" t="n">
-        <v>44242.8</v>
+        <v>43262.6</v>
       </c>
       <c r="I30" t="n">
-        <v>48.09</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01834345813974994</v>
+        <v>0.01836995191939347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1523,16 +1523,16 @@
         <v>331</v>
       </c>
       <c r="H31" t="n">
-        <v>42947.25</v>
+        <v>42894.29</v>
       </c>
       <c r="I31" t="n">
-        <v>129.75</v>
+        <v>129.59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0177682994470381</v>
+        <v>0.01786746042960352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1558,16 +1558,16 @@
         <v>1504</v>
       </c>
       <c r="H32" t="n">
-        <v>41600.64</v>
+        <v>41720.96</v>
       </c>
       <c r="I32" t="n">
-        <v>27.66</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01668793512203454</v>
+        <v>0.01662235150222956</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>39071.2</v>
+        <v>38813.6</v>
       </c>
       <c r="I33" t="n">
-        <v>69.77</v>
+        <v>69.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01616450872067748</v>
+        <v>0.01613952147536671</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>37845.71</v>
+        <v>37686.18</v>
       </c>
       <c r="I34" t="n">
-        <v>102.01</v>
+        <v>101.58</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,33 +1646,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01411564175417281</v>
+        <v>0.01355884633027981</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>121</v>
+        <v>373</v>
       </c>
       <c r="H35" t="n">
-        <v>33048.73</v>
+        <v>31660.24</v>
       </c>
       <c r="I35" t="n">
-        <v>273.13</v>
+        <v>84.88</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,33 +1681,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01323901603797988</v>
+        <v>0.01107328795531072</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>373</v>
+        <v>87</v>
       </c>
       <c r="H36" t="n">
-        <v>30996.3</v>
+        <v>25856.4</v>
       </c>
       <c r="I36" t="n">
-        <v>83.09999999999999</v>
+        <v>297.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,33 +1716,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01114698472731806</v>
+        <v>0.01092946934323973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>87</v>
+        <v>522</v>
       </c>
       <c r="H37" t="n">
-        <v>26098.26</v>
+        <v>25520.58</v>
       </c>
       <c r="I37" t="n">
-        <v>299.98</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,62 +1751,27 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01086234607470369</v>
+        <v>0.008889627896086166</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>522</v>
+        <v>575</v>
       </c>
       <c r="H38" t="n">
-        <v>25431.84</v>
+        <v>20757.5</v>
       </c>
       <c r="I38" t="n">
-        <v>48.72</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>09/18/2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Quality Dividend Strategy</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>0.008720961508873078</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NKE</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>575</v>
-      </c>
-      <c r="H39" t="n">
-        <v>20418.25</v>
-      </c>
-      <c r="I39" t="n">
-        <v>35.51</v>
+        <v>36.1</v>
       </c>
     </row>
   </sheetData>
@@ -1873,7 +1838,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1882,7 +1847,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06062428813029756</v>
+        <v>0.06033916925316867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1899,16 +1864,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>155165.8</v>
+        <v>154136.54</v>
       </c>
       <c r="I2" t="n">
-        <v>159.8</v>
+        <v>158.74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1917,7 +1882,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05705269927152342</v>
+        <v>0.05596407807346605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1934,16 +1899,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>146024.44</v>
+        <v>142960.36</v>
       </c>
       <c r="I3" t="n">
-        <v>48.61</v>
+        <v>47.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1952,7 +1917,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.053537028328406</v>
+        <v>0.0532993397042263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1969,16 +1934,16 @@
         <v>556</v>
       </c>
       <c r="H4" t="n">
-        <v>137026.2</v>
+        <v>136153.28</v>
       </c>
       <c r="I4" t="n">
-        <v>246.45</v>
+        <v>244.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1987,7 +1952,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05052917035703617</v>
+        <v>0.05062735530479229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2013,7 +1978,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2022,33 +1987,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04968743615977729</v>
+        <v>0.05017054222999121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1095</v>
+        <v>1781</v>
       </c>
       <c r="H6" t="n">
-        <v>127173.3</v>
+        <v>128160.76</v>
       </c>
       <c r="I6" t="n">
-        <v>116.14</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2057,33 +2022,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04902251228638156</v>
+        <v>0.04929960541548803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1781</v>
+        <v>1095</v>
       </c>
       <c r="H7" t="n">
-        <v>125471.45</v>
+        <v>125935.95</v>
       </c>
       <c r="I7" t="n">
-        <v>70.45</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2092,7 +2057,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0431949488774793</v>
+        <v>0.04318199468836628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2109,16 +2074,16 @@
         <v>450</v>
       </c>
       <c r="H8" t="n">
-        <v>110556</v>
+        <v>110308.5</v>
       </c>
       <c r="I8" t="n">
-        <v>245.68</v>
+        <v>245.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2127,7 +2092,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04253213481923552</v>
+        <v>0.04170937117106172</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2144,16 +2109,16 @@
         <v>703</v>
       </c>
       <c r="H9" t="n">
-        <v>108859.55</v>
+        <v>106546.68</v>
       </c>
       <c r="I9" t="n">
-        <v>154.85</v>
+        <v>151.56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2162,7 +2127,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03886992158555516</v>
+        <v>0.03908134445560997</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2179,16 +2144,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>99486.24000000001</v>
+        <v>99833.38</v>
       </c>
       <c r="I10" t="n">
-        <v>48.72</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2197,7 +2162,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03800760106230443</v>
+        <v>0.03790072303676514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2214,16 +2179,16 @@
         <v>796</v>
       </c>
       <c r="H11" t="n">
-        <v>97279.16</v>
+        <v>96817.48</v>
       </c>
       <c r="I11" t="n">
-        <v>122.21</v>
+        <v>121.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2232,7 +2197,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03696344572947685</v>
+        <v>0.03665758454487762</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2249,16 +2214,16 @@
         <v>804</v>
       </c>
       <c r="H12" t="n">
-        <v>94606.67999999999</v>
+        <v>93641.88</v>
       </c>
       <c r="I12" t="n">
-        <v>117.67</v>
+        <v>116.47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2267,7 +2232,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03558949503187957</v>
+        <v>0.03654901936098948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2284,16 +2249,16 @@
         <v>295</v>
       </c>
       <c r="H13" t="n">
-        <v>91090.10000000001</v>
+        <v>93364.55</v>
       </c>
       <c r="I13" t="n">
-        <v>308.78</v>
+        <v>316.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2302,7 +2267,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03513006324721814</v>
+        <v>0.03595227295538158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2319,16 +2284,16 @@
         <v>1082</v>
       </c>
       <c r="H14" t="n">
-        <v>89914.2</v>
+        <v>91840.16</v>
       </c>
       <c r="I14" t="n">
-        <v>83.09999999999999</v>
+        <v>84.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2337,7 +2302,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03318564197492561</v>
+        <v>0.03313047071609675</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2354,16 +2319,16 @@
         <v>1798</v>
       </c>
       <c r="H15" t="n">
-        <v>84937.52</v>
+        <v>84631.86</v>
       </c>
       <c r="I15" t="n">
-        <v>47.24</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2337,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03286013656763152</v>
+        <v>0.03306735861518287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2389,16 +2354,16 @@
         <v>327</v>
       </c>
       <c r="H16" t="n">
-        <v>84104.39999999999</v>
+        <v>84470.64</v>
       </c>
       <c r="I16" t="n">
-        <v>257.2</v>
+        <v>258.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2407,7 +2372,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03248372991626421</v>
+        <v>0.03303602570017762</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2424,16 +2389,16 @@
         <v>710</v>
       </c>
       <c r="H17" t="n">
-        <v>83141</v>
+        <v>84390.60000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>117.1</v>
+        <v>118.86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2442,7 +2407,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03184953510985005</v>
+        <v>0.03159081261151709</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,16 +2424,16 @@
         <v>910</v>
       </c>
       <c r="H18" t="n">
-        <v>81517.8</v>
+        <v>80698.8</v>
       </c>
       <c r="I18" t="n">
-        <v>89.58</v>
+        <v>88.68000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2477,7 +2442,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0312613069242926</v>
+        <v>0.03112005552831412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,16 +2459,16 @@
         <v>215</v>
       </c>
       <c r="H19" t="n">
-        <v>80012.25</v>
+        <v>79496.25</v>
       </c>
       <c r="I19" t="n">
-        <v>372.15</v>
+        <v>369.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2512,7 +2477,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03076616847171707</v>
+        <v>0.03096504685321879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,16 +2494,16 @@
         <v>756</v>
       </c>
       <c r="H20" t="n">
-        <v>78744.96000000001</v>
+        <v>79100.28</v>
       </c>
       <c r="I20" t="n">
-        <v>104.16</v>
+        <v>104.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2547,7 +2512,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03025963701732103</v>
+        <v>0.03004151270663033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2564,16 +2529,16 @@
         <v>1179</v>
       </c>
       <c r="H21" t="n">
-        <v>77448.50999999999</v>
+        <v>76741.11</v>
       </c>
       <c r="I21" t="n">
-        <v>65.69</v>
+        <v>65.09</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2582,7 +2547,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02916957757667827</v>
+        <v>0.02935272879918729</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2599,16 +2564,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>74658.53999999999</v>
+        <v>74981.61</v>
       </c>
       <c r="I22" t="n">
-        <v>76.26000000000001</v>
+        <v>76.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2617,7 +2582,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02621128072605366</v>
+        <v>0.02604123819521956</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2634,16 +2599,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>67086.88</v>
+        <v>66522.39999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>85.56999999999999</v>
+        <v>84.84999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2652,7 +2617,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02563601227542029</v>
+        <v>0.02522957320306702</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2669,16 +2634,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>65614.5</v>
+        <v>64449</v>
       </c>
       <c r="I24" t="n">
-        <v>20.83</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2687,7 +2652,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02450472939094759</v>
+        <v>0.02440459446229718</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2704,16 +2669,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>62719.02</v>
+        <v>62341.59</v>
       </c>
       <c r="I25" t="n">
-        <v>38.22</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2722,7 +2687,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02228409424461454</v>
+        <v>0.02225857555440186</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2739,16 +2704,16 @@
         <v>586</v>
       </c>
       <c r="H26" t="n">
-        <v>57035.38</v>
+        <v>56859.58</v>
       </c>
       <c r="I26" t="n">
-        <v>97.33</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2757,7 +2722,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02207995790746861</v>
+        <v>0.02219001425087837</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2774,16 +2739,16 @@
         <v>953</v>
       </c>
       <c r="H27" t="n">
-        <v>56512.9</v>
+        <v>56684.44</v>
       </c>
       <c r="I27" t="n">
-        <v>59.3</v>
+        <v>59.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2792,7 +2757,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02114265299089174</v>
+        <v>0.02105937517321135</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2809,16 +2774,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>54113.9</v>
+        <v>53796.22</v>
       </c>
       <c r="I28" t="n">
-        <v>74.95</v>
+        <v>74.51000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2827,7 +2792,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01556479401935231</v>
+        <v>0.01578021743641567</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2844,10 +2809,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>39837.56</v>
+        <v>40310.6</v>
       </c>
       <c r="I29" t="n">
-        <v>272.86</v>
+        <v>276.1</v>
       </c>
     </row>
   </sheetData>
@@ -2861,7 +2826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2914,7 +2879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2923,7 +2888,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.09421464517698616</v>
+        <v>0.1071066543168815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2940,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>279504.68</v>
+        <v>317111.75</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -2949,7 +2914,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2958,7 +2923,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03823807069165453</v>
+        <v>0.03824853745304416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2975,16 +2940,16 @@
         <v>411</v>
       </c>
       <c r="H3" t="n">
-        <v>113440.11</v>
+        <v>113242.83</v>
       </c>
       <c r="I3" t="n">
-        <v>276.01</v>
+        <v>275.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2993,7 +2958,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03600828501964191</v>
+        <v>0.03678351389536768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3010,16 +2975,16 @@
         <v>277</v>
       </c>
       <c r="H4" t="n">
-        <v>106825.05</v>
+        <v>108905.32</v>
       </c>
       <c r="I4" t="n">
-        <v>385.65</v>
+        <v>393.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3028,7 +2993,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03447355583291388</v>
+        <v>0.03431393064434709</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3045,16 +3010,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>102272</v>
+        <v>101593.6</v>
       </c>
       <c r="I5" t="n">
-        <v>159.8</v>
+        <v>158.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3063,7 +3028,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03340375043851632</v>
+        <v>0.0325381100216949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3080,16 +3045,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>99098.23</v>
+        <v>96335.91</v>
       </c>
       <c r="I6" t="n">
-        <v>209.51</v>
+        <v>203.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3098,33 +3063,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03103354516105084</v>
+        <v>0.03154766180803378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>341</v>
+        <v>838</v>
       </c>
       <c r="H7" t="n">
-        <v>92066.59</v>
+        <v>93403.48</v>
       </c>
       <c r="I7" t="n">
-        <v>269.99</v>
+        <v>111.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3133,33 +3098,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0309333624568004</v>
+        <v>0.03103622706292211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>838</v>
+        <v>341</v>
       </c>
       <c r="H8" t="n">
-        <v>91769.38</v>
+        <v>91889.27</v>
       </c>
       <c r="I8" t="n">
-        <v>109.51</v>
+        <v>269.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3168,7 +3133,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03048445657135725</v>
+        <v>0.02956719770943327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3185,16 +3150,16 @@
         <v>553</v>
       </c>
       <c r="H9" t="n">
-        <v>90437.62</v>
+        <v>87539.89999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>163.54</v>
+        <v>158.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3203,7 +3168,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02738039048535657</v>
+        <v>0.0280236423149667</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3220,16 +3185,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>81228.85000000001</v>
+        <v>82969.88</v>
       </c>
       <c r="I10" t="n">
-        <v>70.45</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3238,7 +3203,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02590598125732985</v>
+        <v>0.02590324556838489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3255,16 +3220,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>76854.75</v>
+        <v>76692</v>
       </c>
       <c r="I11" t="n">
-        <v>146.39</v>
+        <v>146.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3273,7 +3238,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02459549602548101</v>
+        <v>0.02458991535094823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3290,16 +3255,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>72966.96000000001</v>
+        <v>72803.61</v>
       </c>
       <c r="I12" t="n">
-        <v>245.68</v>
+        <v>245.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3308,7 +3273,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02404461755604055</v>
+        <v>0.02425639738510431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3325,16 +3290,16 @@
         <v>204</v>
       </c>
       <c r="H13" t="n">
-        <v>71332.67999999999</v>
+        <v>71816.16</v>
       </c>
       <c r="I13" t="n">
-        <v>349.67</v>
+        <v>352.04</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3343,7 +3308,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02381773765772999</v>
+        <v>0.02424436986496284</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3360,16 +3325,16 @@
         <v>265</v>
       </c>
       <c r="H14" t="n">
-        <v>70659.60000000001</v>
+        <v>71780.55</v>
       </c>
       <c r="I14" t="n">
-        <v>266.64</v>
+        <v>270.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3378,7 +3343,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02346831672680545</v>
+        <v>0.02388852955129105</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3395,16 +3360,16 @@
         <v>141</v>
       </c>
       <c r="H15" t="n">
-        <v>69622.98</v>
+        <v>70727.00999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3413,7 +3378,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02226347484928227</v>
+        <v>0.02216625013877161</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3430,16 +3395,16 @@
         <v>268</v>
       </c>
       <c r="H16" t="n">
-        <v>66048.60000000001</v>
+        <v>65627.84</v>
       </c>
       <c r="I16" t="n">
-        <v>246.45</v>
+        <v>244.88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3448,33 +3413,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02223566598315845</v>
+        <v>0.0218743809656445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>426</v>
+        <v>183</v>
       </c>
       <c r="H17" t="n">
-        <v>65966.10000000001</v>
+        <v>64763.7</v>
       </c>
       <c r="I17" t="n">
-        <v>154.85</v>
+        <v>353.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3483,33 +3448,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0220356039441062</v>
+        <v>0.02180712007373285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>234</v>
+        <v>426</v>
       </c>
       <c r="H18" t="n">
-        <v>65372.58</v>
+        <v>64564.56</v>
       </c>
       <c r="I18" t="n">
-        <v>279.37</v>
+        <v>151.56</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3518,33 +3483,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02177793204676036</v>
+        <v>0.02164845205528686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>183</v>
+        <v>1311</v>
       </c>
       <c r="H19" t="n">
-        <v>64608.15</v>
+        <v>64094.79</v>
       </c>
       <c r="I19" t="n">
-        <v>353.05</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3553,33 +3518,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02152976572547138</v>
+        <v>0.02131023251459404</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1311</v>
+        <v>234</v>
       </c>
       <c r="H20" t="n">
-        <v>63871.92</v>
+        <v>63093.42</v>
       </c>
       <c r="I20" t="n">
-        <v>48.72</v>
+        <v>269.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3588,7 +3553,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0214531817935522</v>
+        <v>0.02128728531666054</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3605,16 +3570,16 @@
         <v>548</v>
       </c>
       <c r="H21" t="n">
-        <v>63644.72</v>
+        <v>63025.48</v>
       </c>
       <c r="I21" t="n">
-        <v>116.14</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3623,7 +3588,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02037202701100447</v>
+        <v>0.02032890711247522</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3640,16 +3605,16 @@
         <v>656</v>
       </c>
       <c r="H22" t="n">
-        <v>60437.28</v>
+        <v>60188</v>
       </c>
       <c r="I22" t="n">
-        <v>92.13</v>
+        <v>91.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3658,33 +3623,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0196787705177817</v>
+        <v>0.01932526274009667</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1201</v>
+        <v>1010</v>
       </c>
       <c r="H23" t="n">
-        <v>58380.61</v>
+        <v>57216.5</v>
       </c>
       <c r="I23" t="n">
-        <v>48.61</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3693,33 +3658,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0192897800984417</v>
+        <v>0.01930468997256459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1010</v>
+        <v>1201</v>
       </c>
       <c r="H24" t="n">
-        <v>57226.6</v>
+        <v>57155.59</v>
       </c>
       <c r="I24" t="n">
-        <v>56.66</v>
+        <v>47.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3728,7 +3693,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01740683334626867</v>
+        <v>0.01742042239211893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3745,16 +3710,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>51640.5</v>
+        <v>51576.82</v>
       </c>
       <c r="I25" t="n">
-        <v>129.75</v>
+        <v>129.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3763,7 +3728,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01685277960993262</v>
+        <v>0.0169629578082936</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3780,16 +3745,16 @@
         <v>480</v>
       </c>
       <c r="H26" t="n">
-        <v>49996.8</v>
+        <v>50222.4</v>
       </c>
       <c r="I26" t="n">
-        <v>104.16</v>
+        <v>104.63</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3798,7 +3763,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0164364859402165</v>
+        <v>0.01639146314654174</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3815,16 +3780,16 @@
         <v>399</v>
       </c>
       <c r="H27" t="n">
-        <v>48761.79</v>
+        <v>48530.37</v>
       </c>
       <c r="I27" t="n">
-        <v>122.21</v>
+        <v>121.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3833,7 +3798,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01622298463459024</v>
+        <v>0.01630271078856431</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3850,16 +3815,16 @@
         <v>1740</v>
       </c>
       <c r="H28" t="n">
-        <v>48128.4</v>
+        <v>48267.6</v>
       </c>
       <c r="I28" t="n">
-        <v>27.66</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3868,7 +3833,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01594511844428102</v>
+        <v>0.01587192899303376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,16 +3850,16 @@
         <v>678</v>
       </c>
       <c r="H29" t="n">
-        <v>47304.06</v>
+        <v>46992.18</v>
       </c>
       <c r="I29" t="n">
-        <v>69.77</v>
+        <v>69.31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3903,7 +3868,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01566874887658501</v>
+        <v>0.01564384181663556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,16 +3885,16 @@
         <v>984</v>
       </c>
       <c r="H30" t="n">
-        <v>46484.16</v>
+        <v>46316.88</v>
       </c>
       <c r="I30" t="n">
-        <v>47.24</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3938,7 +3903,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01488081751999015</v>
+        <v>0.01478369680419265</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3955,16 +3920,16 @@
         <v>918</v>
       </c>
       <c r="H31" t="n">
-        <v>44146.62</v>
+        <v>43770.24</v>
       </c>
       <c r="I31" t="n">
-        <v>48.09</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3973,7 +3938,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01378146731206831</v>
+        <v>0.01410504879324439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3990,16 +3955,16 @@
         <v>492</v>
       </c>
       <c r="H32" t="n">
-        <v>40885.2</v>
+        <v>41760.96</v>
       </c>
       <c r="I32" t="n">
-        <v>83.09999999999999</v>
+        <v>84.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,7 +3973,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0137236990275071</v>
+        <v>0.01361113349406752</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4025,16 +3990,16 @@
         <v>346</v>
       </c>
       <c r="H33" t="n">
-        <v>40713.82</v>
+        <v>40298.62</v>
       </c>
       <c r="I33" t="n">
-        <v>117.67</v>
+        <v>116.47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4043,7 +4008,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01326452577161387</v>
+        <v>0.01334914904383056</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4060,16 +4025,16 @@
         <v>153</v>
       </c>
       <c r="H34" t="n">
-        <v>39351.6</v>
+        <v>39522.96</v>
       </c>
       <c r="I34" t="n">
-        <v>257.2</v>
+        <v>258.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4078,33 +4043,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01298128994206402</v>
+        <v>0.01293449513616171</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="H35" t="n">
-        <v>38511.33</v>
+        <v>38295.29</v>
       </c>
       <c r="I35" t="n">
-        <v>273.13</v>
+        <v>316.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4113,7 +4078,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01292885084748362</v>
+        <v>0.01290031076903116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4130,16 +4095,16 @@
         <v>376</v>
       </c>
       <c r="H36" t="n">
-        <v>38355.76</v>
+        <v>38194.08</v>
       </c>
       <c r="I36" t="n">
-        <v>102.01</v>
+        <v>101.58</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4148,33 +4113,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01259400513317961</v>
+        <v>0.01244519021749401</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Allison Transmission</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>121</v>
+        <v>310</v>
       </c>
       <c r="H37" t="n">
-        <v>37362.38</v>
+        <v>36846.6</v>
       </c>
       <c r="I37" t="n">
-        <v>308.78</v>
+        <v>118.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4183,33 +4148,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01223623817164626</v>
+        <v>0.01200312058924432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>GGG</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Allison Transmission</t>
+          <t>Graco Inc.</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>310</v>
+        <v>464</v>
       </c>
       <c r="H38" t="n">
-        <v>36301</v>
+        <v>35537.76</v>
       </c>
       <c r="I38" t="n">
-        <v>117.1</v>
+        <v>76.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4218,33 +4183,33 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01192735414060112</v>
+        <v>0.01164423370911154</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GGG</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Graco Inc.</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>464</v>
+        <v>116</v>
       </c>
       <c r="H39" t="n">
-        <v>35384.64</v>
+        <v>34475.2</v>
       </c>
       <c r="I39" t="n">
-        <v>76.26000000000001</v>
+        <v>297.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4253,33 +4218,33 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.01172950332775218</v>
+        <v>0.011434807596679</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>American States Water Co</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>116</v>
+        <v>399</v>
       </c>
       <c r="H40" t="n">
-        <v>34797.68</v>
+        <v>33855.15</v>
       </c>
       <c r="I40" t="n">
-        <v>299.98</v>
+        <v>84.84999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4288,33 +4253,33 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01150863351529601</v>
+        <v>0.01141181649035969</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>American States Water Co</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="H41" t="n">
-        <v>34142.43</v>
+        <v>33787.08</v>
       </c>
       <c r="I41" t="n">
-        <v>85.56999999999999</v>
+        <v>88.68000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4323,33 +4288,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01150443690459006</v>
+        <v>0.01123970237315402</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Snap-On</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>381</v>
+        <v>90</v>
       </c>
       <c r="H42" t="n">
-        <v>34129.98</v>
+        <v>33277.5</v>
       </c>
       <c r="I42" t="n">
-        <v>89.58</v>
+        <v>369.75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4358,33 +4323,33 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01128989403052352</v>
+        <v>0.01083840336990511</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Snap-On</t>
+          <t>Eastman Chemical</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>90</v>
+        <v>493</v>
       </c>
       <c r="H43" t="n">
-        <v>33493.5</v>
+        <v>32089.37</v>
       </c>
       <c r="I43" t="n">
-        <v>372.15</v>
+        <v>65.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4393,33 +4358,33 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.01091630129608698</v>
+        <v>0.009046123857713634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Eastman Chemical</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>493</v>
+        <v>705</v>
       </c>
       <c r="H44" t="n">
-        <v>32385.17</v>
+        <v>26782.95</v>
       </c>
       <c r="I44" t="n">
-        <v>65.69</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4428,7 +4393,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.009106648602701387</v>
+        <v>0.008962924221756033</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4445,16 +4410,16 @@
         <v>1297</v>
       </c>
       <c r="H45" t="n">
-        <v>27016.51</v>
+        <v>26536.62</v>
       </c>
       <c r="I45" t="n">
-        <v>20.83</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4463,33 +4428,33 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.009082577922338938</v>
+        <v>0.008808191070191483</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>HWC</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Hancock Whitney Corp</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>705</v>
+        <v>350</v>
       </c>
       <c r="H46" t="n">
-        <v>26945.1</v>
+        <v>26078.5</v>
       </c>
       <c r="I46" t="n">
-        <v>38.22</v>
+        <v>74.51000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4498,33 +4463,33 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.008842376734462155</v>
+        <v>0.00865869314924173</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HWC</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hancock Whitney Corp</t>
+          <t>Amdocs Ltd</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>350</v>
+        <v>431</v>
       </c>
       <c r="H47" t="n">
-        <v>26232.5</v>
+        <v>25635.88</v>
       </c>
       <c r="I47" t="n">
-        <v>74.95</v>
+        <v>59.48</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4533,33 +4498,33 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008615119309726639</v>
+        <v>0.008422543717696749</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Amdocs Ltd</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>431</v>
+        <v>257</v>
       </c>
       <c r="H48" t="n">
-        <v>25558.3</v>
+        <v>24936.71</v>
       </c>
       <c r="I48" t="n">
-        <v>59.3</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4568,33 +4533,33 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.008431584164081074</v>
+        <v>0.00764502415462788</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>257</v>
+        <v>627</v>
       </c>
       <c r="H49" t="n">
-        <v>25013.81</v>
+        <v>22634.7</v>
       </c>
       <c r="I49" t="n">
-        <v>97.33</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4603,62 +4568,27 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.007504945554032248</v>
+        <v>0.00606155265989959</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Huntington Ingalls</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>627</v>
+        <v>65</v>
       </c>
       <c r="H50" t="n">
-        <v>22264.77</v>
+        <v>17946.5</v>
       </c>
       <c r="I50" t="n">
-        <v>35.51</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>09/18/2026</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Quality All-Cap Dividend Strategy</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.005978366893157241</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>HII</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Huntington Ingalls</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>65</v>
-      </c>
-      <c r="H51" t="n">
-        <v>17735.9</v>
-      </c>
-      <c r="I51" t="n">
-        <v>272.86</v>
+        <v>276.1</v>
       </c>
     </row>
   </sheetData>
@@ -4725,7 +4655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4734,7 +4664,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0716395398211782</v>
+        <v>0.07170507428644318</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4760,7 +4690,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4769,7 +4699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05450436628495581</v>
+        <v>0.05399788120871097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4786,16 +4716,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>119788.06</v>
+        <v>118566.46</v>
       </c>
       <c r="I3" t="n">
-        <v>117.67</v>
+        <v>116.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4804,7 +4734,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04178921399226684</v>
+        <v>0.04249071076185357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4821,16 +4751,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>91843.08</v>
+        <v>93299.46000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4839,7 +4769,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03891765779783742</v>
+        <v>0.03992589194597988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4856,16 +4786,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>85532.06</v>
+        <v>87667.73</v>
       </c>
       <c r="I5" t="n">
-        <v>308.78</v>
+        <v>316.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4874,7 +4804,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03871618539443332</v>
+        <v>0.03944163622081077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4891,16 +4821,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>85089.27</v>
+        <v>86604.42</v>
       </c>
       <c r="I6" t="n">
-        <v>109.51</v>
+        <v>111.46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4909,7 +4839,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03521418560826825</v>
+        <v>0.03534834072631956</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4926,16 +4856,16 @@
         <v>2798</v>
       </c>
       <c r="H7" t="n">
-        <v>77392.67999999999</v>
+        <v>77616.52</v>
       </c>
       <c r="I7" t="n">
-        <v>27.66</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4944,7 +4874,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03420652783691221</v>
+        <v>0.03409660177366999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4961,16 +4891,16 @@
         <v>816</v>
       </c>
       <c r="H8" t="n">
-        <v>75178.08</v>
+        <v>74868</v>
       </c>
       <c r="I8" t="n">
-        <v>92.13</v>
+        <v>91.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4979,7 +4909,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03387116972086406</v>
+        <v>0.03382625818523611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4996,16 +4926,16 @@
         <v>303</v>
       </c>
       <c r="H9" t="n">
-        <v>74441.03999999999</v>
+        <v>74274.39</v>
       </c>
       <c r="I9" t="n">
-        <v>245.68</v>
+        <v>245.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5014,7 +4944,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03357725361231843</v>
+        <v>0.0332965148206863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5031,16 +4961,16 @@
         <v>246</v>
       </c>
       <c r="H10" t="n">
-        <v>73795.08</v>
+        <v>73111.2</v>
       </c>
       <c r="I10" t="n">
-        <v>299.98</v>
+        <v>297.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5049,7 +4979,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03232236341675756</v>
+        <v>0.0324979125463608</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5066,16 +4996,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>71037.12</v>
+        <v>71357.66</v>
       </c>
       <c r="I11" t="n">
-        <v>104.16</v>
+        <v>104.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5084,33 +5014,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03158441539910378</v>
+        <v>0.03158443439941429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>568</v>
+        <v>197</v>
       </c>
       <c r="H12" t="n">
-        <v>69415.28</v>
+        <v>69351.88</v>
       </c>
       <c r="I12" t="n">
-        <v>122.21</v>
+        <v>352.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5119,33 +5049,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0313431299120757</v>
+        <v>0.03146327369075548</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>197</v>
+        <v>568</v>
       </c>
       <c r="H13" t="n">
-        <v>68884.99000000001</v>
+        <v>69085.84</v>
       </c>
       <c r="I13" t="n">
-        <v>349.67</v>
+        <v>121.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5154,7 +5084,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03107255109563377</v>
+        <v>0.03079837447179028</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5171,16 +5101,16 @@
         <v>588</v>
       </c>
       <c r="H14" t="n">
-        <v>68290.32000000001</v>
+        <v>67625.88</v>
       </c>
       <c r="I14" t="n">
-        <v>116.14</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5189,7 +5119,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0307686657909487</v>
+        <v>0.03074325463804732</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5206,16 +5136,16 @@
         <v>245</v>
       </c>
       <c r="H15" t="n">
-        <v>67622.45</v>
+        <v>67504.85000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>276.01</v>
+        <v>275.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5224,7 +5154,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03026627927641454</v>
+        <v>0.03046547854786441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5241,16 +5171,16 @@
         <v>1076</v>
       </c>
       <c r="H16" t="n">
-        <v>66518.32000000001</v>
+        <v>66894.92</v>
       </c>
       <c r="I16" t="n">
-        <v>61.82</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5259,7 +5189,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02949187157429459</v>
+        <v>0.02933080149776205</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5276,16 +5206,16 @@
         <v>263</v>
       </c>
       <c r="H17" t="n">
-        <v>64816.35</v>
+        <v>64403.44</v>
       </c>
       <c r="I17" t="n">
-        <v>246.45</v>
+        <v>244.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5294,33 +5224,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02819354189194995</v>
+        <v>0.0279152833613511</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1433</v>
+        <v>1082</v>
       </c>
       <c r="H18" t="n">
-        <v>61962.92</v>
+        <v>61295.3</v>
       </c>
       <c r="I18" t="n">
-        <v>43.24</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5329,33 +5259,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02789469351110165</v>
+        <v>0.02613995836177715</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1082</v>
+        <v>213</v>
       </c>
       <c r="H19" t="n">
-        <v>61306.12</v>
+        <v>57397.11</v>
       </c>
       <c r="I19" t="n">
-        <v>56.66</v>
+        <v>269.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5364,33 +5294,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02616646442681868</v>
+        <v>0.0259743164983495</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>213</v>
+        <v>1433</v>
       </c>
       <c r="H20" t="n">
-        <v>57507.87</v>
+        <v>57033.4</v>
       </c>
       <c r="I20" t="n">
-        <v>269.99</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5399,7 +5329,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02515689562744869</v>
+        <v>0.02559827380875555</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5416,16 +5346,16 @@
         <v>1557</v>
       </c>
       <c r="H21" t="n">
-        <v>55289.07</v>
+        <v>56207.7</v>
       </c>
       <c r="I21" t="n">
-        <v>35.51</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5434,7 +5364,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02316247854108918</v>
+        <v>0.02363513695891923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5451,16 +5381,16 @@
         <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>50905.8</v>
+        <v>51897.12</v>
       </c>
       <c r="I22" t="n">
-        <v>385.65</v>
+        <v>393.16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5469,7 +5399,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02305136591227805</v>
+        <v>0.02343847624168481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5486,16 +5416,16 @@
         <v>190</v>
       </c>
       <c r="H23" t="n">
-        <v>50661.6</v>
+        <v>51465.3</v>
       </c>
       <c r="I23" t="n">
-        <v>266.64</v>
+        <v>270.87</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5504,7 +5434,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02219666318310527</v>
+        <v>0.02242679070030443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5521,16 +5451,16 @@
         <v>443</v>
       </c>
       <c r="H24" t="n">
-        <v>48783.16</v>
+        <v>49243.88</v>
       </c>
       <c r="I24" t="n">
-        <v>110.12</v>
+        <v>111.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5539,7 +5469,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02178469559403118</v>
+        <v>0.02177773564407505</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5556,16 +5486,16 @@
         <v>369</v>
       </c>
       <c r="H25" t="n">
-        <v>47877.75</v>
+        <v>47818.71</v>
       </c>
       <c r="I25" t="n">
-        <v>129.75</v>
+        <v>129.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5574,33 +5504,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02099641928861</v>
+        <v>0.02082426681216639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>298</v>
+        <v>959</v>
       </c>
       <c r="H26" t="n">
-        <v>46145.3</v>
+        <v>45725.12</v>
       </c>
       <c r="I26" t="n">
-        <v>154.85</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5609,33 +5539,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02098413865858701</v>
+        <v>0.0205691206859485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>959</v>
+        <v>298</v>
       </c>
       <c r="H27" t="n">
-        <v>46118.31</v>
+        <v>45164.88</v>
       </c>
       <c r="I27" t="n">
-        <v>48.09</v>
+        <v>151.56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5644,7 +5574,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02021131892974532</v>
+        <v>0.01952451262303398</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5661,16 +5591,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>44419.83</v>
+        <v>42871.17</v>
       </c>
       <c r="I28" t="n">
-        <v>279.37</v>
+        <v>269.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5679,7 +5609,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01907923503441429</v>
+        <v>0.0189707821342733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5696,16 +5626,16 @@
         <v>601</v>
       </c>
       <c r="H29" t="n">
-        <v>41931.77</v>
+        <v>41655.31</v>
       </c>
       <c r="I29" t="n">
-        <v>69.77</v>
+        <v>69.31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5714,7 +5644,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01878357625032261</v>
+        <v>0.01876094603250461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5731,16 +5661,16 @@
         <v>282</v>
       </c>
       <c r="H30" t="n">
-        <v>41281.98</v>
+        <v>41194.56</v>
       </c>
       <c r="I30" t="n">
-        <v>146.39</v>
+        <v>146.08</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5749,7 +5679,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01830055026959646</v>
+        <v>0.01870964719690347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5766,16 +5696,16 @@
         <v>484</v>
       </c>
       <c r="H31" t="n">
-        <v>40220.4</v>
+        <v>41081.92</v>
       </c>
       <c r="I31" t="n">
-        <v>83.09999999999999</v>
+        <v>84.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5784,7 +5714,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01788667620257512</v>
+        <v>0.01778428251223332</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5801,16 +5731,16 @@
         <v>246</v>
       </c>
       <c r="H32" t="n">
-        <v>39310.8</v>
+        <v>39050.04</v>
       </c>
       <c r="I32" t="n">
-        <v>159.8</v>
+        <v>158.74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5819,7 +5749,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01732010189710572</v>
+        <v>0.01741143689140642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5836,16 +5766,16 @@
         <v>148</v>
       </c>
       <c r="H33" t="n">
-        <v>38065.6</v>
+        <v>38231.36</v>
       </c>
       <c r="I33" t="n">
-        <v>257.2</v>
+        <v>258.32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5854,7 +5784,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01675589817638696</v>
+        <v>0.01670053085095305</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5871,16 +5801,16 @@
         <v>361</v>
       </c>
       <c r="H34" t="n">
-        <v>36825.61</v>
+        <v>36670.38</v>
       </c>
       <c r="I34" t="n">
-        <v>102.01</v>
+        <v>101.58</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5889,7 +5819,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01647431729866471</v>
+        <v>0.01643856248967386</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5906,16 +5836,16 @@
         <v>372</v>
       </c>
       <c r="H35" t="n">
-        <v>36206.76</v>
+        <v>36095.16</v>
       </c>
       <c r="I35" t="n">
-        <v>97.33</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5924,7 +5854,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.016315592771906</v>
+        <v>0.01638750047398138</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5941,10 +5871,10 @@
         <v>736</v>
       </c>
       <c r="H36" t="n">
-        <v>35857.92</v>
+        <v>35983.04</v>
       </c>
       <c r="I36" t="n">
-        <v>48.72</v>
+        <v>48.89</v>
       </c>
     </row>
   </sheetData>
@@ -5958,7 +5888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6011,7 +5941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6020,7 +5950,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1056255747317636</v>
+        <v>0.1060254858980799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -6037,16 +5967,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>222070</v>
+        <v>222991.8</v>
       </c>
       <c r="I2" t="n">
-        <v>53</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6055,7 +5985,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09895433059220057</v>
+        <v>0.0991001029364648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6072,16 +6002,16 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>208044.2</v>
+        <v>208426.4</v>
       </c>
       <c r="I3" t="n">
-        <v>212.29</v>
+        <v>212.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6090,7 +6020,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09565661710217371</v>
+        <v>0.09836151080081641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6107,16 +6037,16 @@
         <v>4300</v>
       </c>
       <c r="H4" t="n">
-        <v>201111</v>
+        <v>206873</v>
       </c>
       <c r="I4" t="n">
-        <v>46.77</v>
+        <v>48.11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6125,7 +6055,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08467822581549263</v>
+        <v>0.08204510998777549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6142,16 +6072,16 @@
         <v>934</v>
       </c>
       <c r="H5" t="n">
-        <v>178029.74</v>
+        <v>172556.5</v>
       </c>
       <c r="I5" t="n">
-        <v>190.61</v>
+        <v>184.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6160,7 +6090,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05481368972325943</v>
+        <v>0.05489897242073478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6177,16 +6107,16 @@
         <v>1475</v>
       </c>
       <c r="H6" t="n">
-        <v>115241.75</v>
+        <v>115463</v>
       </c>
       <c r="I6" t="n">
-        <v>78.13</v>
+        <v>78.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6195,7 +6125,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03823927384702826</v>
+        <v>0.03836690879007611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6212,16 +6142,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>80395.25999999999</v>
+        <v>80692.92</v>
       </c>
       <c r="I7" t="n">
-        <v>29.71</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6230,7 +6160,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02696434424104914</v>
+        <v>0.02747945020958752</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6247,16 +6177,16 @@
         <v>147</v>
       </c>
       <c r="H8" t="n">
-        <v>56690.55</v>
+        <v>57794.52</v>
       </c>
       <c r="I8" t="n">
-        <v>385.65</v>
+        <v>393.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6265,7 +6195,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02466050619426432</v>
+        <v>0.0250424527630176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6282,16 +6212,16 @@
         <v>105</v>
       </c>
       <c r="H9" t="n">
-        <v>51846.9</v>
+        <v>52669.05</v>
       </c>
       <c r="I9" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6300,33 +6230,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0232535984624204</v>
+        <v>0.02497379992507099</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GARA</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guiness Atkinson Real Asset Fund</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1860</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>48888.98</v>
+        <v>52524.66</v>
       </c>
       <c r="I10" t="n">
-        <v>26.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6335,33 +6265,33 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0209020393641075</v>
+        <v>0.02331466352394937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>GARA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Guiness Atkinson Real Asset Fund</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>275</v>
+        <v>1860</v>
       </c>
       <c r="H11" t="n">
-        <v>43945</v>
+        <v>49035.18</v>
       </c>
       <c r="I11" t="n">
-        <v>159.8</v>
+        <v>26.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6370,33 +6300,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02080329631320322</v>
+        <v>0.02075584639727485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sprott Physical Gold and Silver Trust</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>980</v>
+        <v>275</v>
       </c>
       <c r="H12" t="n">
-        <v>43737.4</v>
+        <v>43653.5</v>
       </c>
       <c r="I12" t="n">
-        <v>44.63</v>
+        <v>158.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6405,7 +6335,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02074249989332564</v>
+        <v>0.02069890433845854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6422,16 +6352,16 @@
         <v>158</v>
       </c>
       <c r="H13" t="n">
-        <v>43609.58</v>
+        <v>43533.74</v>
       </c>
       <c r="I13" t="n">
-        <v>276.01</v>
+        <v>275.53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6440,33 +6370,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02029008929458711</v>
+        <v>0.02066526972556053</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CEF</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Sprott Physical Gold and Silver Trust</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>158</v>
+        <v>980</v>
       </c>
       <c r="H14" t="n">
-        <v>42658.42</v>
+        <v>43463</v>
       </c>
       <c r="I14" t="n">
-        <v>269.99</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6475,33 +6405,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02012960805482264</v>
+        <v>0.02024365314878388</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="H15" t="n">
-        <v>42321.02</v>
+        <v>42576.26</v>
       </c>
       <c r="I15" t="n">
-        <v>209.51</v>
+        <v>269.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6510,33 +6440,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01800528639663268</v>
+        <v>0.01956139447279278</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="H16" t="n">
-        <v>37854.79</v>
+        <v>41141.34</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>203.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6545,7 +6475,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01757885054746006</v>
+        <v>0.01790091725164893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6562,16 +6492,16 @@
         <v>22</v>
       </c>
       <c r="H17" t="n">
-        <v>36958.24</v>
+        <v>37649.04</v>
       </c>
       <c r="I17" t="n">
-        <v>1679.92</v>
+        <v>1711.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6580,7 +6510,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01742413407540734</v>
+        <v>0.01685971820289892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6597,16 +6527,16 @@
         <v>224</v>
       </c>
       <c r="H18" t="n">
-        <v>36632.96</v>
+        <v>35459.2</v>
       </c>
       <c r="I18" t="n">
-        <v>163.54</v>
+        <v>158.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6615,33 +6545,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01646541800751621</v>
+        <v>0.0166967657780699</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>99</v>
+        <v>488</v>
       </c>
       <c r="H19" t="n">
-        <v>34617.33</v>
+        <v>35116.48</v>
       </c>
       <c r="I19" t="n">
-        <v>349.67</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6650,33 +6580,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01635234389628559</v>
+        <v>0.01657099495811257</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>488</v>
+        <v>99</v>
       </c>
       <c r="H20" t="n">
-        <v>34379.6</v>
+        <v>34851.96</v>
       </c>
       <c r="I20" t="n">
-        <v>70.45</v>
+        <v>352.04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6685,7 +6615,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01593875510783034</v>
+        <v>0.01621667613521752</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6702,16 +6632,16 @@
         <v>306</v>
       </c>
       <c r="H21" t="n">
-        <v>33510.06</v>
+        <v>34106.76</v>
       </c>
       <c r="I21" t="n">
-        <v>109.51</v>
+        <v>111.46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6720,7 +6650,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01472378750489738</v>
+        <v>0.01468548819791911</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6737,16 +6667,16 @@
         <v>126</v>
       </c>
       <c r="H22" t="n">
-        <v>30955.68</v>
+        <v>30886.38</v>
       </c>
       <c r="I22" t="n">
-        <v>245.68</v>
+        <v>245.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6755,7 +6685,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.014105701667763</v>
+        <v>0.01413452528112586</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6772,16 +6702,16 @@
         <v>84</v>
       </c>
       <c r="H23" t="n">
-        <v>29656.2</v>
+        <v>29727.6</v>
       </c>
       <c r="I23" t="n">
-        <v>353.05</v>
+        <v>353.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6790,7 +6720,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01399544335066222</v>
+        <v>0.01396073218377669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6807,16 +6737,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>29424.39</v>
+        <v>29362.08</v>
       </c>
       <c r="I24" t="n">
-        <v>146.39</v>
+        <v>146.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6825,33 +6755,33 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01309439398552462</v>
+        <v>0.01326537436182375</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coca-Cola Femsa</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>250</v>
+        <v>103</v>
       </c>
       <c r="H25" t="n">
-        <v>27530</v>
+        <v>27899.61</v>
       </c>
       <c r="I25" t="n">
-        <v>110.12</v>
+        <v>270.87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6860,33 +6790,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01306296363483216</v>
+        <v>0.01321325830415128</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Coca-Cola Femsa</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>103</v>
+        <v>250</v>
       </c>
       <c r="H26" t="n">
-        <v>27463.92</v>
+        <v>27790</v>
       </c>
       <c r="I26" t="n">
-        <v>266.64</v>
+        <v>111.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6895,7 +6825,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01217330586925698</v>
+        <v>0.01223777845521415</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6912,16 +6842,16 @@
         <v>414</v>
       </c>
       <c r="H27" t="n">
-        <v>25593.48</v>
+        <v>25738.38</v>
       </c>
       <c r="I27" t="n">
-        <v>61.82</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6930,7 +6860,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01177390069244896</v>
+        <v>0.01172726836377237</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6947,16 +6877,16 @@
         <v>524</v>
       </c>
       <c r="H28" t="n">
-        <v>24753.76</v>
+        <v>24664.68</v>
       </c>
       <c r="I28" t="n">
-        <v>47.24</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6965,7 +6895,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01118820600062567</v>
+        <v>0.0110905500217277</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6982,16 +6912,16 @@
         <v>259</v>
       </c>
       <c r="H29" t="n">
-        <v>23522.38</v>
+        <v>23325.54</v>
       </c>
       <c r="I29" t="n">
-        <v>90.81999999999999</v>
+        <v>90.06</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7000,7 +6930,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01104818683239251</v>
+        <v>0.0109367170749222</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7017,16 +6947,16 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>23228</v>
+        <v>23002</v>
       </c>
       <c r="I30" t="n">
-        <v>116.14</v>
+        <v>115.01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7035,7 +6965,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01095519903638198</v>
+        <v>0.01090604938292443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7052,16 +6982,16 @@
         <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>23032.5</v>
+        <v>22937.5</v>
       </c>
       <c r="I31" t="n">
-        <v>92.13</v>
+        <v>91.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7070,7 +7000,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.009769188451459869</v>
+        <v>0.008988724297948182</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7087,16 +7017,16 @@
         <v>475</v>
       </c>
       <c r="H32" t="n">
-        <v>20539</v>
+        <v>18905</v>
       </c>
       <c r="I32" t="n">
-        <v>43.24</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7105,7 +7035,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.008669982330844272</v>
+        <v>0.008705939649643253</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7122,16 +7052,16 @@
         <v>175</v>
       </c>
       <c r="H33" t="n">
-        <v>18228</v>
+        <v>18310.25</v>
       </c>
       <c r="I33" t="n">
-        <v>104.16</v>
+        <v>104.63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7140,33 +7070,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.008623336227750905</v>
+        <v>0.008573165184676206</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>377</v>
+        <v>650</v>
       </c>
       <c r="H34" t="n">
-        <v>18129.93</v>
+        <v>18031</v>
       </c>
       <c r="I34" t="n">
-        <v>48.09</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7175,7 +7105,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.008588062698583941</v>
+        <v>0.008548754652782174</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -7192,16 +7122,16 @@
         <v>177</v>
       </c>
       <c r="H35" t="n">
-        <v>18055.77</v>
+        <v>17979.66</v>
       </c>
       <c r="I35" t="n">
-        <v>102.01</v>
+        <v>101.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7210,33 +7140,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.00855154774666717</v>
+        <v>0.008546710139982325</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>650</v>
+        <v>377</v>
       </c>
       <c r="H36" t="n">
-        <v>17979</v>
+        <v>17975.36</v>
       </c>
       <c r="I36" t="n">
-        <v>27.66</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7245,7 +7175,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.008369767307386828</v>
+        <v>0.00819116460940736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -7262,16 +7192,16 @@
         <v>362</v>
       </c>
       <c r="H37" t="n">
-        <v>17596.82</v>
+        <v>17227.58</v>
       </c>
       <c r="I37" t="n">
-        <v>48.61</v>
+        <v>47.59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7280,7 +7210,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008146301699603349</v>
+        <v>0.008133300142490656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -7297,16 +7227,16 @@
         <v>132</v>
       </c>
       <c r="H38" t="n">
-        <v>17127</v>
+        <v>17105.88</v>
       </c>
       <c r="I38" t="n">
-        <v>129.75</v>
+        <v>129.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7315,7 +7245,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.007994762508764696</v>
+        <v>0.008019744097842205</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7332,16 +7262,16 @@
         <v>345</v>
       </c>
       <c r="H39" t="n">
-        <v>16808.4</v>
+        <v>16867.05</v>
       </c>
       <c r="I39" t="n">
-        <v>48.72</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7350,7 +7280,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.007798584419431981</v>
+        <v>0.007744352978383248</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7367,16 +7297,16 @@
         <v>235</v>
       </c>
       <c r="H40" t="n">
-        <v>16395.95</v>
+        <v>16287.85</v>
       </c>
       <c r="I40" t="n">
-        <v>69.77</v>
+        <v>69.31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7385,7 +7315,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.007330349247940154</v>
+        <v>0.007326392751241679</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7402,16 +7332,16 @@
         <v>272</v>
       </c>
       <c r="H41" t="n">
-        <v>15411.52</v>
+        <v>15408.8</v>
       </c>
       <c r="I41" t="n">
-        <v>56.66</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7420,33 +7350,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.00717550910925335</v>
+        <v>0.007022245321518777</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="H42" t="n">
-        <v>15085.98</v>
+        <v>14769.12</v>
       </c>
       <c r="I42" t="n">
-        <v>279.37</v>
+        <v>84.88</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7455,33 +7385,33 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.007145148950586586</v>
+        <v>0.006922824943274874</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H43" t="n">
-        <v>15022.15</v>
+        <v>14560.02</v>
       </c>
       <c r="I43" t="n">
-        <v>273.13</v>
+        <v>269.63</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7490,33 +7420,33 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.006877482033937331</v>
+        <v>0.004720209493143643</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="H44" t="n">
-        <v>14459.4</v>
+        <v>9927.5</v>
       </c>
       <c r="I44" t="n">
-        <v>83.09999999999999</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7525,33 +7455,33 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.004644752301748795</v>
+        <v>0.004097964399849553</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>275</v>
+        <v>29</v>
       </c>
       <c r="H45" t="n">
-        <v>9765.25</v>
+        <v>8618.799999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>35.51</v>
+        <v>297.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/18/2026</t>
+          <t>09/21/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7560,313 +7490,30 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.004137799960971762</v>
+        <v>0.002522168046066963</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H46" t="n">
-        <v>8699.42</v>
+        <v>5304.6</v>
       </c>
       <c r="I46" t="n">
-        <v>299.98</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>09/18/2026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Dividend Core Plus</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.002577854769453217</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>JKHY</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Jack Henry &amp; Associates</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>35</v>
-      </c>
-      <c r="H47" t="n">
-        <v>5419.75</v>
-      </c>
-      <c r="I47" t="n">
-        <v>154.85</v>
+        <v>151.56</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98134DFC-9C7F-4F91-8C9A-03146AE1A1B7}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D03BA1F6-C27A-46A3-B460-6DC7BFC36AB6}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EF6E36F-DFA6-4C75-8C30-E4069DA2BD16}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -7516,4 +7516,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09C8D40A-3371-4AF7-83C0-C27A0FA79598}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E09A5321-6F7C-446B-ACD1-BB5AC82E8694}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4E6B1B0-FA67-4DEC-A663-5AB0C8F538BD}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1095689346521751</v>
+        <v>0.1098151437223026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04529290145129176</v>
+        <v>0.04736675300036343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>105760.04</v>
+        <v>110354.56</v>
       </c>
       <c r="I3" t="n">
-        <v>393.16</v>
+        <v>410.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0410635670299699</v>
+        <v>0.03991308364684736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>95884.44</v>
+        <v>92989.08</v>
       </c>
       <c r="I4" t="n">
-        <v>275.53</v>
+        <v>267.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,33 +596,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03813798759860614</v>
+        <v>0.03778244044047551</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>561</v>
+        <v>327</v>
       </c>
       <c r="H5" t="n">
-        <v>89053.14</v>
+        <v>88025.13</v>
       </c>
       <c r="I5" t="n">
-        <v>158.74</v>
+        <v>269.19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,33 +631,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03773694257664829</v>
+        <v>0.03760002910477633</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>327</v>
+        <v>561</v>
       </c>
       <c r="H6" t="n">
-        <v>88116.69</v>
+        <v>87600.14999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>269.47</v>
+        <v>156.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0374190615600447</v>
+        <v>0.03727113242706716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -683,16 +683,16 @@
         <v>429</v>
       </c>
       <c r="H7" t="n">
-        <v>87374.42999999999</v>
+        <v>86833.89</v>
       </c>
       <c r="I7" t="n">
-        <v>203.67</v>
+        <v>202.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03517879824324936</v>
+        <v>0.0360114949788037</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         <v>48</v>
       </c>
       <c r="H8" t="n">
-        <v>82143.36</v>
+        <v>83899.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1711.32</v>
+        <v>1747.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,33 +736,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03220445701339115</v>
+        <v>0.03222172328347168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1045</v>
+        <v>473</v>
       </c>
       <c r="H9" t="n">
-        <v>75198.2</v>
+        <v>75069.83</v>
       </c>
       <c r="I9" t="n">
-        <v>71.95999999999999</v>
+        <v>158.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,33 +771,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03206642849016298</v>
+        <v>0.0321916003893605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>473</v>
+        <v>1045</v>
       </c>
       <c r="H10" t="n">
-        <v>74875.89999999999</v>
+        <v>74999.64999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>158.3</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03202949526073948</v>
+        <v>0.0306556632916635</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         <v>671</v>
       </c>
       <c r="H11" t="n">
-        <v>74789.66</v>
+        <v>71421.24000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>111.46</v>
+        <v>106.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02964516065787777</v>
+        <v>0.02949794492585514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         <v>138</v>
       </c>
       <c r="H12" t="n">
-        <v>69222.17999999999</v>
+        <v>68724</v>
       </c>
       <c r="I12" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02955450636747462</v>
+        <v>0.02874124563583948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         <v>195</v>
       </c>
       <c r="H13" t="n">
-        <v>69010.5</v>
+        <v>66961.05</v>
       </c>
       <c r="I13" t="n">
-        <v>353.9</v>
+        <v>343.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,33 +911,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02819305605437256</v>
+        <v>0.02780171437124991</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>187</v>
+        <v>437</v>
       </c>
       <c r="H14" t="n">
-        <v>65831.48</v>
+        <v>64772.14</v>
       </c>
       <c r="I14" t="n">
-        <v>352.04</v>
+        <v>148.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02760964036430588</v>
+        <v>0.02774957231971634</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -963,16 +963,16 @@
         <v>263</v>
       </c>
       <c r="H15" t="n">
-        <v>64469.19</v>
+        <v>64650.66</v>
       </c>
       <c r="I15" t="n">
-        <v>245.13</v>
+        <v>245.82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,33 +981,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02733888090653194</v>
+        <v>0.02729002005683414</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>437</v>
+        <v>187</v>
       </c>
       <c r="H16" t="n">
-        <v>63836.96</v>
+        <v>63580</v>
       </c>
       <c r="I16" t="n">
-        <v>146.08</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02598468533492379</v>
+        <v>0.02609499359817678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>224</v>
       </c>
       <c r="H17" t="n">
-        <v>60674.88</v>
+        <v>60795.84</v>
       </c>
       <c r="I17" t="n">
-        <v>270.87</v>
+        <v>271.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0245955393823642</v>
+        <v>0.02508781673495624</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1068,16 +1068,16 @@
         <v>213</v>
       </c>
       <c r="H18" t="n">
-        <v>57431.19</v>
+        <v>58449.33</v>
       </c>
       <c r="I18" t="n">
-        <v>269.63</v>
+        <v>274.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02390923826747489</v>
+        <v>0.02425590034656436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         <v>898</v>
       </c>
       <c r="H19" t="n">
-        <v>55828.66</v>
+        <v>56511.14</v>
       </c>
       <c r="I19" t="n">
-        <v>62.17</v>
+        <v>62.93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.023845701464167</v>
+        <v>0.02356783816109869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1138,16 +1138,16 @@
         <v>1170</v>
       </c>
       <c r="H20" t="n">
-        <v>55680.3</v>
+        <v>54908.1</v>
       </c>
       <c r="I20" t="n">
-        <v>47.59</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0229122552035447</v>
+        <v>0.02259101168036036</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         <v>353</v>
       </c>
       <c r="H21" t="n">
-        <v>53500.68</v>
+        <v>52632.3</v>
       </c>
       <c r="I21" t="n">
-        <v>151.56</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,33 +1191,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02180758590888005</v>
+        <v>0.0219477904573882</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Coca-Cola Femsa</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>555</v>
+        <v>457</v>
       </c>
       <c r="H22" t="n">
-        <v>50921.25</v>
+        <v>51133.73</v>
       </c>
       <c r="I22" t="n">
-        <v>91.75</v>
+        <v>111.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02175571065284956</v>
+        <v>0.0216231345062937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Coca-Cola Femsa</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>457</v>
+        <v>555</v>
       </c>
       <c r="H23" t="n">
-        <v>50800.12</v>
+        <v>50377.35</v>
       </c>
       <c r="I23" t="n">
-        <v>111.16</v>
+        <v>90.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0214444676818868</v>
+        <v>0.02144253878532936</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1278,16 +1278,16 @@
         <v>556</v>
       </c>
       <c r="H24" t="n">
-        <v>50073.36</v>
+        <v>49956.6</v>
       </c>
       <c r="I24" t="n">
-        <v>90.06</v>
+        <v>89.84999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,33 +1296,33 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02098233122698295</v>
+        <v>0.02096409211095138</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>426</v>
+        <v>864</v>
       </c>
       <c r="H25" t="n">
-        <v>48994.26</v>
+        <v>48841.92</v>
       </c>
       <c r="I25" t="n">
-        <v>115.01</v>
+        <v>56.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,33 +1331,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02096149204628086</v>
+        <v>0.02094171240592207</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>864</v>
+        <v>426</v>
       </c>
       <c r="H26" t="n">
-        <v>48945.6</v>
+        <v>48789.78</v>
       </c>
       <c r="I26" t="n">
-        <v>56.65</v>
+        <v>114.53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,33 +1366,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01908861243612926</v>
+        <v>0.01907170648925</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>426</v>
+        <v>938</v>
       </c>
       <c r="H27" t="n">
-        <v>44572.38</v>
+        <v>44433.06</v>
       </c>
       <c r="I27" t="n">
-        <v>104.63</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,33 +1401,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01890843446438693</v>
+        <v>0.01904739527918364</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>938</v>
+        <v>426</v>
       </c>
       <c r="H28" t="n">
-        <v>44151.66</v>
+        <v>44376.42</v>
       </c>
       <c r="I28" t="n">
-        <v>47.07</v>
+        <v>104.17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,33 +1436,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01878592612012802</v>
+        <v>0.01863854716964076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>920</v>
+        <v>331</v>
       </c>
       <c r="H29" t="n">
-        <v>43865.6</v>
+        <v>43423.89</v>
       </c>
       <c r="I29" t="n">
-        <v>47.68</v>
+        <v>131.19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01852768473164964</v>
+        <v>0.01838269142796605</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1488,16 +1488,16 @@
         <v>1087</v>
       </c>
       <c r="H30" t="n">
-        <v>43262.6</v>
+        <v>42827.8</v>
       </c>
       <c r="I30" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,33 +1506,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01836995191939347</v>
+        <v>0.01834243027852706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>331</v>
+        <v>920</v>
       </c>
       <c r="H31" t="n">
-        <v>42894.29</v>
+        <v>42734</v>
       </c>
       <c r="I31" t="n">
-        <v>129.59</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01786746042960352</v>
+        <v>0.01803026472667216</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1558,16 +1558,16 @@
         <v>1504</v>
       </c>
       <c r="H32" t="n">
-        <v>41720.96</v>
+        <v>42006.72</v>
       </c>
       <c r="I32" t="n">
-        <v>27.74</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01662235150222956</v>
+        <v>0.01661403372670479</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>38813.6</v>
+        <v>38707.2</v>
       </c>
       <c r="I33" t="n">
-        <v>69.31</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01613952147536671</v>
+        <v>0.016108906529415</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>37686.18</v>
+        <v>37530.36</v>
       </c>
       <c r="I34" t="n">
-        <v>101.58</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01355884633027981</v>
+        <v>0.01395274170315358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         <v>373</v>
       </c>
       <c r="H35" t="n">
-        <v>31660.24</v>
+        <v>32506.95</v>
       </c>
       <c r="I35" t="n">
-        <v>84.88</v>
+        <v>87.15000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01107328795531072</v>
+        <v>0.01140251121923285</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
         <v>87</v>
       </c>
       <c r="H36" t="n">
-        <v>25856.4</v>
+        <v>26565.45</v>
       </c>
       <c r="I36" t="n">
-        <v>297.2</v>
+        <v>305.35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01092946934323973</v>
+        <v>0.01107277755600761</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         <v>522</v>
       </c>
       <c r="H37" t="n">
-        <v>25520.58</v>
+        <v>25797.24</v>
       </c>
       <c r="I37" t="n">
-        <v>48.89</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008889627896086166</v>
+        <v>0.008909603512578402</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06033916925316867</v>
+        <v>0.05955004527297714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1864,16 +1864,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>154136.54</v>
+        <v>151621.65</v>
       </c>
       <c r="I2" t="n">
-        <v>158.74</v>
+        <v>156.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05596407807346605</v>
+        <v>0.05536959668016471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>142960.36</v>
+        <v>140977.72</v>
       </c>
       <c r="I3" t="n">
-        <v>47.59</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0532993397042263</v>
+        <v>0.05126485932138298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         <v>556</v>
       </c>
       <c r="H4" t="n">
-        <v>136153.28</v>
+        <v>130526.56</v>
       </c>
       <c r="I4" t="n">
-        <v>244.88</v>
+        <v>234.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05062735530479229</v>
+        <v>0.05079399805073717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05017054222999121</v>
+        <v>0.05020277724453754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2004,16 +2004,16 @@
         <v>1781</v>
       </c>
       <c r="H6" t="n">
-        <v>128160.76</v>
+        <v>127822.37</v>
       </c>
       <c r="I6" t="n">
-        <v>71.95999999999999</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04929960541548803</v>
+        <v>0.04925544617275903</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2039,16 +2039,16 @@
         <v>1095</v>
       </c>
       <c r="H7" t="n">
-        <v>125935.95</v>
+        <v>125410.35</v>
       </c>
       <c r="I7" t="n">
-        <v>115.01</v>
+        <v>114.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04318199468836628</v>
+        <v>0.04344608080740091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2074,16 +2074,16 @@
         <v>450</v>
       </c>
       <c r="H8" t="n">
-        <v>110308.5</v>
+        <v>110619</v>
       </c>
       <c r="I8" t="n">
-        <v>245.13</v>
+        <v>245.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04170937117106172</v>
+        <v>0.04116743855769428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2109,16 +2109,16 @@
         <v>703</v>
       </c>
       <c r="H9" t="n">
-        <v>106546.68</v>
+        <v>104817.3</v>
       </c>
       <c r="I9" t="n">
-        <v>151.56</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03908134445560997</v>
+        <v>0.03963504506613312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>99833.38</v>
+        <v>100915.64</v>
       </c>
       <c r="I10" t="n">
-        <v>48.89</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03790072303676514</v>
+        <v>0.03794419095060543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>796</v>
       </c>
       <c r="H11" t="n">
-        <v>96817.48</v>
+        <v>96610.52</v>
       </c>
       <c r="I11" t="n">
-        <v>121.63</v>
+        <v>121.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2197,33 +2197,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03665758454487762</v>
+        <v>0.03703527124308589</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Principal Financial</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>804</v>
+        <v>1082</v>
       </c>
       <c r="H12" t="n">
-        <v>93641.88</v>
+        <v>94296.3</v>
       </c>
       <c r="I12" t="n">
-        <v>116.47</v>
+        <v>87.15000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03654901936098948</v>
+        <v>0.0364306457348192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2249,16 +2249,16 @@
         <v>295</v>
       </c>
       <c r="H13" t="n">
-        <v>93364.55</v>
+        <v>92756.85000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>316.49</v>
+        <v>314.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2267,33 +2267,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03595227295538158</v>
+        <v>0.03586881472808275</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Principal Financial</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1082</v>
+        <v>804</v>
       </c>
       <c r="H14" t="n">
-        <v>91840.16</v>
+        <v>91326.36</v>
       </c>
       <c r="I14" t="n">
-        <v>84.88</v>
+        <v>113.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2302,33 +2302,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03313047071609675</v>
+        <v>0.03377597272469508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1798</v>
+        <v>327</v>
       </c>
       <c r="H15" t="n">
-        <v>84631.86</v>
+        <v>85997.73</v>
       </c>
       <c r="I15" t="n">
-        <v>47.07</v>
+        <v>262.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2337,33 +2337,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03306735861518287</v>
+        <v>0.03345137313145258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>327</v>
+        <v>1798</v>
       </c>
       <c r="H16" t="n">
-        <v>84470.64</v>
+        <v>85171.25999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>258.32</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2372,33 +2372,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03303602570017762</v>
+        <v>0.03292784744533146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Allison Transmission</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>710</v>
+        <v>910</v>
       </c>
       <c r="H17" t="n">
-        <v>84390.60000000001</v>
+        <v>83838.3</v>
       </c>
       <c r="I17" t="n">
-        <v>118.86</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2407,33 +2407,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03159081261151709</v>
+        <v>0.03217434844399354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Allison Transmission</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>910</v>
+        <v>710</v>
       </c>
       <c r="H18" t="n">
-        <v>80698.8</v>
+        <v>81919.8</v>
       </c>
       <c r="I18" t="n">
-        <v>88.68000000000001</v>
+        <v>115.38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03112005552831412</v>
+        <v>0.03139559534529517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
         <v>215</v>
       </c>
       <c r="H19" t="n">
-        <v>79496.25</v>
+        <v>79937</v>
       </c>
       <c r="I19" t="n">
-        <v>369.75</v>
+        <v>371.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2477,33 +2477,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03096504685321879</v>
+        <v>0.03105724935380048</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Eastman Chemical</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>756</v>
+        <v>1179</v>
       </c>
       <c r="H20" t="n">
-        <v>79100.28</v>
+        <v>79075.53</v>
       </c>
       <c r="I20" t="n">
-        <v>104.63</v>
+        <v>67.06999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2512,33 +2512,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03004151270663033</v>
+        <v>0.03093038580810219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eastman Chemical</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1179</v>
+        <v>756</v>
       </c>
       <c r="H21" t="n">
-        <v>76741.11</v>
+        <v>78752.52</v>
       </c>
       <c r="I21" t="n">
-        <v>65.09</v>
+        <v>104.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02935272879918729</v>
+        <v>0.02985307664953568</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2564,16 +2564,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>74981.61</v>
+        <v>76009.56</v>
       </c>
       <c r="I22" t="n">
-        <v>76.59</v>
+        <v>77.64</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02604123819521956</v>
+        <v>0.02598531148645228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2599,16 +2599,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>66522.39999999999</v>
+        <v>66161.75999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>84.84999999999999</v>
+        <v>84.39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02522957320306702</v>
+        <v>0.02515178488203248</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>64449</v>
+        <v>64039.5</v>
       </c>
       <c r="I24" t="n">
-        <v>20.46</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02440459446229718</v>
+        <v>0.0243946921794372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2669,16 +2669,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>62341.59</v>
+        <v>62111.85</v>
       </c>
       <c r="I25" t="n">
-        <v>37.99</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02225857555440186</v>
+        <v>0.02253437639379887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2704,16 +2704,16 @@
         <v>586</v>
       </c>
       <c r="H26" t="n">
-        <v>56859.58</v>
+        <v>57375.26</v>
       </c>
       <c r="I26" t="n">
-        <v>97.03</v>
+        <v>97.91</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02219001425087837</v>
+        <v>0.02200479050981971</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2739,16 +2739,16 @@
         <v>953</v>
       </c>
       <c r="H27" t="n">
-        <v>56684.44</v>
+        <v>56026.87</v>
       </c>
       <c r="I27" t="n">
-        <v>59.48</v>
+        <v>58.79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02105937517321135</v>
+        <v>0.020862138829047</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2774,16 +2774,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>53796.22</v>
+        <v>53117.54</v>
       </c>
       <c r="I28" t="n">
-        <v>74.51000000000001</v>
+        <v>73.56999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01578021743641567</v>
+        <v>0.01553684698682623</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>40310.6</v>
+        <v>39558.7</v>
       </c>
       <c r="I29" t="n">
-        <v>276.1</v>
+        <v>270.95</v>
       </c>
     </row>
   </sheetData>
@@ -2879,7 +2879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1071066543168815</v>
+        <v>0.1074940188625454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2923,33 +2923,33 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03824853745304416</v>
+        <v>0.03852030687791689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>411</v>
+        <v>277</v>
       </c>
       <c r="H3" t="n">
-        <v>113242.83</v>
+        <v>113636.48</v>
       </c>
       <c r="I3" t="n">
-        <v>275.53</v>
+        <v>410.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2958,33 +2958,33 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03678351389536768</v>
+        <v>0.03722772479003748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>277</v>
+        <v>411</v>
       </c>
       <c r="H4" t="n">
-        <v>108905.32</v>
+        <v>109823.31</v>
       </c>
       <c r="I4" t="n">
-        <v>393.16</v>
+        <v>267.21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03431393064434709</v>
+        <v>0.03387614072656512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3010,16 +3010,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>101593.6</v>
+        <v>99936</v>
       </c>
       <c r="I5" t="n">
-        <v>158.74</v>
+        <v>156.15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0325381100216949</v>
+        <v>0.03245376382716432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>96335.91</v>
+        <v>95739.92999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>203.67</v>
+        <v>202.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3063,33 +3063,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03154766180803378</v>
+        <v>0.03111610778763174</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>838</v>
+        <v>341</v>
       </c>
       <c r="H7" t="n">
-        <v>93403.48</v>
+        <v>91793.78999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>111.46</v>
+        <v>269.19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3098,33 +3098,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03103622706292211</v>
+        <v>0.03023575727533647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>341</v>
+        <v>838</v>
       </c>
       <c r="H8" t="n">
-        <v>91889.27</v>
+        <v>89196.72</v>
       </c>
       <c r="I8" t="n">
-        <v>269.47</v>
+        <v>106.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02956719770943327</v>
+        <v>0.02975098772190574</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3150,16 +3150,16 @@
         <v>553</v>
       </c>
       <c r="H9" t="n">
-        <v>87539.89999999999</v>
+        <v>87766.63</v>
       </c>
       <c r="I9" t="n">
-        <v>158.3</v>
+        <v>158.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0280236423149667</v>
+        <v>0.02805073331729559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>82969.88</v>
+        <v>82750.81</v>
       </c>
       <c r="I10" t="n">
-        <v>71.95999999999999</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02590324556838489</v>
+        <v>0.02637777005991863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3220,16 +3220,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>76692</v>
+        <v>77815.5</v>
       </c>
       <c r="I11" t="n">
-        <v>146.08</v>
+        <v>148.22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02458991535094823</v>
+        <v>0.02474831467420207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>72803.61</v>
+        <v>73008.53999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>245.13</v>
+        <v>245.82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3273,33 +3273,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02425639738510431</v>
+        <v>0.02438056044836911</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="H13" t="n">
-        <v>71816.16</v>
+        <v>71923.64999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>352.04</v>
+        <v>271.41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3308,33 +3308,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02424436986496284</v>
+        <v>0.02380238201987222</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>265</v>
+        <v>141</v>
       </c>
       <c r="H14" t="n">
-        <v>71780.55</v>
+        <v>70218</v>
       </c>
       <c r="I14" t="n">
-        <v>270.87</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3343,33 +3343,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02388852955129105</v>
+        <v>0.02351153859264486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>141</v>
+        <v>204</v>
       </c>
       <c r="H15" t="n">
-        <v>70727.00999999999</v>
+        <v>69360</v>
       </c>
       <c r="I15" t="n">
-        <v>501.61</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3378,33 +3378,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02216625013877161</v>
+        <v>0.02196227870577848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>268</v>
+        <v>1311</v>
       </c>
       <c r="H16" t="n">
-        <v>65627.84</v>
+        <v>64789.62</v>
       </c>
       <c r="I16" t="n">
-        <v>244.88</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3413,33 +3413,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0218743809656445</v>
+        <v>0.02176645769057953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="H17" t="n">
-        <v>64763.7</v>
+        <v>64211.94</v>
       </c>
       <c r="I17" t="n">
-        <v>353.9</v>
+        <v>274.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02180712007373285</v>
+        <v>0.02153075248231814</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3465,16 +3465,16 @@
         <v>426</v>
       </c>
       <c r="H18" t="n">
-        <v>64564.56</v>
+        <v>63516.6</v>
       </c>
       <c r="I18" t="n">
-        <v>151.56</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3483,33 +3483,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02164845205528686</v>
+        <v>0.0213270536101859</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1311</v>
+        <v>268</v>
       </c>
       <c r="H19" t="n">
-        <v>64094.79</v>
+        <v>62915.68</v>
       </c>
       <c r="I19" t="n">
-        <v>48.89</v>
+        <v>234.76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3518,33 +3518,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02131023251459404</v>
+        <v>0.02130152515039046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="H20" t="n">
-        <v>63093.42</v>
+        <v>62840.37</v>
       </c>
       <c r="I20" t="n">
-        <v>269.63</v>
+        <v>343.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02128728531666054</v>
+        <v>0.02127510856730908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3570,16 +3570,16 @@
         <v>548</v>
       </c>
       <c r="H21" t="n">
-        <v>63025.48</v>
+        <v>62762.44</v>
       </c>
       <c r="I21" t="n">
-        <v>115.01</v>
+        <v>114.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02032890711247522</v>
+        <v>0.02018450673131011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3605,16 +3605,16 @@
         <v>656</v>
       </c>
       <c r="H22" t="n">
-        <v>60188</v>
+        <v>59545.12</v>
       </c>
       <c r="I22" t="n">
-        <v>91.75</v>
+        <v>90.77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01932526274009667</v>
+        <v>0.01935407078155473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3640,16 +3640,16 @@
         <v>1010</v>
       </c>
       <c r="H23" t="n">
-        <v>57216.5</v>
+        <v>57095.3</v>
       </c>
       <c r="I23" t="n">
-        <v>56.65</v>
+        <v>56.53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01930468997256459</v>
+        <v>0.0191058132048665</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3675,16 +3675,16 @@
         <v>1201</v>
       </c>
       <c r="H24" t="n">
-        <v>57155.59</v>
+        <v>56362.93</v>
       </c>
       <c r="I24" t="n">
-        <v>47.59</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01742042239211893</v>
+        <v>0.01769928693327125</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>51576.82</v>
+        <v>52213.62</v>
       </c>
       <c r="I25" t="n">
-        <v>129.59</v>
+        <v>131.19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0169629578082936</v>
+        <v>0.0169494600359572</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,16 +3745,16 @@
         <v>480</v>
       </c>
       <c r="H26" t="n">
-        <v>50222.4</v>
+        <v>50001.6</v>
       </c>
       <c r="I26" t="n">
-        <v>104.63</v>
+        <v>104.17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3763,33 +3763,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01639146314654174</v>
+        <v>0.01647373781477903</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>399</v>
+        <v>1740</v>
       </c>
       <c r="H27" t="n">
-        <v>48530.37</v>
+        <v>48598.2</v>
       </c>
       <c r="I27" t="n">
-        <v>121.63</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3798,33 +3798,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01630271078856431</v>
+        <v>0.01641557929868416</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1740</v>
+        <v>399</v>
       </c>
       <c r="H28" t="n">
-        <v>48267.6</v>
+        <v>48426.63</v>
       </c>
       <c r="I28" t="n">
-        <v>27.74</v>
+        <v>121.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01587192899303376</v>
+        <v>0.01588566460814604</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3850,16 +3850,16 @@
         <v>678</v>
       </c>
       <c r="H29" t="n">
-        <v>46992.18</v>
+        <v>46863.36</v>
       </c>
       <c r="I29" t="n">
-        <v>69.31</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01564384181663556</v>
+        <v>0.01580048612750072</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3885,16 +3885,16 @@
         <v>984</v>
       </c>
       <c r="H30" t="n">
-        <v>46316.88</v>
+        <v>46612.08</v>
       </c>
       <c r="I30" t="n">
-        <v>47.07</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3903,33 +3903,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01478369680419265</v>
+        <v>0.01453464604192197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>918</v>
+        <v>492</v>
       </c>
       <c r="H31" t="n">
-        <v>43770.24</v>
+        <v>42877.8</v>
       </c>
       <c r="I31" t="n">
-        <v>47.68</v>
+        <v>87.15000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3938,33 +3938,33 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01410504879324439</v>
+        <v>0.01445440986566939</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>492</v>
+        <v>918</v>
       </c>
       <c r="H32" t="n">
-        <v>41760.96</v>
+        <v>42641.1</v>
       </c>
       <c r="I32" t="n">
-        <v>84.88</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3973,33 +3973,33 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01361113349406752</v>
+        <v>0.0136396313260581</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Principal Financial</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>346</v>
+        <v>153</v>
       </c>
       <c r="H33" t="n">
-        <v>40298.62</v>
+        <v>40237.47</v>
       </c>
       <c r="I33" t="n">
-        <v>116.47</v>
+        <v>262.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4008,33 +4008,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01334914904383056</v>
+        <v>0.01332257470276141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Principal Financial</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>153</v>
+        <v>346</v>
       </c>
       <c r="H34" t="n">
-        <v>39522.96</v>
+        <v>39302.14</v>
       </c>
       <c r="I34" t="n">
-        <v>258.32</v>
+        <v>113.59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01293449513616171</v>
+        <v>0.01289678060325727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4060,16 +4060,16 @@
         <v>121</v>
       </c>
       <c r="H35" t="n">
-        <v>38295.29</v>
+        <v>38046.03</v>
       </c>
       <c r="I35" t="n">
-        <v>316.49</v>
+        <v>314.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01290031076903116</v>
+        <v>0.01289343488690909</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>376</v>
       </c>
       <c r="H36" t="n">
-        <v>38194.08</v>
+        <v>38036.16</v>
       </c>
       <c r="I36" t="n">
-        <v>101.58</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4113,33 +4113,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01244519021749401</v>
+        <v>0.01221168162252721</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>GGG</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Allison Transmission</t>
+          <t>Graco Inc.</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>310</v>
+        <v>464</v>
       </c>
       <c r="H37" t="n">
-        <v>36846.6</v>
+        <v>36024.96</v>
       </c>
       <c r="I37" t="n">
-        <v>118.86</v>
+        <v>77.64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4148,33 +4148,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01200312058924432</v>
+        <v>0.01212450994916382</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GGG</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Graco Inc.</t>
+          <t>Allison Transmission</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>464</v>
+        <v>310</v>
       </c>
       <c r="H38" t="n">
-        <v>35537.76</v>
+        <v>35767.8</v>
       </c>
       <c r="I38" t="n">
-        <v>76.59</v>
+        <v>115.38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01164423370911154</v>
+        <v>0.01200681666485923</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4200,16 +4200,16 @@
         <v>116</v>
       </c>
       <c r="H39" t="n">
-        <v>34475.2</v>
+        <v>35420.6</v>
       </c>
       <c r="I39" t="n">
-        <v>297.2</v>
+        <v>305.35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4218,33 +4218,33 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.011434807596679</v>
+        <v>0.01189865884163612</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>American States Water Co</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="H40" t="n">
-        <v>33855.15</v>
+        <v>35101.53</v>
       </c>
       <c r="I40" t="n">
-        <v>84.84999999999999</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4253,33 +4253,33 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01141181649035969</v>
+        <v>0.01141394691452547</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>American States Water Co</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="H41" t="n">
-        <v>33787.08</v>
+        <v>33671.61</v>
       </c>
       <c r="I41" t="n">
-        <v>88.68000000000001</v>
+        <v>84.39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01123970237315402</v>
+        <v>0.01134289366186681</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4305,16 +4305,16 @@
         <v>90</v>
       </c>
       <c r="H42" t="n">
-        <v>33277.5</v>
+        <v>33462</v>
       </c>
       <c r="I42" t="n">
-        <v>369.75</v>
+        <v>371.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01083840336990511</v>
+        <v>0.01120849213452256</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4340,16 +4340,16 @@
         <v>493</v>
       </c>
       <c r="H43" t="n">
-        <v>32089.37</v>
+        <v>33065.51</v>
       </c>
       <c r="I43" t="n">
-        <v>65.09</v>
+        <v>67.06999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.009046123857713634</v>
+        <v>0.009045383127029752</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4375,16 +4375,16 @@
         <v>705</v>
       </c>
       <c r="H44" t="n">
-        <v>26782.95</v>
+        <v>26684.25</v>
       </c>
       <c r="I44" t="n">
-        <v>37.99</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.008962924221756033</v>
+        <v>0.008938184612546793</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4410,16 +4410,16 @@
         <v>1297</v>
       </c>
       <c r="H45" t="n">
-        <v>26536.62</v>
+        <v>26368.01</v>
       </c>
       <c r="I45" t="n">
-        <v>20.46</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.008808191070191483</v>
+        <v>0.008728523111178039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4445,16 +4445,16 @@
         <v>350</v>
       </c>
       <c r="H46" t="n">
-        <v>26078.5</v>
+        <v>25749.5</v>
       </c>
       <c r="I46" t="n">
-        <v>74.51000000000001</v>
+        <v>73.56999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.00865869314924173</v>
+        <v>0.008589199618142241</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4480,16 +4480,16 @@
         <v>431</v>
       </c>
       <c r="H47" t="n">
-        <v>25635.88</v>
+        <v>25338.49</v>
       </c>
       <c r="I47" t="n">
-        <v>59.48</v>
+        <v>58.79</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008422543717696749</v>
+        <v>0.008529668239716055</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4515,16 +4515,16 @@
         <v>257</v>
       </c>
       <c r="H48" t="n">
-        <v>24936.71</v>
+        <v>25162.87</v>
       </c>
       <c r="I48" t="n">
-        <v>97.03</v>
+        <v>97.91</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.00764502415462788</v>
+        <v>0.007672673335970857</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.00606155265989959</v>
+        <v>0.005970002015700881</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         <v>65</v>
       </c>
       <c r="H50" t="n">
-        <v>17946.5</v>
+        <v>17611.75</v>
       </c>
       <c r="I50" t="n">
-        <v>276.1</v>
+        <v>270.95</v>
       </c>
     </row>
   </sheetData>
@@ -4655,7 +4655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07170507428644318</v>
+        <v>0.07201872499666682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05399788120871097</v>
+        <v>0.05289300991750739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4716,16 +4716,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>118566.46</v>
+        <v>115634.62</v>
       </c>
       <c r="I3" t="n">
-        <v>116.47</v>
+        <v>113.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04249071076185357</v>
+        <v>0.04236943678838462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4751,16 +4751,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>93299.46000000001</v>
+        <v>92628</v>
       </c>
       <c r="I4" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03992589194597988</v>
+        <v>0.03983952472898024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4786,16 +4786,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>87667.73</v>
+        <v>87097.11</v>
       </c>
       <c r="I5" t="n">
-        <v>316.49</v>
+        <v>314.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03944163622081077</v>
+        <v>0.03782999542054397</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4821,16 +4821,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>86604.42</v>
+        <v>82703.88</v>
       </c>
       <c r="I6" t="n">
-        <v>111.46</v>
+        <v>106.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03534834072631956</v>
+        <v>0.03574613160016227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4856,16 +4856,16 @@
         <v>2798</v>
       </c>
       <c r="H7" t="n">
-        <v>77616.52</v>
+        <v>78148.14</v>
       </c>
       <c r="I7" t="n">
-        <v>27.74</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4874,33 +4874,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03409660177366999</v>
+        <v>0.03435923101805046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>816</v>
+        <v>246</v>
       </c>
       <c r="H8" t="n">
-        <v>74868</v>
+        <v>75116.10000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>91.75</v>
+        <v>305.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03382625818523611</v>
+        <v>0.03406985199130041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4926,16 +4926,16 @@
         <v>303</v>
       </c>
       <c r="H9" t="n">
-        <v>74274.39</v>
+        <v>74483.46000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>245.13</v>
+        <v>245.82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4944,33 +4944,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0332965148206863</v>
+        <v>0.03387996072744574</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>246</v>
+        <v>816</v>
       </c>
       <c r="H10" t="n">
-        <v>73111.2</v>
+        <v>74068.32000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>297.2</v>
+        <v>90.77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0324979125463608</v>
+        <v>0.03249656394424785</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4996,16 +4996,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>71357.66</v>
+        <v>71043.94</v>
       </c>
       <c r="I11" t="n">
-        <v>104.63</v>
+        <v>104.17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5014,33 +5014,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03158443439941429</v>
+        <v>0.03153334858171983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>197</v>
+        <v>568</v>
       </c>
       <c r="H12" t="n">
-        <v>69351.88</v>
+        <v>68938.16</v>
       </c>
       <c r="I12" t="n">
-        <v>352.04</v>
+        <v>121.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5049,33 +5049,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03146327369075548</v>
+        <v>0.03097279564529208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>568</v>
+        <v>1076</v>
       </c>
       <c r="H13" t="n">
-        <v>69085.84</v>
+        <v>67712.67999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>121.63</v>
+        <v>62.93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03079837447179028</v>
+        <v>0.03080399121302122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5101,16 +5101,16 @@
         <v>588</v>
       </c>
       <c r="H14" t="n">
-        <v>67625.88</v>
+        <v>67343.64</v>
       </c>
       <c r="I14" t="n">
-        <v>115.01</v>
+        <v>114.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5119,33 +5119,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03074325463804732</v>
+        <v>0.03063765682176018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>245</v>
+        <v>197</v>
       </c>
       <c r="H15" t="n">
-        <v>67504.85000000001</v>
+        <v>66980</v>
       </c>
       <c r="I15" t="n">
-        <v>275.53</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5154,33 +5154,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03046547854786441</v>
+        <v>0.02994533634575875</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1076</v>
+        <v>245</v>
       </c>
       <c r="H16" t="n">
-        <v>66894.92</v>
+        <v>65466.45</v>
       </c>
       <c r="I16" t="n">
-        <v>62.17</v>
+        <v>267.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02933080149776205</v>
+        <v>0.02824166215243801</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5206,16 +5206,16 @@
         <v>263</v>
       </c>
       <c r="H17" t="n">
-        <v>64403.44</v>
+        <v>61741.88</v>
       </c>
       <c r="I17" t="n">
-        <v>244.88</v>
+        <v>234.76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0279152833613511</v>
+        <v>0.02797799899709016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5241,16 +5241,16 @@
         <v>1082</v>
       </c>
       <c r="H18" t="n">
-        <v>61295.3</v>
+        <v>61165.46</v>
       </c>
       <c r="I18" t="n">
-        <v>56.65</v>
+        <v>56.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02613995836177715</v>
+        <v>0.02622701894428142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5276,16 +5276,16 @@
         <v>213</v>
       </c>
       <c r="H19" t="n">
-        <v>57397.11</v>
+        <v>57337.47</v>
       </c>
       <c r="I19" t="n">
-        <v>269.47</v>
+        <v>269.19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0259743164983495</v>
+        <v>0.02582574248563667</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5311,16 +5311,16 @@
         <v>1433</v>
       </c>
       <c r="H20" t="n">
-        <v>57033.4</v>
+        <v>56460.2</v>
       </c>
       <c r="I20" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02559827380875555</v>
+        <v>0.02571024519767766</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02363513695891923</v>
+        <v>0.0247697908056401</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
         <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>51897.12</v>
+        <v>54151.68</v>
       </c>
       <c r="I22" t="n">
-        <v>393.16</v>
+        <v>410.24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02343847624168481</v>
+        <v>0.02358793107224316</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5416,16 +5416,16 @@
         <v>190</v>
       </c>
       <c r="H23" t="n">
-        <v>51465.3</v>
+        <v>51567.9</v>
       </c>
       <c r="I23" t="n">
-        <v>270.87</v>
+        <v>271.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02242679070030443</v>
+        <v>0.02267281289715629</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5451,16 +5451,16 @@
         <v>443</v>
       </c>
       <c r="H24" t="n">
-        <v>49243.88</v>
+        <v>49567.27</v>
       </c>
       <c r="I24" t="n">
-        <v>111.16</v>
+        <v>111.89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02177773564407505</v>
+        <v>0.02214305313865092</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5486,16 +5486,16 @@
         <v>369</v>
       </c>
       <c r="H25" t="n">
-        <v>47818.71</v>
+        <v>48409.11</v>
       </c>
       <c r="I25" t="n">
-        <v>129.59</v>
+        <v>131.19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02082426681216639</v>
+        <v>0.02037580283422752</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5521,16 +5521,16 @@
         <v>959</v>
       </c>
       <c r="H26" t="n">
-        <v>45725.12</v>
+        <v>44545.55</v>
       </c>
       <c r="I26" t="n">
-        <v>47.68</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0205691206859485</v>
+        <v>0.02032377187777074</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5556,16 +5556,16 @@
         <v>298</v>
       </c>
       <c r="H27" t="n">
-        <v>45164.88</v>
+        <v>44431.8</v>
       </c>
       <c r="I27" t="n">
-        <v>151.56</v>
+        <v>149.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01952451262303398</v>
+        <v>0.01995756085316534</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5591,16 +5591,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>42871.17</v>
+        <v>43631.19</v>
       </c>
       <c r="I28" t="n">
-        <v>269.63</v>
+        <v>274.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5609,33 +5609,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0189707821342733</v>
+        <v>0.01929403922567837</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>601</v>
+        <v>484</v>
       </c>
       <c r="H29" t="n">
-        <v>41655.31</v>
+        <v>42180.6</v>
       </c>
       <c r="I29" t="n">
-        <v>69.31</v>
+        <v>87.15000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01876094603250461</v>
+        <v>0.01911905054258293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5661,16 +5661,16 @@
         <v>282</v>
       </c>
       <c r="H30" t="n">
-        <v>41194.56</v>
+        <v>41798.04</v>
       </c>
       <c r="I30" t="n">
-        <v>146.08</v>
+        <v>148.22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5679,33 +5679,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01870964719690347</v>
+        <v>0.01900153148031589</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>484</v>
+        <v>601</v>
       </c>
       <c r="H31" t="n">
-        <v>41081.92</v>
+        <v>41541.12</v>
       </c>
       <c r="I31" t="n">
-        <v>84.88</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5714,33 +5714,33 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01778428251223332</v>
+        <v>0.01780374455655564</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>246</v>
+        <v>148</v>
       </c>
       <c r="H32" t="n">
-        <v>39050.04</v>
+        <v>38922.52</v>
       </c>
       <c r="I32" t="n">
-        <v>158.74</v>
+        <v>262.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5749,33 +5749,33 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01741143689140642</v>
+        <v>0.01757063672332922</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>148</v>
+        <v>246</v>
       </c>
       <c r="H33" t="n">
-        <v>38231.36</v>
+        <v>38412.9</v>
       </c>
       <c r="I33" t="n">
-        <v>258.32</v>
+        <v>156.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01670053085095305</v>
+        <v>0.01670422867178595</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5801,16 +5801,16 @@
         <v>361</v>
       </c>
       <c r="H34" t="n">
-        <v>36670.38</v>
+        <v>36518.76</v>
       </c>
       <c r="I34" t="n">
-        <v>101.58</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01643856248967386</v>
+        <v>0.01666020705201099</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5836,16 +5836,16 @@
         <v>372</v>
       </c>
       <c r="H35" t="n">
-        <v>36095.16</v>
+        <v>36422.52</v>
       </c>
       <c r="I35" t="n">
-        <v>97.03</v>
+        <v>97.91</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01638750047398138</v>
+        <v>0.01663761075092119</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         <v>736</v>
       </c>
       <c r="H36" t="n">
-        <v>35983.04</v>
+        <v>36373.12</v>
       </c>
       <c r="I36" t="n">
-        <v>48.89</v>
+        <v>49.42</v>
       </c>
     </row>
   </sheetData>
@@ -5888,7 +5888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5941,7 +5941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1060254858980799</v>
+        <v>0.1065075235600705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5967,16 +5967,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>222991.8</v>
+        <v>223997.4</v>
       </c>
       <c r="I2" t="n">
-        <v>53.22</v>
+        <v>53.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0991001029364648</v>
+        <v>0.09915965539471149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6002,16 +6002,16 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>208426.4</v>
+        <v>208544</v>
       </c>
       <c r="I3" t="n">
-        <v>212.68</v>
+        <v>212.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09836151080081641</v>
+        <v>0.09879448250389161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6037,16 +6037,16 @@
         <v>4300</v>
       </c>
       <c r="H4" t="n">
-        <v>206873</v>
+        <v>207776</v>
       </c>
       <c r="I4" t="n">
-        <v>48.11</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6055,33 +6055,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08204510998777549</v>
+        <v>0.05512541549114756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>PXF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SPDR® S&amp;P Oil &amp; Gas Explor &amp; Prodtn ETF</t>
+          <t>Invesco RAFI Developed Markets ex-US ETF</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>934</v>
+        <v>1475</v>
       </c>
       <c r="H5" t="n">
-        <v>172556.5</v>
+        <v>115935</v>
       </c>
       <c r="I5" t="n">
-        <v>184.75</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6090,33 +6090,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05489897242073478</v>
+        <v>0.04416047180337494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PXF</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Invesco RAFI Developed Markets ex-US ETF</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1475</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>115463</v>
+        <v>92874.48</v>
       </c>
       <c r="I6" t="n">
-        <v>78.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03836690879007611</v>
+        <v>0.03830398303771922</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6142,16 +6142,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>80692.92</v>
+        <v>80557.62</v>
       </c>
       <c r="I7" t="n">
-        <v>29.82</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6160,33 +6160,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.02747945020958752</v>
+        <v>0.03784432166139971</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>PICK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>iShares MSCI Global Mtls&amp;Mng Prdcrs ETF</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>147</v>
+        <v>1270</v>
       </c>
       <c r="H8" t="n">
-        <v>57794.52</v>
+        <v>79590.89999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>393.16</v>
+        <v>62.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6195,33 +6195,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0250424527630176</v>
+        <v>0.02867428831940303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="H9" t="n">
-        <v>52669.05</v>
+        <v>60305.28</v>
       </c>
       <c r="I9" t="n">
-        <v>501.61</v>
+        <v>410.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6230,33 +6230,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02497379992507099</v>
+        <v>0.02486313862105581</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H10" t="n">
-        <v>52524.66</v>
+        <v>52290</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6265,33 +6265,33 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02331466352394937</v>
+        <v>0.02461058447918215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GARA</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guiness Atkinson Real Asset Fund</t>
+          <t>SPDR® S&amp;P Oil &amp; Gas Explor &amp; Prodtn ETF</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1860</v>
+        <v>285</v>
       </c>
       <c r="H11" t="n">
-        <v>49035.18</v>
+        <v>51758.85</v>
       </c>
       <c r="I11" t="n">
-        <v>26.36</v>
+        <v>181.61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6300,33 +6300,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02075584639727485</v>
+        <v>0.02334718137405239</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>GARA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Guiness Atkinson Real Asset Fund</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>275</v>
+        <v>1860</v>
       </c>
       <c r="H12" t="n">
-        <v>43653.5</v>
+        <v>49101.77</v>
       </c>
       <c r="I12" t="n">
-        <v>158.74</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6335,33 +6335,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02069890433845854</v>
+        <v>0.02081979982629563</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CEF</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Sprott Physical Gold and Silver Trust</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>158</v>
+        <v>980</v>
       </c>
       <c r="H13" t="n">
-        <v>43533.74</v>
+        <v>43786.4</v>
       </c>
       <c r="I13" t="n">
-        <v>275.53</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6370,33 +6370,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02066526972556053</v>
+        <v>0.02041794322645655</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sprott Physical Gold and Silver Trust</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>980</v>
+        <v>275</v>
       </c>
       <c r="H14" t="n">
-        <v>43463</v>
+        <v>42941.25</v>
       </c>
       <c r="I14" t="n">
-        <v>44.35</v>
+        <v>156.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02024365314878388</v>
+        <v>0.02022336028100054</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6422,16 +6422,16 @@
         <v>158</v>
       </c>
       <c r="H15" t="n">
-        <v>42576.26</v>
+        <v>42532.02</v>
       </c>
       <c r="I15" t="n">
-        <v>269.47</v>
+        <v>269.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6440,33 +6440,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01956139447279278</v>
+        <v>0.02007460938625564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="H16" t="n">
-        <v>41141.34</v>
+        <v>42219.18</v>
       </c>
       <c r="I16" t="n">
-        <v>203.67</v>
+        <v>267.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6475,33 +6475,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01790091725164893</v>
+        <v>0.01944109147894735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASML Holding</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>22</v>
+        <v>202</v>
       </c>
       <c r="H17" t="n">
-        <v>37649.04</v>
+        <v>40886.82</v>
       </c>
       <c r="I17" t="n">
-        <v>1711.32</v>
+        <v>202.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6510,33 +6510,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01685971820289892</v>
+        <v>0.01828422566277216</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>ASML Holding</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>224</v>
+        <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>35459.2</v>
+        <v>38453.8</v>
       </c>
       <c r="I18" t="n">
-        <v>158.3</v>
+        <v>1747.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6545,33 +6545,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0166967657780699</v>
+        <v>0.01690400527142284</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BKH</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Black Hills</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>488</v>
+        <v>224</v>
       </c>
       <c r="H19" t="n">
-        <v>35116.48</v>
+        <v>35551.04</v>
       </c>
       <c r="I19" t="n">
-        <v>71.95999999999999</v>
+        <v>158.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6580,33 +6580,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01657099495811257</v>
+        <v>0.01665329125856932</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>BKH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Black Hills</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>99</v>
+        <v>488</v>
       </c>
       <c r="H20" t="n">
-        <v>34851.96</v>
+        <v>35023.76</v>
       </c>
       <c r="I20" t="n">
-        <v>352.04</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6615,33 +6615,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01621667613521752</v>
+        <v>0.0160048431054645</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>306</v>
+        <v>99</v>
       </c>
       <c r="H21" t="n">
-        <v>34106.76</v>
+        <v>33660</v>
       </c>
       <c r="I21" t="n">
-        <v>111.46</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6650,33 +6650,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01468548819791911</v>
+        <v>0.01548686818314219</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>126</v>
+        <v>306</v>
       </c>
       <c r="H22" t="n">
-        <v>30886.38</v>
+        <v>32570.64</v>
       </c>
       <c r="I22" t="n">
-        <v>245.13</v>
+        <v>106.44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6685,33 +6685,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01413452528112586</v>
+        <v>0.01472736562850106</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="H23" t="n">
-        <v>29727.6</v>
+        <v>30973.32</v>
       </c>
       <c r="I23" t="n">
-        <v>353.9</v>
+        <v>245.82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01396073218377669</v>
+        <v>0.01416576966320504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6737,16 +6737,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>29362.08</v>
+        <v>29792.22</v>
       </c>
       <c r="I24" t="n">
-        <v>146.08</v>
+        <v>148.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6755,33 +6755,33 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01326537436182375</v>
+        <v>0.01371526613828812</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="H25" t="n">
-        <v>27899.61</v>
+        <v>28844.76</v>
       </c>
       <c r="I25" t="n">
-        <v>270.87</v>
+        <v>343.39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01321325830415128</v>
+        <v>0.01330051912559732</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6807,16 +6807,16 @@
         <v>250</v>
       </c>
       <c r="H26" t="n">
-        <v>27790</v>
+        <v>27972.5</v>
       </c>
       <c r="I26" t="n">
-        <v>111.16</v>
+        <v>111.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6825,33 +6825,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01223777845521415</v>
+        <v>0.01329230749040922</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>414</v>
+        <v>103</v>
       </c>
       <c r="H27" t="n">
-        <v>25738.38</v>
+        <v>27955.23</v>
       </c>
       <c r="I27" t="n">
-        <v>62.17</v>
+        <v>271.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6860,33 +6860,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01172726836377237</v>
+        <v>0.01238783415102581</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>524</v>
+        <v>414</v>
       </c>
       <c r="H28" t="n">
-        <v>24664.68</v>
+        <v>26053.02</v>
       </c>
       <c r="I28" t="n">
-        <v>47.07</v>
+        <v>62.93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6895,33 +6895,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0110905500217277</v>
+        <v>0.0118024448895623</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Total SA</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>259</v>
+        <v>524</v>
       </c>
       <c r="H29" t="n">
-        <v>23325.54</v>
+        <v>24821.88</v>
       </c>
       <c r="I29" t="n">
-        <v>90.06</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6930,33 +6930,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0109367170749222</v>
+        <v>0.01106509520599317</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Total SA</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="H30" t="n">
-        <v>23002</v>
+        <v>23271.15</v>
       </c>
       <c r="I30" t="n">
-        <v>115.01</v>
+        <v>89.84999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6965,33 +6965,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01090604938292443</v>
+        <v>0.01089147166291651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H31" t="n">
-        <v>22937.5</v>
+        <v>22906</v>
       </c>
       <c r="I31" t="n">
-        <v>91.75</v>
+        <v>114.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7000,33 +7000,33 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.008988724297948182</v>
+        <v>0.01078995550121073</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>475</v>
+        <v>250</v>
       </c>
       <c r="H32" t="n">
-        <v>18905</v>
+        <v>22692.5</v>
       </c>
       <c r="I32" t="n">
-        <v>39.8</v>
+        <v>90.77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7035,33 +7035,33 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.008705939649643253</v>
+        <v>0.008898711786059658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>175</v>
+        <v>475</v>
       </c>
       <c r="H33" t="n">
-        <v>18310.25</v>
+        <v>18715</v>
       </c>
       <c r="I33" t="n">
-        <v>104.63</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7070,33 +7070,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.008573165184676206</v>
+        <v>0.008667982430238903</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>650</v>
+        <v>175</v>
       </c>
       <c r="H34" t="n">
-        <v>18031</v>
+        <v>18229.75</v>
       </c>
       <c r="I34" t="n">
-        <v>27.74</v>
+        <v>104.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7105,33 +7105,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.008548754652782174</v>
+        <v>0.008632202143736044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>177</v>
+        <v>650</v>
       </c>
       <c r="H35" t="n">
-        <v>17979.66</v>
+        <v>18154.5</v>
       </c>
       <c r="I35" t="n">
-        <v>101.58</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7140,33 +7140,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.008546710139982325</v>
+        <v>0.008513720658144255</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>377</v>
+        <v>177</v>
       </c>
       <c r="H36" t="n">
-        <v>17975.36</v>
+        <v>17905.32</v>
       </c>
       <c r="I36" t="n">
-        <v>47.68</v>
+        <v>101.16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7175,33 +7175,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.00819116460940736</v>
+        <v>0.008326536267611628</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="H37" t="n">
-        <v>17227.58</v>
+        <v>17511.65</v>
       </c>
       <c r="I37" t="n">
-        <v>47.59</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008133300142490656</v>
+        <v>0.008234021047081912</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -7227,16 +7227,16 @@
         <v>132</v>
       </c>
       <c r="H38" t="n">
-        <v>17105.88</v>
+        <v>17317.08</v>
       </c>
       <c r="I38" t="n">
-        <v>129.59</v>
+        <v>131.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008019744097842205</v>
+        <v>0.008106980821861533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7262,16 +7262,16 @@
         <v>345</v>
       </c>
       <c r="H39" t="n">
-        <v>16867.05</v>
+        <v>17049.9</v>
       </c>
       <c r="I39" t="n">
-        <v>48.89</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7280,33 +7280,33 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.007744352978383248</v>
+        <v>0.008077862087702926</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>235</v>
+        <v>362</v>
       </c>
       <c r="H40" t="n">
-        <v>16287.85</v>
+        <v>16988.66</v>
       </c>
       <c r="I40" t="n">
-        <v>69.31</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7315,33 +7315,33 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.007326392751241679</v>
+        <v>0.007723406640840195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>272</v>
+        <v>235</v>
       </c>
       <c r="H41" t="n">
-        <v>15408.8</v>
+        <v>16243.2</v>
       </c>
       <c r="I41" t="n">
-        <v>56.65</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7350,33 +7350,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.007022245321518777</v>
+        <v>0.007311141662641682</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>174</v>
+        <v>272</v>
       </c>
       <c r="H42" t="n">
-        <v>14769.12</v>
+        <v>15376.16</v>
       </c>
       <c r="I42" t="n">
-        <v>84.88</v>
+        <v>56.53</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7385,33 +7385,33 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.006922824943274874</v>
+        <v>0.007210310200106186</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="H43" t="n">
-        <v>14560.02</v>
+        <v>15164.1</v>
       </c>
       <c r="I43" t="n">
-        <v>269.63</v>
+        <v>87.15000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7420,33 +7420,33 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.004720209493143643</v>
+        <v>0.007045811224444674</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>275</v>
+        <v>54</v>
       </c>
       <c r="H44" t="n">
-        <v>9927.5</v>
+        <v>14818.14</v>
       </c>
       <c r="I44" t="n">
-        <v>36.1</v>
+        <v>274.41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7455,33 +7455,33 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.004097964399849553</v>
+        <v>0.0047203826479352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>29</v>
+        <v>275</v>
       </c>
       <c r="H45" t="n">
-        <v>8618.799999999999</v>
+        <v>9927.5</v>
       </c>
       <c r="I45" t="n">
-        <v>297.2</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/21/2026</t>
+          <t>09/22/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7490,278 +7490,65 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.002522168046066963</v>
+        <v>0.004210495734561912</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>29</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8855.15</v>
+      </c>
+      <c r="I46" t="n">
+        <v>305.35</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>09/22/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Dividend Core Plus</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.002481321263988904</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>JKHY</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="G47" t="n">
         <v>35</v>
       </c>
-      <c r="H46" t="n">
-        <v>5304.6</v>
-      </c>
-      <c r="I46" t="n">
-        <v>151.56</v>
+      <c r="H47" t="n">
+        <v>5218.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>149.1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09C8D40A-3371-4AF7-83C0-C27A0FA79598}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E09A5321-6F7C-446B-ACD1-BB5AC82E8694}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4E6B1B0-FA67-4DEC-A663-5AB0C8F538BD}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -7551,4 +7551,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A209656-EA46-4186-ABC5-2007DCFB0327}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84E41DD1-7DDB-4C71-BE49-7A9CA08B8733}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EA3D649-75B9-4528-AB37-30AE75F2E46D}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1098151437223026</v>
+        <v>0.1102943796649651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04736675300036343</v>
+        <v>0.0470922080974801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>110354.56</v>
+        <v>109238.21</v>
       </c>
       <c r="I3" t="n">
-        <v>410.24</v>
+        <v>406.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03991308364684736</v>
+        <v>0.04062584276667997</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>92989.08</v>
+        <v>94238.39999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>267.21</v>
+        <v>270.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,33 +596,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03778244044047551</v>
+        <v>0.0380070997624598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>327</v>
+        <v>429</v>
       </c>
       <c r="H5" t="n">
-        <v>88025.13</v>
+        <v>88163.78999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>269.19</v>
+        <v>205.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,33 +631,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03760002910477633</v>
+        <v>0.03794450455318501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>561</v>
+        <v>327</v>
       </c>
       <c r="H6" t="n">
-        <v>87600.14999999999</v>
+        <v>88018.59</v>
       </c>
       <c r="I6" t="n">
-        <v>156.15</v>
+        <v>269.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,33 +666,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03727113242706716</v>
+        <v>0.03730702925145692</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>429</v>
+        <v>561</v>
       </c>
       <c r="H7" t="n">
-        <v>86833.89</v>
+        <v>86539.86</v>
       </c>
       <c r="I7" t="n">
-        <v>202.41</v>
+        <v>154.26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0360114949788037</v>
+        <v>0.03610057125715761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         <v>48</v>
       </c>
       <c r="H8" t="n">
-        <v>83899.2</v>
+        <v>83741.28</v>
       </c>
       <c r="I8" t="n">
-        <v>1747.9</v>
+        <v>1744.61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03222172328347168</v>
+        <v>0.03287618942645001</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -753,16 +753,16 @@
         <v>473</v>
       </c>
       <c r="H9" t="n">
-        <v>75069.83</v>
+        <v>76261.78999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>158.71</v>
+        <v>161.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0321916003893605</v>
+        <v>0.03176446057323917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -788,16 +788,16 @@
         <v>1045</v>
       </c>
       <c r="H10" t="n">
-        <v>74999.64999999999</v>
+        <v>73682.95</v>
       </c>
       <c r="I10" t="n">
-        <v>71.77</v>
+        <v>70.51000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0306556632916635</v>
+        <v>0.03078655269015974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         <v>671</v>
       </c>
       <c r="H11" t="n">
-        <v>71421.24000000001</v>
+        <v>71414.53</v>
       </c>
       <c r="I11" t="n">
-        <v>106.44</v>
+        <v>106.43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02949794492585514</v>
+        <v>0.02978075717562035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         <v>138</v>
       </c>
       <c r="H12" t="n">
-        <v>68724</v>
+        <v>69081.42</v>
       </c>
       <c r="I12" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02874124563583948</v>
+        <v>0.02886162929794464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         <v>195</v>
       </c>
       <c r="H13" t="n">
-        <v>66961.05</v>
+        <v>66949.35000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>343.39</v>
+        <v>343.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,33 +911,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02780171437124991</v>
+        <v>0.02797611401301793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>437</v>
+        <v>263</v>
       </c>
       <c r="H14" t="n">
-        <v>64772.14</v>
+        <v>64895.25</v>
       </c>
       <c r="I14" t="n">
-        <v>148.22</v>
+        <v>246.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02774957231971634</v>
+        <v>0.02776667871983693</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>263</v>
+        <v>437</v>
       </c>
       <c r="H15" t="n">
-        <v>64650.66</v>
+        <v>64409.43</v>
       </c>
       <c r="I15" t="n">
-        <v>245.82</v>
+        <v>147.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02729002005683414</v>
+        <v>0.02720999520991454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -998,16 +998,16 @@
         <v>187</v>
       </c>
       <c r="H16" t="n">
-        <v>63580</v>
+        <v>63118.11</v>
       </c>
       <c r="I16" t="n">
-        <v>340</v>
+        <v>337.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02609499359817678</v>
+        <v>0.02632571717189292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>224</v>
       </c>
       <c r="H17" t="n">
-        <v>60795.84</v>
+        <v>61066.88</v>
       </c>
       <c r="I17" t="n">
-        <v>271.41</v>
+        <v>272.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02508781673495624</v>
+        <v>0.02530014295073144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1068,16 +1068,16 @@
         <v>213</v>
       </c>
       <c r="H18" t="n">
-        <v>58449.33</v>
+        <v>58687.89</v>
       </c>
       <c r="I18" t="n">
-        <v>274.41</v>
+        <v>275.53</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,33 +1086,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02425590034656436</v>
+        <v>0.02423055377869561</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>898</v>
+        <v>1170</v>
       </c>
       <c r="H19" t="n">
-        <v>56511.14</v>
+        <v>56206.8</v>
       </c>
       <c r="I19" t="n">
-        <v>62.93</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,33 +1121,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02356783816109869</v>
+        <v>0.02406366770834809</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1170</v>
+        <v>898</v>
       </c>
       <c r="H20" t="n">
-        <v>54908.1</v>
+        <v>55819.68</v>
       </c>
       <c r="I20" t="n">
-        <v>46.93</v>
+        <v>62.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02259101168036036</v>
+        <v>0.0225724230666726</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         <v>353</v>
       </c>
       <c r="H21" t="n">
-        <v>52632.3</v>
+        <v>52360.49</v>
       </c>
       <c r="I21" t="n">
-        <v>149.1</v>
+        <v>148.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,33 +1191,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0219477904573882</v>
+        <v>0.02197234969577564</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Coca-Cola Femsa</t>
+          <t>Total SA</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="H22" t="n">
-        <v>51133.73</v>
+        <v>50968.52</v>
       </c>
       <c r="I22" t="n">
-        <v>111.89</v>
+        <v>91.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,33 +1226,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0216231345062937</v>
+        <v>0.02178351650349852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Coca-Cola Femsa</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>555</v>
+        <v>457</v>
       </c>
       <c r="H23" t="n">
-        <v>50377.35</v>
+        <v>50530.49</v>
       </c>
       <c r="I23" t="n">
-        <v>90.77</v>
+        <v>110.57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,33 +1261,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02144253878532936</v>
+        <v>0.02136578832281543</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Total SA</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H24" t="n">
-        <v>49956.6</v>
+        <v>49561.5</v>
       </c>
       <c r="I24" t="n">
-        <v>89.84999999999999</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02096409211095138</v>
+        <v>0.02071290994376372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         <v>864</v>
       </c>
       <c r="H25" t="n">
-        <v>48841.92</v>
+        <v>48047.04</v>
       </c>
       <c r="I25" t="n">
-        <v>56.53</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,33 +1331,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02094171240592207</v>
+        <v>0.01920397741340679</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>426</v>
       </c>
       <c r="H26" t="n">
-        <v>48789.78</v>
+        <v>44546.82</v>
       </c>
       <c r="I26" t="n">
-        <v>114.53</v>
+        <v>104.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,33 +1366,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01907170648925</v>
+        <v>0.01918928564527949</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>938</v>
+        <v>426</v>
       </c>
       <c r="H27" t="n">
-        <v>44433.06</v>
+        <v>44512.74</v>
       </c>
       <c r="I27" t="n">
-        <v>47.37</v>
+        <v>104.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,33 +1401,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01904739527918364</v>
+        <v>0.01897297005223605</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>426</v>
+        <v>938</v>
       </c>
       <c r="H28" t="n">
-        <v>44376.42</v>
+        <v>44010.96</v>
       </c>
       <c r="I28" t="n">
-        <v>104.17</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01863854716964076</v>
+        <v>0.01857576637508996</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>331</v>
       </c>
       <c r="H29" t="n">
-        <v>43423.89</v>
+        <v>43089.58</v>
       </c>
       <c r="I29" t="n">
-        <v>131.19</v>
+        <v>130.18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,33 +1471,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01838269142796605</v>
+        <v>0.01845023970128394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1087</v>
+        <v>920</v>
       </c>
       <c r="H30" t="n">
-        <v>42827.8</v>
+        <v>42798.4</v>
       </c>
       <c r="I30" t="n">
-        <v>39.4</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,33 +1506,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01834243027852706</v>
+        <v>0.01827104151539312</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>920</v>
+        <v>1504</v>
       </c>
       <c r="H31" t="n">
-        <v>42734</v>
+        <v>42382.72</v>
       </c>
       <c r="I31" t="n">
-        <v>46.45</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,33 +1541,33 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01803026472667216</v>
+        <v>0.01788653362965986</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1504</v>
+        <v>1087</v>
       </c>
       <c r="H32" t="n">
-        <v>42006.72</v>
+        <v>41490.79</v>
       </c>
       <c r="I32" t="n">
-        <v>27.93</v>
+        <v>38.17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01661403372670479</v>
+        <v>0.0162495783768626</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>38707.2</v>
+        <v>37693.6</v>
       </c>
       <c r="I33" t="n">
-        <v>69.12</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.016108906529415</v>
+        <v>0.01587052817259917</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>37530.36</v>
+        <v>36814.33</v>
       </c>
       <c r="I34" t="n">
-        <v>101.16</v>
+        <v>99.23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01395274170315358</v>
+        <v>0.01349746705381775</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         <v>373</v>
       </c>
       <c r="H35" t="n">
-        <v>32506.95</v>
+        <v>31309.62</v>
       </c>
       <c r="I35" t="n">
-        <v>87.15000000000001</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01140251121923285</v>
+        <v>0.01112860050381211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
         <v>87</v>
       </c>
       <c r="H36" t="n">
-        <v>26565.45</v>
+        <v>25814.64</v>
       </c>
       <c r="I36" t="n">
-        <v>305.35</v>
+        <v>296.72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01107277755600761</v>
+        <v>0.01104683874492053</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         <v>522</v>
       </c>
       <c r="H37" t="n">
-        <v>25797.24</v>
+        <v>25624.98</v>
       </c>
       <c r="I37" t="n">
-        <v>49.42</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008909603512578402</v>
+        <v>0.008936091213876906</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         <v>575</v>
       </c>
       <c r="H38" t="n">
-        <v>20757.5</v>
+        <v>20728.75</v>
       </c>
       <c r="I38" t="n">
-        <v>36.1</v>
+        <v>36.05</v>
       </c>
     </row>
   </sheetData>
@@ -1838,7 +1838,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.05955004527297714</v>
+        <v>0.05932156623440095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1864,16 +1864,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>151621.65</v>
+        <v>149786.46</v>
       </c>
       <c r="I2" t="n">
-        <v>156.15</v>
+        <v>154.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05536959668016471</v>
+        <v>0.0571535194694465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>140977.72</v>
+        <v>144312.16</v>
       </c>
       <c r="I3" t="n">
-        <v>46.93</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05126485932138298</v>
+        <v>0.05130630807707302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         <v>556</v>
       </c>
       <c r="H4" t="n">
-        <v>130526.56</v>
+        <v>129548</v>
       </c>
       <c r="I4" t="n">
-        <v>234.76</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05079399805073717</v>
+        <v>0.05121905630373449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05020277724453754</v>
+        <v>0.04973414842883086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2004,16 +2004,16 @@
         <v>1781</v>
       </c>
       <c r="H6" t="n">
-        <v>127822.37</v>
+        <v>125578.31</v>
       </c>
       <c r="I6" t="n">
-        <v>71.77</v>
+        <v>70.51000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04925544617275903</v>
+        <v>0.04531363481810471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2039,16 +2039,16 @@
         <v>1095</v>
       </c>
       <c r="H7" t="n">
-        <v>125410.35</v>
+        <v>114416.55</v>
       </c>
       <c r="I7" t="n">
-        <v>114.53</v>
+        <v>104.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04344608080740091</v>
+        <v>0.04397539277416861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2074,16 +2074,16 @@
         <v>450</v>
       </c>
       <c r="H8" t="n">
-        <v>110619</v>
+        <v>111037.5</v>
       </c>
       <c r="I8" t="n">
-        <v>245.82</v>
+        <v>246.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04116743855769428</v>
+        <v>0.04129755818678626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2109,16 +2109,16 @@
         <v>703</v>
       </c>
       <c r="H9" t="n">
-        <v>104817.3</v>
+        <v>104275.99</v>
       </c>
       <c r="I9" t="n">
-        <v>149.1</v>
+        <v>148.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03963504506613312</v>
+        <v>0.03969984597889722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>100915.64</v>
+        <v>100241.78</v>
       </c>
       <c r="I10" t="n">
-        <v>49.42</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03794419095060543</v>
+        <v>0.03912234704173241</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>796</v>
       </c>
       <c r="H11" t="n">
-        <v>96610.52</v>
+        <v>98783.60000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>121.37</v>
+        <v>124.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2197,33 +2197,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03703527124308589</v>
+        <v>0.03648431852642239</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1082</v>
+        <v>295</v>
       </c>
       <c r="H12" t="n">
-        <v>94296.3</v>
+        <v>92122.60000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>87.15000000000001</v>
+        <v>312.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2232,33 +2232,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0364306457348192</v>
+        <v>0.03627405248538524</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Principal Financial</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>295</v>
+        <v>804</v>
       </c>
       <c r="H13" t="n">
-        <v>92756.85000000001</v>
+        <v>91591.67999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>314.43</v>
+        <v>113.92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2267,33 +2267,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03586881472808275</v>
+        <v>0.03596965544036689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Principal Financial</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>804</v>
+        <v>1082</v>
       </c>
       <c r="H14" t="n">
-        <v>91326.36</v>
+        <v>90823.08</v>
       </c>
       <c r="I14" t="n">
-        <v>113.59</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03377597272469508</v>
+        <v>0.03437072738687779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,16 +2319,16 @@
         <v>327</v>
       </c>
       <c r="H15" t="n">
-        <v>85997.73</v>
+        <v>86785.8</v>
       </c>
       <c r="I15" t="n">
-        <v>262.99</v>
+        <v>265.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03345137313145258</v>
+        <v>0.03341086679074418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>1798</v>
       </c>
       <c r="H16" t="n">
-        <v>85171.25999999999</v>
+        <v>84362.16</v>
       </c>
       <c r="I16" t="n">
-        <v>47.37</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03292784744533146</v>
+        <v>0.0330700498234517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         <v>910</v>
       </c>
       <c r="H17" t="n">
-        <v>83838.3</v>
+        <v>83501.60000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>92.13</v>
+        <v>91.76000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03217434844399354</v>
+        <v>0.03222145296115553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
         <v>710</v>
       </c>
       <c r="H18" t="n">
-        <v>81919.8</v>
+        <v>81358.89999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>115.38</v>
+        <v>114.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03139559534529517</v>
+        <v>0.03152634175433277</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
         <v>215</v>
       </c>
       <c r="H19" t="n">
-        <v>79937</v>
+        <v>79603.75</v>
       </c>
       <c r="I19" t="n">
-        <v>371.8</v>
+        <v>370.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2477,33 +2477,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03105724935380048</v>
+        <v>0.03130898262056042</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Eastman Chemical</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1179</v>
+        <v>756</v>
       </c>
       <c r="H20" t="n">
-        <v>79075.53</v>
+        <v>79054.92</v>
       </c>
       <c r="I20" t="n">
-        <v>67.06999999999999</v>
+        <v>104.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2512,33 +2512,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03093038580810219</v>
+        <v>0.03119107332021841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Eastman Chemical</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>756</v>
+        <v>1179</v>
       </c>
       <c r="H21" t="n">
-        <v>78752.52</v>
+        <v>78757.2</v>
       </c>
       <c r="I21" t="n">
-        <v>104.17</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02985307664953568</v>
+        <v>0.03038593402720388</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2564,16 +2564,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>76009.56</v>
+        <v>76724.23</v>
       </c>
       <c r="I22" t="n">
-        <v>77.64</v>
+        <v>78.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02598531148645228</v>
+        <v>0.02584569328834932</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2599,16 +2599,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>66161.75999999999</v>
+        <v>65260.16</v>
       </c>
       <c r="I23" t="n">
-        <v>84.39</v>
+        <v>83.23999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02515178488203248</v>
+        <v>0.02485077515067911</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>64039.5</v>
+        <v>62748</v>
       </c>
       <c r="I24" t="n">
-        <v>20.33</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0243946921794372</v>
+        <v>0.02415040056013492</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2669,16 +2669,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>62111.85</v>
+        <v>60979.56</v>
       </c>
       <c r="I25" t="n">
-        <v>37.85</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02253437639379887</v>
+        <v>0.02246998312857794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2704,16 +2704,16 @@
         <v>586</v>
       </c>
       <c r="H26" t="n">
-        <v>57375.26</v>
+        <v>56736.52</v>
       </c>
       <c r="I26" t="n">
-        <v>97.91</v>
+        <v>96.81999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02200479050981971</v>
+        <v>0.02202663908996833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2739,16 +2739,16 @@
         <v>953</v>
       </c>
       <c r="H27" t="n">
-        <v>56026.87</v>
+        <v>55617.08</v>
       </c>
       <c r="I27" t="n">
-        <v>58.79</v>
+        <v>58.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.020862138829047</v>
+        <v>0.0206993079731598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2774,16 +2774,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>53117.54</v>
+        <v>52265.58</v>
       </c>
       <c r="I28" t="n">
-        <v>73.56999999999999</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01553684698682623</v>
+        <v>0.01560036835923648</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>39558.7</v>
+        <v>39390.8</v>
       </c>
       <c r="I29" t="n">
-        <v>270.95</v>
+        <v>269.8</v>
       </c>
     </row>
   </sheetData>
@@ -2879,7 +2879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1074940188625454</v>
+        <v>0.1079576469825329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03852030687791689</v>
+        <v>0.03829509401366831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2940,16 +2940,16 @@
         <v>277</v>
       </c>
       <c r="H3" t="n">
-        <v>113636.48</v>
+        <v>112486.93</v>
       </c>
       <c r="I3" t="n">
-        <v>410.24</v>
+        <v>406.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03722772479003748</v>
+        <v>0.03789060657632373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>411</v>
       </c>
       <c r="H4" t="n">
-        <v>109823.31</v>
+        <v>111298.8</v>
       </c>
       <c r="I4" t="n">
-        <v>267.21</v>
+        <v>270.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03387614072656512</v>
+        <v>0.03361045385122542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3010,16 +3010,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>99936</v>
+        <v>98726.39999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>156.15</v>
+        <v>154.26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03245376382716432</v>
+        <v>0.03309292658768681</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>95739.92999999999</v>
+        <v>97206.23</v>
       </c>
       <c r="I6" t="n">
-        <v>202.41</v>
+        <v>205.51</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03111610778763174</v>
+        <v>0.03124799161449026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         <v>341</v>
       </c>
       <c r="H7" t="n">
-        <v>91793.78999999999</v>
+        <v>91786.97</v>
       </c>
       <c r="I7" t="n">
-        <v>269.19</v>
+        <v>269.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03023575727533647</v>
+        <v>0.03036331301088059</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3115,16 +3115,16 @@
         <v>838</v>
       </c>
       <c r="H8" t="n">
-        <v>89196.72</v>
+        <v>89188.34</v>
       </c>
       <c r="I8" t="n">
-        <v>106.44</v>
+        <v>106.43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02975098772190574</v>
+        <v>0.03035372961397853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3150,16 +3150,16 @@
         <v>553</v>
       </c>
       <c r="H9" t="n">
-        <v>87766.63</v>
+        <v>89160.19</v>
       </c>
       <c r="I9" t="n">
-        <v>158.71</v>
+        <v>161.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02805073331729559</v>
+        <v>0.02767713281868416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>82750.81</v>
+        <v>81298.03</v>
       </c>
       <c r="I10" t="n">
-        <v>71.77</v>
+        <v>70.51000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02637777005991863</v>
+        <v>0.02634319205799421</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3220,16 +3220,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>77815.5</v>
+        <v>77379.75</v>
       </c>
       <c r="I11" t="n">
-        <v>148.22</v>
+        <v>147.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02474831467420207</v>
+        <v>0.02494908867206332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>73008.53999999999</v>
+        <v>73284.75</v>
       </c>
       <c r="I12" t="n">
-        <v>245.82</v>
+        <v>246.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02438056044836911</v>
+        <v>0.02459487747111294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>265</v>
       </c>
       <c r="H13" t="n">
-        <v>71923.64999999999</v>
+        <v>72244.3</v>
       </c>
       <c r="I13" t="n">
-        <v>271.41</v>
+        <v>272.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02380238201987222</v>
+        <v>0.02402936853939043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3325,16 +3325,16 @@
         <v>141</v>
       </c>
       <c r="H14" t="n">
-        <v>70218</v>
+        <v>70583.19</v>
       </c>
       <c r="I14" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02351153859264486</v>
+        <v>0.02344140415972262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
         <v>204</v>
       </c>
       <c r="H15" t="n">
-        <v>69360</v>
+        <v>68856.12</v>
       </c>
       <c r="I15" t="n">
-        <v>340</v>
+        <v>337.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3378,33 +3378,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02196227870577848</v>
+        <v>0.02194956033860228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1311</v>
+        <v>234</v>
       </c>
       <c r="H16" t="n">
-        <v>64789.62</v>
+        <v>64474.02</v>
       </c>
       <c r="I16" t="n">
-        <v>49.42</v>
+        <v>275.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3413,33 +3413,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02176645769057953</v>
+        <v>0.02190971860007835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>234</v>
+        <v>1311</v>
       </c>
       <c r="H17" t="n">
-        <v>64211.94</v>
+        <v>64356.99</v>
       </c>
       <c r="I17" t="n">
-        <v>274.41</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02153075248231814</v>
+        <v>0.02151194464717102</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3465,16 +3465,16 @@
         <v>426</v>
       </c>
       <c r="H18" t="n">
-        <v>63516.6</v>
+        <v>63188.58</v>
       </c>
       <c r="I18" t="n">
-        <v>149.1</v>
+        <v>148.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3483,33 +3483,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0213270536101859</v>
+        <v>0.02138966186446222</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>268</v>
+        <v>183</v>
       </c>
       <c r="H19" t="n">
-        <v>62915.68</v>
+        <v>62829.39</v>
       </c>
       <c r="I19" t="n">
-        <v>234.76</v>
+        <v>343.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3518,33 +3518,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02130152515039046</v>
+        <v>0.02125845954360657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>183</v>
+        <v>268</v>
       </c>
       <c r="H20" t="n">
-        <v>62840.37</v>
+        <v>62444</v>
       </c>
       <c r="I20" t="n">
-        <v>343.39</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3553,33 +3553,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02127510856730908</v>
+        <v>0.01994327023944827</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>548</v>
+        <v>656</v>
       </c>
       <c r="H21" t="n">
-        <v>62762.44</v>
+        <v>58580.8</v>
       </c>
       <c r="I21" t="n">
-        <v>114.53</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3588,33 +3588,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02018450673131011</v>
+        <v>0.01964206220239425</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>656</v>
+        <v>1201</v>
       </c>
       <c r="H22" t="n">
-        <v>59545.12</v>
+        <v>57696.04</v>
       </c>
       <c r="I22" t="n">
-        <v>90.77</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3623,33 +3623,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01935407078155473</v>
+        <v>0.01949379360492401</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1010</v>
+        <v>548</v>
       </c>
       <c r="H23" t="n">
-        <v>57095.3</v>
+        <v>57260.52</v>
       </c>
       <c r="I23" t="n">
-        <v>56.53</v>
+        <v>104.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3658,33 +3658,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0191058132048665</v>
+        <v>0.01912120883627188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1201</v>
+        <v>1010</v>
       </c>
       <c r="H24" t="n">
-        <v>56362.93</v>
+        <v>56166.1</v>
       </c>
       <c r="I24" t="n">
-        <v>46.93</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01769928693327125</v>
+        <v>0.01763877478745609</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>52213.62</v>
+        <v>51811.64</v>
       </c>
       <c r="I25" t="n">
-        <v>131.19</v>
+        <v>130.18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0169494600359572</v>
+        <v>0.01708792862321393</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,16 +3745,16 @@
         <v>480</v>
       </c>
       <c r="H26" t="n">
-        <v>50001.6</v>
+        <v>50193.6</v>
       </c>
       <c r="I26" t="n">
-        <v>104.17</v>
+        <v>104.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3763,33 +3763,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01647373781477903</v>
+        <v>0.01685721217275108</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1740</v>
+        <v>399</v>
       </c>
       <c r="H27" t="n">
-        <v>48598.2</v>
+        <v>49515.9</v>
       </c>
       <c r="I27" t="n">
-        <v>27.93</v>
+        <v>124.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3798,33 +3798,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01641557929868416</v>
+        <v>0.01669288159780875</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>399</v>
+        <v>1740</v>
       </c>
       <c r="H28" t="n">
-        <v>48426.63</v>
+        <v>49033.2</v>
       </c>
       <c r="I28" t="n">
-        <v>121.37</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3833,33 +3833,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01588566460814604</v>
+        <v>0.01571788756385632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>678</v>
+        <v>984</v>
       </c>
       <c r="H29" t="n">
-        <v>46863.36</v>
+        <v>46169.28</v>
       </c>
       <c r="I29" t="n">
-        <v>69.12</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3868,33 +3868,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01580048612750072</v>
+        <v>0.01553639879339484</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>984</v>
+        <v>678</v>
       </c>
       <c r="H30" t="n">
-        <v>46612.08</v>
+        <v>45636.18</v>
       </c>
       <c r="I30" t="n">
-        <v>47.37</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3903,33 +3903,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01453464604192197</v>
+        <v>0.01453862929753306</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>492</v>
+        <v>918</v>
       </c>
       <c r="H31" t="n">
-        <v>42877.8</v>
+        <v>42705.36</v>
       </c>
       <c r="I31" t="n">
-        <v>87.15000000000001</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3938,33 +3938,33 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01445440986566939</v>
+        <v>0.01405967052546994</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>918</v>
+        <v>492</v>
       </c>
       <c r="H32" t="n">
-        <v>42641.1</v>
+        <v>41298.48</v>
       </c>
       <c r="I32" t="n">
-        <v>46.45</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0136396313260581</v>
+        <v>0.01382399045416048</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,16 +3990,16 @@
         <v>153</v>
       </c>
       <c r="H33" t="n">
-        <v>40237.47</v>
+        <v>40606.2</v>
       </c>
       <c r="I33" t="n">
-        <v>262.99</v>
+        <v>265.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01332257470276141</v>
+        <v>0.01341890724613815</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4025,16 +4025,16 @@
         <v>346</v>
       </c>
       <c r="H34" t="n">
-        <v>39302.14</v>
+        <v>39416.32</v>
       </c>
       <c r="I34" t="n">
-        <v>113.59</v>
+        <v>113.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01289678060325727</v>
+        <v>0.01286383962109366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4060,16 +4060,16 @@
         <v>121</v>
       </c>
       <c r="H35" t="n">
-        <v>38046.03</v>
+        <v>37785.88</v>
       </c>
       <c r="I35" t="n">
-        <v>314.43</v>
+        <v>312.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01289343488690909</v>
+        <v>0.01270199426097851</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>376</v>
       </c>
       <c r="H36" t="n">
-        <v>38036.16</v>
+        <v>37310.48</v>
       </c>
       <c r="I36" t="n">
-        <v>101.16</v>
+        <v>99.23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01221168162252721</v>
+        <v>0.01237966530229734</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4130,16 +4130,16 @@
         <v>464</v>
       </c>
       <c r="H37" t="n">
-        <v>36024.96</v>
+        <v>36363.68</v>
       </c>
       <c r="I37" t="n">
-        <v>77.64</v>
+        <v>78.37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01212450994916382</v>
+        <v>0.01209342983347611</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         <v>310</v>
       </c>
       <c r="H38" t="n">
-        <v>35767.8</v>
+        <v>35522.9</v>
       </c>
       <c r="I38" t="n">
-        <v>115.38</v>
+        <v>114.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4183,33 +4183,33 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01200681666485923</v>
+        <v>0.01190198658609042</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>116</v>
+        <v>381</v>
       </c>
       <c r="H39" t="n">
-        <v>35420.6</v>
+        <v>34960.56</v>
       </c>
       <c r="I39" t="n">
-        <v>305.35</v>
+        <v>91.76000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4218,33 +4218,33 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.01189865884163612</v>
+        <v>0.0117177947189539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>381</v>
+        <v>116</v>
       </c>
       <c r="H40" t="n">
-        <v>35101.53</v>
+        <v>34419.52</v>
       </c>
       <c r="I40" t="n">
-        <v>92.13</v>
+        <v>296.72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4253,33 +4253,33 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01141394691452547</v>
+        <v>0.01134432480529482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>American States Water Co</t>
+          <t>Snap-On</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>399</v>
+        <v>90</v>
       </c>
       <c r="H41" t="n">
-        <v>33671.61</v>
+        <v>33322.5</v>
       </c>
       <c r="I41" t="n">
-        <v>84.39</v>
+        <v>370.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4288,33 +4288,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01134289366186681</v>
+        <v>0.0113069648771942</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Snap-On</t>
+          <t>American States Water Co</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>90</v>
+        <v>399</v>
       </c>
       <c r="H42" t="n">
-        <v>33462</v>
+        <v>33212.76</v>
       </c>
       <c r="I42" t="n">
-        <v>371.8</v>
+        <v>83.23999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01120849213452256</v>
+        <v>0.01121151901021506</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4340,16 +4340,16 @@
         <v>493</v>
       </c>
       <c r="H43" t="n">
-        <v>33065.51</v>
+        <v>32932.4</v>
       </c>
       <c r="I43" t="n">
-        <v>67.06999999999999</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.009045383127029752</v>
+        <v>0.008918789178007433</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4375,16 +4375,16 @@
         <v>705</v>
       </c>
       <c r="H44" t="n">
-        <v>26684.25</v>
+        <v>26197.8</v>
       </c>
       <c r="I44" t="n">
-        <v>37.85</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.008938184612546793</v>
+        <v>0.008795699551580775</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4410,16 +4410,16 @@
         <v>1297</v>
       </c>
       <c r="H45" t="n">
-        <v>26368.01</v>
+        <v>25836.24</v>
       </c>
       <c r="I45" t="n">
-        <v>20.33</v>
+        <v>19.92</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.008728523111178039</v>
+        <v>0.008625567872439111</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4445,16 +4445,16 @@
         <v>350</v>
       </c>
       <c r="H46" t="n">
-        <v>25749.5</v>
+        <v>25336.5</v>
       </c>
       <c r="I46" t="n">
-        <v>73.56999999999999</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.008589199618142241</v>
+        <v>0.008563151531834333</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4480,16 +4480,16 @@
         <v>431</v>
       </c>
       <c r="H47" t="n">
-        <v>25338.49</v>
+        <v>25153.16</v>
       </c>
       <c r="I47" t="n">
-        <v>58.79</v>
+        <v>58.36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008529668239716055</v>
+        <v>0.008471089642304801</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4515,16 +4515,16 @@
         <v>257</v>
       </c>
       <c r="H48" t="n">
-        <v>25162.87</v>
+        <v>24882.74</v>
       </c>
       <c r="I48" t="n">
-        <v>97.91</v>
+        <v>96.81999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.007672673335970857</v>
+        <v>0.0076950932279319</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4550,16 +4550,16 @@
         <v>627</v>
       </c>
       <c r="H49" t="n">
-        <v>22634.7</v>
+        <v>22603.35</v>
       </c>
       <c r="I49" t="n">
-        <v>36.1</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.005970002015700881</v>
+        <v>0.005970303071811999</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         <v>65</v>
       </c>
       <c r="H50" t="n">
-        <v>17611.75</v>
+        <v>17537</v>
       </c>
       <c r="I50" t="n">
-        <v>270.95</v>
+        <v>269.8</v>
       </c>
     </row>
   </sheetData>
@@ -4655,7 +4655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07201872499666682</v>
+        <v>0.07253411403434032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05289300991750739</v>
+        <v>0.05342629288343978</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4716,16 +4716,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>115634.62</v>
+        <v>115970.56</v>
       </c>
       <c r="I3" t="n">
-        <v>113.59</v>
+        <v>113.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04236943678838462</v>
+        <v>0.04289457806826947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4751,16 +4751,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>92628</v>
+        <v>93109.74000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03983952472898024</v>
+        <v>0.03985026613163237</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4786,16 +4786,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>87097.11</v>
+        <v>86501.56</v>
       </c>
       <c r="I5" t="n">
-        <v>314.43</v>
+        <v>312.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03782999542054397</v>
+        <v>0.03809713942211845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4821,16 +4821,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>82703.88</v>
+        <v>82696.11</v>
       </c>
       <c r="I6" t="n">
-        <v>106.44</v>
+        <v>106.43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03574613160016227</v>
+        <v>0.03632419389720996</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4856,16 +4856,16 @@
         <v>2798</v>
       </c>
       <c r="H7" t="n">
-        <v>78148.14</v>
+        <v>78847.64</v>
       </c>
       <c r="I7" t="n">
-        <v>27.93</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4874,33 +4874,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03435923101805046</v>
+        <v>0.03444348413945398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>246</v>
+        <v>303</v>
       </c>
       <c r="H8" t="n">
-        <v>75116.10000000001</v>
+        <v>74765.25</v>
       </c>
       <c r="I8" t="n">
-        <v>305.35</v>
+        <v>246.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4909,33 +4909,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03406985199130041</v>
+        <v>0.03362708438758997</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>303</v>
+        <v>246</v>
       </c>
       <c r="H9" t="n">
-        <v>74483.46000000001</v>
+        <v>72993.12</v>
       </c>
       <c r="I9" t="n">
-        <v>245.82</v>
+        <v>296.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03387996072744574</v>
+        <v>0.03356981160446924</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4961,16 +4961,16 @@
         <v>816</v>
       </c>
       <c r="H10" t="n">
-        <v>74068.32000000001</v>
+        <v>72868.8</v>
       </c>
       <c r="I10" t="n">
-        <v>90.77</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03249656394424785</v>
+        <v>0.0328547955509754</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4996,16 +4996,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>71043.94</v>
+        <v>71316.74000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>104.17</v>
+        <v>104.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03153334858171983</v>
+        <v>0.03247337318886975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>568</v>
       </c>
       <c r="H12" t="n">
-        <v>68938.16</v>
+        <v>70488.8</v>
       </c>
       <c r="I12" t="n">
-        <v>121.37</v>
+        <v>124.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03097279564529208</v>
+        <v>0.03081275731895101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5066,16 +5066,16 @@
         <v>1076</v>
       </c>
       <c r="H13" t="n">
-        <v>67712.67999999999</v>
+        <v>66884.16</v>
       </c>
       <c r="I13" t="n">
-        <v>62.93</v>
+        <v>62.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5084,33 +5084,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03080399121302122</v>
+        <v>0.03063274332277643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>588</v>
+        <v>197</v>
       </c>
       <c r="H14" t="n">
-        <v>67343.64</v>
+        <v>66493.41</v>
       </c>
       <c r="I14" t="n">
-        <v>114.53</v>
+        <v>337.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5119,33 +5119,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03063765682176018</v>
+        <v>0.03056483324427075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>197</v>
+        <v>245</v>
       </c>
       <c r="H15" t="n">
-        <v>66980</v>
+        <v>66346</v>
       </c>
       <c r="I15" t="n">
-        <v>340</v>
+        <v>270.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5154,33 +5154,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02994533634575875</v>
+        <v>0.02830475118783324</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>245</v>
+        <v>588</v>
       </c>
       <c r="H16" t="n">
-        <v>65466.45</v>
+        <v>61440.12</v>
       </c>
       <c r="I16" t="n">
-        <v>267.21</v>
+        <v>104.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02824166215243801</v>
+        <v>0.02823052507122761</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5206,16 +5206,16 @@
         <v>263</v>
       </c>
       <c r="H17" t="n">
-        <v>61741.88</v>
+        <v>61279</v>
       </c>
       <c r="I17" t="n">
-        <v>234.76</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02797799899709016</v>
+        <v>0.02771963083839924</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5241,16 +5241,16 @@
         <v>1082</v>
       </c>
       <c r="H18" t="n">
-        <v>61165.46</v>
+        <v>60170.02</v>
       </c>
       <c r="I18" t="n">
-        <v>56.53</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02622701894428142</v>
+        <v>0.02641274535026612</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5276,16 +5276,16 @@
         <v>213</v>
       </c>
       <c r="H19" t="n">
-        <v>57337.47</v>
+        <v>57333.21</v>
       </c>
       <c r="I19" t="n">
-        <v>269.19</v>
+        <v>269.17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5294,33 +5294,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02582574248563667</v>
+        <v>0.0258583713453099</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1433</v>
+        <v>1557</v>
       </c>
       <c r="H20" t="n">
-        <v>56460.2</v>
+        <v>56129.85</v>
       </c>
       <c r="I20" t="n">
-        <v>39.4</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5329,33 +5329,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02571024519767766</v>
+        <v>0.02519855497709216</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1557</v>
+        <v>1433</v>
       </c>
       <c r="H21" t="n">
-        <v>56207.7</v>
+        <v>54697.61</v>
       </c>
       <c r="I21" t="n">
-        <v>36.1</v>
+        <v>38.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0247697908056401</v>
+        <v>0.02469468624251499</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
         <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>54151.68</v>
+        <v>53603.88</v>
       </c>
       <c r="I22" t="n">
-        <v>410.24</v>
+        <v>406.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02358793107224316</v>
+        <v>0.02386264611913435</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5416,16 +5416,16 @@
         <v>190</v>
       </c>
       <c r="H23" t="n">
-        <v>51567.9</v>
+        <v>51797.8</v>
       </c>
       <c r="I23" t="n">
-        <v>271.41</v>
+        <v>272.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02267281289715629</v>
+        <v>0.02256567464558262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5451,16 +5451,16 @@
         <v>443</v>
       </c>
       <c r="H24" t="n">
-        <v>49567.27</v>
+        <v>48982.51</v>
       </c>
       <c r="I24" t="n">
-        <v>111.89</v>
+        <v>110.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02214305313865092</v>
+        <v>0.02212982194784542</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5486,16 +5486,16 @@
         <v>369</v>
       </c>
       <c r="H25" t="n">
-        <v>48409.11</v>
+        <v>48036.42</v>
       </c>
       <c r="I25" t="n">
-        <v>131.19</v>
+        <v>130.18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02037580283422752</v>
+        <v>0.02055254461128045</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5521,16 +5521,16 @@
         <v>959</v>
       </c>
       <c r="H26" t="n">
-        <v>44545.55</v>
+        <v>44612.68</v>
       </c>
       <c r="I26" t="n">
-        <v>46.45</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02032377187777074</v>
+        <v>0.02036350572915562</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5556,16 +5556,16 @@
         <v>298</v>
       </c>
       <c r="H27" t="n">
-        <v>44431.8</v>
+        <v>44202.34</v>
       </c>
       <c r="I27" t="n">
-        <v>149.1</v>
+        <v>148.33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01995756085316534</v>
+        <v>0.02018242293587003</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5591,16 +5591,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>43631.19</v>
+        <v>43809.27</v>
       </c>
       <c r="I28" t="n">
-        <v>274.41</v>
+        <v>275.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5609,33 +5609,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01929403922567837</v>
+        <v>0.01914804385597029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>484</v>
+        <v>282</v>
       </c>
       <c r="H29" t="n">
-        <v>42180.6</v>
+        <v>41563.98</v>
       </c>
       <c r="I29" t="n">
-        <v>87.15000000000001</v>
+        <v>147.39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5644,33 +5644,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01911905054258293</v>
+        <v>0.01871636960211102</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>282</v>
+        <v>484</v>
       </c>
       <c r="H30" t="n">
-        <v>41798.04</v>
+        <v>40626.96</v>
       </c>
       <c r="I30" t="n">
-        <v>148.22</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01900153148031589</v>
+        <v>0.01863637105972915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5696,16 +5696,16 @@
         <v>601</v>
       </c>
       <c r="H31" t="n">
-        <v>41541.12</v>
+        <v>40453.31</v>
       </c>
       <c r="I31" t="n">
-        <v>69.12</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01780374455655564</v>
+        <v>0.01809547219076296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5731,16 +5731,16 @@
         <v>148</v>
       </c>
       <c r="H32" t="n">
-        <v>38922.52</v>
+        <v>39279.2</v>
       </c>
       <c r="I32" t="n">
-        <v>262.99</v>
+        <v>265.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01757063672332922</v>
+        <v>0.01748218535194671</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5766,16 +5766,16 @@
         <v>246</v>
       </c>
       <c r="H33" t="n">
-        <v>38412.9</v>
+        <v>37947.96</v>
       </c>
       <c r="I33" t="n">
-        <v>156.15</v>
+        <v>154.26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5784,33 +5784,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01670422867178595</v>
+        <v>0.01664478281547464</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>361</v>
+        <v>736</v>
       </c>
       <c r="H34" t="n">
-        <v>36518.76</v>
+        <v>36130.24</v>
       </c>
       <c r="I34" t="n">
-        <v>101.16</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01666020705201099</v>
+        <v>0.01659263288747218</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5836,16 +5836,16 @@
         <v>372</v>
       </c>
       <c r="H35" t="n">
-        <v>36422.52</v>
+        <v>36017.04</v>
       </c>
       <c r="I35" t="n">
-        <v>97.91</v>
+        <v>96.81999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5854,27 +5854,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01663761075092119</v>
+        <v>0.01650279404065451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>736</v>
+        <v>361</v>
       </c>
       <c r="H36" t="n">
-        <v>36373.12</v>
+        <v>35822.03</v>
       </c>
       <c r="I36" t="n">
-        <v>49.42</v>
+        <v>99.23</v>
       </c>
     </row>
   </sheetData>
@@ -5941,7 +5941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1065075235600705</v>
+        <v>0.1059547508164773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5967,16 +5967,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>223997.4</v>
+        <v>221053.51</v>
       </c>
       <c r="I2" t="n">
-        <v>53.46</v>
+        <v>52.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09915965539471149</v>
+        <v>0.09925882844895438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6002,16 +6002,16 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>208544</v>
+        <v>207083.8</v>
       </c>
       <c r="I3" t="n">
-        <v>212.8</v>
+        <v>211.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09879448250389161</v>
+        <v>0.09860130110559737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6037,16 +6037,16 @@
         <v>4300</v>
       </c>
       <c r="H4" t="n">
-        <v>207776</v>
+        <v>205712</v>
       </c>
       <c r="I4" t="n">
-        <v>48.32</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05512541549114756</v>
+        <v>0.05468589919287152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6072,16 +6072,16 @@
         <v>1475</v>
       </c>
       <c r="H5" t="n">
-        <v>115935</v>
+        <v>114091.25</v>
       </c>
       <c r="I5" t="n">
-        <v>78.59999999999999</v>
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04416047180337494</v>
+        <v>0.04486567703289343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>92874.48</v>
+        <v>93603.31</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6116,7 +6116,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03830398303771922</v>
+        <v>0.03809384040626504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6142,16 +6142,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>80557.62</v>
+        <v>79475.22</v>
       </c>
       <c r="I7" t="n">
-        <v>29.77</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03784432166139971</v>
+        <v>0.03733358579929214</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1270</v>
       </c>
       <c r="H8" t="n">
-        <v>79590.89999999999</v>
+        <v>77889.10000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>62.67</v>
+        <v>61.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02867428831940303</v>
+        <v>0.02861295086236043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6212,16 +6212,16 @@
         <v>147</v>
       </c>
       <c r="H9" t="n">
-        <v>60305.28</v>
+        <v>59695.23</v>
       </c>
       <c r="I9" t="n">
-        <v>410.24</v>
+        <v>406.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02486313862105581</v>
+        <v>0.02519384702228044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6247,16 +6247,16 @@
         <v>105</v>
       </c>
       <c r="H10" t="n">
-        <v>52290</v>
+        <v>52561.95</v>
       </c>
       <c r="I10" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02461058447918215</v>
+        <v>0.02495097699393884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6282,16 +6282,16 @@
         <v>285</v>
       </c>
       <c r="H11" t="n">
-        <v>51758.85</v>
+        <v>52055.25</v>
       </c>
       <c r="I11" t="n">
-        <v>181.61</v>
+        <v>182.65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02334718137405239</v>
+        <v>0.02314599301816012</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6317,16 +6317,16 @@
         <v>1860</v>
       </c>
       <c r="H12" t="n">
-        <v>49101.77</v>
+        <v>48289.51</v>
       </c>
       <c r="I12" t="n">
-        <v>26.4</v>
+        <v>25.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6335,33 +6335,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02081979982629563</v>
+        <v>0.02050825770798267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprott Physical Gold and Silver Trust</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>980</v>
+        <v>158</v>
       </c>
       <c r="H13" t="n">
-        <v>43786.4</v>
+        <v>42786.4</v>
       </c>
       <c r="I13" t="n">
-        <v>44.68</v>
+        <v>270.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6370,33 +6370,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02041794322645655</v>
+        <v>0.02041450326246537</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CEF</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Sprott Physical Gold and Silver Trust</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>275</v>
+        <v>980</v>
       </c>
       <c r="H14" t="n">
-        <v>42941.25</v>
+        <v>42590.8</v>
       </c>
       <c r="I14" t="n">
-        <v>156.15</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02022336028100054</v>
+        <v>0.02038481435471822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6422,16 +6422,16 @@
         <v>158</v>
       </c>
       <c r="H15" t="n">
-        <v>42532.02</v>
+        <v>42528.86</v>
       </c>
       <c r="I15" t="n">
-        <v>269.19</v>
+        <v>269.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6440,33 +6440,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02007460938625564</v>
+        <v>0.02033335485946906</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>158</v>
+        <v>275</v>
       </c>
       <c r="H16" t="n">
-        <v>42219.18</v>
+        <v>42421.5</v>
       </c>
       <c r="I16" t="n">
-        <v>267.21</v>
+        <v>154.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01944109147894735</v>
+        <v>0.0198979047640521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6492,16 +6492,16 @@
         <v>202</v>
       </c>
       <c r="H17" t="n">
-        <v>40886.82</v>
+        <v>41513.02</v>
       </c>
       <c r="I17" t="n">
-        <v>202.41</v>
+        <v>205.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01828422566277216</v>
+        <v>0.01839687500136306</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6527,16 +6527,16 @@
         <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>38453.8</v>
+        <v>38381.42</v>
       </c>
       <c r="I18" t="n">
-        <v>1747.9</v>
+        <v>1744.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01690400527142284</v>
+        <v>0.0173107901440131</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6562,16 +6562,16 @@
         <v>224</v>
       </c>
       <c r="H19" t="n">
-        <v>35551.04</v>
+        <v>36115.52</v>
       </c>
       <c r="I19" t="n">
-        <v>158.71</v>
+        <v>161.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01665329125856932</v>
+        <v>0.01649276822735848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6597,16 +6597,16 @@
         <v>488</v>
       </c>
       <c r="H20" t="n">
-        <v>35023.76</v>
+        <v>34408.88</v>
       </c>
       <c r="I20" t="n">
-        <v>71.77</v>
+        <v>70.51000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0160048431054645</v>
+        <v>0.01601660972162565</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6632,16 +6632,16 @@
         <v>99</v>
       </c>
       <c r="H21" t="n">
-        <v>33660</v>
+        <v>33415.47</v>
       </c>
       <c r="I21" t="n">
-        <v>340</v>
+        <v>337.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01548686818314219</v>
+        <v>0.01561020145572757</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6667,16 +6667,16 @@
         <v>306</v>
       </c>
       <c r="H22" t="n">
-        <v>32570.64</v>
+        <v>32567.58</v>
       </c>
       <c r="I22" t="n">
-        <v>106.44</v>
+        <v>106.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01472736562850106</v>
+        <v>0.01490221159691012</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>126</v>
       </c>
       <c r="H23" t="n">
-        <v>30973.32</v>
+        <v>31090.5</v>
       </c>
       <c r="I23" t="n">
-        <v>245.82</v>
+        <v>246.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01416576966320504</v>
+        <v>0.01419995916504994</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6737,16 +6737,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>29792.22</v>
+        <v>29625.39</v>
       </c>
       <c r="I24" t="n">
-        <v>148.22</v>
+        <v>147.39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01371526613828812</v>
+        <v>0.01382337401571672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>84</v>
       </c>
       <c r="H25" t="n">
-        <v>28844.76</v>
+        <v>28839.72</v>
       </c>
       <c r="I25" t="n">
-        <v>343.39</v>
+        <v>343.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6790,33 +6790,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01330051912559732</v>
+        <v>0.01345916004347349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KOF</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coca-Cola Femsa</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>250</v>
+        <v>103</v>
       </c>
       <c r="H26" t="n">
-        <v>27972.5</v>
+        <v>28079.86</v>
       </c>
       <c r="I26" t="n">
-        <v>111.89</v>
+        <v>272.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6825,33 +6825,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01329230749040922</v>
+        <v>0.01324952587020434</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>KOF</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Coca-Cola Femsa</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>103</v>
+        <v>250</v>
       </c>
       <c r="H27" t="n">
-        <v>27955.23</v>
+        <v>27642.5</v>
       </c>
       <c r="I27" t="n">
-        <v>271.41</v>
+        <v>110.57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01238783415102581</v>
+        <v>0.01233486401845156</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6877,16 +6877,16 @@
         <v>414</v>
       </c>
       <c r="H28" t="n">
-        <v>26053.02</v>
+        <v>25734.24</v>
       </c>
       <c r="I28" t="n">
-        <v>62.93</v>
+        <v>62.16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0118024448895623</v>
+        <v>0.01178453117507149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>524</v>
       </c>
       <c r="H29" t="n">
-        <v>24821.88</v>
+        <v>24586.08</v>
       </c>
       <c r="I29" t="n">
-        <v>47.37</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01106509520599317</v>
+        <v>0.01138020314584797</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6947,16 +6947,16 @@
         <v>259</v>
       </c>
       <c r="H30" t="n">
-        <v>23271.15</v>
+        <v>23742.53</v>
       </c>
       <c r="I30" t="n">
-        <v>89.84999999999999</v>
+        <v>91.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6965,33 +6965,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01089147166291651</v>
+        <v>0.01070075662665504</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>22906</v>
+        <v>22325</v>
       </c>
       <c r="I31" t="n">
-        <v>114.53</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7000,33 +7000,33 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01078995550121073</v>
+        <v>0.01001677097352013</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H32" t="n">
-        <v>22692.5</v>
+        <v>20898</v>
       </c>
       <c r="I32" t="n">
-        <v>90.77</v>
+        <v>104.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7035,33 +7035,33 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.008898711786059658</v>
+        <v>0.008779653264521403</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>475</v>
+        <v>650</v>
       </c>
       <c r="H33" t="n">
-        <v>18715</v>
+        <v>18317</v>
       </c>
       <c r="I33" t="n">
-        <v>39.4</v>
+        <v>28.18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.008667982430238903</v>
+        <v>0.008771385042715813</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -7087,16 +7087,16 @@
         <v>175</v>
       </c>
       <c r="H34" t="n">
-        <v>18229.75</v>
+        <v>18299.75</v>
       </c>
       <c r="I34" t="n">
-        <v>104.17</v>
+        <v>104.57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7105,33 +7105,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.008632202143736044</v>
+        <v>0.008690380434881337</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>650</v>
+        <v>475</v>
       </c>
       <c r="H35" t="n">
-        <v>18154.5</v>
+        <v>18130.75</v>
       </c>
       <c r="I35" t="n">
-        <v>27.93</v>
+        <v>38.17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.008513720658144255</v>
+        <v>0.00841858840632239</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -7157,16 +7157,16 @@
         <v>177</v>
       </c>
       <c r="H36" t="n">
-        <v>17905.32</v>
+        <v>17563.71</v>
       </c>
       <c r="I36" t="n">
-        <v>101.16</v>
+        <v>99.23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.008326536267611628</v>
+        <v>0.00840628433364126</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -7192,16 +7192,16 @@
         <v>377</v>
       </c>
       <c r="H37" t="n">
-        <v>17511.65</v>
+        <v>17538.04</v>
       </c>
       <c r="I37" t="n">
-        <v>46.45</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7210,33 +7210,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008234021047081912</v>
+        <v>0.008335556286706021</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>132</v>
+        <v>362</v>
       </c>
       <c r="H38" t="n">
-        <v>17317.08</v>
+        <v>17390.48</v>
       </c>
       <c r="I38" t="n">
-        <v>131.19</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7245,33 +7245,33 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008106980821861533</v>
+        <v>0.008236471833856653</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>345</v>
+        <v>132</v>
       </c>
       <c r="H39" t="n">
-        <v>17049.9</v>
+        <v>17183.76</v>
       </c>
       <c r="I39" t="n">
-        <v>49.42</v>
+        <v>130.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7280,33 +7280,33 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.008077862087702926</v>
+        <v>0.008117740168728379</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="H40" t="n">
-        <v>16988.66</v>
+        <v>16936.05</v>
       </c>
       <c r="I40" t="n">
-        <v>46.93</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.007723406640840195</v>
+        <v>0.007581767668843691</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7332,16 +7332,16 @@
         <v>235</v>
       </c>
       <c r="H41" t="n">
-        <v>16243.2</v>
+        <v>15817.85</v>
       </c>
       <c r="I41" t="n">
-        <v>69.12</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.007311141662641682</v>
+        <v>0.007250113714412272</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7367,16 +7367,16 @@
         <v>272</v>
       </c>
       <c r="H42" t="n">
-        <v>15376.16</v>
+        <v>15125.92</v>
       </c>
       <c r="I42" t="n">
-        <v>56.53</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7385,33 +7385,33 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.007210310200106186</v>
+        <v>0.007131578569338508</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Union Pacific</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="H43" t="n">
-        <v>15164.1</v>
+        <v>14878.62</v>
       </c>
       <c r="I43" t="n">
-        <v>87.15000000000001</v>
+        <v>275.53</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7420,33 +7420,33 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.007045811224444674</v>
+        <v>0.007000696213035062</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Union Pacific</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="H44" t="n">
-        <v>14818.14</v>
+        <v>14605.56</v>
       </c>
       <c r="I44" t="n">
-        <v>274.41</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0047203826479352</v>
+        <v>0.004751830952183712</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7472,16 +7472,16 @@
         <v>275</v>
       </c>
       <c r="H45" t="n">
-        <v>9927.5</v>
+        <v>9913.75</v>
       </c>
       <c r="I45" t="n">
-        <v>36.1</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.004210495734561912</v>
+        <v>0.004124467040607901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7507,16 +7507,16 @@
         <v>29</v>
       </c>
       <c r="H46" t="n">
-        <v>8855.15</v>
+        <v>8604.879999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>305.35</v>
+        <v>296.72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/22/2026</t>
+          <t>09/23/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.002481321263988904</v>
+        <v>0.002488399241438341</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7542,261 +7542,13 @@
         <v>35</v>
       </c>
       <c r="H47" t="n">
-        <v>5218.5</v>
+        <v>5191.55</v>
       </c>
       <c r="I47" t="n">
-        <v>149.1</v>
+        <v>148.33</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A209656-EA46-4186-ABC5-2007DCFB0327}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84E41DD1-7DDB-4C71-BE49-7A9CA08B8733}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EA3D649-75B9-4528-AB37-30AE75F2E46D}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -7551,4 +7551,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D023554-40DF-4EA4-859C-B84CC3DFAD81}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08002B98-DB9F-4C83-AFEF-EC4EAA18A263}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEDA619B-7ADA-405D-975C-DFAA2EE81B0D}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1102943796649651</v>
+        <v>0.1106340009769927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0470922080974801</v>
+        <v>0.04723139954319341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>109238.21</v>
+        <v>109224.76</v>
       </c>
       <c r="I3" t="n">
-        <v>406.09</v>
+        <v>406.04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04062584276667997</v>
+        <v>0.04046652504984885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>94238.39999999999</v>
+        <v>93580.67999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>270.8</v>
+        <v>268.91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,33 +596,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0380070997624598</v>
+        <v>0.03827486221687254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>429</v>
+        <v>327</v>
       </c>
       <c r="H5" t="n">
-        <v>88163.78999999999</v>
+        <v>88512.36</v>
       </c>
       <c r="I5" t="n">
-        <v>205.51</v>
+        <v>270.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,33 +631,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03794450455318501</v>
+        <v>0.03815010358996224</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>327</v>
+        <v>429</v>
       </c>
       <c r="H6" t="n">
-        <v>88018.59</v>
+        <v>88223.85000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>269.17</v>
+        <v>205.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03730702925145692</v>
+        <v>0.03789495617662422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -683,16 +683,16 @@
         <v>561</v>
       </c>
       <c r="H7" t="n">
-        <v>86539.86</v>
+        <v>87633.81</v>
       </c>
       <c r="I7" t="n">
-        <v>154.26</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03610057125715761</v>
+        <v>0.03575281020742212</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         <v>48</v>
       </c>
       <c r="H8" t="n">
-        <v>83741.28</v>
+        <v>82680</v>
       </c>
       <c r="I8" t="n">
-        <v>1744.61</v>
+        <v>1722.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03287618942645001</v>
+        <v>0.03316355087138199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -753,16 +753,16 @@
         <v>473</v>
       </c>
       <c r="H9" t="n">
-        <v>76261.78999999999</v>
+        <v>76692.22</v>
       </c>
       <c r="I9" t="n">
-        <v>161.23</v>
+        <v>162.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03176446057323917</v>
+        <v>0.03160017838178829</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -788,16 +788,16 @@
         <v>1045</v>
       </c>
       <c r="H10" t="n">
-        <v>73682.95</v>
+        <v>73076.85000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>70.51000000000001</v>
+        <v>69.93000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03078655269015974</v>
+        <v>0.03103803592637652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         <v>671</v>
       </c>
       <c r="H11" t="n">
-        <v>71414.53</v>
+        <v>71776.87</v>
       </c>
       <c r="I11" t="n">
-        <v>106.43</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02978075717562035</v>
+        <v>0.02971372468007105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         <v>138</v>
       </c>
       <c r="H12" t="n">
-        <v>69081.42</v>
+        <v>68714.34</v>
       </c>
       <c r="I12" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02886162929794464</v>
+        <v>0.02835686920908959</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         <v>195</v>
       </c>
       <c r="H13" t="n">
-        <v>66949.35000000001</v>
+        <v>65576.55</v>
       </c>
       <c r="I13" t="n">
-        <v>343.33</v>
+        <v>336.29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02797611401301793</v>
+        <v>0.02790986394823308</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>263</v>
       </c>
       <c r="H14" t="n">
-        <v>64895.25</v>
+        <v>64542.83</v>
       </c>
       <c r="I14" t="n">
-        <v>246.75</v>
+        <v>245.41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02776667871983693</v>
+        <v>0.02752904116926149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -963,16 +963,16 @@
         <v>437</v>
       </c>
       <c r="H15" t="n">
-        <v>64409.43</v>
+        <v>63662.16</v>
       </c>
       <c r="I15" t="n">
-        <v>147.39</v>
+        <v>145.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02720999520991454</v>
+        <v>0.02737707010468365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -998,16 +998,16 @@
         <v>187</v>
       </c>
       <c r="H16" t="n">
-        <v>63118.11</v>
+        <v>63310.72</v>
       </c>
       <c r="I16" t="n">
-        <v>337.53</v>
+        <v>338.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02632571717189292</v>
+        <v>0.02621595997231604</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>224</v>
       </c>
       <c r="H17" t="n">
-        <v>61066.88</v>
+        <v>60625.6</v>
       </c>
       <c r="I17" t="n">
-        <v>272.62</v>
+        <v>270.65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02530014295073144</v>
+        <v>0.02524357261400293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1068,16 +1068,16 @@
         <v>213</v>
       </c>
       <c r="H18" t="n">
-        <v>58687.89</v>
+        <v>58376.91</v>
       </c>
       <c r="I18" t="n">
-        <v>275.53</v>
+        <v>274.07</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02423055377869561</v>
+        <v>0.02474027008221144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         <v>1170</v>
       </c>
       <c r="H19" t="n">
-        <v>56206.8</v>
+        <v>57213</v>
       </c>
       <c r="I19" t="n">
-        <v>48.04</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02406366770834809</v>
+        <v>0.02417271367924529</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1138,16 +1138,16 @@
         <v>898</v>
       </c>
       <c r="H20" t="n">
-        <v>55819.68</v>
+        <v>55900.5</v>
       </c>
       <c r="I20" t="n">
-        <v>62.16</v>
+        <v>62.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0225724230666726</v>
+        <v>0.02255339418209671</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         <v>353</v>
       </c>
       <c r="H21" t="n">
-        <v>52360.49</v>
+        <v>52155.75</v>
       </c>
       <c r="I21" t="n">
-        <v>148.33</v>
+        <v>147.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02197234969577564</v>
+        <v>0.02209290161898609</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1208,16 +1208,16 @@
         <v>556</v>
       </c>
       <c r="H22" t="n">
-        <v>50968.52</v>
+        <v>51090.84</v>
       </c>
       <c r="I22" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02178351650349852</v>
+        <v>0.02153242831992896</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
         <v>457</v>
       </c>
       <c r="H23" t="n">
-        <v>50530.49</v>
+        <v>49794.72</v>
       </c>
       <c r="I23" t="n">
-        <v>110.57</v>
+        <v>108.96</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02136578832281543</v>
+        <v>0.02124198214150589</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1278,16 +1278,16 @@
         <v>555</v>
       </c>
       <c r="H24" t="n">
-        <v>49561.5</v>
+        <v>49123.05</v>
       </c>
       <c r="I24" t="n">
-        <v>89.3</v>
+        <v>88.51000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02071290994376372</v>
+        <v>0.0207019668183911</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         <v>864</v>
       </c>
       <c r="H25" t="n">
-        <v>48047.04</v>
+        <v>47874.24</v>
       </c>
       <c r="I25" t="n">
-        <v>55.61</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01920397741340679</v>
+        <v>0.01920784702055742</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         <v>426</v>
       </c>
       <c r="H26" t="n">
-        <v>44546.82</v>
+        <v>44419.02</v>
       </c>
       <c r="I26" t="n">
-        <v>104.57</v>
+        <v>104.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,33 +1366,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01918928564527949</v>
+        <v>0.01889753961120998</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>426</v>
+        <v>938</v>
       </c>
       <c r="H27" t="n">
-        <v>44512.74</v>
+        <v>43701.42</v>
       </c>
       <c r="I27" t="n">
-        <v>104.49</v>
+        <v>46.59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,33 +1401,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01897297005223605</v>
+        <v>0.01882531616707786</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>938</v>
+        <v>920</v>
       </c>
       <c r="H28" t="n">
-        <v>44010.96</v>
+        <v>43534.4</v>
       </c>
       <c r="I28" t="n">
-        <v>46.92</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,33 +1436,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01857576637508996</v>
+        <v>0.01871415727264245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>331</v>
+        <v>426</v>
       </c>
       <c r="H29" t="n">
-        <v>43089.58</v>
+        <v>43277.34</v>
       </c>
       <c r="I29" t="n">
-        <v>130.18</v>
+        <v>101.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,33 +1471,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01845023970128394</v>
+        <v>0.01847688626440814</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>920</v>
+        <v>1504</v>
       </c>
       <c r="H30" t="n">
-        <v>42798.4</v>
+        <v>42728.64</v>
       </c>
       <c r="I30" t="n">
-        <v>46.52</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,33 +1506,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01827104151539312</v>
+        <v>0.0183424067476398</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1504</v>
+        <v>331</v>
       </c>
       <c r="H31" t="n">
-        <v>42382.72</v>
+        <v>42417.65</v>
       </c>
       <c r="I31" t="n">
-        <v>28.18</v>
+        <v>128.15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01788653362965986</v>
+        <v>0.01815313047095994</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1558,16 +1558,16 @@
         <v>1087</v>
       </c>
       <c r="H32" t="n">
-        <v>41490.79</v>
+        <v>41979.94</v>
       </c>
       <c r="I32" t="n">
-        <v>38.17</v>
+        <v>38.62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0162495783768626</v>
+        <v>0.01611799645074225</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>37693.6</v>
+        <v>37273.6</v>
       </c>
       <c r="I33" t="n">
-        <v>67.31</v>
+        <v>66.56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01587052817259917</v>
+        <v>0.01574773778828454</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>36814.33</v>
+        <v>36417.36</v>
       </c>
       <c r="I34" t="n">
-        <v>99.23</v>
+        <v>98.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01349746705381775</v>
+        <v>0.01319385937787542</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         <v>373</v>
       </c>
       <c r="H35" t="n">
-        <v>31309.62</v>
+        <v>30511.4</v>
       </c>
       <c r="I35" t="n">
-        <v>83.94</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01112860050381211</v>
+        <v>0.01099206917655055</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
         <v>87</v>
       </c>
       <c r="H36" t="n">
-        <v>25814.64</v>
+        <v>25419.66</v>
       </c>
       <c r="I36" t="n">
-        <v>296.72</v>
+        <v>292.18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01104683874492053</v>
+        <v>0.01079418333950265</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         <v>522</v>
       </c>
       <c r="H37" t="n">
-        <v>25624.98</v>
+        <v>24962.04</v>
       </c>
       <c r="I37" t="n">
-        <v>49.09</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008936091213876906</v>
+        <v>0.008948688832062715</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         <v>575</v>
       </c>
       <c r="H38" t="n">
-        <v>20728.75</v>
+        <v>20694.25</v>
       </c>
       <c r="I38" t="n">
-        <v>36.05</v>
+        <v>35.99</v>
       </c>
     </row>
   </sheetData>
@@ -1838,7 +1838,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.05932156623440095</v>
+        <v>0.06042155628573654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1864,16 +1864,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>149786.46</v>
+        <v>151679.91</v>
       </c>
       <c r="I2" t="n">
-        <v>154.26</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0571535194694465</v>
+        <v>0.05851573068263978</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>144312.16</v>
+        <v>146895.6</v>
       </c>
       <c r="I3" t="n">
-        <v>48.04</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05130630807707302</v>
+        <v>0.05240045050734259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         <v>556</v>
       </c>
       <c r="H4" t="n">
-        <v>129548</v>
+        <v>131544.04</v>
       </c>
       <c r="I4" t="n">
-        <v>233</v>
+        <v>236.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05121905630373449</v>
+        <v>0.05151756947007212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04973414842883086</v>
+        <v>0.0496125206477287</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2004,16 +2004,16 @@
         <v>1781</v>
       </c>
       <c r="H6" t="n">
-        <v>125578.31</v>
+        <v>124545.33</v>
       </c>
       <c r="I6" t="n">
-        <v>70.51000000000001</v>
+        <v>69.93000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04531363481810471</v>
+        <v>0.04431277262664141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2039,16 +2039,16 @@
         <v>1095</v>
       </c>
       <c r="H7" t="n">
-        <v>114416.55</v>
+        <v>111241.05</v>
       </c>
       <c r="I7" t="n">
-        <v>104.49</v>
+        <v>101.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04397539277416861</v>
+        <v>0.04399148415658456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2074,16 +2074,16 @@
         <v>450</v>
       </c>
       <c r="H8" t="n">
-        <v>111037.5</v>
+        <v>110434.5</v>
       </c>
       <c r="I8" t="n">
-        <v>246.75</v>
+        <v>245.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04129755818678626</v>
+        <v>0.0413758243506075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2109,16 +2109,16 @@
         <v>703</v>
       </c>
       <c r="H9" t="n">
-        <v>104275.99</v>
+        <v>103868.25</v>
       </c>
       <c r="I9" t="n">
-        <v>148.33</v>
+        <v>147.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03969984597889722</v>
+        <v>0.03889816860831713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>100241.78</v>
+        <v>97648.44</v>
       </c>
       <c r="I10" t="n">
-        <v>49.09</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03912234704173241</v>
+        <v>0.03828177913831878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>796</v>
       </c>
       <c r="H11" t="n">
-        <v>98783.60000000001</v>
+        <v>96101.08</v>
       </c>
       <c r="I11" t="n">
-        <v>124.1</v>
+        <v>120.73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2197,33 +2197,33 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03648431852642239</v>
+        <v>0.03655912640384299</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Principal Financial</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>295</v>
+        <v>804</v>
       </c>
       <c r="H12" t="n">
-        <v>92122.60000000001</v>
+        <v>91776.60000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>312.28</v>
+        <v>114.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2232,33 +2232,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03627405248538524</v>
+        <v>0.03641374889823608</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Principal Financial</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>804</v>
+        <v>295</v>
       </c>
       <c r="H13" t="n">
-        <v>91591.67999999999</v>
+        <v>91411.64999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>113.92</v>
+        <v>309.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03596965544036689</v>
+        <v>0.03525692318195241</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         <v>1082</v>
       </c>
       <c r="H14" t="n">
-        <v>90823.08</v>
+        <v>88507.60000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>83.94</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03437072738687779</v>
+        <v>0.03470130585130298</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,16 +2319,16 @@
         <v>327</v>
       </c>
       <c r="H15" t="n">
-        <v>86785.8</v>
+        <v>87112.8</v>
       </c>
       <c r="I15" t="n">
-        <v>265.4</v>
+        <v>266.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03341086679074418</v>
+        <v>0.03336923441357351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>1798</v>
       </c>
       <c r="H16" t="n">
-        <v>84362.16</v>
+        <v>83768.82000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>46.92</v>
+        <v>46.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0330700498234517</v>
+        <v>0.03268641624694547</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         <v>910</v>
       </c>
       <c r="H17" t="n">
-        <v>83501.60000000001</v>
+        <v>82054.7</v>
       </c>
       <c r="I17" t="n">
-        <v>91.76000000000001</v>
+        <v>90.17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03222145296115553</v>
+        <v>0.03188601339171612</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
         <v>710</v>
       </c>
       <c r="H18" t="n">
-        <v>81358.89999999999</v>
+        <v>80045.39999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>114.59</v>
+        <v>112.74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03152634175433277</v>
+        <v>0.03149254406396377</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2459,16 +2459,16 @@
         <v>215</v>
       </c>
       <c r="H19" t="n">
-        <v>79603.75</v>
+        <v>79057.64999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>370.25</v>
+        <v>367.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03130898262056042</v>
+        <v>0.03140111099405844</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2494,16 +2494,16 @@
         <v>756</v>
       </c>
       <c r="H20" t="n">
-        <v>79054.92</v>
+        <v>78828.12</v>
       </c>
       <c r="I20" t="n">
-        <v>104.57</v>
+        <v>104.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03119107332021841</v>
+        <v>0.03108637138327594</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,16 +2529,16 @@
         <v>1179</v>
       </c>
       <c r="H21" t="n">
-        <v>78757.2</v>
+        <v>78038.00999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>66.8</v>
+        <v>66.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.03038593402720388</v>
+        <v>0.03008724809388559</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2564,16 +2564,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>76724.23</v>
+        <v>75529.85000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>78.37</v>
+        <v>77.15000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02584569328834932</v>
+        <v>0.0257652200648157</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2599,16 +2599,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>65260.16</v>
+        <v>64680</v>
       </c>
       <c r="I23" t="n">
-        <v>83.23999999999999</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02485077515067911</v>
+        <v>0.02489522562106868</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>62748</v>
+        <v>62496</v>
       </c>
       <c r="I24" t="n">
-        <v>19.92</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02415040056013492</v>
+        <v>0.0240688982061328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2669,16 +2669,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>60979.56</v>
+        <v>60421.62</v>
       </c>
       <c r="I25" t="n">
-        <v>37.16</v>
+        <v>36.82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02246998312857794</v>
+        <v>0.02252390917216579</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2704,16 +2704,16 @@
         <v>586</v>
       </c>
       <c r="H26" t="n">
-        <v>56736.52</v>
+        <v>56543.14</v>
       </c>
       <c r="I26" t="n">
-        <v>96.81999999999999</v>
+        <v>96.48999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02202663908996833</v>
+        <v>0.02196140438550336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2739,16 +2739,16 @@
         <v>953</v>
       </c>
       <c r="H27" t="n">
-        <v>55617.08</v>
+        <v>55131.05</v>
       </c>
       <c r="I27" t="n">
-        <v>58.36</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0206993079731598</v>
+        <v>0.0210471573397619</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2774,16 +2774,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>52265.58</v>
+        <v>52835.96</v>
       </c>
       <c r="I28" t="n">
-        <v>72.39</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01560036835923648</v>
+        <v>0.01547028581380925</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>39390.8</v>
+        <v>38836</v>
       </c>
       <c r="I29" t="n">
-        <v>269.8</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -2879,7 +2879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1079576469825329</v>
+        <v>0.1083921907725117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03829509401366831</v>
+        <v>0.03844450274747616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2940,16 +2940,16 @@
         <v>277</v>
       </c>
       <c r="H3" t="n">
-        <v>112486.93</v>
+        <v>112473.08</v>
       </c>
       <c r="I3" t="n">
-        <v>406.09</v>
+        <v>406.04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03789060657632373</v>
+        <v>0.03777760613563341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>411</v>
       </c>
       <c r="H4" t="n">
-        <v>111298.8</v>
+        <v>110522.01</v>
       </c>
       <c r="I4" t="n">
-        <v>270.8</v>
+        <v>268.91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03361045385122542</v>
+        <v>0.0341723201274232</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3010,16 +3010,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>98726.39999999999</v>
+        <v>99974.39999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>154.26</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03309292658768681</v>
+        <v>0.03324876469354922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>97206.23</v>
+        <v>97272.45</v>
       </c>
       <c r="I6" t="n">
-        <v>205.51</v>
+        <v>205.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03124799161449026</v>
+        <v>0.03154977065851859</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         <v>341</v>
       </c>
       <c r="H7" t="n">
-        <v>91786.97</v>
+        <v>92301.88</v>
       </c>
       <c r="I7" t="n">
-        <v>269.17</v>
+        <v>270.68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3098,33 +3098,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03036331301088059</v>
+        <v>0.03064791678629329</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>838</v>
+        <v>553</v>
       </c>
       <c r="H8" t="n">
-        <v>89188.34</v>
+        <v>89663.42</v>
       </c>
       <c r="I8" t="n">
-        <v>106.43</v>
+        <v>162.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3133,33 +3133,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03035372961397853</v>
+        <v>0.03064020553679267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>553</v>
+        <v>838</v>
       </c>
       <c r="H9" t="n">
-        <v>89160.19</v>
+        <v>89640.86</v>
       </c>
       <c r="I9" t="n">
-        <v>161.23</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02767713281868416</v>
+        <v>0.02755995444360598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>81298.03</v>
+        <v>80629.28999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>70.51000000000001</v>
+        <v>69.93000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02634319205799421</v>
+        <v>0.02614236632563518</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3220,16 +3220,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>77379.75</v>
+        <v>76482</v>
       </c>
       <c r="I11" t="n">
-        <v>147.39</v>
+        <v>145.68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02494908867206332</v>
+        <v>0.02491347822536435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>73284.75</v>
+        <v>72886.77</v>
       </c>
       <c r="I12" t="n">
-        <v>246.75</v>
+        <v>245.41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02459487747111294</v>
+        <v>0.02451543282339358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>265</v>
       </c>
       <c r="H13" t="n">
-        <v>72244.3</v>
+        <v>71722.25</v>
       </c>
       <c r="I13" t="n">
-        <v>272.62</v>
+        <v>270.65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02402936853939043</v>
+        <v>0.0239978903990196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3325,16 +3325,16 @@
         <v>141</v>
       </c>
       <c r="H14" t="n">
-        <v>70583.19</v>
+        <v>70208.13</v>
       </c>
       <c r="I14" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02344140415972262</v>
+        <v>0.02360758017329878</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
         <v>204</v>
       </c>
       <c r="H15" t="n">
-        <v>68856.12</v>
+        <v>69066.24000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>337.53</v>
+        <v>338.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02194956033860228</v>
+        <v>0.0219211340092419</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3395,16 +3395,16 @@
         <v>234</v>
       </c>
       <c r="H16" t="n">
-        <v>64474.02</v>
+        <v>64132.38</v>
       </c>
       <c r="I16" t="n">
-        <v>275.53</v>
+        <v>274.07</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3413,33 +3413,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02190971860007835</v>
+        <v>0.0216728905667632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1311</v>
+        <v>268</v>
       </c>
       <c r="H17" t="n">
-        <v>64356.99</v>
+        <v>63406.12</v>
       </c>
       <c r="I17" t="n">
-        <v>49.09</v>
+        <v>236.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02151194464717102</v>
+        <v>0.02151407847709221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3465,16 +3465,16 @@
         <v>426</v>
       </c>
       <c r="H18" t="n">
-        <v>63188.58</v>
+        <v>62941.5</v>
       </c>
       <c r="I18" t="n">
-        <v>148.33</v>
+        <v>147.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3483,33 +3483,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02138966186446222</v>
+        <v>0.02142880354245505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>183</v>
+        <v>1311</v>
       </c>
       <c r="H19" t="n">
-        <v>62829.39</v>
+        <v>62692.02</v>
       </c>
       <c r="I19" t="n">
-        <v>343.33</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3518,33 +3518,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02125845954360657</v>
+        <v>0.02103539651174861</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>268</v>
+        <v>183</v>
       </c>
       <c r="H20" t="n">
-        <v>62444</v>
+        <v>61541.07</v>
       </c>
       <c r="I20" t="n">
-        <v>233</v>
+        <v>336.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3553,33 +3553,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01994327023944827</v>
+        <v>0.02007416670198995</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>656</v>
+        <v>1201</v>
       </c>
       <c r="H21" t="n">
-        <v>58580.8</v>
+        <v>58728.9</v>
       </c>
       <c r="I21" t="n">
-        <v>89.3</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3588,33 +3588,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01964206220239425</v>
+        <v>0.01984640455694375</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1201</v>
+        <v>656</v>
       </c>
       <c r="H22" t="n">
-        <v>57696.04</v>
+        <v>58062.56</v>
       </c>
       <c r="I22" t="n">
-        <v>48.04</v>
+        <v>88.51000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3623,33 +3623,33 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01949379360492401</v>
+        <v>0.01912912846531837</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>548</v>
+        <v>1010</v>
       </c>
       <c r="H23" t="n">
-        <v>57260.52</v>
+        <v>55964.1</v>
       </c>
       <c r="I23" t="n">
-        <v>104.49</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3658,33 +3658,33 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01912120883627188</v>
+        <v>0.01902905312716273</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1010</v>
+        <v>548</v>
       </c>
       <c r="H24" t="n">
-        <v>56166.1</v>
+        <v>55671.32</v>
       </c>
       <c r="I24" t="n">
-        <v>55.61</v>
+        <v>101.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01763877478745609</v>
+        <v>0.01743361064515571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>51811.64</v>
+        <v>51003.7</v>
       </c>
       <c r="I25" t="n">
-        <v>130.18</v>
+        <v>128.15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01708792862321393</v>
+        <v>0.01710748905169204</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,16 +3745,16 @@
         <v>480</v>
       </c>
       <c r="H26" t="n">
-        <v>50193.6</v>
+        <v>50049.6</v>
       </c>
       <c r="I26" t="n">
-        <v>104.57</v>
+        <v>104.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3763,33 +3763,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01685721217275108</v>
+        <v>0.01689686529538524</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MSC Industrial</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>399</v>
+        <v>1740</v>
       </c>
       <c r="H27" t="n">
-        <v>49515.9</v>
+        <v>49433.4</v>
       </c>
       <c r="I27" t="n">
-        <v>124.1</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3798,33 +3798,33 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01669288159780875</v>
+        <v>0.01646545575051751</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>MSC Industrial</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1740</v>
+        <v>399</v>
       </c>
       <c r="H28" t="n">
-        <v>49033.2</v>
+        <v>48171.27</v>
       </c>
       <c r="I28" t="n">
-        <v>28.18</v>
+        <v>120.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01571788756385632</v>
+        <v>0.01567016136551818</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3850,16 +3850,16 @@
         <v>984</v>
       </c>
       <c r="H29" t="n">
-        <v>46169.28</v>
+        <v>45844.56</v>
       </c>
       <c r="I29" t="n">
-        <v>46.92</v>
+        <v>46.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01553639879339484</v>
+        <v>0.01542512410745064</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3885,16 +3885,16 @@
         <v>678</v>
       </c>
       <c r="H30" t="n">
-        <v>45636.18</v>
+        <v>45127.68</v>
       </c>
       <c r="I30" t="n">
-        <v>67.31</v>
+        <v>66.56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01453862929753306</v>
+        <v>0.01484817498257987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3920,16 +3920,16 @@
         <v>918</v>
       </c>
       <c r="H31" t="n">
-        <v>42705.36</v>
+        <v>43439.76</v>
       </c>
       <c r="I31" t="n">
-        <v>46.52</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3938,33 +3938,33 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01405967052546994</v>
+        <v>0.01393193087968187</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>492</v>
+        <v>153</v>
       </c>
       <c r="H32" t="n">
-        <v>41298.48</v>
+        <v>40759.2</v>
       </c>
       <c r="I32" t="n">
-        <v>83.94</v>
+        <v>266.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3973,33 +3973,33 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01382399045416048</v>
+        <v>0.01375637690168906</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>153</v>
+        <v>492</v>
       </c>
       <c r="H33" t="n">
-        <v>40606.2</v>
+        <v>40245.6</v>
       </c>
       <c r="I33" t="n">
-        <v>265.4</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01341890724613815</v>
+        <v>0.01350012141628951</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4025,16 +4025,16 @@
         <v>346</v>
       </c>
       <c r="H34" t="n">
-        <v>39416.32</v>
+        <v>39495.9</v>
       </c>
       <c r="I34" t="n">
-        <v>113.92</v>
+        <v>114.15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01286383962109366</v>
+        <v>0.01281594285521133</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4060,16 +4060,16 @@
         <v>121</v>
       </c>
       <c r="H35" t="n">
-        <v>37785.88</v>
+        <v>37494.27</v>
       </c>
       <c r="I35" t="n">
-        <v>312.28</v>
+        <v>309.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01270199426097851</v>
+        <v>0.01261560418301241</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>376</v>
       </c>
       <c r="H36" t="n">
-        <v>37310.48</v>
+        <v>36908.16</v>
       </c>
       <c r="I36" t="n">
-        <v>99.23</v>
+        <v>98.16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01237966530229734</v>
+        <v>0.01223600288667344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4130,16 +4130,16 @@
         <v>464</v>
       </c>
       <c r="H37" t="n">
-        <v>36363.68</v>
+        <v>35797.6</v>
       </c>
       <c r="I37" t="n">
-        <v>78.37</v>
+        <v>77.15000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01209342983347611</v>
+        <v>0.01194607904684964</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         <v>310</v>
       </c>
       <c r="H38" t="n">
-        <v>35522.9</v>
+        <v>34949.4</v>
       </c>
       <c r="I38" t="n">
-        <v>114.59</v>
+        <v>112.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01190198658609042</v>
+        <v>0.01174282814744569</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4200,16 +4200,16 @@
         <v>381</v>
       </c>
       <c r="H39" t="n">
-        <v>34960.56</v>
+        <v>34354.77</v>
       </c>
       <c r="I39" t="n">
-        <v>91.76000000000001</v>
+        <v>90.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0117177947189539</v>
+        <v>0.01158494920099885</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4235,16 +4235,16 @@
         <v>116</v>
       </c>
       <c r="H40" t="n">
-        <v>34419.52</v>
+        <v>33892.88</v>
       </c>
       <c r="I40" t="n">
-        <v>296.72</v>
+        <v>292.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01134432480529482</v>
+        <v>0.01131184928406603</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4270,16 +4270,16 @@
         <v>90</v>
       </c>
       <c r="H41" t="n">
-        <v>33322.5</v>
+        <v>33093.9</v>
       </c>
       <c r="I41" t="n">
-        <v>370.25</v>
+        <v>367.71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0113069648771942</v>
+        <v>0.01125155387573672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4305,16 +4305,16 @@
         <v>399</v>
       </c>
       <c r="H42" t="n">
-        <v>33212.76</v>
+        <v>32917.5</v>
       </c>
       <c r="I42" t="n">
-        <v>83.23999999999999</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01121151901021506</v>
+        <v>0.01115385412197954</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4340,16 +4340,16 @@
         <v>493</v>
       </c>
       <c r="H43" t="n">
-        <v>32932.4</v>
+        <v>32631.67</v>
       </c>
       <c r="I43" t="n">
-        <v>66.8</v>
+        <v>66.19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.008918789178007433</v>
+        <v>0.008872756456649544</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4375,16 +4375,16 @@
         <v>705</v>
       </c>
       <c r="H44" t="n">
-        <v>26197.8</v>
+        <v>25958.1</v>
       </c>
       <c r="I44" t="n">
-        <v>37.16</v>
+        <v>36.82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.008795699551580775</v>
+        <v>0.008795637125429259</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4410,16 +4410,16 @@
         <v>1297</v>
       </c>
       <c r="H45" t="n">
-        <v>25836.24</v>
+        <v>25732.48</v>
       </c>
       <c r="I45" t="n">
-        <v>19.92</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.008625567872439111</v>
+        <v>0.008754797582418003</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4445,16 +4445,16 @@
         <v>350</v>
       </c>
       <c r="H46" t="n">
-        <v>25336.5</v>
+        <v>25613</v>
       </c>
       <c r="I46" t="n">
-        <v>72.39</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.008563151531834333</v>
+        <v>0.008522485936890716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4480,16 +4480,16 @@
         <v>431</v>
       </c>
       <c r="H47" t="n">
-        <v>25153.16</v>
+        <v>24933.35</v>
       </c>
       <c r="I47" t="n">
-        <v>58.36</v>
+        <v>57.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008471089642304801</v>
+        <v>0.008476197931244715</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4515,16 +4515,16 @@
         <v>257</v>
       </c>
       <c r="H48" t="n">
-        <v>24882.74</v>
+        <v>24797.93</v>
       </c>
       <c r="I48" t="n">
-        <v>96.81999999999999</v>
+        <v>96.48999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0076950932279319</v>
+        <v>0.00771320807595742</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4550,16 +4550,16 @@
         <v>627</v>
       </c>
       <c r="H49" t="n">
-        <v>22603.35</v>
+        <v>22565.73</v>
       </c>
       <c r="I49" t="n">
-        <v>36.05</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.005970303071811999</v>
+        <v>0.00590990708624555</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         <v>65</v>
       </c>
       <c r="H50" t="n">
-        <v>17537</v>
+        <v>17290</v>
       </c>
       <c r="I50" t="n">
-        <v>269.8</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -4655,7 +4655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07253411403434032</v>
+        <v>0.07282548649541262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05342629288343978</v>
+        <v>0.05374920734111025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4716,16 +4716,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>115970.56</v>
+        <v>116204.7</v>
       </c>
       <c r="I3" t="n">
-        <v>113.92</v>
+        <v>114.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04289457806826947</v>
+        <v>0.04283804151564247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4751,16 +4751,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>93109.74000000001</v>
+        <v>92614.98</v>
       </c>
       <c r="I4" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03985026613163237</v>
+        <v>0.03970156908821058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4786,16 +4786,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>86501.56</v>
+        <v>85833.99000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>312.28</v>
+        <v>309.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03809713942211845</v>
+        <v>0.03844424928690014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4821,16 +4821,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>82696.11</v>
+        <v>83115.69</v>
       </c>
       <c r="I6" t="n">
-        <v>106.43</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03632419389720996</v>
+        <v>0.03676777200586134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4856,16 +4856,16 @@
         <v>2798</v>
       </c>
       <c r="H7" t="n">
-        <v>78847.64</v>
+        <v>79491.17999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>28.18</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03444348413945398</v>
+        <v>0.0343940449138056</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4891,16 +4891,16 @@
         <v>303</v>
       </c>
       <c r="H8" t="n">
-        <v>74765.25</v>
+        <v>74359.23</v>
       </c>
       <c r="I8" t="n">
-        <v>246.75</v>
+        <v>245.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4909,33 +4909,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03362708438758997</v>
+        <v>0.03340649174153473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>246</v>
+        <v>816</v>
       </c>
       <c r="H9" t="n">
-        <v>72993.12</v>
+        <v>72224.16</v>
       </c>
       <c r="I9" t="n">
-        <v>296.72</v>
+        <v>88.51000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4944,33 +4944,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03356981160446924</v>
+        <v>0.03324558366940146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>816</v>
+        <v>246</v>
       </c>
       <c r="H10" t="n">
-        <v>72868.8</v>
+        <v>71876.28</v>
       </c>
       <c r="I10" t="n">
-        <v>89.3</v>
+        <v>292.18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0328547955509754</v>
+        <v>0.03289213910736881</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4996,16 +4996,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>71316.74000000001</v>
+        <v>71112.14</v>
       </c>
       <c r="I11" t="n">
-        <v>104.57</v>
+        <v>104.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03247337318886975</v>
+        <v>0.03171844635975991</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>568</v>
       </c>
       <c r="H12" t="n">
-        <v>70488.8</v>
+        <v>68574.64</v>
       </c>
       <c r="I12" t="n">
-        <v>124.1</v>
+        <v>120.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03081275731895101</v>
+        <v>0.03098132568575028</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5066,16 +5066,16 @@
         <v>1076</v>
       </c>
       <c r="H13" t="n">
-        <v>66884.16</v>
+        <v>66981</v>
       </c>
       <c r="I13" t="n">
-        <v>62.16</v>
+        <v>62.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5084,7 +5084,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03063274332277643</v>
+        <v>0.03084965007929145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5101,16 +5101,16 @@
         <v>197</v>
       </c>
       <c r="H14" t="n">
-        <v>66493.41</v>
+        <v>66696.32000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>337.53</v>
+        <v>338.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03056483324427075</v>
+        <v>0.03047343472160764</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5136,16 +5136,16 @@
         <v>245</v>
       </c>
       <c r="H15" t="n">
-        <v>66346</v>
+        <v>65882.95</v>
       </c>
       <c r="I15" t="n">
-        <v>270.8</v>
+        <v>268.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5154,33 +5154,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02830475118783324</v>
+        <v>0.02878064368955086</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>588</v>
+        <v>263</v>
       </c>
       <c r="H16" t="n">
-        <v>61440.12</v>
+        <v>62223.17</v>
       </c>
       <c r="I16" t="n">
-        <v>104.49</v>
+        <v>236.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5189,33 +5189,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02823052507122761</v>
+        <v>0.02773088827069933</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>263</v>
+        <v>1082</v>
       </c>
       <c r="H17" t="n">
-        <v>61279</v>
+        <v>59953.62</v>
       </c>
       <c r="I17" t="n">
-        <v>233</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5224,33 +5224,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02771963083839924</v>
+        <v>0.02762973098837339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1082</v>
+        <v>588</v>
       </c>
       <c r="H18" t="n">
-        <v>60170.02</v>
+        <v>59734.92</v>
       </c>
       <c r="I18" t="n">
-        <v>55.61</v>
+        <v>101.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02641274535026612</v>
+        <v>0.02666761283647337</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5276,16 +5276,16 @@
         <v>213</v>
       </c>
       <c r="H19" t="n">
-        <v>57333.21</v>
+        <v>57654.84</v>
       </c>
       <c r="I19" t="n">
-        <v>269.17</v>
+        <v>270.68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0258583713453099</v>
+        <v>0.02591903507109102</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5311,16 +5311,16 @@
         <v>1557</v>
       </c>
       <c r="H20" t="n">
-        <v>56129.85</v>
+        <v>56036.43</v>
       </c>
       <c r="I20" t="n">
-        <v>36.05</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02519855497709216</v>
+        <v>0.02559804687165924</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5346,16 +5346,16 @@
         <v>1433</v>
       </c>
       <c r="H21" t="n">
-        <v>54697.61</v>
+        <v>55342.46</v>
       </c>
       <c r="I21" t="n">
-        <v>38.17</v>
+        <v>38.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02469468624251499</v>
+        <v>0.0247908330354929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
         <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>53603.88</v>
+        <v>53597.28</v>
       </c>
       <c r="I22" t="n">
-        <v>406.09</v>
+        <v>406.04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02386264611913435</v>
+        <v>0.02378537497799644</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5416,16 +5416,16 @@
         <v>190</v>
       </c>
       <c r="H23" t="n">
-        <v>51797.8</v>
+        <v>51423.5</v>
       </c>
       <c r="I23" t="n">
-        <v>272.62</v>
+        <v>270.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02256567464558262</v>
+        <v>0.0223264251697746</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5451,16 +5451,16 @@
         <v>443</v>
       </c>
       <c r="H24" t="n">
-        <v>48982.51</v>
+        <v>48269.28</v>
       </c>
       <c r="I24" t="n">
-        <v>110.57</v>
+        <v>108.96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02212982194784542</v>
+        <v>0.0218722442359186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5486,16 +5486,16 @@
         <v>369</v>
       </c>
       <c r="H25" t="n">
-        <v>48036.42</v>
+        <v>47287.35</v>
       </c>
       <c r="I25" t="n">
-        <v>130.18</v>
+        <v>128.15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02055254461128045</v>
+        <v>0.02098996494319681</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5521,16 +5521,16 @@
         <v>959</v>
       </c>
       <c r="H26" t="n">
-        <v>44612.68</v>
+        <v>45379.88</v>
       </c>
       <c r="I26" t="n">
-        <v>46.52</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02036350572915562</v>
+        <v>0.02036536150969293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5556,16 +5556,16 @@
         <v>298</v>
       </c>
       <c r="H27" t="n">
-        <v>44202.34</v>
+        <v>44029.5</v>
       </c>
       <c r="I27" t="n">
-        <v>148.33</v>
+        <v>147.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02018242293587003</v>
+        <v>0.02015612273600393</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5591,16 +5591,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>43809.27</v>
+        <v>43577.13</v>
       </c>
       <c r="I28" t="n">
-        <v>275.53</v>
+        <v>274.07</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01914804385597029</v>
+        <v>0.01900191675704795</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5626,16 +5626,16 @@
         <v>282</v>
       </c>
       <c r="H29" t="n">
-        <v>41563.98</v>
+        <v>41081.76</v>
       </c>
       <c r="I29" t="n">
-        <v>147.39</v>
+        <v>145.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5644,33 +5644,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01871636960211102</v>
+        <v>0.01850274465331611</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>484</v>
+        <v>601</v>
       </c>
       <c r="H30" t="n">
-        <v>40626.96</v>
+        <v>40002.56</v>
       </c>
       <c r="I30" t="n">
-        <v>83.94</v>
+        <v>66.56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5679,33 +5679,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01863637105972915</v>
+        <v>0.01831247460458453</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>601</v>
+        <v>484</v>
       </c>
       <c r="H31" t="n">
-        <v>40453.31</v>
+        <v>39591.2</v>
       </c>
       <c r="I31" t="n">
-        <v>67.31</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01809547219076296</v>
+        <v>0.01823661820631542</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5731,16 +5731,16 @@
         <v>148</v>
       </c>
       <c r="H32" t="n">
-        <v>39279.2</v>
+        <v>39427.2</v>
       </c>
       <c r="I32" t="n">
-        <v>265.4</v>
+        <v>266.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01748218535194671</v>
+        <v>0.01777429196042577</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5766,16 +5766,16 @@
         <v>246</v>
       </c>
       <c r="H33" t="n">
-        <v>37947.96</v>
+        <v>38427.66</v>
       </c>
       <c r="I33" t="n">
-        <v>154.26</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5784,33 +5784,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01664478281547464</v>
+        <v>0.01660250487355388</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>736</v>
+        <v>372</v>
       </c>
       <c r="H34" t="n">
-        <v>36130.24</v>
+        <v>35894.28</v>
       </c>
       <c r="I34" t="n">
-        <v>49.09</v>
+        <v>96.48999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5819,33 +5819,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01659263288747218</v>
+        <v>0.01639042148492979</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="H35" t="n">
-        <v>36017.04</v>
+        <v>35435.76</v>
       </c>
       <c r="I35" t="n">
-        <v>96.81999999999999</v>
+        <v>98.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5854,27 +5854,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01650279404065451</v>
+        <v>0.01627930111224583</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>361</v>
+        <v>736</v>
       </c>
       <c r="H36" t="n">
-        <v>35822.03</v>
+        <v>35195.52</v>
       </c>
       <c r="I36" t="n">
-        <v>99.23</v>
+        <v>47.82</v>
       </c>
     </row>
   </sheetData>
@@ -5941,7 +5941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1059547508164773</v>
+        <v>0.1063116570438224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5967,16 +5967,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>221053.51</v>
+        <v>221273.9</v>
       </c>
       <c r="I2" t="n">
-        <v>52.76</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5985,33 +5985,33 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09925882844895438</v>
+        <v>0.09935138588473787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RSP</t>
+          <t>CGGR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Invesco S&amp;P 500® Equal Weight ETF</t>
+          <t>Capital Group Growth ETF</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>980</v>
+        <v>4300</v>
       </c>
       <c r="H3" t="n">
-        <v>207083.8</v>
+        <v>206787</v>
       </c>
       <c r="I3" t="n">
-        <v>211.31</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6020,33 +6020,33 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09860130110559737</v>
+        <v>0.09899959837031574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CGGR</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Capital Group Growth ETF</t>
+          <t>Invesco S&amp;P 500® Equal Weight ETF</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4300</v>
+        <v>980</v>
       </c>
       <c r="H4" t="n">
-        <v>205712</v>
+        <v>206054.8</v>
       </c>
       <c r="I4" t="n">
-        <v>47.84</v>
+        <v>210.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05468589919287152</v>
+        <v>0.05461702951564509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6072,16 +6072,16 @@
         <v>1475</v>
       </c>
       <c r="H5" t="n">
-        <v>114091.25</v>
+        <v>113678.25</v>
       </c>
       <c r="I5" t="n">
-        <v>77.34999999999999</v>
+        <v>77.06999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04486567703289343</v>
+        <v>0.04497196908847627</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03809384040626504</v>
+        <v>0.03798907340869504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6142,16 +6142,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>79475.22</v>
+        <v>79069.32000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>29.37</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03733358579929214</v>
+        <v>0.03709864069054591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1270</v>
       </c>
       <c r="H8" t="n">
-        <v>77889.10000000001</v>
+        <v>77216</v>
       </c>
       <c r="I8" t="n">
-        <v>61.33</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02861295086236043</v>
+        <v>0.02867720697394869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6212,16 +6212,16 @@
         <v>147</v>
       </c>
       <c r="H9" t="n">
-        <v>59695.23</v>
+        <v>59687.88</v>
       </c>
       <c r="I9" t="n">
-        <v>406.09</v>
+        <v>406.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6230,33 +6230,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02519384702228044</v>
+        <v>0.02520178944055725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>SPDR® S&amp;P Oil &amp; Gas Explor &amp; Prodtn ETF</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>105</v>
+        <v>285</v>
       </c>
       <c r="H10" t="n">
-        <v>52561.95</v>
+        <v>52454.25</v>
       </c>
       <c r="I10" t="n">
-        <v>500.59</v>
+        <v>184.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6265,33 +6265,33 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02495097699393884</v>
+        <v>0.02511934374610923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SPDR® S&amp;P Oil &amp; Gas Explor &amp; Prodtn ETF</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>285</v>
+        <v>105</v>
       </c>
       <c r="H11" t="n">
-        <v>52055.25</v>
+        <v>52282.65</v>
       </c>
       <c r="I11" t="n">
-        <v>182.65</v>
+        <v>497.93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02314599301816012</v>
+        <v>0.02311646589170212</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6317,16 +6317,16 @@
         <v>1860</v>
       </c>
       <c r="H12" t="n">
-        <v>48289.51</v>
+        <v>48113.92</v>
       </c>
       <c r="I12" t="n">
-        <v>25.96</v>
+        <v>25.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6335,33 +6335,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02050825770798267</v>
+        <v>0.02063916975917296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>158</v>
+        <v>275</v>
       </c>
       <c r="H13" t="n">
-        <v>42786.4</v>
+        <v>42957.75</v>
       </c>
       <c r="I13" t="n">
-        <v>270.8</v>
+        <v>156.21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6370,33 +6370,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02041450326246537</v>
+        <v>0.02054773479349463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sprott Physical Gold and Silver Trust</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>980</v>
+        <v>158</v>
       </c>
       <c r="H14" t="n">
-        <v>42590.8</v>
+        <v>42767.44</v>
       </c>
       <c r="I14" t="n">
-        <v>43.46</v>
+        <v>270.68</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6405,33 +6405,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02038481435471822</v>
+        <v>0.02041337137327708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>158</v>
       </c>
       <c r="H15" t="n">
-        <v>42528.86</v>
+        <v>42487.78</v>
       </c>
       <c r="I15" t="n">
-        <v>269.17</v>
+        <v>268.91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6440,33 +6440,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02033335485946906</v>
+        <v>0.02024157107362253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CEF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Sprott Physical Gold and Silver Trust</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>275</v>
+        <v>980</v>
       </c>
       <c r="H16" t="n">
-        <v>42421.5</v>
+        <v>42130.2</v>
       </c>
       <c r="I16" t="n">
-        <v>154.26</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0198979047640521</v>
+        <v>0.01995863244040322</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6492,16 +6492,16 @@
         <v>202</v>
       </c>
       <c r="H17" t="n">
-        <v>41513.02</v>
+        <v>41541.3</v>
       </c>
       <c r="I17" t="n">
-        <v>205.51</v>
+        <v>205.65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01839687500136306</v>
+        <v>0.01820675752393594</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6527,16 +6527,16 @@
         <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>38381.42</v>
+        <v>37895</v>
       </c>
       <c r="I18" t="n">
-        <v>1744.61</v>
+        <v>1722.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0173107901440131</v>
+        <v>0.01744973692952996</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6562,16 +6562,16 @@
         <v>224</v>
       </c>
       <c r="H19" t="n">
-        <v>36115.52</v>
+        <v>36319.36</v>
       </c>
       <c r="I19" t="n">
-        <v>161.23</v>
+        <v>162.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01649276822735848</v>
+        <v>0.01639585418077937</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6597,16 +6597,16 @@
         <v>488</v>
       </c>
       <c r="H20" t="n">
-        <v>34408.88</v>
+        <v>34125.84</v>
       </c>
       <c r="I20" t="n">
-        <v>70.51000000000001</v>
+        <v>69.93000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01601660972162565</v>
+        <v>0.01610354671864551</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6632,16 +6632,16 @@
         <v>99</v>
       </c>
       <c r="H21" t="n">
-        <v>33415.47</v>
+        <v>33517.44</v>
       </c>
       <c r="I21" t="n">
-        <v>337.53</v>
+        <v>338.56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01561020145572757</v>
+        <v>0.01572657387029003</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6667,16 +6667,16 @@
         <v>306</v>
       </c>
       <c r="H22" t="n">
-        <v>32567.58</v>
+        <v>32732.82</v>
       </c>
       <c r="I22" t="n">
-        <v>106.43</v>
+        <v>106.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01490221159691012</v>
+        <v>0.01485639704070693</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>126</v>
       </c>
       <c r="H23" t="n">
-        <v>31090.5</v>
+        <v>30921.66</v>
       </c>
       <c r="I23" t="n">
-        <v>246.75</v>
+        <v>245.41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01419995916504994</v>
+        <v>0.0140684641154106</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6737,16 +6737,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>29625.39</v>
+        <v>29281.68</v>
       </c>
       <c r="I24" t="n">
-        <v>147.39</v>
+        <v>145.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01382337401571672</v>
+        <v>0.01357200266443729</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>84</v>
       </c>
       <c r="H25" t="n">
-        <v>28839.72</v>
+        <v>28248.36</v>
       </c>
       <c r="I25" t="n">
-        <v>343.33</v>
+        <v>336.29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01345916004347349</v>
+        <v>0.01339355770304489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6807,16 +6807,16 @@
         <v>103</v>
       </c>
       <c r="H26" t="n">
-        <v>28079.86</v>
+        <v>27876.95</v>
       </c>
       <c r="I26" t="n">
-        <v>272.62</v>
+        <v>270.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01324952587020434</v>
+        <v>0.0130875333144746</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6842,16 +6842,16 @@
         <v>250</v>
       </c>
       <c r="H27" t="n">
-        <v>27642.5</v>
+        <v>27240</v>
       </c>
       <c r="I27" t="n">
-        <v>110.57</v>
+        <v>108.96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01233486401845156</v>
+        <v>0.0123819884292945</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6877,16 +6877,16 @@
         <v>414</v>
       </c>
       <c r="H28" t="n">
-        <v>25734.24</v>
+        <v>25771.5</v>
       </c>
       <c r="I28" t="n">
-        <v>62.16</v>
+        <v>62.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01178453117507149</v>
+        <v>0.01172937022069011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>524</v>
       </c>
       <c r="H29" t="n">
-        <v>24586.08</v>
+        <v>24413.16</v>
       </c>
       <c r="I29" t="n">
-        <v>46.92</v>
+        <v>46.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01138020314584797</v>
+        <v>0.0114345403815408</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6947,16 +6947,16 @@
         <v>259</v>
       </c>
       <c r="H30" t="n">
-        <v>23742.53</v>
+        <v>23799.51</v>
       </c>
       <c r="I30" t="n">
-        <v>91.67</v>
+        <v>91.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01070075662665504</v>
+        <v>0.01063121855418637</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6982,16 +6982,16 @@
         <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>22325</v>
+        <v>22127.5</v>
       </c>
       <c r="I31" t="n">
-        <v>89.3</v>
+        <v>88.51000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01001677097352013</v>
+        <v>0.009761839276192914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         <v>200</v>
       </c>
       <c r="H32" t="n">
-        <v>20898</v>
+        <v>20318</v>
       </c>
       <c r="I32" t="n">
-        <v>104.49</v>
+        <v>101.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.008779653264521403</v>
+        <v>0.008872280982075816</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7052,16 +7052,16 @@
         <v>650</v>
       </c>
       <c r="H33" t="n">
-        <v>18317</v>
+        <v>18466.5</v>
       </c>
       <c r="I33" t="n">
-        <v>28.18</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7070,33 +7070,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.008771385042715813</v>
+        <v>0.008813665744764292</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>175</v>
+        <v>475</v>
       </c>
       <c r="H34" t="n">
-        <v>18299.75</v>
+        <v>18344.5</v>
       </c>
       <c r="I34" t="n">
-        <v>104.57</v>
+        <v>38.62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7105,33 +7105,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.008690380434881337</v>
+        <v>0.00876694171338277</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>475</v>
+        <v>175</v>
       </c>
       <c r="H35" t="n">
-        <v>18130.75</v>
+        <v>18247.25</v>
       </c>
       <c r="I35" t="n">
-        <v>38.17</v>
+        <v>104.27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7140,33 +7140,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.00841858840632239</v>
+        <v>0.008571104361902851</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>177</v>
+        <v>377</v>
       </c>
       <c r="H36" t="n">
-        <v>17563.71</v>
+        <v>17839.64</v>
       </c>
       <c r="I36" t="n">
-        <v>99.23</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7175,33 +7175,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.00840628433364126</v>
+        <v>0.008504878752796126</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="H37" t="n">
-        <v>17538.04</v>
+        <v>17701.8</v>
       </c>
       <c r="I37" t="n">
-        <v>46.52</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7210,33 +7210,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008335556286706021</v>
+        <v>0.008347540081363522</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>362</v>
+        <v>177</v>
       </c>
       <c r="H38" t="n">
-        <v>17390.48</v>
+        <v>17374.32</v>
       </c>
       <c r="I38" t="n">
-        <v>48.04</v>
+        <v>98.16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008236471833856653</v>
+        <v>0.008127242879625162</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7262,16 +7262,16 @@
         <v>132</v>
       </c>
       <c r="H39" t="n">
-        <v>17183.76</v>
+        <v>16915.8</v>
       </c>
       <c r="I39" t="n">
-        <v>130.18</v>
+        <v>128.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.008117740168728379</v>
+        <v>0.007926461669194954</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7297,16 +7297,16 @@
         <v>345</v>
       </c>
       <c r="H40" t="n">
-        <v>16936.05</v>
+        <v>16497.9</v>
       </c>
       <c r="I40" t="n">
-        <v>49.09</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.007581767668843691</v>
+        <v>0.007515049966655136</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7332,16 +7332,16 @@
         <v>235</v>
       </c>
       <c r="H41" t="n">
-        <v>15817.85</v>
+        <v>15641.6</v>
       </c>
       <c r="I41" t="n">
-        <v>67.31</v>
+        <v>66.56</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.007250113714412272</v>
+        <v>0.007241153454470273</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7367,16 +7367,16 @@
         <v>272</v>
       </c>
       <c r="H42" t="n">
-        <v>15125.92</v>
+        <v>15071.52</v>
       </c>
       <c r="I42" t="n">
-        <v>55.61</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.007131578569338508</v>
+        <v>0.007110595220150328</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7402,16 +7402,16 @@
         <v>54</v>
       </c>
       <c r="H43" t="n">
-        <v>14878.62</v>
+        <v>14799.78</v>
       </c>
       <c r="I43" t="n">
-        <v>275.53</v>
+        <v>274.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.007000696213035062</v>
+        <v>0.006838380292642434</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7437,16 +7437,16 @@
         <v>174</v>
       </c>
       <c r="H44" t="n">
-        <v>14605.56</v>
+        <v>14233.2</v>
       </c>
       <c r="I44" t="n">
-        <v>83.94</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.004751830952183712</v>
+        <v>0.004755161126897348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7472,16 +7472,16 @@
         <v>275</v>
       </c>
       <c r="H45" t="n">
-        <v>9913.75</v>
+        <v>9897.25</v>
       </c>
       <c r="I45" t="n">
-        <v>36.05</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.004124467040607901</v>
+        <v>0.004070981976170061</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7507,16 +7507,16 @@
         <v>29</v>
       </c>
       <c r="H46" t="n">
-        <v>8604.879999999999</v>
+        <v>8473.219999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>296.72</v>
+        <v>292.18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/23/2026</t>
+          <t>09/24/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.002488399241438341</v>
+        <v>0.002484541360223083</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7542,261 +7542,13 @@
         <v>35</v>
       </c>
       <c r="H47" t="n">
-        <v>5191.55</v>
+        <v>5171.25</v>
       </c>
       <c r="I47" t="n">
-        <v>148.33</v>
+        <v>147.75</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D023554-40DF-4EA4-859C-B84CC3DFAD81}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08002B98-DB9F-4C83-AFEF-EC4EAA18A263}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEDA619B-7ADA-405D-975C-DFAA2EE81B0D}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -7551,4 +7551,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA71D68D-ADE0-40B7-9E76-C920E4478FDB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9543BD6-9640-4573-B3D2-51B4B063FD13}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AB248A9-D2E1-479D-A485-E992A1201700}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1106340009769927</v>
+        <v>0.1104877826114799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>255846.16</v>
+        <v>256537.88</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04723139954319341</v>
+        <v>0.04803466972814616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>109224.76</v>
+        <v>111530.09</v>
       </c>
       <c r="I3" t="n">
-        <v>406.04</v>
+        <v>414.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04046652504984885</v>
+        <v>0.03964010867825565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>93580.67999999999</v>
+        <v>92039.03999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>268.91</v>
+        <v>264.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03827486221687254</v>
+        <v>0.03819726085973186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -613,16 +613,16 @@
         <v>327</v>
       </c>
       <c r="H5" t="n">
-        <v>88512.36</v>
+        <v>88688.94</v>
       </c>
       <c r="I5" t="n">
-        <v>270.68</v>
+        <v>271.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,33 +631,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03815010358996224</v>
+        <v>0.03803518435721943</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>429</v>
+        <v>561</v>
       </c>
       <c r="H6" t="n">
-        <v>88223.85000000001</v>
+        <v>88312.62</v>
       </c>
       <c r="I6" t="n">
-        <v>205.65</v>
+        <v>157.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,33 +666,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03789495617662422</v>
+        <v>0.03777523401011743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>561</v>
+        <v>429</v>
       </c>
       <c r="H7" t="n">
-        <v>87633.81</v>
+        <v>87709.05</v>
       </c>
       <c r="I7" t="n">
-        <v>156.21</v>
+        <v>204.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03575281020742212</v>
+        <v>0.03605251221830588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         <v>48</v>
       </c>
       <c r="H8" t="n">
-        <v>82680</v>
+        <v>83709.12</v>
       </c>
       <c r="I8" t="n">
-        <v>1722.5</v>
+        <v>1743.94</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03316355087138199</v>
+        <v>0.03271465880021378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -753,16 +753,16 @@
         <v>473</v>
       </c>
       <c r="H9" t="n">
-        <v>76692.22</v>
+        <v>75959.07000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>162.14</v>
+        <v>160.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03160017838178829</v>
+        <v>0.0317118578165965</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -788,16 +788,16 @@
         <v>1045</v>
       </c>
       <c r="H10" t="n">
-        <v>73076.85000000001</v>
+        <v>73630.7</v>
       </c>
       <c r="I10" t="n">
-        <v>69.93000000000001</v>
+        <v>70.45999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03103803592637652</v>
+        <v>0.03083540776713651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         <v>671</v>
       </c>
       <c r="H11" t="n">
-        <v>71776.87</v>
+        <v>71595.7</v>
       </c>
       <c r="I11" t="n">
-        <v>106.97</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02971372468007105</v>
+        <v>0.0306785339754828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         <v>138</v>
       </c>
       <c r="H12" t="n">
-        <v>68714.34</v>
+        <v>71231.46000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02835686920908959</v>
+        <v>0.02827914536980978</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -893,16 +893,16 @@
         <v>195</v>
       </c>
       <c r="H13" t="n">
-        <v>65576.55</v>
+        <v>65660.39999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>336.29</v>
+        <v>336.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02790986394823308</v>
+        <v>0.02816481924419349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>263</v>
       </c>
       <c r="H14" t="n">
-        <v>64542.83</v>
+        <v>65394.95</v>
       </c>
       <c r="I14" t="n">
-        <v>245.41</v>
+        <v>248.65</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02752904116926149</v>
+        <v>0.02762959036460361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>437</v>
+        <v>187</v>
       </c>
       <c r="H15" t="n">
-        <v>63662.16</v>
+        <v>64152.22</v>
       </c>
       <c r="I15" t="n">
-        <v>145.68</v>
+        <v>343.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,33 +981,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02737707010468365</v>
+        <v>0.0275220432678711</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>187</v>
+        <v>437</v>
       </c>
       <c r="H16" t="n">
-        <v>63310.72</v>
+        <v>63902.51</v>
       </c>
       <c r="I16" t="n">
-        <v>338.56</v>
+        <v>146.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02621595997231604</v>
+        <v>0.02682655538906546</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>224</v>
       </c>
       <c r="H17" t="n">
-        <v>60625.6</v>
+        <v>62287.68</v>
       </c>
       <c r="I17" t="n">
-        <v>270.65</v>
+        <v>278.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02524357261400293</v>
+        <v>0.02511654750657089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1068,16 +1068,16 @@
         <v>213</v>
       </c>
       <c r="H18" t="n">
-        <v>58376.91</v>
+        <v>58317.27</v>
       </c>
       <c r="I18" t="n">
-        <v>274.07</v>
+        <v>273.79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,33 +1086,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02474027008221144</v>
+        <v>0.02418783347013204</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1170</v>
+        <v>898</v>
       </c>
       <c r="H19" t="n">
-        <v>57213</v>
+        <v>56160.92</v>
       </c>
       <c r="I19" t="n">
-        <v>48.9</v>
+        <v>62.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,33 +1121,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02417271367924529</v>
+        <v>0.02370872754186654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>898</v>
+        <v>1170</v>
       </c>
       <c r="H20" t="n">
-        <v>55900.5</v>
+        <v>55048.5</v>
       </c>
       <c r="I20" t="n">
-        <v>62.25</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02255339418209671</v>
+        <v>0.02246893618762722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         <v>353</v>
       </c>
       <c r="H21" t="n">
-        <v>52155.75</v>
+        <v>52169.87</v>
       </c>
       <c r="I21" t="n">
-        <v>147.75</v>
+        <v>147.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02209290161898609</v>
+        <v>0.02177672153750752</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1208,16 +1208,16 @@
         <v>556</v>
       </c>
       <c r="H22" t="n">
-        <v>51090.84</v>
+        <v>50562.64</v>
       </c>
       <c r="I22" t="n">
-        <v>91.89</v>
+        <v>90.94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02153242831992896</v>
+        <v>0.02169595461968185</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
         <v>457</v>
       </c>
       <c r="H23" t="n">
-        <v>49794.72</v>
+        <v>50375.11</v>
       </c>
       <c r="I23" t="n">
-        <v>108.96</v>
+        <v>110.23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02124198214150589</v>
+        <v>0.02118778155930921</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1278,16 +1278,16 @@
         <v>555</v>
       </c>
       <c r="H24" t="n">
-        <v>49123.05</v>
+        <v>49195.2</v>
       </c>
       <c r="I24" t="n">
-        <v>88.51000000000001</v>
+        <v>88.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0207019668183911</v>
+        <v>0.02066723483312772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         <v>864</v>
       </c>
       <c r="H25" t="n">
-        <v>47874.24</v>
+        <v>47986.56</v>
       </c>
       <c r="I25" t="n">
-        <v>55.41</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01920784702055742</v>
+        <v>0.01935824484033963</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         <v>426</v>
       </c>
       <c r="H26" t="n">
-        <v>44419.02</v>
+        <v>44947.26</v>
       </c>
       <c r="I26" t="n">
-        <v>104.27</v>
+        <v>105.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01889753961120998</v>
+        <v>0.01892671270689643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1383,16 +1383,16 @@
         <v>938</v>
       </c>
       <c r="H27" t="n">
-        <v>43701.42</v>
+        <v>43945.3</v>
       </c>
       <c r="I27" t="n">
-        <v>46.59</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01882531616707786</v>
+        <v>0.01865464710677658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1418,16 +1418,16 @@
         <v>920</v>
       </c>
       <c r="H28" t="n">
-        <v>43534.4</v>
+        <v>43313.6</v>
       </c>
       <c r="I28" t="n">
-        <v>47.32</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01871415727264245</v>
+        <v>0.01859866628248724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>426</v>
       </c>
       <c r="H29" t="n">
-        <v>43277.34</v>
+        <v>43183.62</v>
       </c>
       <c r="I29" t="n">
-        <v>101.59</v>
+        <v>101.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01847688626440814</v>
+        <v>0.01857112809272681</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1488,16 +1488,16 @@
         <v>1504</v>
       </c>
       <c r="H30" t="n">
-        <v>42728.64</v>
+        <v>43119.68</v>
       </c>
       <c r="I30" t="n">
-        <v>28.41</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0183424067476398</v>
+        <v>0.01833719991367807</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1523,16 +1523,16 @@
         <v>331</v>
       </c>
       <c r="H31" t="n">
-        <v>42417.65</v>
+        <v>42576.53</v>
       </c>
       <c r="I31" t="n">
-        <v>128.15</v>
+        <v>128.63</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01815313047095994</v>
+        <v>0.01816452417985497</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1558,16 +1558,16 @@
         <v>1087</v>
       </c>
       <c r="H32" t="n">
-        <v>41979.94</v>
+        <v>42175.6</v>
       </c>
       <c r="I32" t="n">
-        <v>38.62</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01611799645074225</v>
+        <v>0.01616423690235522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>37273.6</v>
+        <v>37531.2</v>
       </c>
       <c r="I33" t="n">
-        <v>66.56</v>
+        <v>67.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01574773778828454</v>
+        <v>0.01575003134654827</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>36417.36</v>
+        <v>36569.47</v>
       </c>
       <c r="I34" t="n">
-        <v>98.16</v>
+        <v>98.56999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01319385937787542</v>
+        <v>0.01346218662210849</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         <v>373</v>
       </c>
       <c r="H35" t="n">
-        <v>30511.4</v>
+        <v>31257.4</v>
       </c>
       <c r="I35" t="n">
-        <v>81.8</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01099206917655055</v>
+        <v>0.01098616139638589</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1698,16 +1698,16 @@
         <v>87</v>
       </c>
       <c r="H36" t="n">
-        <v>25419.66</v>
+        <v>25508.4</v>
       </c>
       <c r="I36" t="n">
-        <v>292.18</v>
+        <v>293.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01079418333950265</v>
+        <v>0.01077782900428525</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         <v>522</v>
       </c>
       <c r="H37" t="n">
-        <v>24962.04</v>
+        <v>25024.68</v>
       </c>
       <c r="I37" t="n">
-        <v>47.82</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008948688832062715</v>
+        <v>0.008853329891504657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         <v>575</v>
       </c>
       <c r="H38" t="n">
-        <v>20694.25</v>
+        <v>20556.25</v>
       </c>
       <c r="I38" t="n">
-        <v>35.99</v>
+        <v>35.75</v>
       </c>
     </row>
   </sheetData>
@@ -1838,7 +1838,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06042155628573654</v>
+        <v>0.06068846235277696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1864,16 +1864,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>151679.91</v>
+        <v>152854.82</v>
       </c>
       <c r="I2" t="n">
-        <v>156.21</v>
+        <v>157.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05851573068263978</v>
+        <v>0.05611598005028078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>146895.6</v>
+        <v>141338.2</v>
       </c>
       <c r="I3" t="n">
-        <v>48.9</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05240045050734259</v>
+        <v>0.05216776917668535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         <v>556</v>
       </c>
       <c r="H4" t="n">
-        <v>131544.04</v>
+        <v>131393.92</v>
       </c>
       <c r="I4" t="n">
-        <v>236.59</v>
+        <v>236.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05151756947007212</v>
+        <v>0.05182115905582704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>129327.69</v>
+        <v>130520.92</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0496125206477287</v>
+        <v>0.04982342219360723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2004,16 +2004,16 @@
         <v>1781</v>
       </c>
       <c r="H6" t="n">
-        <v>124545.33</v>
+        <v>125489.26</v>
       </c>
       <c r="I6" t="n">
-        <v>69.93000000000001</v>
+        <v>70.45999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2022,33 +2022,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04431277262664141</v>
+        <v>0.04442505492341096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1095</v>
+        <v>450</v>
       </c>
       <c r="H7" t="n">
-        <v>111241.05</v>
+        <v>111892.5</v>
       </c>
       <c r="I7" t="n">
-        <v>101.59</v>
+        <v>248.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2057,33 +2057,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04399148415658456</v>
+        <v>0.04407076220709032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>450</v>
+        <v>1095</v>
       </c>
       <c r="H8" t="n">
-        <v>110434.5</v>
+        <v>111000.15</v>
       </c>
       <c r="I8" t="n">
-        <v>245.41</v>
+        <v>101.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0413758243506075</v>
+        <v>0.04125032458469537</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2109,16 +2109,16 @@
         <v>703</v>
       </c>
       <c r="H9" t="n">
-        <v>103868.25</v>
+        <v>103896.37</v>
       </c>
       <c r="I9" t="n">
-        <v>147.75</v>
+        <v>147.79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03889816860831713</v>
+        <v>0.03886697701493694</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>97648.44</v>
+        <v>97893.48</v>
       </c>
       <c r="I10" t="n">
-        <v>47.82</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03828177913831878</v>
+        <v>0.03831019331609747</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>796</v>
       </c>
       <c r="H11" t="n">
-        <v>96101.08</v>
+        <v>96491.12</v>
       </c>
       <c r="I11" t="n">
-        <v>120.73</v>
+        <v>121.22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03655912640384299</v>
+        <v>0.03663628480069835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2214,16 +2214,16 @@
         <v>804</v>
       </c>
       <c r="H12" t="n">
-        <v>91776.60000000001</v>
+        <v>92275.08</v>
       </c>
       <c r="I12" t="n">
-        <v>114.15</v>
+        <v>114.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2232,33 +2232,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03641374889823608</v>
+        <v>0.03599964975305359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>295</v>
+        <v>1082</v>
       </c>
       <c r="H13" t="n">
-        <v>91411.64999999999</v>
+        <v>90671.60000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>309.87</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2267,33 +2267,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03525692318195241</v>
+        <v>0.03594795600994276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1082</v>
+        <v>295</v>
       </c>
       <c r="H14" t="n">
-        <v>88507.60000000001</v>
+        <v>90541.39999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>81.8</v>
+        <v>306.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03470130585130298</v>
+        <v>0.03527478595276606</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,16 +2319,16 @@
         <v>327</v>
       </c>
       <c r="H15" t="n">
-        <v>87112.8</v>
+        <v>88845.89999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>266.4</v>
+        <v>271.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03336923441357351</v>
+        <v>0.03344462098929707</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>1798</v>
       </c>
       <c r="H16" t="n">
-        <v>83768.82000000001</v>
+        <v>84236.3</v>
       </c>
       <c r="I16" t="n">
-        <v>46.59</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03268641624694547</v>
+        <v>0.03302285245391588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         <v>910</v>
       </c>
       <c r="H17" t="n">
-        <v>82054.7</v>
+        <v>83174</v>
       </c>
       <c r="I17" t="n">
-        <v>90.17</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03188601339171612</v>
+        <v>0.03209641481816472</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2424,16 +2424,16 @@
         <v>710</v>
       </c>
       <c r="H18" t="n">
-        <v>80045.39999999999</v>
+        <v>80840.60000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>112.74</v>
+        <v>113.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2442,33 +2442,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03149254406396377</v>
+        <v>0.03166958807781247</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Snap-On</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>215</v>
+        <v>756</v>
       </c>
       <c r="H19" t="n">
-        <v>79057.64999999999</v>
+        <v>79765.56</v>
       </c>
       <c r="I19" t="n">
-        <v>367.71</v>
+        <v>105.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2477,33 +2477,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03140111099405844</v>
+        <v>0.03151571382988596</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Snap-On</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>756</v>
+        <v>215</v>
       </c>
       <c r="H20" t="n">
-        <v>78828.12</v>
+        <v>79378</v>
       </c>
       <c r="I20" t="n">
-        <v>104.27</v>
+        <v>369.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03108637138327594</v>
+        <v>0.03134881291750886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,16 +2529,16 @@
         <v>1179</v>
       </c>
       <c r="H21" t="n">
-        <v>78038.00999999999</v>
+        <v>78957.63</v>
       </c>
       <c r="I21" t="n">
-        <v>66.19</v>
+        <v>66.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.03008724809388559</v>
+        <v>0.03026384383255093</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2564,16 +2564,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>75529.85000000001</v>
+        <v>76224.94</v>
       </c>
       <c r="I22" t="n">
-        <v>77.15000000000001</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0257652200648157</v>
+        <v>0.02577349979099767</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2599,16 +2599,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>64680</v>
+        <v>64915.2</v>
       </c>
       <c r="I23" t="n">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02489522562106868</v>
+        <v>0.02465041153341246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>62496</v>
+        <v>62086.5</v>
       </c>
       <c r="I24" t="n">
-        <v>19.84</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0240688982061328</v>
+        <v>0.02400242927241819</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2669,16 +2669,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>60421.62</v>
+        <v>60454.44</v>
       </c>
       <c r="I25" t="n">
-        <v>36.82</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02252390917216579</v>
+        <v>0.02250302485818703</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2704,16 +2704,16 @@
         <v>586</v>
       </c>
       <c r="H26" t="n">
-        <v>56543.14</v>
+        <v>56677.92</v>
       </c>
       <c r="I26" t="n">
-        <v>96.48999999999999</v>
+        <v>96.72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02196140438550336</v>
+        <v>0.02183589367837374</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2739,16 +2739,16 @@
         <v>953</v>
       </c>
       <c r="H27" t="n">
-        <v>55131.05</v>
+        <v>54997.63</v>
       </c>
       <c r="I27" t="n">
-        <v>57.85</v>
+        <v>57.71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0210471573397619</v>
+        <v>0.02116969949728351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2774,16 +2774,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>52835.96</v>
+        <v>53319.7</v>
       </c>
       <c r="I28" t="n">
-        <v>73.18000000000001</v>
+        <v>73.84999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01547028581380925</v>
+        <v>0.0153044130583223</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>38836</v>
+        <v>38546.92</v>
       </c>
       <c r="I29" t="n">
-        <v>266</v>
+        <v>264.02</v>
       </c>
     </row>
   </sheetData>
@@ -2879,7 +2879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1083921907725117</v>
+        <v>0.1081822497179671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>317111.75</v>
+        <v>317691.65</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -2914,7 +2914,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03844450274747616</v>
+        <v>0.03910837312813185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2940,16 +2940,16 @@
         <v>277</v>
       </c>
       <c r="H3" t="n">
-        <v>112473.08</v>
+        <v>114846.97</v>
       </c>
       <c r="I3" t="n">
-        <v>406.04</v>
+        <v>414.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03777760613563341</v>
+        <v>0.03701560622579365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>411</v>
       </c>
       <c r="H4" t="n">
-        <v>110522.01</v>
+        <v>108701.28</v>
       </c>
       <c r="I4" t="n">
-        <v>268.91</v>
+        <v>264.48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0341723201274232</v>
+        <v>0.03430758044911007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3010,16 +3010,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>99974.39999999999</v>
+        <v>100748.8</v>
       </c>
       <c r="I5" t="n">
-        <v>156.21</v>
+        <v>157.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03324876469354922</v>
+        <v>0.03293051054895067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>97272.45</v>
+        <v>96704.85000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>205.65</v>
+        <v>204.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03154977065851859</v>
+        <v>0.03149388947131879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         <v>341</v>
       </c>
       <c r="H7" t="n">
-        <v>92301.88</v>
+        <v>92486.02</v>
       </c>
       <c r="I7" t="n">
-        <v>270.68</v>
+        <v>271.22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3098,33 +3098,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03064791678629329</v>
+        <v>0.03044799126962304</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>553</v>
+        <v>838</v>
       </c>
       <c r="H8" t="n">
-        <v>89663.42</v>
+        <v>89414.60000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>162.14</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3133,33 +3133,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03064020553679267</v>
+        <v>0.03024083912076759</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>838</v>
+        <v>553</v>
       </c>
       <c r="H9" t="n">
-        <v>89640.86</v>
+        <v>88806.27</v>
       </c>
       <c r="I9" t="n">
-        <v>106.97</v>
+        <v>160.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02755995444360598</v>
+        <v>0.02766445726962775</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>80629.28999999999</v>
+        <v>81240.38</v>
       </c>
       <c r="I10" t="n">
-        <v>69.93000000000001</v>
+        <v>70.45999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02614236632563518</v>
+        <v>0.02614243228468743</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3220,16 +3220,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>76482</v>
+        <v>76770.75</v>
       </c>
       <c r="I11" t="n">
-        <v>145.68</v>
+        <v>146.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02491347822536435</v>
+        <v>0.02514751762765762</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>72886.77</v>
+        <v>73849.05</v>
       </c>
       <c r="I12" t="n">
-        <v>245.41</v>
+        <v>248.65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02451543282339358</v>
+        <v>0.02509286321329157</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>265</v>
       </c>
       <c r="H13" t="n">
-        <v>71722.25</v>
+        <v>73688.55</v>
       </c>
       <c r="I13" t="n">
-        <v>270.65</v>
+        <v>278.07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0239978903990196</v>
+        <v>0.0247834681490878</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3325,16 +3325,16 @@
         <v>141</v>
       </c>
       <c r="H14" t="n">
-        <v>70208.13</v>
+        <v>72779.97</v>
       </c>
       <c r="I14" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02360758017329878</v>
+        <v>0.02383144954550155</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
         <v>204</v>
       </c>
       <c r="H15" t="n">
-        <v>69066.24000000001</v>
+        <v>69984.24000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>338.56</v>
+        <v>343.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0219211340092419</v>
+        <v>0.02181642812194162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3395,16 +3395,16 @@
         <v>234</v>
       </c>
       <c r="H16" t="n">
-        <v>64132.38</v>
+        <v>64066.86</v>
       </c>
       <c r="I16" t="n">
-        <v>274.07</v>
+        <v>273.79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0216728905667632</v>
+        <v>0.02156678855077807</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3430,16 +3430,16 @@
         <v>268</v>
       </c>
       <c r="H17" t="n">
-        <v>63406.12</v>
+        <v>63333.76</v>
       </c>
       <c r="I17" t="n">
-        <v>236.59</v>
+        <v>236.32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02151407847709221</v>
+        <v>0.02143901640524268</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3465,16 +3465,16 @@
         <v>426</v>
       </c>
       <c r="H18" t="n">
-        <v>62941.5</v>
+        <v>62958.54</v>
       </c>
       <c r="I18" t="n">
-        <v>147.75</v>
+        <v>147.79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02142880354245505</v>
+        <v>0.021401830971917</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3500,16 +3500,16 @@
         <v>1311</v>
       </c>
       <c r="H19" t="n">
-        <v>62692.02</v>
+        <v>62849.34</v>
       </c>
       <c r="I19" t="n">
-        <v>47.82</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02103539651174861</v>
+        <v>0.02098312707898113</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3535,16 +3535,16 @@
         <v>183</v>
       </c>
       <c r="H20" t="n">
-        <v>61541.07</v>
+        <v>61619.76</v>
       </c>
       <c r="I20" t="n">
-        <v>336.29</v>
+        <v>336.72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3553,33 +3553,33 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02007416670198995</v>
+        <v>0.01980084823582991</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1201</v>
+        <v>656</v>
       </c>
       <c r="H21" t="n">
-        <v>58728.9</v>
+        <v>58147.84</v>
       </c>
       <c r="I21" t="n">
-        <v>48.9</v>
+        <v>88.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3588,33 +3588,33 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01984640455694375</v>
+        <v>0.01924211666855472</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>656</v>
+        <v>1201</v>
       </c>
       <c r="H22" t="n">
-        <v>58062.56</v>
+        <v>56507.05</v>
       </c>
       <c r="I22" t="n">
-        <v>88.51000000000001</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01912912846531837</v>
+        <v>0.01910193916279905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3640,16 +3640,16 @@
         <v>1010</v>
       </c>
       <c r="H23" t="n">
-        <v>55964.1</v>
+        <v>56095.4</v>
       </c>
       <c r="I23" t="n">
-        <v>55.41</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01902905312716273</v>
+        <v>0.01891647511145746</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3675,16 +3675,16 @@
         <v>548</v>
       </c>
       <c r="H24" t="n">
-        <v>55671.32</v>
+        <v>55550.76</v>
       </c>
       <c r="I24" t="n">
-        <v>101.59</v>
+        <v>101.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01743361064515571</v>
+        <v>0.01743313727926559</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>51003.7</v>
+        <v>51194.74</v>
       </c>
       <c r="I25" t="n">
-        <v>128.15</v>
+        <v>128.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01710748905169204</v>
+        <v>0.01724586844040911</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,16 +3745,16 @@
         <v>480</v>
       </c>
       <c r="H26" t="n">
-        <v>50049.6</v>
+        <v>50644.8</v>
       </c>
       <c r="I26" t="n">
-        <v>104.27</v>
+        <v>105.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01689686529538524</v>
+        <v>0.01698740924723883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,16 +3780,16 @@
         <v>1740</v>
       </c>
       <c r="H27" t="n">
-        <v>49433.4</v>
+        <v>49885.8</v>
       </c>
       <c r="I27" t="n">
-        <v>28.41</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01646545575051751</v>
+        <v>0.01647014352443312</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,16 +3815,16 @@
         <v>399</v>
       </c>
       <c r="H28" t="n">
-        <v>48171.27</v>
+        <v>48366.78</v>
       </c>
       <c r="I28" t="n">
-        <v>120.73</v>
+        <v>121.22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01567016136551818</v>
+        <v>0.01569838233047097</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3850,16 +3850,16 @@
         <v>984</v>
       </c>
       <c r="H29" t="n">
-        <v>45844.56</v>
+        <v>46100.4</v>
       </c>
       <c r="I29" t="n">
-        <v>46.59</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01542512410745064</v>
+        <v>0.01547334916418026</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3885,16 +3885,16 @@
         <v>678</v>
       </c>
       <c r="H30" t="n">
-        <v>45127.68</v>
+        <v>45439.56</v>
       </c>
       <c r="I30" t="n">
-        <v>66.56</v>
+        <v>67.02</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01484817498257987</v>
+        <v>0.01471734070048959</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3920,16 +3920,16 @@
         <v>918</v>
       </c>
       <c r="H31" t="n">
-        <v>43439.76</v>
+        <v>43219.44</v>
       </c>
       <c r="I31" t="n">
-        <v>47.32</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01393193087968187</v>
+        <v>0.01415569763637433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,16 +3955,16 @@
         <v>153</v>
       </c>
       <c r="H32" t="n">
-        <v>40759.2</v>
+        <v>41570.1</v>
       </c>
       <c r="I32" t="n">
-        <v>266.4</v>
+        <v>271.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01375637690168906</v>
+        <v>0.01403974855169122</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,16 +3990,16 @@
         <v>492</v>
       </c>
       <c r="H33" t="n">
-        <v>40245.6</v>
+        <v>41229.6</v>
       </c>
       <c r="I33" t="n">
-        <v>81.8</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01350012141628951</v>
+        <v>0.01352242834473412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4025,16 +4025,16 @@
         <v>346</v>
       </c>
       <c r="H34" t="n">
-        <v>39495.9</v>
+        <v>39710.42</v>
       </c>
       <c r="I34" t="n">
-        <v>114.15</v>
+        <v>114.77</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01281594285521133</v>
+        <v>0.01264622103255169</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4060,16 +4060,16 @@
         <v>121</v>
       </c>
       <c r="H35" t="n">
-        <v>37494.27</v>
+        <v>37137.32</v>
       </c>
       <c r="I35" t="n">
-        <v>309.87</v>
+        <v>306.92</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01261560418301241</v>
+        <v>0.01262068158658625</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4095,16 +4095,16 @@
         <v>376</v>
       </c>
       <c r="H36" t="n">
-        <v>36908.16</v>
+        <v>37062.32</v>
       </c>
       <c r="I36" t="n">
-        <v>98.16</v>
+        <v>98.56999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01223600288667344</v>
+        <v>0.01230219447961879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4130,16 +4130,16 @@
         <v>464</v>
       </c>
       <c r="H37" t="n">
-        <v>35797.6</v>
+        <v>36127.04</v>
       </c>
       <c r="I37" t="n">
-        <v>77.15000000000001</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01194607904684964</v>
+        <v>0.01201940811285155</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         <v>310</v>
       </c>
       <c r="H38" t="n">
-        <v>34949.4</v>
+        <v>35296.6</v>
       </c>
       <c r="I38" t="n">
-        <v>112.74</v>
+        <v>113.86</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01174282814744569</v>
+        <v>0.01185827123510691</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4200,16 +4200,16 @@
         <v>381</v>
       </c>
       <c r="H39" t="n">
-        <v>34354.77</v>
+        <v>34823.4</v>
       </c>
       <c r="I39" t="n">
-        <v>90.17</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.01158494920099885</v>
+        <v>0.01158169606159847</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4235,16 +4235,16 @@
         <v>116</v>
       </c>
       <c r="H40" t="n">
-        <v>33892.88</v>
+        <v>34011.2</v>
       </c>
       <c r="I40" t="n">
-        <v>292.18</v>
+        <v>293.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01131184928406603</v>
+        <v>0.01131499614053001</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4270,16 +4270,16 @@
         <v>90</v>
       </c>
       <c r="H41" t="n">
-        <v>33093.9</v>
+        <v>33228</v>
       </c>
       <c r="I41" t="n">
-        <v>367.71</v>
+        <v>369.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01125155387573672</v>
+        <v>0.01125002378999392</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4305,16 +4305,16 @@
         <v>399</v>
       </c>
       <c r="H42" t="n">
-        <v>32917.5</v>
+        <v>33037.2</v>
       </c>
       <c r="I42" t="n">
-        <v>82.5</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01115385412197954</v>
+        <v>0.01124287615038305</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4340,16 +4340,16 @@
         <v>493</v>
       </c>
       <c r="H43" t="n">
-        <v>32631.67</v>
+        <v>33016.21</v>
       </c>
       <c r="I43" t="n">
-        <v>66.19</v>
+        <v>66.97</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.008872756456649544</v>
+        <v>0.008844207980049156</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4375,16 +4375,16 @@
         <v>705</v>
       </c>
       <c r="H44" t="n">
-        <v>25958.1</v>
+        <v>25972.2</v>
       </c>
       <c r="I44" t="n">
-        <v>36.82</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4393,33 +4393,33 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.008795637125429259</v>
+        <v>0.008801744394557279</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>HWC</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hormel Foods</t>
+          <t>Hancock Whitney Corp</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1297</v>
+        <v>350</v>
       </c>
       <c r="H45" t="n">
-        <v>25732.48</v>
+        <v>25847.5</v>
       </c>
       <c r="I45" t="n">
-        <v>19.84</v>
+        <v>73.84999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4428,33 +4428,33 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.008754797582418003</v>
+        <v>0.008705161020434896</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HWC</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hancock Whitney Corp</t>
+          <t>Hormel Foods</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>350</v>
+        <v>1297</v>
       </c>
       <c r="H46" t="n">
-        <v>25613</v>
+        <v>25563.87</v>
       </c>
       <c r="I46" t="n">
-        <v>73.18000000000001</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4463,7 +4463,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.008522485936890716</v>
+        <v>0.00846990526523908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4480,16 +4480,16 @@
         <v>431</v>
       </c>
       <c r="H47" t="n">
-        <v>24933.35</v>
+        <v>24873.01</v>
       </c>
       <c r="I47" t="n">
-        <v>57.85</v>
+        <v>57.71</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008476197931244715</v>
+        <v>0.008464467065878174</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4515,16 +4515,16 @@
         <v>257</v>
       </c>
       <c r="H48" t="n">
-        <v>24797.93</v>
+        <v>24857.04</v>
       </c>
       <c r="I48" t="n">
-        <v>96.48999999999999</v>
+        <v>96.72</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.00771320807595742</v>
+        <v>0.007632974215692042</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4550,16 +4550,16 @@
         <v>627</v>
       </c>
       <c r="H49" t="n">
-        <v>22565.73</v>
+        <v>22415.25</v>
       </c>
       <c r="I49" t="n">
-        <v>35.99</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.00590990708624555</v>
+        <v>0.005843867920623497</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         <v>65</v>
       </c>
       <c r="H50" t="n">
-        <v>17290</v>
+        <v>17161.3</v>
       </c>
       <c r="I50" t="n">
-        <v>266</v>
+        <v>264.02</v>
       </c>
     </row>
   </sheetData>
@@ -4655,7 +4655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07282548649541262</v>
+        <v>0.07274244415577236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>157447.23</v>
+        <v>158199.81</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05374920734111025</v>
+        <v>0.05372273216662925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4716,16 +4716,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>116204.7</v>
+        <v>116835.86</v>
       </c>
       <c r="I3" t="n">
-        <v>114.15</v>
+        <v>114.77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.04283804151564247</v>
+        <v>0.0441456215173622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4751,16 +4751,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>92614.98</v>
+        <v>96007.62</v>
       </c>
       <c r="I4" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03970156908821058</v>
+        <v>0.03909191000924864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4786,16 +4786,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>85833.99000000001</v>
+        <v>85016.84</v>
       </c>
       <c r="I5" t="n">
-        <v>309.87</v>
+        <v>306.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03844424928690014</v>
+        <v>0.03812127082158977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4821,16 +4821,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>83115.69</v>
+        <v>82905.89999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>106.97</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03676777200586134</v>
+        <v>0.03688564098339239</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4856,16 +4856,16 @@
         <v>2798</v>
       </c>
       <c r="H7" t="n">
-        <v>79491.17999999999</v>
+        <v>80218.66</v>
       </c>
       <c r="I7" t="n">
-        <v>28.41</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0343940449138056</v>
+        <v>0.03464280297187359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4891,16 +4891,16 @@
         <v>303</v>
       </c>
       <c r="H8" t="n">
-        <v>74359.23</v>
+        <v>75340.95</v>
       </c>
       <c r="I8" t="n">
-        <v>245.41</v>
+        <v>248.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03340649174153473</v>
+        <v>0.03325843718758962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4926,16 +4926,16 @@
         <v>816</v>
       </c>
       <c r="H9" t="n">
-        <v>72224.16</v>
+        <v>72330.24000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>88.51000000000001</v>
+        <v>88.64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03324558366940146</v>
+        <v>0.03316507660857635</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4961,16 +4961,16 @@
         <v>246</v>
       </c>
       <c r="H10" t="n">
-        <v>71876.28</v>
+        <v>72127.2</v>
       </c>
       <c r="I10" t="n">
-        <v>292.18</v>
+        <v>293.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03289213910736881</v>
+        <v>0.03308719335959455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4996,16 +4996,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>71112.14</v>
+        <v>71957.82000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>104.27</v>
+        <v>105.51</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03171844635975991</v>
+        <v>0.03165953611296769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>568</v>
       </c>
       <c r="H12" t="n">
-        <v>68574.64</v>
+        <v>68852.96000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>120.73</v>
+        <v>121.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5049,33 +5049,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03098132568575028</v>
+        <v>0.03107550830648668</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1076</v>
+        <v>197</v>
       </c>
       <c r="H13" t="n">
-        <v>66981</v>
+        <v>67582.82000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>62.25</v>
+        <v>343.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5084,33 +5084,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03084965007929145</v>
+        <v>0.03094226348484334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>197</v>
+        <v>1076</v>
       </c>
       <c r="H14" t="n">
-        <v>66696.32000000001</v>
+        <v>67293.03999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>338.56</v>
+        <v>62.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03047343472160764</v>
+        <v>0.0297948259193742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5136,16 +5136,16 @@
         <v>245</v>
       </c>
       <c r="H15" t="n">
-        <v>65882.95</v>
+        <v>64797.6</v>
       </c>
       <c r="I15" t="n">
-        <v>268.91</v>
+        <v>264.48</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02878064368955086</v>
+        <v>0.02857841629494137</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5171,16 +5171,16 @@
         <v>263</v>
       </c>
       <c r="H16" t="n">
-        <v>62223.17</v>
+        <v>62152.16</v>
       </c>
       <c r="I16" t="n">
-        <v>236.59</v>
+        <v>236.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02773088827069933</v>
+        <v>0.0276321748236066</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5206,16 +5206,16 @@
         <v>1082</v>
       </c>
       <c r="H17" t="n">
-        <v>59953.62</v>
+        <v>60094.28</v>
       </c>
       <c r="I17" t="n">
-        <v>55.41</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02762973098837339</v>
+        <v>0.02740745465922834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5241,16 +5241,16 @@
         <v>588</v>
       </c>
       <c r="H18" t="n">
-        <v>59734.92</v>
+        <v>59605.56</v>
       </c>
       <c r="I18" t="n">
-        <v>101.59</v>
+        <v>101.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02666761283647337</v>
+        <v>0.0265633746016306</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5276,16 +5276,16 @@
         <v>213</v>
       </c>
       <c r="H19" t="n">
-        <v>57654.84</v>
+        <v>57769.86</v>
       </c>
       <c r="I19" t="n">
-        <v>270.68</v>
+        <v>271.22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02591903507109102</v>
+        <v>0.02559449650054395</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5311,16 +5311,16 @@
         <v>1557</v>
       </c>
       <c r="H20" t="n">
-        <v>56036.43</v>
+        <v>55662.75</v>
       </c>
       <c r="I20" t="n">
-        <v>35.99</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02559804687165924</v>
+        <v>0.02556582711470137</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5346,16 +5346,16 @@
         <v>1433</v>
       </c>
       <c r="H21" t="n">
-        <v>55342.46</v>
+        <v>55600.4</v>
       </c>
       <c r="I21" t="n">
-        <v>38.62</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0247908330354929</v>
+        <v>0.02516492472290624</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
         <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>53597.28</v>
+        <v>54728.52</v>
       </c>
       <c r="I22" t="n">
-        <v>406.04</v>
+        <v>414.61</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02378537497799644</v>
+        <v>0.02429347655231171</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5416,16 +5416,16 @@
         <v>190</v>
       </c>
       <c r="H23" t="n">
-        <v>51423.5</v>
+        <v>52833.3</v>
       </c>
       <c r="I23" t="n">
-        <v>270.65</v>
+        <v>278.07</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0223264251697746</v>
+        <v>0.02245357330925883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5451,16 +5451,16 @@
         <v>443</v>
       </c>
       <c r="H24" t="n">
-        <v>48269.28</v>
+        <v>48831.89</v>
       </c>
       <c r="I24" t="n">
-        <v>108.96</v>
+        <v>110.23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0218722442359186</v>
+        <v>0.02182481482347123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5486,16 +5486,16 @@
         <v>369</v>
       </c>
       <c r="H25" t="n">
-        <v>47287.35</v>
+        <v>47464.47</v>
       </c>
       <c r="I25" t="n">
-        <v>128.15</v>
+        <v>128.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02098996494319681</v>
+        <v>0.02076046100022976</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5521,16 +5521,16 @@
         <v>959</v>
       </c>
       <c r="H26" t="n">
-        <v>45379.88</v>
+        <v>45149.72</v>
       </c>
       <c r="I26" t="n">
-        <v>47.32</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02036536150969293</v>
+        <v>0.02025084944723331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5556,16 +5556,16 @@
         <v>298</v>
       </c>
       <c r="H27" t="n">
-        <v>44029.5</v>
+        <v>44041.42</v>
       </c>
       <c r="I27" t="n">
-        <v>147.75</v>
+        <v>147.79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02015612273600393</v>
+        <v>0.02001689162509119</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5591,16 +5591,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>43577.13</v>
+        <v>43532.61</v>
       </c>
       <c r="I28" t="n">
-        <v>274.07</v>
+        <v>273.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01900191675704795</v>
+        <v>0.01896127426265179</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5626,16 +5626,16 @@
         <v>282</v>
       </c>
       <c r="H29" t="n">
-        <v>41081.76</v>
+        <v>41236.86</v>
       </c>
       <c r="I29" t="n">
-        <v>145.68</v>
+        <v>146.23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5644,33 +5644,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01850274465331611</v>
+        <v>0.01864967689280285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>601</v>
+        <v>484</v>
       </c>
       <c r="H30" t="n">
-        <v>40002.56</v>
+        <v>40559.2</v>
       </c>
       <c r="I30" t="n">
-        <v>66.56</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5679,33 +5679,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01831247460458453</v>
+        <v>0.01852084628293319</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>484</v>
+        <v>601</v>
       </c>
       <c r="H31" t="n">
-        <v>39591.2</v>
+        <v>40279.02</v>
       </c>
       <c r="I31" t="n">
-        <v>81.8</v>
+        <v>67.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01823661820631542</v>
+        <v>0.01848984564149764</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5731,16 +5731,16 @@
         <v>148</v>
       </c>
       <c r="H32" t="n">
-        <v>39427.2</v>
+        <v>40211.6</v>
       </c>
       <c r="I32" t="n">
-        <v>266.4</v>
+        <v>271.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01777429196042577</v>
+        <v>0.01780643369618721</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5766,16 +5766,16 @@
         <v>246</v>
       </c>
       <c r="H33" t="n">
-        <v>38427.66</v>
+        <v>38725.32</v>
       </c>
       <c r="I33" t="n">
-        <v>156.21</v>
+        <v>157.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01660250487355388</v>
+        <v>0.01654402430656285</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5801,16 +5801,16 @@
         <v>372</v>
       </c>
       <c r="H34" t="n">
-        <v>35894.28</v>
+        <v>35979.84</v>
       </c>
       <c r="I34" t="n">
-        <v>96.48999999999999</v>
+        <v>96.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5819,7 +5819,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01639042148492979</v>
+        <v>0.01636190588393783</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5836,16 +5836,16 @@
         <v>361</v>
       </c>
       <c r="H35" t="n">
-        <v>35435.76</v>
+        <v>35583.77</v>
       </c>
       <c r="I35" t="n">
-        <v>98.16</v>
+        <v>98.56999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01627930111224583</v>
+        <v>0.01622399395297129</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         <v>736</v>
       </c>
       <c r="H36" t="n">
-        <v>35195.52</v>
+        <v>35283.84</v>
       </c>
       <c r="I36" t="n">
-        <v>47.82</v>
+        <v>47.94</v>
       </c>
     </row>
   </sheetData>
@@ -5941,7 +5941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1063116570438224</v>
+        <v>0.1058777926067169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5967,16 +5967,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>221273.9</v>
+        <v>221603.23</v>
       </c>
       <c r="I2" t="n">
-        <v>52.81</v>
+        <v>52.89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09935138588473787</v>
+        <v>0.09892214824782883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -6002,16 +6002,16 @@
         <v>4300</v>
       </c>
       <c r="H3" t="n">
-        <v>206787</v>
+        <v>207045</v>
       </c>
       <c r="I3" t="n">
-        <v>48.09</v>
+        <v>48.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.09899959837031574</v>
+        <v>0.0988470410889766</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6037,16 +6037,16 @@
         <v>980</v>
       </c>
       <c r="H4" t="n">
-        <v>206054.8</v>
+        <v>206887.8</v>
       </c>
       <c r="I4" t="n">
-        <v>210.26</v>
+        <v>211.11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05461702951564509</v>
+        <v>0.05483479544961845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6072,16 +6072,16 @@
         <v>1475</v>
       </c>
       <c r="H5" t="n">
-        <v>113678.25</v>
+        <v>114769.75</v>
       </c>
       <c r="I5" t="n">
-        <v>77.06999999999999</v>
+        <v>77.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04497196908847627</v>
+        <v>0.04643473340307852</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>93603.31</v>
+        <v>97188.34</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6116,7 +6116,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03798907340869504</v>
+        <v>0.03781659781636734</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6142,16 +6142,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>79069.32000000001</v>
+        <v>79150.5</v>
       </c>
       <c r="I7" t="n">
-        <v>29.22</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03709864069054591</v>
+        <v>0.03709863644482003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1270</v>
       </c>
       <c r="H8" t="n">
-        <v>77216</v>
+        <v>77647.8</v>
       </c>
       <c r="I8" t="n">
-        <v>60.8</v>
+        <v>61.14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02867720697394869</v>
+        <v>0.02911963315752493</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6212,16 +6212,16 @@
         <v>147</v>
       </c>
       <c r="H9" t="n">
-        <v>59687.88</v>
+        <v>60947.67</v>
       </c>
       <c r="I9" t="n">
-        <v>406.04</v>
+        <v>414.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6230,33 +6230,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02520178944055725</v>
+        <v>0.02589469802416668</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SPDR® S&amp;P Oil &amp; Gas Explor &amp; Prodtn ETF</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>285</v>
+        <v>105</v>
       </c>
       <c r="H10" t="n">
-        <v>52454.25</v>
+        <v>54197.85</v>
       </c>
       <c r="I10" t="n">
-        <v>184.05</v>
+        <v>516.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6265,33 +6265,33 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02511934374610923</v>
+        <v>0.0247144119562876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>SPDR® S&amp;P Oil &amp; Gas Explor &amp; Prodtn ETF</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>105</v>
+        <v>285</v>
       </c>
       <c r="H11" t="n">
-        <v>52282.65</v>
+        <v>51727.5</v>
       </c>
       <c r="I11" t="n">
-        <v>497.93</v>
+        <v>181.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02311646589170212</v>
+        <v>0.02293281472572744</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6317,16 +6317,16 @@
         <v>1860</v>
       </c>
       <c r="H12" t="n">
-        <v>48113.92</v>
+        <v>47998.6</v>
       </c>
       <c r="I12" t="n">
-        <v>25.87</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02063916975917296</v>
+        <v>0.02068337442933968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6352,16 +6352,16 @@
         <v>275</v>
       </c>
       <c r="H13" t="n">
-        <v>42957.75</v>
+        <v>43290.5</v>
       </c>
       <c r="I13" t="n">
-        <v>156.21</v>
+        <v>157.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02054773479349463</v>
+        <v>0.02047423061435258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6387,16 +6387,16 @@
         <v>158</v>
       </c>
       <c r="H14" t="n">
-        <v>42767.44</v>
+        <v>42852.76</v>
       </c>
       <c r="I14" t="n">
-        <v>270.68</v>
+        <v>271.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6405,33 +6405,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02041337137327708</v>
+        <v>0.02037248239202962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>CEF</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Sprott Physical Gold and Silver Trust</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>158</v>
+        <v>980</v>
       </c>
       <c r="H15" t="n">
-        <v>42487.78</v>
+        <v>42639.8</v>
       </c>
       <c r="I15" t="n">
-        <v>268.91</v>
+        <v>43.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6440,33 +6440,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02024157107362253</v>
+        <v>0.01996543216902872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sprott Physical Gold and Silver Trust</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>980</v>
+        <v>158</v>
       </c>
       <c r="H16" t="n">
-        <v>42130.2</v>
+        <v>41787.84</v>
       </c>
       <c r="I16" t="n">
-        <v>42.99</v>
+        <v>264.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01995863244040322</v>
+        <v>0.01973182597151469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6492,16 +6492,16 @@
         <v>202</v>
       </c>
       <c r="H17" t="n">
-        <v>41541.3</v>
+        <v>41298.9</v>
       </c>
       <c r="I17" t="n">
-        <v>205.65</v>
+        <v>204.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01820675752393594</v>
+        <v>0.01833086723532087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6527,16 +6527,16 @@
         <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>37895</v>
+        <v>38366.68</v>
       </c>
       <c r="I18" t="n">
-        <v>1722.5</v>
+        <v>1743.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01744973692952996</v>
+        <v>0.01718681129375072</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6562,16 +6562,16 @@
         <v>224</v>
       </c>
       <c r="H19" t="n">
-        <v>36319.36</v>
+        <v>35972.16</v>
       </c>
       <c r="I19" t="n">
-        <v>162.14</v>
+        <v>160.59</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01639585418077937</v>
+        <v>0.01642824810057961</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6597,16 +6597,16 @@
         <v>488</v>
       </c>
       <c r="H20" t="n">
-        <v>34125.84</v>
+        <v>34384.48</v>
       </c>
       <c r="I20" t="n">
-        <v>69.93000000000001</v>
+        <v>70.45999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01610354671864551</v>
+        <v>0.01622684433631392</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6632,16 +6632,16 @@
         <v>99</v>
       </c>
       <c r="H21" t="n">
-        <v>33517.44</v>
+        <v>33962.94</v>
       </c>
       <c r="I21" t="n">
-        <v>338.56</v>
+        <v>343.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01572657387029003</v>
+        <v>0.0155996422261888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6667,16 +6667,16 @@
         <v>306</v>
       </c>
       <c r="H22" t="n">
-        <v>32732.82</v>
+        <v>32650.2</v>
       </c>
       <c r="I22" t="n">
-        <v>106.97</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01485639704070693</v>
+        <v>0.0149688280923937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>126</v>
       </c>
       <c r="H23" t="n">
-        <v>30921.66</v>
+        <v>31329.9</v>
       </c>
       <c r="I23" t="n">
-        <v>245.41</v>
+        <v>248.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0140684641154106</v>
+        <v>0.01404304635897646</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6737,16 +6737,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>29281.68</v>
+        <v>29392.23</v>
       </c>
       <c r="I24" t="n">
-        <v>145.68</v>
+        <v>146.23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6755,33 +6755,33 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01357200266443729</v>
+        <v>0.01368422334090269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="H25" t="n">
-        <v>28248.36</v>
+        <v>28641.21</v>
       </c>
       <c r="I25" t="n">
-        <v>336.29</v>
+        <v>278.07</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6790,33 +6790,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01339355770304489</v>
+        <v>0.01351378455733174</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="H26" t="n">
-        <v>27876.95</v>
+        <v>28284.48</v>
       </c>
       <c r="I26" t="n">
-        <v>270.65</v>
+        <v>336.72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0130875333144746</v>
+        <v>0.01316644739230381</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6842,16 +6842,16 @@
         <v>250</v>
       </c>
       <c r="H27" t="n">
-        <v>27240</v>
+        <v>27557.5</v>
       </c>
       <c r="I27" t="n">
-        <v>108.96</v>
+        <v>110.23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0123819884292945</v>
+        <v>0.01237049306521556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6877,16 +6877,16 @@
         <v>414</v>
       </c>
       <c r="H28" t="n">
-        <v>25771.5</v>
+        <v>25891.56</v>
       </c>
       <c r="I28" t="n">
-        <v>62.25</v>
+        <v>62.54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01172937022069011</v>
+        <v>0.01172923464075563</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>524</v>
       </c>
       <c r="H29" t="n">
-        <v>24413.16</v>
+        <v>24549.4</v>
       </c>
       <c r="I29" t="n">
-        <v>46.59</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0114345403815408</v>
+        <v>0.01125339352251591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -6947,16 +6947,16 @@
         <v>259</v>
       </c>
       <c r="H30" t="n">
-        <v>23799.51</v>
+        <v>23553.46</v>
       </c>
       <c r="I30" t="n">
-        <v>91.89</v>
+        <v>90.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01063121855418637</v>
+        <v>0.01058762493743817</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6982,16 +6982,16 @@
         <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>22127.5</v>
+        <v>22160</v>
       </c>
       <c r="I31" t="n">
-        <v>88.51000000000001</v>
+        <v>88.64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.009761839276192914</v>
+        <v>0.009686530143574979</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         <v>200</v>
       </c>
       <c r="H32" t="n">
-        <v>20318</v>
+        <v>20274</v>
       </c>
       <c r="I32" t="n">
-        <v>101.59</v>
+        <v>101.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.008872280982075816</v>
+        <v>0.008903686124622251</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7052,16 +7052,16 @@
         <v>650</v>
       </c>
       <c r="H33" t="n">
-        <v>18466.5</v>
+        <v>18635.5</v>
       </c>
       <c r="I33" t="n">
-        <v>28.41</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7070,33 +7070,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.008813665744764292</v>
+        <v>0.008821866144002382</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>475</v>
+        <v>175</v>
       </c>
       <c r="H34" t="n">
-        <v>18344.5</v>
+        <v>18464.25</v>
       </c>
       <c r="I34" t="n">
-        <v>38.62</v>
+        <v>105.51</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7105,33 +7105,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.00876694171338277</v>
+        <v>0.008805502147878409</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>175</v>
+        <v>475</v>
       </c>
       <c r="H35" t="n">
-        <v>18247.25</v>
+        <v>18430</v>
       </c>
       <c r="I35" t="n">
-        <v>104.27</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.008571104361902851</v>
+        <v>0.008480209793979248</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -7157,16 +7157,16 @@
         <v>377</v>
       </c>
       <c r="H36" t="n">
-        <v>17839.64</v>
+        <v>17749.16</v>
       </c>
       <c r="I36" t="n">
-        <v>47.32</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7175,33 +7175,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.008504878752796126</v>
+        <v>0.008335790958697685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>362</v>
+        <v>177</v>
       </c>
       <c r="H37" t="n">
-        <v>17701.8</v>
+        <v>17446.89</v>
       </c>
       <c r="I37" t="n">
-        <v>48.9</v>
+        <v>98.56999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7210,33 +7210,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008347540081363522</v>
+        <v>0.008137612215565916</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>177</v>
+        <v>362</v>
       </c>
       <c r="H38" t="n">
-        <v>17374.32</v>
+        <v>17032.1</v>
       </c>
       <c r="I38" t="n">
-        <v>98.16</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.008127242879625162</v>
+        <v>0.008112318494257796</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7262,16 +7262,16 @@
         <v>132</v>
       </c>
       <c r="H39" t="n">
-        <v>16915.8</v>
+        <v>16979.16</v>
       </c>
       <c r="I39" t="n">
-        <v>128.15</v>
+        <v>128.63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.007926461669194954</v>
+        <v>0.007902161783744187</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7297,16 +7297,16 @@
         <v>345</v>
       </c>
       <c r="H40" t="n">
-        <v>16497.9</v>
+        <v>16539.3</v>
       </c>
       <c r="I40" t="n">
-        <v>47.82</v>
+        <v>47.94</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.007515049966655136</v>
+        <v>0.007524905978211644</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7332,16 +7332,16 @@
         <v>235</v>
       </c>
       <c r="H41" t="n">
-        <v>15641.6</v>
+        <v>15749.7</v>
       </c>
       <c r="I41" t="n">
-        <v>66.56</v>
+        <v>67.02</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.007241153454470273</v>
+        <v>0.007217778854462365</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7367,16 +7367,16 @@
         <v>272</v>
       </c>
       <c r="H42" t="n">
-        <v>15071.52</v>
+        <v>15106.88</v>
       </c>
       <c r="I42" t="n">
-        <v>55.41</v>
+        <v>55.54</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.007110595220150328</v>
+        <v>0.007063828290051655</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7402,16 +7402,16 @@
         <v>54</v>
       </c>
       <c r="H43" t="n">
-        <v>14799.78</v>
+        <v>14784.66</v>
       </c>
       <c r="I43" t="n">
-        <v>274.07</v>
+        <v>273.79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7420,7 +7420,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.006838380292642434</v>
+        <v>0.006966618986361621</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7437,16 +7437,16 @@
         <v>174</v>
       </c>
       <c r="H44" t="n">
-        <v>14233.2</v>
+        <v>14581.2</v>
       </c>
       <c r="I44" t="n">
-        <v>81.8</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.004755161126897348</v>
+        <v>0.004697183558943549</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7472,16 +7472,16 @@
         <v>275</v>
       </c>
       <c r="H45" t="n">
-        <v>9897.25</v>
+        <v>9831.25</v>
       </c>
       <c r="I45" t="n">
-        <v>35.99</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.004070981976170061</v>
+        <v>0.004062475510742297</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7507,16 +7507,16 @@
         <v>29</v>
       </c>
       <c r="H46" t="n">
-        <v>8473.219999999999</v>
+        <v>8502.799999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>292.18</v>
+        <v>293.2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/24/2026</t>
+          <t>09/25/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.002484541360223083</v>
+        <v>0.002471393417537887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7542,261 +7542,13 @@
         <v>35</v>
       </c>
       <c r="H47" t="n">
-        <v>5171.25</v>
+        <v>5172.65</v>
       </c>
       <c r="I47" t="n">
-        <v>147.75</v>
+        <v>147.79</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
-    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
-    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
-                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA71D68D-ADE0-40B7-9E76-C920E4478FDB}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9543BD6-9640-4573-B3D2-51B4B063FD13}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AB248A9-D2E1-479D-A485-E992A1201700}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -7551,4 +7551,252 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100816A82F3E39F6D48966CE5F2A60D183C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ee6fa4220ecdfcc2f6fea1f3e0d62b76">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="db58b361-de72-439a-9b19-5afb42a4fe9e" xmlns:ns3="e26837be-2e64-4fb1-8d10-81cb111b0084" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54ce9d38be15445670b4f969d736cc65" ns2:_="" ns3:_="">
+    <xsd:import namespace="db58b361-de72-439a-9b19-5afb42a4fe9e"/>
+    <xsd:import namespace="e26837be-2e64-4fb1-8d10-81cb111b0084"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MigrationWizId" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdPermissions" minOccurs="0"/>
+                <xsd:element ref="ns2:MigrationWizIdVersion" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="db58b361-de72-439a-9b19-5afb42a4fe9e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MigrationWizId" ma:index="8" nillable="true" ma:displayName="MigrationWizId" ma:internalName="MigrationWizId">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdPermissions" ma:index="9" nillable="true" ma:displayName="MigrationWizIdPermissions" ma:internalName="MigrationWizIdPermissions">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MigrationWizIdVersion" ma:index="10" nillable="true" ma:displayName="MigrationWizIdVersion" ma:internalName="MigrationWizIdVersion">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="13" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="96639c25-1a56-4197-b479-8befda008741" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e26837be-2e64-4fb1-8d10-81cb111b0084" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{b3bc2a0c-107b-4c5c-910e-cb5bd0310dcf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e26837be-2e64-4fb1-8d10-81cb111b0084">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <MigrationWizIdPermissions xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <TaxCatchAll xmlns="e26837be-2e64-4fb1-8d10-81cb111b0084" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <MigrationWizId xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+    <MigrationWizIdVersion xmlns="db58b361-de72-439a-9b19-5afb42a4fe9e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8002310C-09B6-4F3A-9A17-A3AC87D9AF34}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DA27D83-C0F5-409E-AC88-50C71A081BA0}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECA3CFED-5911-47DA-88D2-A850AFBD80E2}"/>
 </file>
--- a/data/Tamarac_Holdings.xlsx
+++ b/data/Tamarac_Holdings.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1104877826114799</v>
+        <v>0.1106858129191776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -517,7 +517,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.04803466972814616</v>
+        <v>0.04852930436291106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         <v>269</v>
       </c>
       <c r="H3" t="n">
-        <v>111530.09</v>
+        <v>112476.97</v>
       </c>
       <c r="I3" t="n">
-        <v>414.61</v>
+        <v>418.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03964010867825565</v>
+        <v>0.03952497315682901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -578,16 +578,16 @@
         <v>348</v>
       </c>
       <c r="H4" t="n">
-        <v>92039.03999999999</v>
+        <v>91607.52</v>
       </c>
       <c r="I4" t="n">
-        <v>264.48</v>
+        <v>263.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03819726085973186</v>
+        <v>0.03836871666376172</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -613,16 +613,16 @@
         <v>327</v>
       </c>
       <c r="H5" t="n">
-        <v>88688.94</v>
+        <v>88927.64999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>271.22</v>
+        <v>271.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -631,33 +631,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03803518435721943</v>
+        <v>0.03819832451255956</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CFR</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cullen/Frost Bankers</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>561</v>
+        <v>429</v>
       </c>
       <c r="H6" t="n">
-        <v>88312.62</v>
+        <v>88532.73</v>
       </c>
       <c r="I6" t="n">
-        <v>157.42</v>
+        <v>206.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,33 +666,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03777523401011743</v>
+        <v>0.0378613068552479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CFR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Cullen/Frost Bankers</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>429</v>
+        <v>561</v>
       </c>
       <c r="H7" t="n">
-        <v>87709.05</v>
+        <v>87751.62</v>
       </c>
       <c r="I7" t="n">
-        <v>204.45</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03605251221830588</v>
+        <v>0.03668603592355132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -718,16 +718,16 @@
         <v>48</v>
       </c>
       <c r="H8" t="n">
-        <v>83709.12</v>
+        <v>85027.67999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1743.94</v>
+        <v>1771.41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03271465880021378</v>
+        <v>0.03316716963315712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -753,16 +753,16 @@
         <v>473</v>
       </c>
       <c r="H9" t="n">
-        <v>75959.07000000001</v>
+        <v>76871.96000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>160.59</v>
+        <v>162.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0317118578165965</v>
+        <v>0.03143955665698452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -788,16 +788,16 @@
         <v>1045</v>
       </c>
       <c r="H10" t="n">
-        <v>73630.7</v>
+        <v>72867.85000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>70.45999999999999</v>
+        <v>69.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03083540776713651</v>
+        <v>0.03090225530528402</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -823,16 +823,16 @@
         <v>671</v>
       </c>
       <c r="H11" t="n">
-        <v>71595.7</v>
+        <v>71622.53999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>106.7</v>
+        <v>106.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0306785339754828</v>
+        <v>0.03031970675188047</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -858,16 +858,16 @@
         <v>138</v>
       </c>
       <c r="H12" t="n">
-        <v>71231.46000000001</v>
+        <v>70272.36</v>
       </c>
       <c r="I12" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,33 +876,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02827914536980978</v>
+        <v>0.02870550733001001</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>RGA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Reinsurance Group of America</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>195</v>
+        <v>263</v>
       </c>
       <c r="H13" t="n">
-        <v>65660.39999999999</v>
+        <v>66531.11</v>
       </c>
       <c r="I13" t="n">
-        <v>336.72</v>
+        <v>252.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,33 +911,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02816481924419349</v>
+        <v>0.02811444607240505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>RGA</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reinsurance Group of America</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>263</v>
+        <v>195</v>
       </c>
       <c r="H14" t="n">
-        <v>65394.95</v>
+        <v>65161.2</v>
       </c>
       <c r="I14" t="n">
-        <v>248.65</v>
+        <v>334.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,33 +946,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02762959036460361</v>
+        <v>0.02809930614384816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>187</v>
+        <v>437</v>
       </c>
       <c r="H15" t="n">
-        <v>64152.22</v>
+        <v>65126.11</v>
       </c>
       <c r="I15" t="n">
-        <v>343.06</v>
+        <v>149.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -981,33 +981,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0275220432678711</v>
+        <v>0.02715709260198588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>437</v>
+        <v>187</v>
       </c>
       <c r="H16" t="n">
-        <v>63902.51</v>
+        <v>62942.33</v>
       </c>
       <c r="I16" t="n">
-        <v>146.23</v>
+        <v>336.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02682655538906546</v>
+        <v>0.02689783265127215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>224</v>
       </c>
       <c r="H17" t="n">
-        <v>62287.68</v>
+        <v>62341.44</v>
       </c>
       <c r="I17" t="n">
-        <v>278.07</v>
+        <v>278.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02511654750657089</v>
+        <v>0.0251900538875749</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1068,16 +1068,16 @@
         <v>213</v>
       </c>
       <c r="H18" t="n">
-        <v>58317.27</v>
+        <v>58383.3</v>
       </c>
       <c r="I18" t="n">
-        <v>273.79</v>
+        <v>274.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.02418783347013204</v>
+        <v>0.02422731148276772</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1103,16 +1103,16 @@
         <v>898</v>
       </c>
       <c r="H19" t="n">
-        <v>56160.92</v>
+        <v>56151.94</v>
       </c>
       <c r="I19" t="n">
-        <v>62.54</v>
+        <v>62.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02370872754186654</v>
+        <v>0.02358968275610763</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1138,16 +1138,16 @@
         <v>1170</v>
       </c>
       <c r="H20" t="n">
-        <v>55048.5</v>
+        <v>54674.1</v>
       </c>
       <c r="I20" t="n">
-        <v>47.05</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02246893618762722</v>
+        <v>0.02251377704375132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1173,16 +1173,16 @@
         <v>353</v>
       </c>
       <c r="H21" t="n">
-        <v>52169.87</v>
+        <v>52180.46</v>
       </c>
       <c r="I21" t="n">
-        <v>147.79</v>
+        <v>147.82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02177672153750752</v>
+        <v>0.02167181752866239</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1208,16 +1208,16 @@
         <v>556</v>
       </c>
       <c r="H22" t="n">
-        <v>50562.64</v>
+        <v>50229.04</v>
       </c>
       <c r="I22" t="n">
-        <v>90.94</v>
+        <v>90.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02169595461968185</v>
+        <v>0.02144696219188784</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
         <v>457</v>
       </c>
       <c r="H23" t="n">
-        <v>50375.11</v>
+        <v>49707.89</v>
       </c>
       <c r="I23" t="n">
-        <v>110.23</v>
+        <v>108.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02118778155930921</v>
+        <v>0.02143169282535527</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1278,16 +1278,16 @@
         <v>555</v>
       </c>
       <c r="H24" t="n">
-        <v>49195.2</v>
+        <v>49672.5</v>
       </c>
       <c r="I24" t="n">
-        <v>88.64</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02066723483312772</v>
+        <v>0.02063344882925703</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         <v>864</v>
       </c>
       <c r="H25" t="n">
-        <v>47986.56</v>
+        <v>47822.4</v>
       </c>
       <c r="I25" t="n">
-        <v>55.54</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01935824484033963</v>
+        <v>0.01908047788448851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         <v>426</v>
       </c>
       <c r="H26" t="n">
-        <v>44947.26</v>
+        <v>44223.06</v>
       </c>
       <c r="I26" t="n">
-        <v>105.51</v>
+        <v>103.81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1366,33 +1366,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01892671270689643</v>
+        <v>0.01863685942499535</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>938</v>
+        <v>1504</v>
       </c>
       <c r="H27" t="n">
-        <v>43945.3</v>
+        <v>43194.88</v>
       </c>
       <c r="I27" t="n">
-        <v>46.85</v>
+        <v>28.72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01865464710677658</v>
+        <v>0.01852930509639291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1418,16 +1418,16 @@
         <v>920</v>
       </c>
       <c r="H28" t="n">
-        <v>43313.6</v>
+        <v>42945.6</v>
       </c>
       <c r="I28" t="n">
-        <v>47.08</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1436,33 +1436,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01859866628248724</v>
+        <v>0.01835150046378274</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>426</v>
+        <v>331</v>
       </c>
       <c r="H29" t="n">
-        <v>43183.62</v>
+        <v>42533.5</v>
       </c>
       <c r="I29" t="n">
-        <v>101.37</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,33 +1471,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01857112809272681</v>
+        <v>0.01825153120055591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1504</v>
+        <v>426</v>
       </c>
       <c r="H30" t="n">
-        <v>43119.68</v>
+        <v>42301.8</v>
       </c>
       <c r="I30" t="n">
-        <v>28.67</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1506,33 +1506,33 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01833719991367807</v>
+        <v>0.01815487123490762</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>331</v>
+        <v>1087</v>
       </c>
       <c r="H31" t="n">
-        <v>42576.53</v>
+        <v>42077.77</v>
       </c>
       <c r="I31" t="n">
-        <v>128.63</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1541,33 +1541,33 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01816452417985497</v>
+        <v>0.01788006146871399</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1087</v>
+        <v>938</v>
       </c>
       <c r="H32" t="n">
-        <v>42175.6</v>
+        <v>41440.84</v>
       </c>
       <c r="I32" t="n">
-        <v>38.8</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01616423690235522</v>
+        <v>0.01612313942024533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         <v>560</v>
       </c>
       <c r="H33" t="n">
-        <v>37531.2</v>
+        <v>37368.8</v>
       </c>
       <c r="I33" t="n">
-        <v>67.02</v>
+        <v>66.73</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01575003134654827</v>
+        <v>0.015703026897138</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1628,16 +1628,16 @@
         <v>371</v>
       </c>
       <c r="H34" t="n">
-        <v>36569.47</v>
+        <v>36395.1</v>
       </c>
       <c r="I34" t="n">
-        <v>98.56999999999999</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01346218662210849</v>
+        <v>0.01310329104294084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         <v>373</v>
       </c>
       <c r="H35" t="n">
-        <v>31257.4</v>
+        <v>30369.66</v>
       </c>
       <c r="I35" t="n">
-        <v>83.8</v>
+        <v>81.42</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1681,33 +1681,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01098616139638589</v>
+        <v>0.01091426188561731</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>87</v>
+        <v>522</v>
       </c>
       <c r="H36" t="n">
-        <v>25508.4</v>
+        <v>25296.12</v>
       </c>
       <c r="I36" t="n">
-        <v>293.2</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1716,33 +1716,33 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01077782900428525</v>
+        <v>0.01088160468434999</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>522</v>
+        <v>87</v>
       </c>
       <c r="H37" t="n">
-        <v>25024.68</v>
+        <v>25220.43</v>
       </c>
       <c r="I37" t="n">
-        <v>47.94</v>
+        <v>289.89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008853329891504657</v>
+        <v>0.009027975209641954</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         <v>575</v>
       </c>
       <c r="H38" t="n">
-        <v>20556.25</v>
+        <v>20924.25</v>
       </c>
       <c r="I38" t="n">
-        <v>35.75</v>
+        <v>36.39</v>
       </c>
     </row>
   </sheetData>
@@ -1838,7 +1838,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06068846235277696</v>
+        <v>0.06070095344739634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1864,16 +1864,16 @@
         <v>971</v>
       </c>
       <c r="H2" t="n">
-        <v>152854.82</v>
+        <v>151883.82</v>
       </c>
       <c r="I2" t="n">
-        <v>157.42</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05611598005028078</v>
+        <v>0.05610217655843052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         <v>3004</v>
       </c>
       <c r="H3" t="n">
-        <v>141338.2</v>
+        <v>140376.92</v>
       </c>
       <c r="I3" t="n">
-        <v>47.05</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05216776917668535</v>
+        <v>0.05280095582493709</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1934,16 +1934,16 @@
         <v>556</v>
       </c>
       <c r="H4" t="n">
-        <v>131393.92</v>
+        <v>132116.72</v>
       </c>
       <c r="I4" t="n">
-        <v>236.32</v>
+        <v>237.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05182115905582704</v>
+        <v>0.05216318821077414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04982342219360723</v>
+        <v>0.04963266395856156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2004,16 +2004,16 @@
         <v>1781</v>
       </c>
       <c r="H6" t="n">
-        <v>125489.26</v>
+        <v>124189.13</v>
       </c>
       <c r="I6" t="n">
-        <v>70.45999999999999</v>
+        <v>69.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04442505492341096</v>
+        <v>0.04549519551927607</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2039,16 +2039,16 @@
         <v>450</v>
       </c>
       <c r="H7" t="n">
-        <v>111892.5</v>
+        <v>113836.5</v>
       </c>
       <c r="I7" t="n">
-        <v>248.65</v>
+        <v>252.97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.04407076220709032</v>
+        <v>0.04345576192166137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2074,16 +2074,16 @@
         <v>1095</v>
       </c>
       <c r="H8" t="n">
-        <v>111000.15</v>
+        <v>108733.5</v>
       </c>
       <c r="I8" t="n">
-        <v>101.37</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04125032458469537</v>
+        <v>0.04153101299290254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2109,16 +2109,16 @@
         <v>703</v>
       </c>
       <c r="H9" t="n">
-        <v>103896.37</v>
+        <v>103917.46</v>
       </c>
       <c r="I9" t="n">
-        <v>147.79</v>
+        <v>147.82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03886697701493694</v>
+        <v>0.03954787463662823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>2042</v>
       </c>
       <c r="H10" t="n">
-        <v>97893.48</v>
+        <v>98955.32000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>47.94</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03831019331609747</v>
+        <v>0.03885572212652889</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
         <v>796</v>
       </c>
       <c r="H11" t="n">
-        <v>96491.12</v>
+        <v>97223.44</v>
       </c>
       <c r="I11" t="n">
-        <v>121.22</v>
+        <v>122.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03663628480069835</v>
+        <v>0.03683631917988665</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2214,16 +2214,16 @@
         <v>804</v>
       </c>
       <c r="H12" t="n">
-        <v>92275.08</v>
+        <v>92170.56</v>
       </c>
       <c r="I12" t="n">
-        <v>114.77</v>
+        <v>114.64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2232,33 +2232,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03599964975305359</v>
+        <v>0.03581855668840681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1082</v>
+        <v>295</v>
       </c>
       <c r="H13" t="n">
-        <v>90671.60000000001</v>
+        <v>89623.95</v>
       </c>
       <c r="I13" t="n">
-        <v>83.8</v>
+        <v>303.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2267,33 +2267,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03594795600994276</v>
+        <v>0.0354396488695625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="H14" t="n">
-        <v>90541.39999999999</v>
+        <v>88675.86</v>
       </c>
       <c r="I14" t="n">
-        <v>306.92</v>
+        <v>271.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2302,33 +2302,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03527478595276606</v>
+        <v>0.03520808143567462</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>327</v>
+        <v>1082</v>
       </c>
       <c r="H15" t="n">
-        <v>88845.89999999999</v>
+        <v>88096.44</v>
       </c>
       <c r="I15" t="n">
-        <v>271.7</v>
+        <v>81.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2337,33 +2337,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03344462098929707</v>
+        <v>0.03226977037740165</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1798</v>
+        <v>910</v>
       </c>
       <c r="H16" t="n">
-        <v>84236.3</v>
+        <v>80744.3</v>
       </c>
       <c r="I16" t="n">
-        <v>46.85</v>
+        <v>88.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2372,33 +2372,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03302285245391588</v>
+        <v>0.03225150619644711</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>ALSN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Allison Transmission</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>910</v>
+        <v>710</v>
       </c>
       <c r="H17" t="n">
-        <v>83174</v>
+        <v>80698.60000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>91.40000000000001</v>
+        <v>113.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2407,33 +2407,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03209641481816472</v>
+        <v>0.03174675936978761</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ALSN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Allison Transmission</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>710</v>
+        <v>1798</v>
       </c>
       <c r="H18" t="n">
-        <v>80840.60000000001</v>
+        <v>79435.64</v>
       </c>
       <c r="I18" t="n">
-        <v>113.86</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2442,33 +2442,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.03166958807781247</v>
+        <v>0.03172458257763953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Snap-On</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>756</v>
+        <v>215</v>
       </c>
       <c r="H19" t="n">
-        <v>79765.56</v>
+        <v>79380.14999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>105.51</v>
+        <v>369.21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2477,33 +2477,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03151571382988596</v>
+        <v>0.03136497803976029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Snap-On</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>215</v>
+        <v>756</v>
       </c>
       <c r="H20" t="n">
-        <v>79378</v>
+        <v>78480.36</v>
       </c>
       <c r="I20" t="n">
-        <v>369.2</v>
+        <v>103.81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03134881291750886</v>
+        <v>0.03132012488815138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2529,16 +2529,16 @@
         <v>1179</v>
       </c>
       <c r="H21" t="n">
-        <v>78957.63</v>
+        <v>78368.13</v>
       </c>
       <c r="I21" t="n">
-        <v>66.97</v>
+        <v>66.47</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.03026384383255093</v>
+        <v>0.03061618258947088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2564,16 +2564,16 @@
         <v>979</v>
       </c>
       <c r="H22" t="n">
-        <v>76224.94</v>
+        <v>76606.75</v>
       </c>
       <c r="I22" t="n">
-        <v>77.86</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02577349979099767</v>
+        <v>0.02548928312014685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2599,16 +2599,16 @@
         <v>784</v>
       </c>
       <c r="H23" t="n">
-        <v>64915.2</v>
+        <v>63778.4</v>
       </c>
       <c r="I23" t="n">
-        <v>82.8</v>
+        <v>81.34999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02465041153341246</v>
+        <v>0.02514042527429973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         <v>3150</v>
       </c>
       <c r="H24" t="n">
-        <v>62086.5</v>
+        <v>62905.5</v>
       </c>
       <c r="I24" t="n">
-        <v>19.71</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02400242927241819</v>
+        <v>0.02401656667520501</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2669,16 +2669,16 @@
         <v>1641</v>
       </c>
       <c r="H25" t="n">
-        <v>60454.44</v>
+        <v>60093.42</v>
       </c>
       <c r="I25" t="n">
-        <v>36.84</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02250302485818703</v>
+        <v>0.02258831571763738</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2704,16 +2704,16 @@
         <v>586</v>
       </c>
       <c r="H26" t="n">
-        <v>56677.92</v>
+        <v>56519.7</v>
       </c>
       <c r="I26" t="n">
-        <v>96.72</v>
+        <v>96.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02183589367837374</v>
+        <v>0.02186956224726815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2739,16 +2739,16 @@
         <v>953</v>
       </c>
       <c r="H27" t="n">
-        <v>54997.63</v>
+        <v>54721.26</v>
       </c>
       <c r="I27" t="n">
-        <v>57.71</v>
+        <v>57.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02116969949728351</v>
+        <v>0.02101510231552207</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2774,16 +2774,16 @@
         <v>722</v>
       </c>
       <c r="H28" t="n">
-        <v>53319.7</v>
+        <v>52583.26</v>
       </c>
       <c r="I28" t="n">
-        <v>73.84999999999999</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0153044130583223</v>
+        <v>0.01499872924063519</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
         <v>146</v>
       </c>
       <c r="H29" t="n">
-        <v>38546.92</v>
+        <v>37529.3</v>
       </c>
       <c r="I29" t="n">
-        <v>264.02</v>
+        <v>257.05</v>
       </c>
     </row>
   </sheetData>
@@ -2879,7 +2879,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1081822497179671</v>
+        <v>0.1084304405441855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.03910837312813185</v>
+        <v>0.0395308833864946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2940,16 +2940,16 @@
         <v>277</v>
       </c>
       <c r="H3" t="n">
-        <v>114846.97</v>
+        <v>115822.01</v>
       </c>
       <c r="I3" t="n">
-        <v>414.61</v>
+        <v>418.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03701560622579365</v>
+        <v>0.03692658333449406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         <v>411</v>
       </c>
       <c r="H4" t="n">
-        <v>108701.28</v>
+        <v>108191.64</v>
       </c>
       <c r="I4" t="n">
-        <v>264.48</v>
+        <v>263.24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03430758044911007</v>
+        <v>0.03416785202365172</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3010,16 +3010,16 @@
         <v>640</v>
       </c>
       <c r="H5" t="n">
-        <v>100748.8</v>
+        <v>100108.8</v>
       </c>
       <c r="I5" t="n">
-        <v>157.42</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03293051054895067</v>
+        <v>0.03331602098180415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3045,16 +3045,16 @@
         <v>473</v>
       </c>
       <c r="H6" t="n">
-        <v>96704.85000000001</v>
+        <v>97613.00999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>204.45</v>
+        <v>206.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03149388947131879</v>
+        <v>0.03165110408895862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3080,16 +3080,16 @@
         <v>341</v>
       </c>
       <c r="H7" t="n">
-        <v>92486.02</v>
+        <v>92734.95</v>
       </c>
       <c r="I7" t="n">
-        <v>271.22</v>
+        <v>271.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3098,33 +3098,33 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03044799126962304</v>
+        <v>0.03067449114282445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>838</v>
+        <v>553</v>
       </c>
       <c r="H8" t="n">
-        <v>89414.60000000001</v>
+        <v>89873.56</v>
       </c>
       <c r="I8" t="n">
-        <v>106.7</v>
+        <v>162.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3133,33 +3133,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03024083912076759</v>
+        <v>0.03052928541700472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>553</v>
+        <v>838</v>
       </c>
       <c r="H9" t="n">
-        <v>88806.27</v>
+        <v>89448.12</v>
       </c>
       <c r="I9" t="n">
-        <v>160.59</v>
+        <v>106.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02766445726962775</v>
+        <v>0.02744065000095344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3185,16 +3185,16 @@
         <v>1153</v>
       </c>
       <c r="H10" t="n">
-        <v>81240.38</v>
+        <v>80398.69</v>
       </c>
       <c r="I10" t="n">
-        <v>70.45999999999999</v>
+        <v>69.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.02614243228468743</v>
+        <v>0.02670412958920224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3220,16 +3220,16 @@
         <v>525</v>
       </c>
       <c r="H11" t="n">
-        <v>76770.75</v>
+        <v>78240.75</v>
       </c>
       <c r="I11" t="n">
-        <v>146.23</v>
+        <v>149.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02514751762765762</v>
+        <v>0.02564312161715737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>297</v>
       </c>
       <c r="H12" t="n">
-        <v>73849.05</v>
+        <v>75132.09</v>
       </c>
       <c r="I12" t="n">
-        <v>248.65</v>
+        <v>252.97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02509286321329157</v>
+        <v>0.02517213818991103</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3290,16 +3290,16 @@
         <v>265</v>
       </c>
       <c r="H13" t="n">
-        <v>73688.55</v>
+        <v>73752.14999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>278.07</v>
+        <v>278.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0247834681490878</v>
+        <v>0.02450586220846953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3325,16 +3325,16 @@
         <v>141</v>
       </c>
       <c r="H14" t="n">
-        <v>72779.97</v>
+        <v>71800.02</v>
       </c>
       <c r="I14" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02383144954550155</v>
+        <v>0.02343563894261794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
         <v>204</v>
       </c>
       <c r="H15" t="n">
-        <v>69984.24000000001</v>
+        <v>68664.36</v>
       </c>
       <c r="I15" t="n">
-        <v>343.06</v>
+        <v>336.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02181642812194162</v>
+        <v>0.02189123761433368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3395,16 +3395,16 @@
         <v>234</v>
       </c>
       <c r="H16" t="n">
-        <v>64066.86</v>
+        <v>64139.4</v>
       </c>
       <c r="I16" t="n">
-        <v>273.79</v>
+        <v>274.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02156678855077807</v>
+        <v>0.0217351783202527</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3430,16 +3430,16 @@
         <v>268</v>
       </c>
       <c r="H17" t="n">
-        <v>63333.76</v>
+        <v>63682.16</v>
       </c>
       <c r="I17" t="n">
-        <v>236.32</v>
+        <v>237.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3448,33 +3448,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02143901640524268</v>
+        <v>0.02168360680565284</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>426</v>
+        <v>1311</v>
       </c>
       <c r="H18" t="n">
-        <v>62958.54</v>
+        <v>63531.06</v>
       </c>
       <c r="I18" t="n">
-        <v>147.79</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3483,33 +3483,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.021401830971917</v>
+        <v>0.02149256352582411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1311</v>
+        <v>426</v>
       </c>
       <c r="H19" t="n">
-        <v>62849.34</v>
+        <v>62971.32</v>
       </c>
       <c r="I19" t="n">
-        <v>47.94</v>
+        <v>147.82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02098312707898113</v>
+        <v>0.02087137080952817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3535,16 +3535,16 @@
         <v>183</v>
       </c>
       <c r="H20" t="n">
-        <v>61619.76</v>
+        <v>61151.28</v>
       </c>
       <c r="I20" t="n">
-        <v>336.72</v>
+        <v>334.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01980084823582991</v>
+        <v>0.02003882703631089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3570,16 +3570,16 @@
         <v>656</v>
       </c>
       <c r="H21" t="n">
-        <v>58147.84</v>
+        <v>58712</v>
       </c>
       <c r="I21" t="n">
-        <v>88.64</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01924211666855472</v>
+        <v>0.01915509059946138</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3605,16 +3605,16 @@
         <v>1201</v>
       </c>
       <c r="H22" t="n">
-        <v>56507.05</v>
+        <v>56122.73</v>
       </c>
       <c r="I22" t="n">
-        <v>47.05</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01910193916279905</v>
+        <v>0.01908026582682256</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3640,16 +3640,16 @@
         <v>1010</v>
       </c>
       <c r="H23" t="n">
-        <v>56095.4</v>
+        <v>55903.5</v>
       </c>
       <c r="I23" t="n">
-        <v>55.54</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01891647511145746</v>
+        <v>0.01857270792237887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3675,16 +3675,16 @@
         <v>548</v>
       </c>
       <c r="H24" t="n">
-        <v>55550.76</v>
+        <v>54416.4</v>
       </c>
       <c r="I24" t="n">
-        <v>101.37</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01743313727926559</v>
+        <v>0.01745547300582586</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3710,16 +3710,16 @@
         <v>398</v>
       </c>
       <c r="H25" t="n">
-        <v>51194.74</v>
+        <v>51143</v>
       </c>
       <c r="I25" t="n">
-        <v>128.63</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3728,33 +3728,33 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01724586844040911</v>
+        <v>0.01705607534609888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>480</v>
+        <v>1740</v>
       </c>
       <c r="H26" t="n">
-        <v>50644.8</v>
+        <v>49972.8</v>
       </c>
       <c r="I26" t="n">
-        <v>105.51</v>
+        <v>28.72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3763,33 +3763,33 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01698740924723883</v>
+        <v>0.01700692711246301</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1740</v>
+        <v>480</v>
       </c>
       <c r="H27" t="n">
-        <v>49885.8</v>
+        <v>49828.8</v>
       </c>
       <c r="I27" t="n">
-        <v>28.67</v>
+        <v>103.81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01647014352443312</v>
+        <v>0.01663321623095432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,16 +3815,16 @@
         <v>399</v>
       </c>
       <c r="H28" t="n">
-        <v>48366.78</v>
+        <v>48733.86</v>
       </c>
       <c r="I28" t="n">
-        <v>121.22</v>
+        <v>122.14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3833,33 +3833,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01569838233047097</v>
+        <v>0.01544174017703692</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>984</v>
+        <v>678</v>
       </c>
       <c r="H29" t="n">
-        <v>46100.4</v>
+        <v>45242.94</v>
       </c>
       <c r="I29" t="n">
-        <v>46.85</v>
+        <v>66.73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3868,33 +3868,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01547334916418026</v>
+        <v>0.01483768790722149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>678</v>
+        <v>984</v>
       </c>
       <c r="H30" t="n">
-        <v>45439.56</v>
+        <v>43473.12</v>
       </c>
       <c r="I30" t="n">
-        <v>67.02</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01471734070048959</v>
+        <v>0.01462577710652819</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3920,16 +3920,16 @@
         <v>918</v>
       </c>
       <c r="H31" t="n">
-        <v>43219.44</v>
+        <v>42852.24</v>
       </c>
       <c r="I31" t="n">
-        <v>47.08</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01415569763637433</v>
+        <v>0.01416101912220906</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,16 +3955,16 @@
         <v>153</v>
       </c>
       <c r="H32" t="n">
-        <v>41570.1</v>
+        <v>41490.54</v>
       </c>
       <c r="I32" t="n">
-        <v>271.7</v>
+        <v>271.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3973,7 +3973,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01403974855169122</v>
+        <v>0.01367230137399245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3990,16 +3990,16 @@
         <v>492</v>
       </c>
       <c r="H33" t="n">
-        <v>41229.6</v>
+        <v>40058.64</v>
       </c>
       <c r="I33" t="n">
-        <v>83.8</v>
+        <v>81.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01352242834473412</v>
+        <v>0.01353809939159231</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4025,16 +4025,16 @@
         <v>346</v>
       </c>
       <c r="H34" t="n">
-        <v>39710.42</v>
+        <v>39665.44</v>
       </c>
       <c r="I34" t="n">
-        <v>114.77</v>
+        <v>114.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4043,33 +4043,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01264622103255169</v>
+        <v>0.01258932004582622</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>121</v>
+        <v>376</v>
       </c>
       <c r="H35" t="n">
-        <v>37137.32</v>
+        <v>36885.6</v>
       </c>
       <c r="I35" t="n">
-        <v>306.92</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4078,33 +4078,33 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01262068158658625</v>
+        <v>0.01254679658451586</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>376</v>
+        <v>121</v>
       </c>
       <c r="H36" t="n">
-        <v>37062.32</v>
+        <v>36761.01</v>
       </c>
       <c r="I36" t="n">
-        <v>98.56999999999999</v>
+        <v>303.81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01230219447961879</v>
+        <v>0.01239218101979793</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4130,16 +4130,16 @@
         <v>464</v>
       </c>
       <c r="H37" t="n">
-        <v>36127.04</v>
+        <v>36308</v>
       </c>
       <c r="I37" t="n">
-        <v>77.86</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.01201940811285155</v>
+        <v>0.01202582189490393</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4165,16 +4165,16 @@
         <v>310</v>
       </c>
       <c r="H38" t="n">
-        <v>35296.6</v>
+        <v>35234.6</v>
       </c>
       <c r="I38" t="n">
-        <v>113.86</v>
+        <v>113.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01185827123510691</v>
+        <v>0.01153827483030796</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4200,16 +4200,16 @@
         <v>381</v>
       </c>
       <c r="H39" t="n">
-        <v>34823.4</v>
+        <v>33806.13</v>
       </c>
       <c r="I39" t="n">
-        <v>91.40000000000001</v>
+        <v>88.73</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4218,7 +4218,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.01158169606159847</v>
+        <v>0.01147721838923074</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4235,16 +4235,16 @@
         <v>116</v>
       </c>
       <c r="H40" t="n">
-        <v>34011.2</v>
+        <v>33627.24</v>
       </c>
       <c r="I40" t="n">
-        <v>293.2</v>
+        <v>289.89</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.01131499614053001</v>
+        <v>0.01134126208793554</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4270,16 +4270,16 @@
         <v>90</v>
       </c>
       <c r="H41" t="n">
-        <v>33228</v>
+        <v>33228.9</v>
       </c>
       <c r="I41" t="n">
-        <v>369.2</v>
+        <v>369.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4288,33 +4288,33 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01125002378999392</v>
+        <v>0.0111845372448574</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AWR</t>
+          <t>EMN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>American States Water Co</t>
+          <t>Eastman Chemical</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>399</v>
+        <v>493</v>
       </c>
       <c r="H42" t="n">
-        <v>33037.2</v>
+        <v>32769.71</v>
       </c>
       <c r="I42" t="n">
-        <v>82.8</v>
+        <v>66.47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4323,33 +4323,33 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.01124287615038305</v>
+        <v>0.01107837023406037</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EMN</t>
+          <t>AWR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eastman Chemical</t>
+          <t>American States Water Co</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>493</v>
+        <v>399</v>
       </c>
       <c r="H43" t="n">
-        <v>33016.21</v>
+        <v>32458.65</v>
       </c>
       <c r="I43" t="n">
-        <v>66.97</v>
+        <v>81.34999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4358,33 +4358,33 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.008844207980049156</v>
+        <v>0.008840227935718793</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>HRL</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Hormel Foods</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>705</v>
+        <v>1297</v>
       </c>
       <c r="H44" t="n">
-        <v>25972.2</v>
+        <v>25901.09</v>
       </c>
       <c r="I44" t="n">
-        <v>36.84</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4393,33 +4393,33 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.008801744394557279</v>
+        <v>0.00881156154583632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>HWC</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hancock Whitney Corp</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>350</v>
+        <v>705</v>
       </c>
       <c r="H45" t="n">
-        <v>25847.5</v>
+        <v>25817.1</v>
       </c>
       <c r="I45" t="n">
-        <v>73.84999999999999</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4428,33 +4428,33 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.008705161020434896</v>
+        <v>0.008700090621492759</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HRL</t>
+          <t>HWC</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hormel Foods</t>
+          <t>Hancock Whitney Corp</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1297</v>
+        <v>350</v>
       </c>
       <c r="H46" t="n">
-        <v>25563.87</v>
+        <v>25490.5</v>
       </c>
       <c r="I46" t="n">
-        <v>19.71</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4463,33 +4463,33 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.00846990526523908</v>
+        <v>0.008460202871416606</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DOX</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Amdocs Ltd</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>431</v>
+        <v>257</v>
       </c>
       <c r="H47" t="n">
-        <v>24873.01</v>
+        <v>24787.65</v>
       </c>
       <c r="I47" t="n">
-        <v>57.71</v>
+        <v>96.45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4498,33 +4498,33 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.008464467065878174</v>
+        <v>0.008446676867951402</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>DOX</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Amdocs Ltd</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>257</v>
+        <v>431</v>
       </c>
       <c r="H48" t="n">
-        <v>24857.04</v>
+        <v>24748.02</v>
       </c>
       <c r="I48" t="n">
-        <v>96.72</v>
+        <v>57.42</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.007632974215692042</v>
+        <v>0.007787445466664372</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4550,16 +4550,16 @@
         <v>627</v>
       </c>
       <c r="H49" t="n">
-        <v>22415.25</v>
+        <v>22816.53</v>
       </c>
       <c r="I49" t="n">
-        <v>35.75</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.005843867920623497</v>
+        <v>0.005702645657266683</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         <v>65</v>
       </c>
       <c r="H50" t="n">
-        <v>17161.3</v>
+        <v>16708.25</v>
       </c>
       <c r="I50" t="n">
-        <v>264.02</v>
+        <v>257.05</v>
       </c>
     </row>
   </sheetData>
@@ -4655,7 +4655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.07274244415577236</v>
+        <v>0.07289191994723282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.05372273216662925</v>
+        <v>0.05377214825605849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4716,16 +4716,16 @@
         <v>1018</v>
       </c>
       <c r="H3" t="n">
-        <v>116835.86</v>
+        <v>116703.52</v>
       </c>
       <c r="I3" t="n">
-        <v>114.77</v>
+        <v>114.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0441456215173622</v>
+        <v>0.04364071212505603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4751,16 +4751,16 @@
         <v>186</v>
       </c>
       <c r="H4" t="n">
-        <v>96007.62</v>
+        <v>94714.92</v>
       </c>
       <c r="I4" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03909191000924864</v>
+        <v>0.03877530885258179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4786,16 +4786,16 @@
         <v>277</v>
       </c>
       <c r="H5" t="n">
-        <v>85016.84</v>
+        <v>84155.37</v>
       </c>
       <c r="I5" t="n">
-        <v>306.92</v>
+        <v>303.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4804,7 +4804,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03812127082158977</v>
+        <v>0.03821392520525308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4821,16 +4821,16 @@
         <v>777</v>
       </c>
       <c r="H6" t="n">
-        <v>82905.89999999999</v>
+        <v>82936.98</v>
       </c>
       <c r="I6" t="n">
-        <v>106.7</v>
+        <v>106.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03688564098339239</v>
+        <v>0.03702589606520327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4856,16 +4856,16 @@
         <v>2798</v>
       </c>
       <c r="H7" t="n">
-        <v>80218.66</v>
+        <v>80358.56</v>
       </c>
       <c r="I7" t="n">
-        <v>28.67</v>
+        <v>28.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03464280297187359</v>
+        <v>0.03531710375431298</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4891,16 +4891,16 @@
         <v>303</v>
       </c>
       <c r="H8" t="n">
-        <v>75340.95</v>
+        <v>76649.91</v>
       </c>
       <c r="I8" t="n">
-        <v>248.65</v>
+        <v>252.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.03325843718758962</v>
+        <v>0.03365012067704953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4926,16 +4926,16 @@
         <v>816</v>
       </c>
       <c r="H9" t="n">
-        <v>72330.24000000001</v>
+        <v>73032</v>
       </c>
       <c r="I9" t="n">
-        <v>88.64</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.03316507660857635</v>
+        <v>0.03285804903104382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4961,16 +4961,16 @@
         <v>246</v>
       </c>
       <c r="H10" t="n">
-        <v>72127.2</v>
+        <v>71312.94</v>
       </c>
       <c r="I10" t="n">
-        <v>293.2</v>
+        <v>289.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03308719335959455</v>
+        <v>0.03262097952602198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4996,16 +4996,16 @@
         <v>682</v>
       </c>
       <c r="H11" t="n">
-        <v>71957.82000000001</v>
+        <v>70798.42</v>
       </c>
       <c r="I11" t="n">
-        <v>105.51</v>
+        <v>103.81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03165953611296769</v>
+        <v>0.03196536614132248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5031,16 +5031,16 @@
         <v>568</v>
       </c>
       <c r="H12" t="n">
-        <v>68852.96000000001</v>
+        <v>69375.52</v>
       </c>
       <c r="I12" t="n">
-        <v>121.22</v>
+        <v>122.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5049,33 +5049,33 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03107550830648668</v>
+        <v>0.03100088784953221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>UL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Unilever PLC</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>197</v>
+        <v>1076</v>
       </c>
       <c r="H13" t="n">
-        <v>67582.82000000001</v>
+        <v>67282.28</v>
       </c>
       <c r="I13" t="n">
-        <v>343.06</v>
+        <v>62.53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5084,33 +5084,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03094226348484334</v>
+        <v>0.03055208595384976</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Unilever PLC</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1076</v>
+        <v>197</v>
       </c>
       <c r="H14" t="n">
-        <v>67293.03999999999</v>
+        <v>66308.23</v>
       </c>
       <c r="I14" t="n">
-        <v>62.54</v>
+        <v>336.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0297948259193742</v>
+        <v>0.02971607176198785</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5136,16 +5136,16 @@
         <v>245</v>
       </c>
       <c r="H15" t="n">
-        <v>64797.6</v>
+        <v>64493.8</v>
       </c>
       <c r="I15" t="n">
-        <v>264.48</v>
+        <v>263.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5154,7 +5154,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.02857841629494137</v>
+        <v>0.02879467439750759</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5171,16 +5171,16 @@
         <v>263</v>
       </c>
       <c r="H16" t="n">
-        <v>62152.16</v>
+        <v>62494.06</v>
       </c>
       <c r="I16" t="n">
-        <v>236.32</v>
+        <v>237.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0276321748236066</v>
+        <v>0.02759423242128952</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5206,16 +5206,16 @@
         <v>1082</v>
       </c>
       <c r="H17" t="n">
-        <v>60094.28</v>
+        <v>59888.7</v>
       </c>
       <c r="I17" t="n">
-        <v>55.54</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.02740745465922834</v>
+        <v>0.0269029563224318</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5241,16 +5241,16 @@
         <v>588</v>
       </c>
       <c r="H18" t="n">
-        <v>59605.56</v>
+        <v>58388.4</v>
       </c>
       <c r="I18" t="n">
-        <v>101.37</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0265633746016306</v>
+        <v>0.02668960206156658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5276,16 +5276,16 @@
         <v>213</v>
       </c>
       <c r="H19" t="n">
-        <v>57769.86</v>
+        <v>57925.35</v>
       </c>
       <c r="I19" t="n">
-        <v>271.22</v>
+        <v>271.95</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.02559449650054395</v>
+        <v>0.02610622640717364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5311,16 +5311,16 @@
         <v>1557</v>
       </c>
       <c r="H20" t="n">
-        <v>55662.75</v>
+        <v>56659.23</v>
       </c>
       <c r="I20" t="n">
-        <v>35.75</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.02556582711470137</v>
+        <v>0.0255589373648333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5346,16 +5346,16 @@
         <v>1433</v>
       </c>
       <c r="H21" t="n">
-        <v>55600.4</v>
+        <v>55471.43</v>
       </c>
       <c r="I21" t="n">
-        <v>38.8</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.02516492472290624</v>
+        <v>0.0254307220745386</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
         <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>54728.52</v>
+        <v>55193.16</v>
       </c>
       <c r="I22" t="n">
-        <v>414.61</v>
+        <v>418.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.02429347655231171</v>
+        <v>0.02436440692120761</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5416,16 +5416,16 @@
         <v>190</v>
       </c>
       <c r="H23" t="n">
-        <v>52833.3</v>
+        <v>52878.9</v>
       </c>
       <c r="I23" t="n">
-        <v>278.07</v>
+        <v>278.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.02245357330925883</v>
+        <v>0.02220170290197319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5451,16 +5451,16 @@
         <v>443</v>
       </c>
       <c r="H24" t="n">
-        <v>48831.89</v>
+        <v>48185.11</v>
       </c>
       <c r="I24" t="n">
-        <v>110.23</v>
+        <v>108.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.02182481482347123</v>
+        <v>0.02184755924914173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5486,16 +5486,16 @@
         <v>369</v>
       </c>
       <c r="H25" t="n">
-        <v>47464.47</v>
+        <v>47416.5</v>
       </c>
       <c r="I25" t="n">
-        <v>128.63</v>
+        <v>128.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.02076046100022976</v>
+        <v>0.02062637392161355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5521,16 +5521,16 @@
         <v>959</v>
       </c>
       <c r="H26" t="n">
-        <v>45149.72</v>
+        <v>44766.12</v>
       </c>
       <c r="I26" t="n">
-        <v>47.08</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.02025084944723331</v>
+        <v>0.02029658135978031</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5556,16 +5556,16 @@
         <v>298</v>
       </c>
       <c r="H27" t="n">
-        <v>44041.42</v>
+        <v>44050.36</v>
       </c>
       <c r="I27" t="n">
-        <v>147.79</v>
+        <v>147.82</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.02001689162509119</v>
+        <v>0.02008073439499267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5591,16 +5591,16 @@
         <v>159</v>
       </c>
       <c r="H28" t="n">
-        <v>43532.61</v>
+        <v>43581.9</v>
       </c>
       <c r="I28" t="n">
-        <v>273.79</v>
+        <v>274.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01896127426265179</v>
+        <v>0.01936405206798657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5626,16 +5626,16 @@
         <v>282</v>
       </c>
       <c r="H29" t="n">
-        <v>41236.86</v>
+        <v>42026.46</v>
       </c>
       <c r="I29" t="n">
-        <v>146.23</v>
+        <v>149.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5644,33 +5644,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01864967689280285</v>
+        <v>0.01849237976955224</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Lincoln Electric</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>484</v>
+        <v>148</v>
       </c>
       <c r="H30" t="n">
-        <v>40559.2</v>
+        <v>40134.64</v>
       </c>
       <c r="I30" t="n">
-        <v>83.8</v>
+        <v>271.18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01852084628293319</v>
+        <v>0.01847859848039885</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5696,16 +5696,16 @@
         <v>601</v>
       </c>
       <c r="H31" t="n">
-        <v>40279.02</v>
+        <v>40104.73</v>
       </c>
       <c r="I31" t="n">
-        <v>67.02</v>
+        <v>66.73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5714,33 +5714,33 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.01848984564149764</v>
+        <v>0.01815724240818108</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LECO</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>148</v>
+        <v>484</v>
       </c>
       <c r="H32" t="n">
-        <v>40211.6</v>
+        <v>39407.28</v>
       </c>
       <c r="I32" t="n">
-        <v>271.7</v>
+        <v>81.42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.01780643369618721</v>
+        <v>0.01772967687549027</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5766,16 +5766,16 @@
         <v>246</v>
       </c>
       <c r="H33" t="n">
-        <v>38725.32</v>
+        <v>38479.32</v>
       </c>
       <c r="I33" t="n">
-        <v>157.42</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.01654402430656285</v>
+        <v>0.01653174142595206</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5801,16 +5801,16 @@
         <v>372</v>
       </c>
       <c r="H34" t="n">
-        <v>35979.84</v>
+        <v>35879.4</v>
       </c>
       <c r="I34" t="n">
-        <v>96.72</v>
+        <v>96.45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5819,33 +5819,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.01636190588393783</v>
+        <v>0.01643367356960274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>McCormick &amp; Co.</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>361</v>
+        <v>736</v>
       </c>
       <c r="H35" t="n">
-        <v>35583.77</v>
+        <v>35666.56</v>
       </c>
       <c r="I35" t="n">
-        <v>98.56999999999999</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5854,27 +5854,27 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.01622399395297129</v>
+        <v>0.01631735045827993</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>McCormick &amp; Co.</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>736</v>
+        <v>361</v>
       </c>
       <c r="H36" t="n">
-        <v>35283.84</v>
+        <v>35414.1</v>
       </c>
       <c r="I36" t="n">
-        <v>47.94</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5941,7 +5941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1058777926067169</v>
+        <v>0.1056287537662108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5967,16 +5967,16 @@
         <v>4190</v>
       </c>
       <c r="H2" t="n">
-        <v>221603.23</v>
+        <v>219784.77</v>
       </c>
       <c r="I2" t="n">
-        <v>52.89</v>
+        <v>52.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5985,33 +5985,33 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09892214824782883</v>
+        <v>0.09878520390028185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CGGR</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Capital Group Growth ETF</t>
+          <t>Invesco S&amp;P 500® Equal Weight ETF</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4300</v>
+        <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>207045</v>
+        <v>205545.2</v>
       </c>
       <c r="I3" t="n">
-        <v>48.15</v>
+        <v>209.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6020,33 +6020,33 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0988470410889766</v>
+        <v>0.09834872218150545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RSP</t>
+          <t>CGGR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Invesco S&amp;P 500® Equal Weight ETF</t>
+          <t>Capital Group Growth ETF</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>980</v>
+        <v>4300</v>
       </c>
       <c r="H4" t="n">
-        <v>206887.8</v>
+        <v>204637</v>
       </c>
       <c r="I4" t="n">
-        <v>211.11</v>
+        <v>47.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05483479544961845</v>
+        <v>0.05482526623210127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6072,16 +6072,16 @@
         <v>1475</v>
       </c>
       <c r="H5" t="n">
-        <v>114769.75</v>
+        <v>114076.5</v>
       </c>
       <c r="I5" t="n">
-        <v>77.81</v>
+        <v>77.34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04643473340307852</v>
+        <v>0.04670880168269518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03781659781636734</v>
+        <v>0.03796176955532899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6142,16 +6142,16 @@
         <v>2706</v>
       </c>
       <c r="H7" t="n">
-        <v>79150.5</v>
+        <v>78988.14</v>
       </c>
       <c r="I7" t="n">
-        <v>29.25</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03709863644482003</v>
+        <v>0.03682931047889038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -6177,16 +6177,16 @@
         <v>1270</v>
       </c>
       <c r="H8" t="n">
-        <v>77647.8</v>
+        <v>76631.8</v>
       </c>
       <c r="I8" t="n">
-        <v>61.14</v>
+        <v>60.34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02911963315752493</v>
+        <v>0.02954018592554461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -6212,16 +6212,16 @@
         <v>147</v>
       </c>
       <c r="H9" t="n">
-        <v>60947.67</v>
+        <v>61465.11</v>
       </c>
       <c r="I9" t="n">
-        <v>414.61</v>
+        <v>418.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.02589469802416668</v>
+        <v>0.02569681588604677</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6247,16 +6247,16 @@
         <v>105</v>
       </c>
       <c r="H10" t="n">
-        <v>54197.85</v>
+        <v>53468.1</v>
       </c>
       <c r="I10" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0247144119562876</v>
+        <v>0.02467400109426092</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6282,16 +6282,16 @@
         <v>285</v>
       </c>
       <c r="H11" t="n">
-        <v>51727.5</v>
+        <v>51339.9</v>
       </c>
       <c r="I11" t="n">
-        <v>181.5</v>
+        <v>180.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02293281472572744</v>
+        <v>0.02297770587198299</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6317,16 +6317,16 @@
         <v>1860</v>
       </c>
       <c r="H12" t="n">
-        <v>47998.6</v>
+        <v>47810.37</v>
       </c>
       <c r="I12" t="n">
-        <v>25.81</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.02068337442933968</v>
+        <v>0.02067328713281835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -6352,16 +6352,16 @@
         <v>275</v>
       </c>
       <c r="H13" t="n">
-        <v>43290.5</v>
+        <v>43015.5</v>
       </c>
       <c r="I13" t="n">
-        <v>157.42</v>
+        <v>156.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.02047423061435258</v>
+        <v>0.02065050665112929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6387,16 +6387,16 @@
         <v>158</v>
       </c>
       <c r="H14" t="n">
-        <v>42852.76</v>
+        <v>42968.1</v>
       </c>
       <c r="I14" t="n">
-        <v>271.22</v>
+        <v>271.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6405,33 +6405,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.02037248239202962</v>
+        <v>0.02003468390815273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CEF</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sprott Physical Gold and Silver Trust</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>980</v>
+        <v>202</v>
       </c>
       <c r="H15" t="n">
-        <v>42639.8</v>
+        <v>41686.74</v>
       </c>
       <c r="I15" t="n">
-        <v>43.51</v>
+        <v>206.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.01996543216902872</v>
+        <v>0.01998911333275703</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -6457,16 +6457,16 @@
         <v>158</v>
       </c>
       <c r="H16" t="n">
-        <v>41787.84</v>
+        <v>41591.92</v>
       </c>
       <c r="I16" t="n">
-        <v>264.48</v>
+        <v>263.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6475,33 +6475,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.01973182597151469</v>
+        <v>0.01953190810405592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CEF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Sprott Physical Gold and Silver Trust</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>202</v>
+        <v>980</v>
       </c>
       <c r="H17" t="n">
-        <v>41298.9</v>
+        <v>40640.6</v>
       </c>
       <c r="I17" t="n">
-        <v>204.45</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01833086723532087</v>
+        <v>0.01872950648763368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6527,16 +6527,16 @@
         <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>38366.68</v>
+        <v>38971.02</v>
       </c>
       <c r="I18" t="n">
-        <v>1743.94</v>
+        <v>1771.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01718681129375072</v>
+        <v>0.01749602510632081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6562,16 +6562,16 @@
         <v>224</v>
       </c>
       <c r="H19" t="n">
-        <v>35972.16</v>
+        <v>36404.48</v>
       </c>
       <c r="I19" t="n">
-        <v>160.59</v>
+        <v>162.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01642824810057961</v>
+        <v>0.01635400207237983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6597,16 +6597,16 @@
         <v>488</v>
       </c>
       <c r="H20" t="n">
-        <v>34384.48</v>
+        <v>34028.24</v>
       </c>
       <c r="I20" t="n">
-        <v>70.45999999999999</v>
+        <v>69.73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01622684433631392</v>
+        <v>0.01601477955359109</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6632,16 +6632,16 @@
         <v>99</v>
       </c>
       <c r="H21" t="n">
-        <v>33962.94</v>
+        <v>33322.41</v>
       </c>
       <c r="I21" t="n">
-        <v>343.06</v>
+        <v>336.59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0155996422261888</v>
+        <v>0.01569759739113694</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6667,16 +6667,16 @@
         <v>306</v>
       </c>
       <c r="H22" t="n">
-        <v>32650.2</v>
+        <v>32662.44</v>
       </c>
       <c r="I22" t="n">
-        <v>106.7</v>
+        <v>106.74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0149688280923937</v>
+        <v>0.01531877816588488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6702,16 +6702,16 @@
         <v>126</v>
       </c>
       <c r="H23" t="n">
-        <v>31329.9</v>
+        <v>31874.22</v>
       </c>
       <c r="I23" t="n">
-        <v>248.65</v>
+        <v>252.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01404304635897646</v>
+        <v>0.01439641376392667</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6737,16 +6737,16 @@
         <v>201</v>
       </c>
       <c r="H24" t="n">
-        <v>29392.23</v>
+        <v>29955.03</v>
       </c>
       <c r="I24" t="n">
-        <v>146.23</v>
+        <v>149.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01368422334090269</v>
+        <v>0.01377687117014266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6772,16 +6772,16 @@
         <v>103</v>
       </c>
       <c r="H25" t="n">
-        <v>28641.21</v>
+        <v>28665.93</v>
       </c>
       <c r="I25" t="n">
-        <v>278.07</v>
+        <v>278.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01351378455733174</v>
+        <v>0.01349019755152019</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6807,16 +6807,16 @@
         <v>84</v>
       </c>
       <c r="H26" t="n">
-        <v>28284.48</v>
+        <v>28069.44</v>
       </c>
       <c r="I26" t="n">
-        <v>336.72</v>
+        <v>334.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01316644739230381</v>
+        <v>0.01306873941623747</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6842,16 +6842,16 @@
         <v>250</v>
       </c>
       <c r="H27" t="n">
-        <v>27557.5</v>
+        <v>27192.5</v>
       </c>
       <c r="I27" t="n">
-        <v>110.23</v>
+        <v>108.77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01237049306521556</v>
+        <v>0.01244151682039879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6877,16 +6877,16 @@
         <v>414</v>
       </c>
       <c r="H28" t="n">
-        <v>25891.56</v>
+        <v>25887.42</v>
       </c>
       <c r="I28" t="n">
-        <v>62.54</v>
+        <v>62.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6895,33 +6895,33 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01172923464075563</v>
+        <v>0.01124512821496697</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portland General Electric Co</t>
+          <t>Total SA</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>524</v>
+        <v>259</v>
       </c>
       <c r="H29" t="n">
-        <v>24549.4</v>
+        <v>23398.06</v>
       </c>
       <c r="I29" t="n">
-        <v>46.85</v>
+        <v>90.34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6930,33 +6930,33 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01125339352251591</v>
+        <v>0.01112606415307569</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Total SA</t>
+          <t>Portland General Electric Co</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>259</v>
+        <v>524</v>
       </c>
       <c r="H30" t="n">
-        <v>23553.46</v>
+        <v>23150.32</v>
       </c>
       <c r="I30" t="n">
-        <v>90.94</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.01058762493743817</v>
+        <v>0.01075344467916938</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6982,16 +6982,16 @@
         <v>250</v>
       </c>
       <c r="H31" t="n">
-        <v>22160</v>
+        <v>22375</v>
       </c>
       <c r="I31" t="n">
-        <v>88.64</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.009686530143574979</v>
+        <v>0.009544733467186766</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7017,16 +7017,16 @@
         <v>200</v>
       </c>
       <c r="H32" t="n">
-        <v>20274</v>
+        <v>19860</v>
       </c>
       <c r="I32" t="n">
-        <v>101.37</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.008903686124622251</v>
+        <v>0.008971857218803754</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -7052,16 +7052,16 @@
         <v>650</v>
       </c>
       <c r="H33" t="n">
-        <v>18635.5</v>
+        <v>18668</v>
       </c>
       <c r="I33" t="n">
-        <v>28.67</v>
+        <v>28.72</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7070,33 +7070,33 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.008821866144002382</v>
+        <v>0.008836928521879651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>175</v>
+        <v>475</v>
       </c>
       <c r="H34" t="n">
-        <v>18464.25</v>
+        <v>18387.25</v>
       </c>
       <c r="I34" t="n">
-        <v>105.51</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7105,33 +7105,33 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.008805502147878409</v>
+        <v>0.008730956027946385</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>475</v>
+        <v>175</v>
       </c>
       <c r="H35" t="n">
-        <v>18430</v>
+        <v>18166.75</v>
       </c>
       <c r="I35" t="n">
-        <v>38.8</v>
+        <v>103.81</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.008480209793979248</v>
+        <v>0.008457787294038314</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -7157,16 +7157,16 @@
         <v>377</v>
       </c>
       <c r="H36" t="n">
-        <v>17749.16</v>
+        <v>17598.36</v>
       </c>
       <c r="I36" t="n">
-        <v>47.08</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7175,7 +7175,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.008335790958697685</v>
+        <v>0.0083450094916511</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -7192,16 +7192,16 @@
         <v>177</v>
       </c>
       <c r="H37" t="n">
-        <v>17446.89</v>
+        <v>17363.7</v>
       </c>
       <c r="I37" t="n">
-        <v>98.56999999999999</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/25/2026</t>
+          <t>09/28/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7210,33 +7210,33 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.008137612215565916</v>
+        <v>0.008151952118349544</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c 